--- a/data/export/2026-10-31-浦东35路.xlsx
+++ b/data/export/2026-10-31-浦东35路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC10"/>
+  <dimension ref="A1:AC21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -665,7 +665,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -715,7 +715,7 @@
       <c r="AB2" s="2" t="inlineStr"/>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>—/9</t>
+          <t>—/20</t>
         </is>
       </c>
     </row>
@@ -776,7 +776,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -826,7 +826,7 @@
       <c r="AB3" s="2" t="inlineStr"/>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>—/9</t>
+          <t>—/20</t>
         </is>
       </c>
     </row>
@@ -887,7 +887,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -937,7 +937,7 @@
       <c r="AB4" s="2" t="inlineStr"/>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>—/9</t>
+          <t>—/20</t>
         </is>
       </c>
     </row>
@@ -998,7 +998,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1048,7 +1048,7 @@
       <c r="AB5" s="2" t="inlineStr"/>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>—/9</t>
+          <t>—/20</t>
         </is>
       </c>
     </row>
@@ -1109,7 +1109,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1159,7 +1159,7 @@
       <c r="AB6" s="2" t="inlineStr"/>
       <c r="AC6" s="2" t="inlineStr">
         <is>
-          <t>—/9</t>
+          <t>—/20</t>
         </is>
       </c>
     </row>
@@ -1220,7 +1220,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1270,7 +1270,7 @@
       <c r="AB7" s="2" t="inlineStr"/>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>—/9</t>
+          <t>—/20</t>
         </is>
       </c>
     </row>
@@ -1331,7 +1331,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1381,7 +1381,7 @@
       <c r="AB8" s="2" t="inlineStr"/>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>—/9</t>
+          <t>—/20</t>
         </is>
       </c>
     </row>
@@ -1442,7 +1442,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1492,7 +1492,7 @@
       <c r="AB9" s="2" t="inlineStr"/>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>—/9</t>
+          <t>—/20</t>
         </is>
       </c>
     </row>
@@ -1553,7 +1553,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1603,7 +1603,1228 @@
       <c r="AB10" s="2" t="inlineStr"/>
       <c r="AC10" s="2" t="inlineStr">
         <is>
-          <t>—/9</t>
+          <t>—/20</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr"/>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
+          <t>沪A68261D</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>07:06</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr"/>
+      <c r="K11" s="2" t="inlineStr"/>
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr"/>
+      <c r="N11" s="2" t="inlineStr">
+        <is>
+          <t>06:41</t>
+        </is>
+      </c>
+      <c r="O11" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="P11" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q11" s="2" t="inlineStr"/>
+      <c r="R11" s="2" t="inlineStr"/>
+      <c r="S11" s="2" t="inlineStr"/>
+      <c r="T11" s="2" t="inlineStr"/>
+      <c r="U11" s="2" t="inlineStr">
+        <is>
+          <t>07:06</t>
+        </is>
+      </c>
+      <c r="V11" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W11" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X11" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y11" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z11" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB11" s="2" t="inlineStr"/>
+      <c r="AC11" s="2" t="inlineStr">
+        <is>
+          <t>—/20</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr"/>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>沪A72873D</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>07:06</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr"/>
+      <c r="K12" s="2" t="inlineStr"/>
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr"/>
+      <c r="N12" s="2" t="inlineStr">
+        <is>
+          <t>06:32</t>
+        </is>
+      </c>
+      <c r="O12" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="P12" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q12" s="2" t="inlineStr"/>
+      <c r="R12" s="2" t="inlineStr"/>
+      <c r="S12" s="2" t="inlineStr"/>
+      <c r="T12" s="2" t="inlineStr"/>
+      <c r="U12" s="2" t="inlineStr">
+        <is>
+          <t>07:06</t>
+        </is>
+      </c>
+      <c r="V12" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W12" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X12" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y12" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z12" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA12" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB12" s="2" t="inlineStr"/>
+      <c r="AC12" s="2" t="inlineStr">
+        <is>
+          <t>—/20</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr"/>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
+          <t>沪A51682D</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>07:12</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr"/>
+      <c r="K13" s="2" t="inlineStr"/>
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr"/>
+      <c r="N13" s="2" t="inlineStr">
+        <is>
+          <t>06:51</t>
+        </is>
+      </c>
+      <c r="O13" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="P13" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q13" s="2" t="inlineStr"/>
+      <c r="R13" s="2" t="inlineStr"/>
+      <c r="S13" s="2" t="inlineStr"/>
+      <c r="T13" s="2" t="inlineStr"/>
+      <c r="U13" s="2" t="inlineStr">
+        <is>
+          <t>07:12</t>
+        </is>
+      </c>
+      <c r="V13" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W13" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X13" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y13" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z13" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB13" s="2" t="inlineStr"/>
+      <c r="AC13" s="2" t="inlineStr">
+        <is>
+          <t>—/20</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr"/>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t>沪A62880D</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>07:18</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr"/>
+      <c r="K14" s="2" t="inlineStr"/>
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr"/>
+      <c r="N14" s="2" t="inlineStr">
+        <is>
+          <t>07:01</t>
+        </is>
+      </c>
+      <c r="O14" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="P14" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q14" s="2" t="inlineStr"/>
+      <c r="R14" s="2" t="inlineStr"/>
+      <c r="S14" s="2" t="inlineStr"/>
+      <c r="T14" s="2" t="inlineStr"/>
+      <c r="U14" s="2" t="inlineStr">
+        <is>
+          <t>07:18</t>
+        </is>
+      </c>
+      <c r="V14" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W14" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X14" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y14" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z14" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA14" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB14" s="2" t="inlineStr"/>
+      <c r="AC14" s="2" t="inlineStr">
+        <is>
+          <t>—/20</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr"/>
+      <c r="B15" s="2" t="inlineStr">
+        <is>
+          <t>沪A68895D</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>07:18</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr"/>
+      <c r="K15" s="2" t="inlineStr"/>
+      <c r="L15" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M15" s="2" t="inlineStr"/>
+      <c r="N15" s="2" t="inlineStr">
+        <is>
+          <t>06:51</t>
+        </is>
+      </c>
+      <c r="O15" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="P15" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q15" s="2" t="inlineStr"/>
+      <c r="R15" s="2" t="inlineStr"/>
+      <c r="S15" s="2" t="inlineStr"/>
+      <c r="T15" s="2" t="inlineStr"/>
+      <c r="U15" s="2" t="inlineStr">
+        <is>
+          <t>07:18</t>
+        </is>
+      </c>
+      <c r="V15" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W15" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X15" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y15" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z15" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA15" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB15" s="2" t="inlineStr"/>
+      <c r="AC15" s="2" t="inlineStr">
+        <is>
+          <t>—/20</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr"/>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
+          <t>沪A02891D</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>07:30</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr"/>
+      <c r="K16" s="2" t="inlineStr"/>
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr"/>
+      <c r="N16" s="2" t="inlineStr">
+        <is>
+          <t>07:11</t>
+        </is>
+      </c>
+      <c r="O16" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="P16" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q16" s="2" t="inlineStr"/>
+      <c r="R16" s="2" t="inlineStr"/>
+      <c r="S16" s="2" t="inlineStr"/>
+      <c r="T16" s="2" t="inlineStr"/>
+      <c r="U16" s="2" t="inlineStr">
+        <is>
+          <t>07:30</t>
+        </is>
+      </c>
+      <c r="V16" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W16" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X16" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y16" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z16" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA16" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB16" s="2" t="inlineStr"/>
+      <c r="AC16" s="2" t="inlineStr">
+        <is>
+          <t>—/20</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="2" t="inlineStr"/>
+      <c r="B17" s="2" t="inlineStr">
+        <is>
+          <t>沪A55575A</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>07:30</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr"/>
+      <c r="K17" s="2" t="inlineStr"/>
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr"/>
+      <c r="N17" s="2" t="inlineStr">
+        <is>
+          <t>07:01</t>
+        </is>
+      </c>
+      <c r="O17" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="P17" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q17" s="2" t="inlineStr"/>
+      <c r="R17" s="2" t="inlineStr"/>
+      <c r="S17" s="2" t="inlineStr"/>
+      <c r="T17" s="2" t="inlineStr"/>
+      <c r="U17" s="2" t="inlineStr">
+        <is>
+          <t>07:30</t>
+        </is>
+      </c>
+      <c r="V17" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W17" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X17" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y17" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z17" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA17" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB17" s="2" t="inlineStr"/>
+      <c r="AC17" s="2" t="inlineStr">
+        <is>
+          <t>—/20</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="inlineStr"/>
+      <c r="B18" s="2" t="inlineStr">
+        <is>
+          <t>沪A59793A</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>07:42</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr"/>
+      <c r="K18" s="2" t="inlineStr"/>
+      <c r="L18" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M18" s="2" t="inlineStr"/>
+      <c r="N18" s="2" t="inlineStr">
+        <is>
+          <t>06:51</t>
+        </is>
+      </c>
+      <c r="O18" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="P18" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q18" s="2" t="inlineStr"/>
+      <c r="R18" s="2" t="inlineStr"/>
+      <c r="S18" s="2" t="inlineStr"/>
+      <c r="T18" s="2" t="inlineStr"/>
+      <c r="U18" s="2" t="inlineStr">
+        <is>
+          <t>07:42</t>
+        </is>
+      </c>
+      <c r="V18" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W18" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X18" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y18" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z18" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA18" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB18" s="2" t="inlineStr"/>
+      <c r="AC18" s="2" t="inlineStr">
+        <is>
+          <t>—/20</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="2" t="inlineStr"/>
+      <c r="B19" s="2" t="inlineStr">
+        <is>
+          <t>沪A65668D</t>
+        </is>
+      </c>
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>07:42</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr"/>
+      <c r="K19" s="2" t="inlineStr"/>
+      <c r="L19" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M19" s="2" t="inlineStr"/>
+      <c r="N19" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="O19" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="P19" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q19" s="2" t="inlineStr"/>
+      <c r="R19" s="2" t="inlineStr"/>
+      <c r="S19" s="2" t="inlineStr"/>
+      <c r="T19" s="2" t="inlineStr"/>
+      <c r="U19" s="2" t="inlineStr">
+        <is>
+          <t>07:42</t>
+        </is>
+      </c>
+      <c r="V19" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W19" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X19" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y19" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z19" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA19" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB19" s="2" t="inlineStr"/>
+      <c r="AC19" s="2" t="inlineStr">
+        <is>
+          <t>—/20</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="2" t="inlineStr"/>
+      <c r="B20" s="2" t="inlineStr">
+        <is>
+          <t>沪A57383A</t>
+        </is>
+      </c>
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>07:54</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr"/>
+      <c r="K20" s="2" t="inlineStr"/>
+      <c r="L20" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M20" s="2" t="inlineStr"/>
+      <c r="N20" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="O20" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="P20" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q20" s="2" t="inlineStr"/>
+      <c r="R20" s="2" t="inlineStr"/>
+      <c r="S20" s="2" t="inlineStr"/>
+      <c r="T20" s="2" t="inlineStr"/>
+      <c r="U20" s="2" t="inlineStr">
+        <is>
+          <t>07:54</t>
+        </is>
+      </c>
+      <c r="V20" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W20" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X20" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y20" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z20" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA20" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB20" s="2" t="inlineStr"/>
+      <c r="AC20" s="2" t="inlineStr">
+        <is>
+          <t>—/20</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="2" t="inlineStr"/>
+      <c r="B21" s="2" t="inlineStr">
+        <is>
+          <t>沪A90275D</t>
+        </is>
+      </c>
+      <c r="C21" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>07:54</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr"/>
+      <c r="K21" s="2" t="inlineStr"/>
+      <c r="L21" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M21" s="2" t="inlineStr"/>
+      <c r="N21" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="O21" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="P21" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q21" s="2" t="inlineStr"/>
+      <c r="R21" s="2" t="inlineStr"/>
+      <c r="S21" s="2" t="inlineStr"/>
+      <c r="T21" s="2" t="inlineStr"/>
+      <c r="U21" s="2" t="inlineStr">
+        <is>
+          <t>07:54</t>
+        </is>
+      </c>
+      <c r="V21" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W21" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X21" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y21" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z21" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA21" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB21" s="2" t="inlineStr"/>
+      <c r="AC21" s="2" t="inlineStr">
+        <is>
+          <t>—/20</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-10-31-浦东35路.xlsx
+++ b/data/export/2026-10-31-浦东35路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC21"/>
+  <dimension ref="A1:AC26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -441,7 +441,7 @@
     <col width="10" customWidth="1" min="9" max="9"/>
     <col width="18" customWidth="1" min="10" max="10"/>
     <col width="26" customWidth="1" min="11" max="11"/>
-    <col width="18" customWidth="1" min="12" max="12"/>
+    <col width="25" customWidth="1" min="12" max="12"/>
     <col width="22" customWidth="1" min="13" max="13"/>
     <col width="14" customWidth="1" min="14" max="14"/>
     <col width="14" customWidth="1" min="15" max="15"/>
@@ -632,32 +632,36 @@
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:13</t>
         </is>
       </c>
       <c r="I2" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>128分钟</t>
         </is>
       </c>
       <c r="J2" s="2" t="inlineStr"/>
       <c r="K2" s="2" t="inlineStr"/>
       <c r="L2" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M2" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M2" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N2" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -665,7 +669,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:11</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -689,17 +693,17 @@
       </c>
       <c r="W2" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X2" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y2" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z2" s="2" t="inlineStr">
@@ -709,13 +713,17 @@
       </c>
       <c r="AA2" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB2" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB2" s="2" t="inlineStr">
+        <is>
+          <t>128.0</t>
+        </is>
+      </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>—/20</t>
+          <t>2/25</t>
         </is>
       </c>
     </row>
@@ -743,32 +751,36 @@
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H3" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="I3" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>131分钟</t>
         </is>
       </c>
       <c r="J3" s="2" t="inlineStr"/>
       <c r="K3" s="2" t="inlineStr"/>
       <c r="L3" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M3" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±4分钟</t>
+        </is>
+      </c>
+      <c r="M3" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="N3" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -776,7 +788,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:14</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -800,17 +812,17 @@
       </c>
       <c r="W3" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X3" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y3" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z3" s="2" t="inlineStr">
@@ -820,13 +832,17 @@
       </c>
       <c r="AA3" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB3" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB3" s="2" t="inlineStr">
+        <is>
+          <t>131.0</t>
+        </is>
+      </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>—/20</t>
+          <t>4/25</t>
         </is>
       </c>
     </row>
@@ -854,32 +870,36 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:23</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>125分钟</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr"/>
       <c r="K4" s="2" t="inlineStr"/>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -887,7 +907,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:11</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -911,17 +931,17 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X4" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y4" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z4" s="2" t="inlineStr">
@@ -931,13 +951,17 @@
       </c>
       <c r="AA4" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB4" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB4" s="2" t="inlineStr">
+        <is>
+          <t>125.0</t>
+        </is>
+      </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>—/20</t>
+          <t>1/25</t>
         </is>
       </c>
     </row>
@@ -998,7 +1022,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:14</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1048,7 +1072,7 @@
       <c r="AB5" s="2" t="inlineStr"/>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>—/20</t>
+          <t>—/25</t>
         </is>
       </c>
     </row>
@@ -1076,32 +1100,36 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:39</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>128分钟</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr"/>
       <c r="K6" s="2" t="inlineStr"/>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M6" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -1109,7 +1137,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:14</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1133,17 +1161,17 @@
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X6" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y6" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z6" s="2" t="inlineStr">
@@ -1153,13 +1181,17 @@
       </c>
       <c r="AA6" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB6" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB6" s="2" t="inlineStr">
+        <is>
+          <t>128.0</t>
+        </is>
+      </c>
       <c r="AC6" s="2" t="inlineStr">
         <is>
-          <t>—/20</t>
+          <t>2/25</t>
         </is>
       </c>
     </row>
@@ -1220,7 +1252,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:14</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1270,7 +1302,7 @@
       <c r="AB7" s="2" t="inlineStr"/>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>—/20</t>
+          <t>—/25</t>
         </is>
       </c>
     </row>
@@ -1331,7 +1363,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:14</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1381,7 +1413,7 @@
       <c r="AB8" s="2" t="inlineStr"/>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>—/20</t>
+          <t>—/25</t>
         </is>
       </c>
     </row>
@@ -1442,7 +1474,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:14</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1492,7 +1524,7 @@
       <c r="AB9" s="2" t="inlineStr"/>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>—/20</t>
+          <t>—/25</t>
         </is>
       </c>
     </row>
@@ -1553,7 +1585,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:14</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1603,7 +1635,7 @@
       <c r="AB10" s="2" t="inlineStr"/>
       <c r="AC10" s="2" t="inlineStr">
         <is>
-          <t>—/20</t>
+          <t>—/25</t>
         </is>
       </c>
     </row>
@@ -1664,7 +1696,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:14</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1714,7 +1746,7 @@
       <c r="AB11" s="2" t="inlineStr"/>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>—/20</t>
+          <t>—/25</t>
         </is>
       </c>
     </row>
@@ -1775,7 +1807,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:14</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1825,7 +1857,7 @@
       <c r="AB12" s="2" t="inlineStr"/>
       <c r="AC12" s="2" t="inlineStr">
         <is>
-          <t>—/20</t>
+          <t>—/25</t>
         </is>
       </c>
     </row>
@@ -1886,7 +1918,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:14</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -1936,7 +1968,7 @@
       <c r="AB13" s="2" t="inlineStr"/>
       <c r="AC13" s="2" t="inlineStr">
         <is>
-          <t>—/20</t>
+          <t>—/25</t>
         </is>
       </c>
     </row>
@@ -1997,7 +2029,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:14</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2047,7 +2079,7 @@
       <c r="AB14" s="2" t="inlineStr"/>
       <c r="AC14" s="2" t="inlineStr">
         <is>
-          <t>—/20</t>
+          <t>—/25</t>
         </is>
       </c>
     </row>
@@ -2108,7 +2140,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:14</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2158,7 +2190,7 @@
       <c r="AB15" s="2" t="inlineStr"/>
       <c r="AC15" s="2" t="inlineStr">
         <is>
-          <t>—/20</t>
+          <t>—/25</t>
         </is>
       </c>
     </row>
@@ -2219,7 +2251,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:14</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2269,7 +2301,7 @@
       <c r="AB16" s="2" t="inlineStr"/>
       <c r="AC16" s="2" t="inlineStr">
         <is>
-          <t>—/20</t>
+          <t>—/25</t>
         </is>
       </c>
     </row>
@@ -2330,7 +2362,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:14</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2380,7 +2412,7 @@
       <c r="AB17" s="2" t="inlineStr"/>
       <c r="AC17" s="2" t="inlineStr">
         <is>
-          <t>—/20</t>
+          <t>—/25</t>
         </is>
       </c>
     </row>
@@ -2441,7 +2473,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:14</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2491,7 +2523,7 @@
       <c r="AB18" s="2" t="inlineStr"/>
       <c r="AC18" s="2" t="inlineStr">
         <is>
-          <t>—/20</t>
+          <t>—/25</t>
         </is>
       </c>
     </row>
@@ -2552,7 +2584,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>07:31</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2602,7 +2634,7 @@
       <c r="AB19" s="2" t="inlineStr"/>
       <c r="AC19" s="2" t="inlineStr">
         <is>
-          <t>—/20</t>
+          <t>—/25</t>
         </is>
       </c>
     </row>
@@ -2663,7 +2695,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:14</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2713,7 +2745,7 @@
       <c r="AB20" s="2" t="inlineStr"/>
       <c r="AC20" s="2" t="inlineStr">
         <is>
-          <t>—/20</t>
+          <t>—/25</t>
         </is>
       </c>
     </row>
@@ -2774,7 +2806,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:14</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -2824,7 +2856,562 @@
       <c r="AB21" s="2" t="inlineStr"/>
       <c r="AC21" s="2" t="inlineStr">
         <is>
-          <t>—/20</t>
+          <t>—/25</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="inlineStr"/>
+      <c r="B22" s="2" t="inlineStr">
+        <is>
+          <t>沪A67672D</t>
+        </is>
+      </c>
+      <c r="C22" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>08:06</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr"/>
+      <c r="K22" s="2" t="inlineStr"/>
+      <c r="L22" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M22" s="2" t="inlineStr"/>
+      <c r="N22" s="2" t="inlineStr">
+        <is>
+          <t>07:41</t>
+        </is>
+      </c>
+      <c r="O22" s="2" t="inlineStr">
+        <is>
+          <t>08:01</t>
+        </is>
+      </c>
+      <c r="P22" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q22" s="2" t="inlineStr"/>
+      <c r="R22" s="2" t="inlineStr"/>
+      <c r="S22" s="2" t="inlineStr"/>
+      <c r="T22" s="2" t="inlineStr"/>
+      <c r="U22" s="2" t="inlineStr">
+        <is>
+          <t>08:06</t>
+        </is>
+      </c>
+      <c r="V22" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W22" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X22" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y22" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z22" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA22" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB22" s="2" t="inlineStr"/>
+      <c r="AC22" s="2" t="inlineStr">
+        <is>
+          <t>—/25</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="2" t="inlineStr"/>
+      <c r="B23" s="2" t="inlineStr">
+        <is>
+          <t>沪A71572D</t>
+        </is>
+      </c>
+      <c r="C23" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>08:06</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr"/>
+      <c r="K23" s="2" t="inlineStr"/>
+      <c r="L23" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M23" s="2" t="inlineStr"/>
+      <c r="N23" s="2" t="inlineStr">
+        <is>
+          <t>06:21</t>
+        </is>
+      </c>
+      <c r="O23" s="2" t="inlineStr">
+        <is>
+          <t>08:01</t>
+        </is>
+      </c>
+      <c r="P23" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q23" s="2" t="inlineStr"/>
+      <c r="R23" s="2" t="inlineStr"/>
+      <c r="S23" s="2" t="inlineStr"/>
+      <c r="T23" s="2" t="inlineStr"/>
+      <c r="U23" s="2" t="inlineStr">
+        <is>
+          <t>08:06</t>
+        </is>
+      </c>
+      <c r="V23" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W23" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X23" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y23" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z23" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA23" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB23" s="2" t="inlineStr"/>
+      <c r="AC23" s="2" t="inlineStr">
+        <is>
+          <t>—/25</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="2" t="inlineStr"/>
+      <c r="B24" s="2" t="inlineStr">
+        <is>
+          <t>沪A36993D</t>
+        </is>
+      </c>
+      <c r="C24" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>08:18</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="inlineStr"/>
+      <c r="K24" s="2" t="inlineStr"/>
+      <c r="L24" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M24" s="2" t="inlineStr"/>
+      <c r="N24" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O24" s="2" t="inlineStr">
+        <is>
+          <t>08:14</t>
+        </is>
+      </c>
+      <c r="P24" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q24" s="2" t="inlineStr"/>
+      <c r="R24" s="2" t="inlineStr"/>
+      <c r="S24" s="2" t="inlineStr"/>
+      <c r="T24" s="2" t="inlineStr"/>
+      <c r="U24" s="2" t="inlineStr">
+        <is>
+          <t>08:18</t>
+        </is>
+      </c>
+      <c r="V24" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W24" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X24" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y24" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z24" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA24" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB24" s="2" t="inlineStr"/>
+      <c r="AC24" s="2" t="inlineStr">
+        <is>
+          <t>—/25</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="2" t="inlineStr"/>
+      <c r="B25" s="2" t="inlineStr">
+        <is>
+          <t>沪A55102D</t>
+        </is>
+      </c>
+      <c r="C25" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
+        <is>
+          <t>08:18</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F25" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G25" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H25" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I25" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J25" s="2" t="inlineStr"/>
+      <c r="K25" s="2" t="inlineStr"/>
+      <c r="L25" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M25" s="2" t="inlineStr"/>
+      <c r="N25" s="2" t="inlineStr">
+        <is>
+          <t>06:51</t>
+        </is>
+      </c>
+      <c r="O25" s="2" t="inlineStr">
+        <is>
+          <t>08:14</t>
+        </is>
+      </c>
+      <c r="P25" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q25" s="2" t="inlineStr"/>
+      <c r="R25" s="2" t="inlineStr"/>
+      <c r="S25" s="2" t="inlineStr"/>
+      <c r="T25" s="2" t="inlineStr"/>
+      <c r="U25" s="2" t="inlineStr">
+        <is>
+          <t>08:18</t>
+        </is>
+      </c>
+      <c r="V25" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W25" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X25" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y25" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z25" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA25" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB25" s="2" t="inlineStr"/>
+      <c r="AC25" s="2" t="inlineStr">
+        <is>
+          <t>—/25</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="2" t="inlineStr"/>
+      <c r="B26" s="2" t="inlineStr">
+        <is>
+          <t>沪A57601A</t>
+        </is>
+      </c>
+      <c r="C26" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>08:30</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G26" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H26" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I26" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J26" s="2" t="inlineStr"/>
+      <c r="K26" s="2" t="inlineStr"/>
+      <c r="L26" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M26" s="2" t="inlineStr"/>
+      <c r="N26" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O26" s="2" t="inlineStr">
+        <is>
+          <t>08:14</t>
+        </is>
+      </c>
+      <c r="P26" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q26" s="2" t="inlineStr"/>
+      <c r="R26" s="2" t="inlineStr"/>
+      <c r="S26" s="2" t="inlineStr"/>
+      <c r="T26" s="2" t="inlineStr"/>
+      <c r="U26" s="2" t="inlineStr">
+        <is>
+          <t>08:30</t>
+        </is>
+      </c>
+      <c r="V26" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W26" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X26" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y26" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z26" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA26" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB26" s="2" t="inlineStr"/>
+      <c r="AC26" s="2" t="inlineStr">
+        <is>
+          <t>—/25</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-10-31-浦东35路.xlsx
+++ b/data/export/2026-10-31-浦东35路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC26"/>
+  <dimension ref="A1:AC36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -436,7 +436,7 @@
     <col width="10" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
-    <col width="35" customWidth="1" min="7" max="7"/>
+    <col width="36" customWidth="1" min="7" max="7"/>
     <col width="10" customWidth="1" min="8" max="8"/>
     <col width="10" customWidth="1" min="9" max="9"/>
     <col width="18" customWidth="1" min="10" max="10"/>
@@ -446,10 +446,10 @@
     <col width="14" customWidth="1" min="14" max="14"/>
     <col width="14" customWidth="1" min="15" max="15"/>
     <col width="10" customWidth="1" min="16" max="16"/>
-    <col width="10" customWidth="1" min="17" max="17"/>
+    <col width="16" customWidth="1" min="17" max="17"/>
     <col width="16" customWidth="1" min="18" max="18"/>
     <col width="20" customWidth="1" min="19" max="19"/>
-    <col width="14" customWidth="1" min="20" max="20"/>
+    <col width="36" customWidth="1" min="20" max="20"/>
     <col width="14" customWidth="1" min="21" max="21"/>
     <col width="14" customWidth="1" min="22" max="22"/>
     <col width="12" customWidth="1" min="23" max="23"/>
@@ -669,7 +669,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>08:11</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -708,14 +708,14 @@
       </c>
       <c r="Z2" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA2" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AA2" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB2" s="2" t="inlineStr">
         <is>
           <t>128.0</t>
@@ -723,7 +723,7 @@
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>2/25</t>
+          <t>3/26</t>
         </is>
       </c>
     </row>
@@ -788,7 +788,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>08:14</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -827,14 +827,14 @@
       </c>
       <c r="Z3" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA3" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AA3" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB3" s="2" t="inlineStr">
         <is>
           <t>131.0</t>
@@ -842,7 +842,7 @@
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>4/25</t>
+          <t>8/26</t>
         </is>
       </c>
     </row>
@@ -907,7 +907,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>08:11</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -946,14 +946,14 @@
       </c>
       <c r="Z4" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA4" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AA4" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB4" s="2" t="inlineStr">
         <is>
           <t>125.0</t>
@@ -961,7 +961,7 @@
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>1/25</t>
+          <t>1/26</t>
         </is>
       </c>
     </row>
@@ -989,32 +989,36 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:43</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>132分钟</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr"/>
       <c r="K5" s="2" t="inlineStr"/>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -1022,7 +1026,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>08:14</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1046,33 +1050,37 @@
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X5" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y5" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z5" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA5" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AA5" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB5" s="2" t="inlineStr"/>
+      <c r="AB5" s="2" t="inlineStr">
+        <is>
+          <t>132.0</t>
+        </is>
+      </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>—/25</t>
+          <t>10/26</t>
         </is>
       </c>
     </row>
@@ -1137,7 +1145,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>08:14</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1176,14 +1184,14 @@
       </c>
       <c r="Z6" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA6" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AA6" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB6" s="2" t="inlineStr">
         <is>
           <t>128.0</t>
@@ -1191,7 +1199,7 @@
       </c>
       <c r="AC6" s="2" t="inlineStr">
         <is>
-          <t>2/25</t>
+          <t>3/26</t>
         </is>
       </c>
     </row>
@@ -1219,32 +1227,36 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:49</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>127分钟</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr"/>
       <c r="K7" s="2" t="inlineStr"/>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
           <t>06:11</t>
@@ -1252,7 +1264,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>08:14</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1276,33 +1288,37 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X7" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y7" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z7" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA7" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AA7" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB7" s="2" t="inlineStr"/>
+      <c r="AB7" s="2" t="inlineStr">
+        <is>
+          <t>127.0</t>
+        </is>
+      </c>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>—/25</t>
+          <t>2/26</t>
         </is>
       </c>
     </row>
@@ -1330,32 +1346,36 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:53</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>131分钟</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr"/>
       <c r="K8" s="2" t="inlineStr"/>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -1363,7 +1383,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>08:14</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1387,33 +1407,37 @@
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X8" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y8" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z8" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA8" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AA8" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB8" s="2" t="inlineStr"/>
+      <c r="AB8" s="2" t="inlineStr">
+        <is>
+          <t>131.0</t>
+        </is>
+      </c>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>—/25</t>
+          <t>8/26</t>
         </is>
       </c>
     </row>
@@ -1441,32 +1465,36 @@
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:04</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>130分钟</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr"/>
       <c r="K9" s="2" t="inlineStr"/>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M9" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
           <t>06:21</t>
@@ -1474,7 +1502,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>08:14</t>
+          <t>09:01</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1498,17 +1526,17 @@
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X9" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y9" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z9" s="2" t="inlineStr">
@@ -1518,13 +1546,17 @@
       </c>
       <c r="AA9" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB9" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB9" s="2" t="inlineStr">
+        <is>
+          <t>130.0</t>
+        </is>
+      </c>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>—/25</t>
+          <t>6/26</t>
         </is>
       </c>
     </row>
@@ -1552,32 +1584,36 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:07</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>133分钟</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr"/>
       <c r="K10" s="2" t="inlineStr"/>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
           <t>06:11</t>
@@ -1585,7 +1621,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>08:14</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1609,33 +1645,37 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X10" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y10" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z10" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA10" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AA10" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB10" s="2" t="inlineStr"/>
+      <c r="AB10" s="2" t="inlineStr">
+        <is>
+          <t>133.0</t>
+        </is>
+      </c>
       <c r="AC10" s="2" t="inlineStr">
         <is>
-          <t>—/25</t>
+          <t>11/26</t>
         </is>
       </c>
     </row>
@@ -1663,32 +1703,36 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:15</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>129分钟</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr"/>
       <c r="K11" s="2" t="inlineStr"/>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
           <t>06:41</t>
@@ -1696,7 +1740,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>08:14</t>
+          <t>09:11</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1720,17 +1764,17 @@
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X11" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y11" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z11" s="2" t="inlineStr">
@@ -1740,13 +1784,17 @@
       </c>
       <c r="AA11" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB11" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB11" s="2" t="inlineStr">
+        <is>
+          <t>129.0</t>
+        </is>
+      </c>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>—/25</t>
+          <t>5/26</t>
         </is>
       </c>
     </row>
@@ -1774,32 +1822,36 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:16</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>130分钟</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr"/>
       <c r="K12" s="2" t="inlineStr"/>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
           <t>06:32</t>
@@ -1807,7 +1859,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>08:14</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1831,33 +1883,37 @@
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X12" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y12" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z12" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA12" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AA12" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB12" s="2" t="inlineStr"/>
+      <c r="AB12" s="2" t="inlineStr">
+        <is>
+          <t>130.0</t>
+        </is>
+      </c>
       <c r="AC12" s="2" t="inlineStr">
         <is>
-          <t>—/25</t>
+          <t>6/26</t>
         </is>
       </c>
     </row>
@@ -1885,12 +1941,12 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>疑似区间车</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>原方向在全程36%处后消失；随后反向物理轨迹由seq38推进至seq60，推进22站，达到≥2站确认条件</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
@@ -1918,7 +1974,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>08:14</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -1926,10 +1982,26 @@
           <t>SHMAAS</t>
         </is>
       </c>
-      <c r="Q13" s="2" t="inlineStr"/>
-      <c r="R13" s="2" t="inlineStr"/>
-      <c r="S13" s="2" t="inlineStr"/>
-      <c r="T13" s="2" t="inlineStr"/>
+      <c r="Q13" s="2" t="inlineStr">
+        <is>
+          <t>物理seq24（站名待映射）</t>
+        </is>
+      </c>
+      <c r="R13" s="2" t="inlineStr">
+        <is>
+          <t>08:02</t>
+        </is>
+      </c>
+      <c r="S13" s="2" t="inlineStr">
+        <is>
+          <t>08:08</t>
+        </is>
+      </c>
+      <c r="T13" s="2" t="inlineStr">
+        <is>
+          <t>折返点按重建物理位置seq24映射；到达按末次同向ETA估算；折返发车结合首次反向物理观测取区间中点，约±6分钟；反向位置物理seq38（站名待映射） ETA 9分钟参与校验</t>
+        </is>
+      </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
           <t>07:12</t>
@@ -1968,7 +2040,7 @@
       <c r="AB13" s="2" t="inlineStr"/>
       <c r="AC13" s="2" t="inlineStr">
         <is>
-          <t>—/25</t>
+          <t>—/26</t>
         </is>
       </c>
     </row>
@@ -1996,32 +2068,36 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:35</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>137分钟</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr"/>
       <c r="K14" s="2" t="inlineStr"/>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
           <t>07:01</t>
@@ -2029,7 +2105,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>08:14</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2053,17 +2129,17 @@
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X14" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y14" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z14" s="2" t="inlineStr">
@@ -2073,13 +2149,17 @@
       </c>
       <c r="AA14" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB14" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB14" s="2" t="inlineStr">
+        <is>
+          <t>137.0</t>
+        </is>
+      </c>
       <c r="AC14" s="2" t="inlineStr">
         <is>
-          <t>—/25</t>
+          <t>12/26</t>
         </is>
       </c>
     </row>
@@ -2140,7 +2220,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>08:14</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2190,7 +2270,7 @@
       <c r="AB15" s="2" t="inlineStr"/>
       <c r="AC15" s="2" t="inlineStr">
         <is>
-          <t>—/25</t>
+          <t>—/26</t>
         </is>
       </c>
     </row>
@@ -2251,7 +2331,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>08:14</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2301,7 +2381,7 @@
       <c r="AB16" s="2" t="inlineStr"/>
       <c r="AC16" s="2" t="inlineStr">
         <is>
-          <t>—/25</t>
+          <t>—/26</t>
         </is>
       </c>
     </row>
@@ -2362,7 +2442,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>08:14</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2412,7 +2492,7 @@
       <c r="AB17" s="2" t="inlineStr"/>
       <c r="AC17" s="2" t="inlineStr">
         <is>
-          <t>—/25</t>
+          <t>—/26</t>
         </is>
       </c>
     </row>
@@ -2473,7 +2553,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>08:14</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2523,7 +2603,7 @@
       <c r="AB18" s="2" t="inlineStr"/>
       <c r="AC18" s="2" t="inlineStr">
         <is>
-          <t>—/25</t>
+          <t>—/26</t>
         </is>
       </c>
     </row>
@@ -2634,7 +2714,7 @@
       <c r="AB19" s="2" t="inlineStr"/>
       <c r="AC19" s="2" t="inlineStr">
         <is>
-          <t>—/25</t>
+          <t>—/26</t>
         </is>
       </c>
     </row>
@@ -2695,7 +2775,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>08:14</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2745,7 +2825,7 @@
       <c r="AB20" s="2" t="inlineStr"/>
       <c r="AC20" s="2" t="inlineStr">
         <is>
-          <t>—/25</t>
+          <t>—/26</t>
         </is>
       </c>
     </row>
@@ -2806,7 +2886,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>08:14</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -2856,7 +2936,7 @@
       <c r="AB21" s="2" t="inlineStr"/>
       <c r="AC21" s="2" t="inlineStr">
         <is>
-          <t>—/25</t>
+          <t>—/26</t>
         </is>
       </c>
     </row>
@@ -2917,7 +2997,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>08:01</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -2967,7 +3047,7 @@
       <c r="AB22" s="2" t="inlineStr"/>
       <c r="AC22" s="2" t="inlineStr">
         <is>
-          <t>—/25</t>
+          <t>—/26</t>
         </is>
       </c>
     </row>
@@ -3078,7 +3158,7 @@
       <c r="AB23" s="2" t="inlineStr"/>
       <c r="AC23" s="2" t="inlineStr">
         <is>
-          <t>—/25</t>
+          <t>—/26</t>
         </is>
       </c>
     </row>
@@ -3139,7 +3219,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>08:14</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -3189,7 +3269,7 @@
       <c r="AB24" s="2" t="inlineStr"/>
       <c r="AC24" s="2" t="inlineStr">
         <is>
-          <t>—/25</t>
+          <t>—/26</t>
         </is>
       </c>
     </row>
@@ -3250,7 +3330,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>08:14</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3300,7 +3380,7 @@
       <c r="AB25" s="2" t="inlineStr"/>
       <c r="AC25" s="2" t="inlineStr">
         <is>
-          <t>—/25</t>
+          <t>—/26</t>
         </is>
       </c>
     </row>
@@ -3361,7 +3441,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>08:14</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3411,7 +3491,1153 @@
       <c r="AB26" s="2" t="inlineStr"/>
       <c r="AC26" s="2" t="inlineStr">
         <is>
-          <t>—/25</t>
+          <t>—/26</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="2" t="inlineStr"/>
+      <c r="B27" s="2" t="inlineStr">
+        <is>
+          <t>沪A15330A</t>
+        </is>
+      </c>
+      <c r="C27" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
+        <is>
+          <t>08:38</t>
+        </is>
+      </c>
+      <c r="E27" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F27" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G27" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H27" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I27" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J27" s="2" t="inlineStr"/>
+      <c r="K27" s="2" t="inlineStr"/>
+      <c r="L27" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M27" s="2" t="inlineStr"/>
+      <c r="N27" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O27" s="2" t="inlineStr">
+        <is>
+          <t>09:21</t>
+        </is>
+      </c>
+      <c r="P27" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q27" s="2" t="inlineStr"/>
+      <c r="R27" s="2" t="inlineStr"/>
+      <c r="S27" s="2" t="inlineStr"/>
+      <c r="T27" s="2" t="inlineStr"/>
+      <c r="U27" s="2" t="inlineStr">
+        <is>
+          <t>08:38</t>
+        </is>
+      </c>
+      <c r="V27" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W27" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X27" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y27" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z27" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA27" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB27" s="2" t="inlineStr">
+        <is>
+          <t>128.0</t>
+        </is>
+      </c>
+      <c r="AC27" s="2" t="inlineStr">
+        <is>
+          <t>3/26</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="2" t="inlineStr"/>
+      <c r="B28" s="2" t="inlineStr">
+        <is>
+          <t>沪A70597D</t>
+        </is>
+      </c>
+      <c r="C28" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>08:45</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G28" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H28" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I28" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J28" s="2" t="inlineStr"/>
+      <c r="K28" s="2" t="inlineStr"/>
+      <c r="L28" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M28" s="2" t="inlineStr"/>
+      <c r="N28" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O28" s="2" t="inlineStr">
+        <is>
+          <t>09:21</t>
+        </is>
+      </c>
+      <c r="P28" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q28" s="2" t="inlineStr"/>
+      <c r="R28" s="2" t="inlineStr"/>
+      <c r="S28" s="2" t="inlineStr"/>
+      <c r="T28" s="2" t="inlineStr"/>
+      <c r="U28" s="2" t="inlineStr">
+        <is>
+          <t>08:45</t>
+        </is>
+      </c>
+      <c r="V28" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W28" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X28" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y28" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z28" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA28" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB28" s="2" t="inlineStr">
+        <is>
+          <t>131.0</t>
+        </is>
+      </c>
+      <c r="AC28" s="2" t="inlineStr">
+        <is>
+          <t>8/26</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="2" t="inlineStr"/>
+      <c r="B29" s="2" t="inlineStr">
+        <is>
+          <t>沪A67057D</t>
+        </is>
+      </c>
+      <c r="C29" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="inlineStr">
+        <is>
+          <t>08:48</t>
+        </is>
+      </c>
+      <c r="E29" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F29" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G29" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H29" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I29" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J29" s="2" t="inlineStr"/>
+      <c r="K29" s="2" t="inlineStr"/>
+      <c r="L29" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M29" s="2" t="inlineStr"/>
+      <c r="N29" s="2" t="inlineStr">
+        <is>
+          <t>07:01</t>
+        </is>
+      </c>
+      <c r="O29" s="2" t="inlineStr">
+        <is>
+          <t>09:21</t>
+        </is>
+      </c>
+      <c r="P29" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q29" s="2" t="inlineStr"/>
+      <c r="R29" s="2" t="inlineStr"/>
+      <c r="S29" s="2" t="inlineStr"/>
+      <c r="T29" s="2" t="inlineStr"/>
+      <c r="U29" s="2" t="inlineStr">
+        <is>
+          <t>08:48</t>
+        </is>
+      </c>
+      <c r="V29" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W29" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X29" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y29" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z29" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA29" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB29" s="2" t="inlineStr"/>
+      <c r="AC29" s="2" t="inlineStr">
+        <is>
+          <t>—/26</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="2" t="inlineStr"/>
+      <c r="B30" s="2" t="inlineStr">
+        <is>
+          <t>沪A67712D</t>
+        </is>
+      </c>
+      <c r="C30" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
+        <is>
+          <t>09:00</t>
+        </is>
+      </c>
+      <c r="E30" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F30" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G30" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H30" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I30" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J30" s="2" t="inlineStr"/>
+      <c r="K30" s="2" t="inlineStr"/>
+      <c r="L30" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M30" s="2" t="inlineStr"/>
+      <c r="N30" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O30" s="2" t="inlineStr">
+        <is>
+          <t>09:21</t>
+        </is>
+      </c>
+      <c r="P30" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q30" s="2" t="inlineStr"/>
+      <c r="R30" s="2" t="inlineStr"/>
+      <c r="S30" s="2" t="inlineStr"/>
+      <c r="T30" s="2" t="inlineStr"/>
+      <c r="U30" s="2" t="inlineStr">
+        <is>
+          <t>09:00</t>
+        </is>
+      </c>
+      <c r="V30" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W30" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X30" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y30" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z30" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA30" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB30" s="2" t="inlineStr">
+        <is>
+          <t>125.0</t>
+        </is>
+      </c>
+      <c r="AC30" s="2" t="inlineStr">
+        <is>
+          <t>1/26</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="2" t="inlineStr"/>
+      <c r="B31" s="2" t="inlineStr">
+        <is>
+          <t>沪A95621D</t>
+        </is>
+      </c>
+      <c r="C31" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D31" s="2" t="inlineStr">
+        <is>
+          <t>09:00</t>
+        </is>
+      </c>
+      <c r="E31" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F31" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G31" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H31" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I31" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J31" s="2" t="inlineStr"/>
+      <c r="K31" s="2" t="inlineStr"/>
+      <c r="L31" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M31" s="2" t="inlineStr"/>
+      <c r="N31" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O31" s="2" t="inlineStr">
+        <is>
+          <t>09:21</t>
+        </is>
+      </c>
+      <c r="P31" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q31" s="2" t="inlineStr"/>
+      <c r="R31" s="2" t="inlineStr"/>
+      <c r="S31" s="2" t="inlineStr"/>
+      <c r="T31" s="2" t="inlineStr"/>
+      <c r="U31" s="2" t="inlineStr">
+        <is>
+          <t>09:00</t>
+        </is>
+      </c>
+      <c r="V31" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W31" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X31" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y31" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z31" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA31" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB31" s="2" t="inlineStr">
+        <is>
+          <t>128.0</t>
+        </is>
+      </c>
+      <c r="AC31" s="2" t="inlineStr">
+        <is>
+          <t>3/26</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="2" t="inlineStr"/>
+      <c r="B32" s="2" t="inlineStr">
+        <is>
+          <t>沪A62981D</t>
+        </is>
+      </c>
+      <c r="C32" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D32" s="2" t="inlineStr">
+        <is>
+          <t>09:15</t>
+        </is>
+      </c>
+      <c r="E32" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F32" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G32" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H32" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I32" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J32" s="2" t="inlineStr"/>
+      <c r="K32" s="2" t="inlineStr"/>
+      <c r="L32" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M32" s="2" t="inlineStr"/>
+      <c r="N32" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O32" s="2" t="inlineStr">
+        <is>
+          <t>09:21</t>
+        </is>
+      </c>
+      <c r="P32" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q32" s="2" t="inlineStr"/>
+      <c r="R32" s="2" t="inlineStr"/>
+      <c r="S32" s="2" t="inlineStr"/>
+      <c r="T32" s="2" t="inlineStr"/>
+      <c r="U32" s="2" t="inlineStr">
+        <is>
+          <t>09:15</t>
+        </is>
+      </c>
+      <c r="V32" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W32" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X32" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y32" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z32" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA32" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB32" s="2" t="inlineStr">
+        <is>
+          <t>132.0</t>
+        </is>
+      </c>
+      <c r="AC32" s="2" t="inlineStr">
+        <is>
+          <t>10/26</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="2" t="inlineStr"/>
+      <c r="B33" s="2" t="inlineStr">
+        <is>
+          <t>沪A73927D</t>
+        </is>
+      </c>
+      <c r="C33" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D33" s="2" t="inlineStr">
+        <is>
+          <t>09:15</t>
+        </is>
+      </c>
+      <c r="E33" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F33" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G33" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H33" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I33" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J33" s="2" t="inlineStr"/>
+      <c r="K33" s="2" t="inlineStr"/>
+      <c r="L33" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M33" s="2" t="inlineStr"/>
+      <c r="N33" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O33" s="2" t="inlineStr">
+        <is>
+          <t>09:21</t>
+        </is>
+      </c>
+      <c r="P33" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q33" s="2" t="inlineStr"/>
+      <c r="R33" s="2" t="inlineStr"/>
+      <c r="S33" s="2" t="inlineStr"/>
+      <c r="T33" s="2" t="inlineStr"/>
+      <c r="U33" s="2" t="inlineStr">
+        <is>
+          <t>09:15</t>
+        </is>
+      </c>
+      <c r="V33" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W33" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X33" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y33" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z33" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA33" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB33" s="2" t="inlineStr">
+        <is>
+          <t>131.0</t>
+        </is>
+      </c>
+      <c r="AC33" s="2" t="inlineStr">
+        <is>
+          <t>8/26</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="2" t="inlineStr"/>
+      <c r="B34" s="2" t="inlineStr">
+        <is>
+          <t>沪A66883D</t>
+        </is>
+      </c>
+      <c r="C34" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D34" s="2" t="inlineStr">
+        <is>
+          <t>09:30</t>
+        </is>
+      </c>
+      <c r="E34" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F34" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G34" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H34" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I34" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J34" s="2" t="inlineStr"/>
+      <c r="K34" s="2" t="inlineStr"/>
+      <c r="L34" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M34" s="2" t="inlineStr"/>
+      <c r="N34" s="2" t="inlineStr">
+        <is>
+          <t>06:11</t>
+        </is>
+      </c>
+      <c r="O34" s="2" t="inlineStr">
+        <is>
+          <t>09:21</t>
+        </is>
+      </c>
+      <c r="P34" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q34" s="2" t="inlineStr"/>
+      <c r="R34" s="2" t="inlineStr"/>
+      <c r="S34" s="2" t="inlineStr"/>
+      <c r="T34" s="2" t="inlineStr"/>
+      <c r="U34" s="2" t="inlineStr">
+        <is>
+          <t>09:30</t>
+        </is>
+      </c>
+      <c r="V34" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W34" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X34" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y34" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z34" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA34" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB34" s="2" t="inlineStr">
+        <is>
+          <t>133.0</t>
+        </is>
+      </c>
+      <c r="AC34" s="2" t="inlineStr">
+        <is>
+          <t>11/26</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="2" t="inlineStr"/>
+      <c r="B35" s="2" t="inlineStr">
+        <is>
+          <t>沪A68375D</t>
+        </is>
+      </c>
+      <c r="C35" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D35" s="2" t="inlineStr">
+        <is>
+          <t>09:30</t>
+        </is>
+      </c>
+      <c r="E35" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F35" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G35" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H35" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I35" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J35" s="2" t="inlineStr"/>
+      <c r="K35" s="2" t="inlineStr"/>
+      <c r="L35" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M35" s="2" t="inlineStr"/>
+      <c r="N35" s="2" t="inlineStr">
+        <is>
+          <t>06:11</t>
+        </is>
+      </c>
+      <c r="O35" s="2" t="inlineStr">
+        <is>
+          <t>09:21</t>
+        </is>
+      </c>
+      <c r="P35" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q35" s="2" t="inlineStr"/>
+      <c r="R35" s="2" t="inlineStr"/>
+      <c r="S35" s="2" t="inlineStr"/>
+      <c r="T35" s="2" t="inlineStr"/>
+      <c r="U35" s="2" t="inlineStr">
+        <is>
+          <t>09:30</t>
+        </is>
+      </c>
+      <c r="V35" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W35" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X35" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y35" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z35" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA35" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB35" s="2" t="inlineStr">
+        <is>
+          <t>127.0</t>
+        </is>
+      </c>
+      <c r="AC35" s="2" t="inlineStr">
+        <is>
+          <t>2/26</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="2" t="inlineStr"/>
+      <c r="B36" s="2" t="inlineStr">
+        <is>
+          <t>沪A72873D</t>
+        </is>
+      </c>
+      <c r="C36" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D36" s="2" t="inlineStr">
+        <is>
+          <t>09:45</t>
+        </is>
+      </c>
+      <c r="E36" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F36" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G36" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H36" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I36" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J36" s="2" t="inlineStr"/>
+      <c r="K36" s="2" t="inlineStr"/>
+      <c r="L36" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M36" s="2" t="inlineStr"/>
+      <c r="N36" s="2" t="inlineStr">
+        <is>
+          <t>06:32</t>
+        </is>
+      </c>
+      <c r="O36" s="2" t="inlineStr">
+        <is>
+          <t>09:21</t>
+        </is>
+      </c>
+      <c r="P36" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q36" s="2" t="inlineStr"/>
+      <c r="R36" s="2" t="inlineStr"/>
+      <c r="S36" s="2" t="inlineStr"/>
+      <c r="T36" s="2" t="inlineStr"/>
+      <c r="U36" s="2" t="inlineStr">
+        <is>
+          <t>09:45</t>
+        </is>
+      </c>
+      <c r="V36" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W36" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X36" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y36" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z36" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA36" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB36" s="2" t="inlineStr">
+        <is>
+          <t>130.0</t>
+        </is>
+      </c>
+      <c r="AC36" s="2" t="inlineStr">
+        <is>
+          <t>6/26</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-10-31-浦东35路.xlsx
+++ b/data/export/2026-10-31-浦东35路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC36"/>
+  <dimension ref="A1:AC38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -669,7 +669,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>09:31</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -723,7 +723,7 @@
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>3/26</t>
+          <t>3/27</t>
         </is>
       </c>
     </row>
@@ -788,7 +788,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>09:31</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -842,7 +842,7 @@
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>8/26</t>
+          <t>8/27</t>
         </is>
       </c>
     </row>
@@ -907,7 +907,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>09:31</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -961,7 +961,7 @@
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>1/26</t>
+          <t>1/27</t>
         </is>
       </c>
     </row>
@@ -1026,7 +1026,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>09:31</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1080,7 +1080,7 @@
       </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>10/26</t>
+          <t>10/27</t>
         </is>
       </c>
     </row>
@@ -1145,7 +1145,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>09:31</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1199,7 +1199,7 @@
       </c>
       <c r="AC6" s="2" t="inlineStr">
         <is>
-          <t>3/26</t>
+          <t>3/27</t>
         </is>
       </c>
     </row>
@@ -1264,7 +1264,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>09:31</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1318,7 +1318,7 @@
       </c>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>2/26</t>
+          <t>2/27</t>
         </is>
       </c>
     </row>
@@ -1383,7 +1383,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>09:31</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1437,7 +1437,7 @@
       </c>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>8/26</t>
+          <t>8/27</t>
         </is>
       </c>
     </row>
@@ -1556,7 +1556,7 @@
       </c>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>6/26</t>
+          <t>6/27</t>
         </is>
       </c>
     </row>
@@ -1621,7 +1621,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>09:31</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1675,7 +1675,7 @@
       </c>
       <c r="AC10" s="2" t="inlineStr">
         <is>
-          <t>11/26</t>
+          <t>11/27</t>
         </is>
       </c>
     </row>
@@ -1794,7 +1794,7 @@
       </c>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>5/26</t>
+          <t>5/27</t>
         </is>
       </c>
     </row>
@@ -1859,7 +1859,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>09:31</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1913,7 +1913,7 @@
       </c>
       <c r="AC12" s="2" t="inlineStr">
         <is>
-          <t>6/26</t>
+          <t>6/27</t>
         </is>
       </c>
     </row>
@@ -2040,7 +2040,7 @@
       <c r="AB13" s="2" t="inlineStr"/>
       <c r="AC13" s="2" t="inlineStr">
         <is>
-          <t>—/26</t>
+          <t>—/27</t>
         </is>
       </c>
     </row>
@@ -2078,24 +2078,24 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>09:35</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>137分钟</t>
+          <t>134分钟</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr"/>
       <c r="K14" s="2" t="inlineStr"/>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -2105,7 +2105,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>09:31</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2144,22 +2144,22 @@
       </c>
       <c r="Z14" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA14" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AA14" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB14" s="2" t="inlineStr">
         <is>
-          <t>137.0</t>
+          <t>134.0</t>
         </is>
       </c>
       <c r="AC14" s="2" t="inlineStr">
         <is>
-          <t>12/26</t>
+          <t>12/27</t>
         </is>
       </c>
     </row>
@@ -2270,7 +2270,7 @@
       <c r="AB15" s="2" t="inlineStr"/>
       <c r="AC15" s="2" t="inlineStr">
         <is>
-          <t>—/26</t>
+          <t>—/27</t>
         </is>
       </c>
     </row>
@@ -2298,32 +2298,36 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:46</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>136分钟</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr"/>
       <c r="K16" s="2" t="inlineStr"/>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
           <t>07:11</t>
@@ -2331,7 +2335,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>09:31</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2355,17 +2359,17 @@
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X16" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y16" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z16" s="2" t="inlineStr">
@@ -2375,13 +2379,17 @@
       </c>
       <c r="AA16" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB16" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB16" s="2" t="inlineStr">
+        <is>
+          <t>136.0</t>
+        </is>
+      </c>
       <c r="AC16" s="2" t="inlineStr">
         <is>
-          <t>—/26</t>
+          <t>13/27</t>
         </is>
       </c>
     </row>
@@ -2442,7 +2450,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>09:31</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2492,7 +2500,7 @@
       <c r="AB17" s="2" t="inlineStr"/>
       <c r="AC17" s="2" t="inlineStr">
         <is>
-          <t>—/26</t>
+          <t>—/27</t>
         </is>
       </c>
     </row>
@@ -2553,7 +2561,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>09:31</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2603,7 +2611,7 @@
       <c r="AB18" s="2" t="inlineStr"/>
       <c r="AC18" s="2" t="inlineStr">
         <is>
-          <t>—/26</t>
+          <t>—/27</t>
         </is>
       </c>
     </row>
@@ -2714,7 +2722,7 @@
       <c r="AB19" s="2" t="inlineStr"/>
       <c r="AC19" s="2" t="inlineStr">
         <is>
-          <t>—/26</t>
+          <t>—/27</t>
         </is>
       </c>
     </row>
@@ -2775,7 +2783,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>09:31</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2825,7 +2833,7 @@
       <c r="AB20" s="2" t="inlineStr"/>
       <c r="AC20" s="2" t="inlineStr">
         <is>
-          <t>—/26</t>
+          <t>—/27</t>
         </is>
       </c>
     </row>
@@ -2886,7 +2894,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>09:31</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -2936,7 +2944,7 @@
       <c r="AB21" s="2" t="inlineStr"/>
       <c r="AC21" s="2" t="inlineStr">
         <is>
-          <t>—/26</t>
+          <t>—/27</t>
         </is>
       </c>
     </row>
@@ -2997,7 +3005,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>09:31</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -3047,7 +3055,7 @@
       <c r="AB22" s="2" t="inlineStr"/>
       <c r="AC22" s="2" t="inlineStr">
         <is>
-          <t>—/26</t>
+          <t>—/27</t>
         </is>
       </c>
     </row>
@@ -3158,7 +3166,7 @@
       <c r="AB23" s="2" t="inlineStr"/>
       <c r="AC23" s="2" t="inlineStr">
         <is>
-          <t>—/26</t>
+          <t>—/27</t>
         </is>
       </c>
     </row>
@@ -3269,7 +3277,7 @@
       <c r="AB24" s="2" t="inlineStr"/>
       <c r="AC24" s="2" t="inlineStr">
         <is>
-          <t>—/26</t>
+          <t>—/27</t>
         </is>
       </c>
     </row>
@@ -3330,7 +3338,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>09:31</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3380,7 +3388,7 @@
       <c r="AB25" s="2" t="inlineStr"/>
       <c r="AC25" s="2" t="inlineStr">
         <is>
-          <t>—/26</t>
+          <t>—/27</t>
         </is>
       </c>
     </row>
@@ -3441,7 +3449,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>09:31</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3491,7 +3499,7 @@
       <c r="AB26" s="2" t="inlineStr"/>
       <c r="AC26" s="2" t="inlineStr">
         <is>
-          <t>—/26</t>
+          <t>—/27</t>
         </is>
       </c>
     </row>
@@ -3552,7 +3560,7 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>09:31</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -3606,7 +3614,7 @@
       </c>
       <c r="AC27" s="2" t="inlineStr">
         <is>
-          <t>3/26</t>
+          <t>3/27</t>
         </is>
       </c>
     </row>
@@ -3667,7 +3675,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>09:31</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -3721,7 +3729,7 @@
       </c>
       <c r="AC28" s="2" t="inlineStr">
         <is>
-          <t>8/26</t>
+          <t>8/27</t>
         </is>
       </c>
     </row>
@@ -3782,7 +3790,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>09:31</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -3832,7 +3840,7 @@
       <c r="AB29" s="2" t="inlineStr"/>
       <c r="AC29" s="2" t="inlineStr">
         <is>
-          <t>—/26</t>
+          <t>—/27</t>
         </is>
       </c>
     </row>
@@ -3893,7 +3901,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>09:31</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -3947,7 +3955,7 @@
       </c>
       <c r="AC30" s="2" t="inlineStr">
         <is>
-          <t>1/26</t>
+          <t>1/27</t>
         </is>
       </c>
     </row>
@@ -4008,7 +4016,7 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>09:31</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
@@ -4062,7 +4070,7 @@
       </c>
       <c r="AC31" s="2" t="inlineStr">
         <is>
-          <t>3/26</t>
+          <t>3/27</t>
         </is>
       </c>
     </row>
@@ -4123,7 +4131,7 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>09:31</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
@@ -4177,7 +4185,7 @@
       </c>
       <c r="AC32" s="2" t="inlineStr">
         <is>
-          <t>10/26</t>
+          <t>10/27</t>
         </is>
       </c>
     </row>
@@ -4238,7 +4246,7 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>09:31</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
@@ -4292,7 +4300,7 @@
       </c>
       <c r="AC33" s="2" t="inlineStr">
         <is>
-          <t>8/26</t>
+          <t>8/27</t>
         </is>
       </c>
     </row>
@@ -4353,7 +4361,7 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>09:31</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
@@ -4407,7 +4415,7 @@
       </c>
       <c r="AC34" s="2" t="inlineStr">
         <is>
-          <t>11/26</t>
+          <t>11/27</t>
         </is>
       </c>
     </row>
@@ -4468,7 +4476,7 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>09:31</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
@@ -4522,7 +4530,7 @@
       </c>
       <c r="AC35" s="2" t="inlineStr">
         <is>
-          <t>2/26</t>
+          <t>2/27</t>
         </is>
       </c>
     </row>
@@ -4530,22 +4538,22 @@
       <c r="A36" s="2" t="inlineStr"/>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>沪A72873D</t>
+          <t>沪A79307D</t>
         </is>
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D36" s="2" t="inlineStr">
+        <is>
+          <t>09:38</t>
+        </is>
+      </c>
+      <c r="E36" s="2" t="inlineStr">
+        <is>
           <t>东高路张杨北路</t>
-        </is>
-      </c>
-      <c r="D36" s="2" t="inlineStr">
-        <is>
-          <t>09:45</t>
-        </is>
-      </c>
-      <c r="E36" s="2" t="inlineStr">
-        <is>
-          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
@@ -4578,12 +4586,12 @@
       <c r="M36" s="2" t="inlineStr"/>
       <c r="N36" s="2" t="inlineStr">
         <is>
-          <t>06:32</t>
+          <t>09:31</t>
         </is>
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>09:31</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
@@ -4597,47 +4605,273 @@
       <c r="T36" s="2" t="inlineStr"/>
       <c r="U36" s="2" t="inlineStr">
         <is>
+          <t>09:38</t>
+        </is>
+      </c>
+      <c r="V36" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W36" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X36" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y36" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z36" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA36" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB36" s="2" t="inlineStr"/>
+      <c r="AC36" s="2" t="inlineStr">
+        <is>
+          <t>—/27</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="2" t="inlineStr"/>
+      <c r="B37" s="2" t="inlineStr">
+        <is>
+          <t>沪A72873D</t>
+        </is>
+      </c>
+      <c r="C37" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D37" s="2" t="inlineStr">
+        <is>
           <t>09:45</t>
         </is>
       </c>
-      <c r="V36" s="2" t="inlineStr">
+      <c r="E37" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F37" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G37" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H37" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I37" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J37" s="2" t="inlineStr"/>
+      <c r="K37" s="2" t="inlineStr"/>
+      <c r="L37" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M37" s="2" t="inlineStr"/>
+      <c r="N37" s="2" t="inlineStr">
+        <is>
+          <t>06:32</t>
+        </is>
+      </c>
+      <c r="O37" s="2" t="inlineStr">
+        <is>
+          <t>09:31</t>
+        </is>
+      </c>
+      <c r="P37" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q37" s="2" t="inlineStr"/>
+      <c r="R37" s="2" t="inlineStr"/>
+      <c r="S37" s="2" t="inlineStr"/>
+      <c r="T37" s="2" t="inlineStr"/>
+      <c r="U37" s="2" t="inlineStr">
+        <is>
+          <t>09:45</t>
+        </is>
+      </c>
+      <c r="V37" s="2" t="inlineStr">
         <is>
           <t>计划发车</t>
         </is>
       </c>
-      <c r="W36" s="2" t="inlineStr">
+      <c r="W37" s="2" t="inlineStr">
         <is>
           <t>D</t>
         </is>
       </c>
-      <c r="X36" s="2" t="inlineStr">
-        <is>
-          <t>待确认</t>
-        </is>
-      </c>
-      <c r="Y36" s="2" t="inlineStr">
+      <c r="X37" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y37" s="2" t="inlineStr">
         <is>
           <t>否</t>
         </is>
       </c>
-      <c r="Z36" s="2" t="inlineStr">
+      <c r="Z37" s="2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA36" s="2" t="inlineStr">
+      <c r="AA37" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB36" s="2" t="inlineStr">
+      <c r="AB37" s="2" t="inlineStr">
         <is>
           <t>130.0</t>
         </is>
       </c>
-      <c r="AC36" s="2" t="inlineStr">
-        <is>
-          <t>6/26</t>
+      <c r="AC37" s="2" t="inlineStr">
+        <is>
+          <t>6/27</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="2" t="inlineStr"/>
+      <c r="B38" s="2" t="inlineStr">
+        <is>
+          <t>沪A62880D</t>
+        </is>
+      </c>
+      <c r="C38" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D38" s="2" t="inlineStr">
+        <is>
+          <t>10:00</t>
+        </is>
+      </c>
+      <c r="E38" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F38" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G38" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H38" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I38" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J38" s="2" t="inlineStr"/>
+      <c r="K38" s="2" t="inlineStr"/>
+      <c r="L38" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M38" s="2" t="inlineStr"/>
+      <c r="N38" s="2" t="inlineStr">
+        <is>
+          <t>07:01</t>
+        </is>
+      </c>
+      <c r="O38" s="2" t="inlineStr">
+        <is>
+          <t>09:31</t>
+        </is>
+      </c>
+      <c r="P38" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q38" s="2" t="inlineStr"/>
+      <c r="R38" s="2" t="inlineStr"/>
+      <c r="S38" s="2" t="inlineStr"/>
+      <c r="T38" s="2" t="inlineStr"/>
+      <c r="U38" s="2" t="inlineStr">
+        <is>
+          <t>10:00</t>
+        </is>
+      </c>
+      <c r="V38" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W38" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X38" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y38" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z38" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA38" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB38" s="2" t="inlineStr">
+        <is>
+          <t>134.0</t>
+        </is>
+      </c>
+      <c r="AC38" s="2" t="inlineStr">
+        <is>
+          <t>12/27</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-10-31-浦东35路.xlsx
+++ b/data/export/2026-10-31-浦东35路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC38"/>
+  <dimension ref="A1:AC47"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -669,7 +669,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>09:31</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -788,7 +788,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>09:31</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -907,7 +907,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>09:31</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -1026,7 +1026,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>09:31</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1080,7 +1080,7 @@
       </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>10/27</t>
+          <t>11/27</t>
         </is>
       </c>
     </row>
@@ -1145,7 +1145,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>09:31</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>09:31</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1383,7 +1383,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>09:31</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1502,7 +1502,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>09:01</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1541,7 +1541,7 @@
       </c>
       <c r="Z9" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AA9" s="2" t="inlineStr">
@@ -1621,7 +1621,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>09:31</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1675,7 +1675,7 @@
       </c>
       <c r="AC10" s="2" t="inlineStr">
         <is>
-          <t>11/27</t>
+          <t>13/27</t>
         </is>
       </c>
     </row>
@@ -1740,7 +1740,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>09:11</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1779,7 +1779,7 @@
       </c>
       <c r="Z11" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AA11" s="2" t="inlineStr">
@@ -1859,7 +1859,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>09:31</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -2105,7 +2105,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>09:31</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2159,7 +2159,7 @@
       </c>
       <c r="AC14" s="2" t="inlineStr">
         <is>
-          <t>12/27</t>
+          <t>14/27</t>
         </is>
       </c>
     </row>
@@ -2220,7 +2220,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2259,7 +2259,7 @@
       </c>
       <c r="Z15" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AA15" s="2" t="inlineStr">
@@ -2308,24 +2308,24 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>09:46</t>
+          <t>09:45</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>136分钟</t>
+          <t>135分钟</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr"/>
       <c r="K16" s="2" t="inlineStr"/>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2335,7 +2335,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>09:31</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2374,22 +2374,22 @@
       </c>
       <c r="Z16" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA16" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AA16" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB16" s="2" t="inlineStr">
         <is>
-          <t>136.0</t>
+          <t>135.0</t>
         </is>
       </c>
       <c r="AC16" s="2" t="inlineStr">
         <is>
-          <t>13/27</t>
+          <t>15/27</t>
         </is>
       </c>
     </row>
@@ -2417,32 +2417,36 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:45</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>135分钟</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr"/>
       <c r="K17" s="2" t="inlineStr"/>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
           <t>07:01</t>
@@ -2450,7 +2454,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>09:31</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2474,33 +2478,37 @@
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X17" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y17" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z17" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA17" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AA17" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB17" s="2" t="inlineStr"/>
+      <c r="AB17" s="2" t="inlineStr">
+        <is>
+          <t>135.0</t>
+        </is>
+      </c>
       <c r="AC17" s="2" t="inlineStr">
         <is>
-          <t>—/27</t>
+          <t>15/27</t>
         </is>
       </c>
     </row>
@@ -2528,32 +2536,36 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:57</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>135分钟</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr"/>
       <c r="K18" s="2" t="inlineStr"/>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M18" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
           <t>06:51</t>
@@ -2561,7 +2573,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>09:31</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2585,33 +2597,37 @@
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X18" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y18" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z18" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA18" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AA18" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB18" s="2" t="inlineStr"/>
+      <c r="AB18" s="2" t="inlineStr">
+        <is>
+          <t>135.0</t>
+        </is>
+      </c>
       <c r="AC18" s="2" t="inlineStr">
         <is>
-          <t>—/27</t>
+          <t>15/27</t>
         </is>
       </c>
     </row>
@@ -2672,7 +2688,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>07:31</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2711,7 +2727,7 @@
       </c>
       <c r="Z19" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AA19" s="2" t="inlineStr">
@@ -2750,32 +2766,36 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>10:11</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>137分钟</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr"/>
       <c r="K20" s="2" t="inlineStr"/>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M20" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M20" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
           <t>07:21</t>
@@ -2783,7 +2803,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>09:31</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2807,33 +2827,37 @@
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X20" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y20" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z20" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA20" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AA20" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB20" s="2" t="inlineStr"/>
+      <c r="AB20" s="2" t="inlineStr">
+        <is>
+          <t>137.0</t>
+        </is>
+      </c>
       <c r="AC20" s="2" t="inlineStr">
         <is>
-          <t>—/27</t>
+          <t>18/27</t>
         </is>
       </c>
     </row>
@@ -2861,32 +2885,36 @@
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>10:05</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>131分钟</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr"/>
       <c r="K21" s="2" t="inlineStr"/>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M21" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M21" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
           <t>07:21</t>
@@ -2894,7 +2922,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>09:31</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -2918,33 +2946,37 @@
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X21" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y21" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z21" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA21" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AA21" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB21" s="2" t="inlineStr"/>
+      <c r="AB21" s="2" t="inlineStr">
+        <is>
+          <t>131.0</t>
+        </is>
+      </c>
       <c r="AC21" s="2" t="inlineStr">
         <is>
-          <t>—/27</t>
+          <t>8/27</t>
         </is>
       </c>
     </row>
@@ -3005,7 +3037,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>09:31</t>
+          <t>09:41</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -3194,32 +3226,36 @@
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>10:35</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>137分钟</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr"/>
       <c r="K24" s="2" t="inlineStr"/>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M24" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M24" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -3227,7 +3263,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -3251,17 +3287,17 @@
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X24" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y24" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z24" s="2" t="inlineStr">
@@ -3271,13 +3307,17 @@
       </c>
       <c r="AA24" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB24" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB24" s="2" t="inlineStr">
+        <is>
+          <t>137.0</t>
+        </is>
+      </c>
       <c r="AC24" s="2" t="inlineStr">
         <is>
-          <t>—/27</t>
+          <t>18/27</t>
         </is>
       </c>
     </row>
@@ -3305,32 +3345,36 @@
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>132分钟</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr"/>
       <c r="K25" s="2" t="inlineStr"/>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M25" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M25" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
           <t>06:51</t>
@@ -3338,7 +3382,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>09:31</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3362,17 +3406,17 @@
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X25" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y25" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z25" s="2" t="inlineStr">
@@ -3382,13 +3426,17 @@
       </c>
       <c r="AA25" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB25" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB25" s="2" t="inlineStr">
+        <is>
+          <t>132.0</t>
+        </is>
+      </c>
       <c r="AC25" s="2" t="inlineStr">
         <is>
-          <t>—/27</t>
+          <t>11/27</t>
         </is>
       </c>
     </row>
@@ -3416,32 +3464,36 @@
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>10:50</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>140分钟</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr"/>
       <c r="K26" s="2" t="inlineStr"/>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M26" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±4分钟</t>
+        </is>
+      </c>
+      <c r="M26" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -3449,7 +3501,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>09:31</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3473,17 +3525,17 @@
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X26" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y26" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z26" s="2" t="inlineStr">
@@ -3493,13 +3545,17 @@
       </c>
       <c r="AA26" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB26" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB26" s="2" t="inlineStr">
+        <is>
+          <t>140.0</t>
+        </is>
+      </c>
       <c r="AC26" s="2" t="inlineStr">
         <is>
-          <t>—/27</t>
+          <t>20/27</t>
         </is>
       </c>
     </row>
@@ -3560,7 +3616,7 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>09:31</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -3675,7 +3731,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>09:31</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -3790,7 +3846,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>09:31</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -3901,7 +3957,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>09:31</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -4016,7 +4072,7 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>09:31</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
@@ -4131,7 +4187,7 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>09:31</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
@@ -4185,7 +4241,7 @@
       </c>
       <c r="AC32" s="2" t="inlineStr">
         <is>
-          <t>10/27</t>
+          <t>11/27</t>
         </is>
       </c>
     </row>
@@ -4246,7 +4302,7 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>09:31</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
@@ -4361,7 +4417,7 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>09:31</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
@@ -4415,7 +4471,7 @@
       </c>
       <c r="AC34" s="2" t="inlineStr">
         <is>
-          <t>11/27</t>
+          <t>13/27</t>
         </is>
       </c>
     </row>
@@ -4476,7 +4532,7 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>09:31</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
@@ -4591,7 +4647,7 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>09:31</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
@@ -4649,22 +4705,22 @@
       <c r="A37" s="2" t="inlineStr"/>
       <c r="B37" s="2" t="inlineStr">
         <is>
-          <t>沪A72873D</t>
+          <t>沪A62217D</t>
         </is>
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D37" s="2" t="inlineStr">
+        <is>
+          <t>09:45</t>
+        </is>
+      </c>
+      <c r="E37" s="2" t="inlineStr">
+        <is>
           <t>东高路张杨北路</t>
-        </is>
-      </c>
-      <c r="D37" s="2" t="inlineStr">
-        <is>
-          <t>09:45</t>
-        </is>
-      </c>
-      <c r="E37" s="2" t="inlineStr">
-        <is>
-          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
@@ -4697,12 +4753,12 @@
       <c r="M37" s="2" t="inlineStr"/>
       <c r="N37" s="2" t="inlineStr">
         <is>
-          <t>06:32</t>
+          <t>06:21</t>
         </is>
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>09:31</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
@@ -4764,7 +4820,7 @@
       <c r="A38" s="2" t="inlineStr"/>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>沪A62880D</t>
+          <t>沪A72873D</t>
         </is>
       </c>
       <c r="C38" s="2" t="inlineStr">
@@ -4774,7 +4830,7 @@
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>09:45</t>
         </is>
       </c>
       <c r="E38" s="2" t="inlineStr">
@@ -4812,12 +4868,12 @@
       <c r="M38" s="2" t="inlineStr"/>
       <c r="N38" s="2" t="inlineStr">
         <is>
-          <t>07:01</t>
+          <t>06:32</t>
         </is>
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>09:31</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
@@ -4831,47 +4887,1074 @@
       <c r="T38" s="2" t="inlineStr"/>
       <c r="U38" s="2" t="inlineStr">
         <is>
+          <t>09:45</t>
+        </is>
+      </c>
+      <c r="V38" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W38" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X38" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y38" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z38" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA38" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB38" s="2" t="inlineStr">
+        <is>
+          <t>130.0</t>
+        </is>
+      </c>
+      <c r="AC38" s="2" t="inlineStr">
+        <is>
+          <t>6/27</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="2" t="inlineStr"/>
+      <c r="B39" s="2" t="inlineStr">
+        <is>
+          <t>沪A62880D</t>
+        </is>
+      </c>
+      <c r="C39" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D39" s="2" t="inlineStr">
+        <is>
           <t>10:00</t>
         </is>
       </c>
-      <c r="V38" s="2" t="inlineStr">
+      <c r="E39" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F39" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G39" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H39" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I39" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J39" s="2" t="inlineStr"/>
+      <c r="K39" s="2" t="inlineStr"/>
+      <c r="L39" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M39" s="2" t="inlineStr"/>
+      <c r="N39" s="2" t="inlineStr">
+        <is>
+          <t>07:01</t>
+        </is>
+      </c>
+      <c r="O39" s="2" t="inlineStr">
+        <is>
+          <t>10:21</t>
+        </is>
+      </c>
+      <c r="P39" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q39" s="2" t="inlineStr"/>
+      <c r="R39" s="2" t="inlineStr"/>
+      <c r="S39" s="2" t="inlineStr"/>
+      <c r="T39" s="2" t="inlineStr"/>
+      <c r="U39" s="2" t="inlineStr">
+        <is>
+          <t>10:00</t>
+        </is>
+      </c>
+      <c r="V39" s="2" t="inlineStr">
         <is>
           <t>计划发车</t>
         </is>
       </c>
-      <c r="W38" s="2" t="inlineStr">
+      <c r="W39" s="2" t="inlineStr">
         <is>
           <t>D</t>
         </is>
       </c>
-      <c r="X38" s="2" t="inlineStr">
-        <is>
-          <t>待确认</t>
-        </is>
-      </c>
-      <c r="Y38" s="2" t="inlineStr">
+      <c r="X39" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y39" s="2" t="inlineStr">
         <is>
           <t>否</t>
         </is>
       </c>
-      <c r="Z38" s="2" t="inlineStr">
+      <c r="Z39" s="2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA38" s="2" t="inlineStr">
+      <c r="AA39" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB38" s="2" t="inlineStr">
+      <c r="AB39" s="2" t="inlineStr">
         <is>
           <t>134.0</t>
         </is>
       </c>
-      <c r="AC38" s="2" t="inlineStr">
-        <is>
-          <t>12/27</t>
+      <c r="AC39" s="2" t="inlineStr">
+        <is>
+          <t>14/27</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="2" t="inlineStr"/>
+      <c r="B40" s="2" t="inlineStr">
+        <is>
+          <t>沪A68261D</t>
+        </is>
+      </c>
+      <c r="C40" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D40" s="2" t="inlineStr">
+        <is>
+          <t>10:00</t>
+        </is>
+      </c>
+      <c r="E40" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F40" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G40" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H40" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I40" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J40" s="2" t="inlineStr"/>
+      <c r="K40" s="2" t="inlineStr"/>
+      <c r="L40" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M40" s="2" t="inlineStr"/>
+      <c r="N40" s="2" t="inlineStr">
+        <is>
+          <t>06:41</t>
+        </is>
+      </c>
+      <c r="O40" s="2" t="inlineStr">
+        <is>
+          <t>10:21</t>
+        </is>
+      </c>
+      <c r="P40" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q40" s="2" t="inlineStr"/>
+      <c r="R40" s="2" t="inlineStr"/>
+      <c r="S40" s="2" t="inlineStr"/>
+      <c r="T40" s="2" t="inlineStr"/>
+      <c r="U40" s="2" t="inlineStr">
+        <is>
+          <t>10:00</t>
+        </is>
+      </c>
+      <c r="V40" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W40" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X40" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y40" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z40" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA40" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB40" s="2" t="inlineStr">
+        <is>
+          <t>129.0</t>
+        </is>
+      </c>
+      <c r="AC40" s="2" t="inlineStr">
+        <is>
+          <t>5/27</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="2" t="inlineStr"/>
+      <c r="B41" s="2" t="inlineStr">
+        <is>
+          <t>沪A68895D</t>
+        </is>
+      </c>
+      <c r="C41" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D41" s="2" t="inlineStr">
+        <is>
+          <t>10:15</t>
+        </is>
+      </c>
+      <c r="E41" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F41" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G41" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H41" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I41" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J41" s="2" t="inlineStr"/>
+      <c r="K41" s="2" t="inlineStr"/>
+      <c r="L41" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M41" s="2" t="inlineStr"/>
+      <c r="N41" s="2" t="inlineStr">
+        <is>
+          <t>06:51</t>
+        </is>
+      </c>
+      <c r="O41" s="2" t="inlineStr">
+        <is>
+          <t>10:21</t>
+        </is>
+      </c>
+      <c r="P41" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q41" s="2" t="inlineStr"/>
+      <c r="R41" s="2" t="inlineStr"/>
+      <c r="S41" s="2" t="inlineStr"/>
+      <c r="T41" s="2" t="inlineStr"/>
+      <c r="U41" s="2" t="inlineStr">
+        <is>
+          <t>10:15</t>
+        </is>
+      </c>
+      <c r="V41" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W41" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X41" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y41" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z41" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA41" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB41" s="2" t="inlineStr"/>
+      <c r="AC41" s="2" t="inlineStr">
+        <is>
+          <t>—/27</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="2" t="inlineStr"/>
+      <c r="B42" s="2" t="inlineStr">
+        <is>
+          <t>沪A02891D</t>
+        </is>
+      </c>
+      <c r="C42" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D42" s="2" t="inlineStr">
+        <is>
+          <t>10:20</t>
+        </is>
+      </c>
+      <c r="E42" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F42" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G42" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H42" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I42" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J42" s="2" t="inlineStr"/>
+      <c r="K42" s="2" t="inlineStr"/>
+      <c r="L42" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M42" s="2" t="inlineStr"/>
+      <c r="N42" s="2" t="inlineStr">
+        <is>
+          <t>07:11</t>
+        </is>
+      </c>
+      <c r="O42" s="2" t="inlineStr">
+        <is>
+          <t>10:21</t>
+        </is>
+      </c>
+      <c r="P42" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q42" s="2" t="inlineStr"/>
+      <c r="R42" s="2" t="inlineStr"/>
+      <c r="S42" s="2" t="inlineStr"/>
+      <c r="T42" s="2" t="inlineStr"/>
+      <c r="U42" s="2" t="inlineStr">
+        <is>
+          <t>10:20</t>
+        </is>
+      </c>
+      <c r="V42" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W42" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X42" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y42" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z42" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA42" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB42" s="2" t="inlineStr">
+        <is>
+          <t>135.0</t>
+        </is>
+      </c>
+      <c r="AC42" s="2" t="inlineStr">
+        <is>
+          <t>15/27</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="2" t="inlineStr"/>
+      <c r="B43" s="2" t="inlineStr">
+        <is>
+          <t>沪A55575A</t>
+        </is>
+      </c>
+      <c r="C43" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D43" s="2" t="inlineStr">
+        <is>
+          <t>10:30</t>
+        </is>
+      </c>
+      <c r="E43" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F43" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G43" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H43" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I43" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J43" s="2" t="inlineStr"/>
+      <c r="K43" s="2" t="inlineStr"/>
+      <c r="L43" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M43" s="2" t="inlineStr"/>
+      <c r="N43" s="2" t="inlineStr">
+        <is>
+          <t>07:01</t>
+        </is>
+      </c>
+      <c r="O43" s="2" t="inlineStr">
+        <is>
+          <t>10:21</t>
+        </is>
+      </c>
+      <c r="P43" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q43" s="2" t="inlineStr"/>
+      <c r="R43" s="2" t="inlineStr"/>
+      <c r="S43" s="2" t="inlineStr"/>
+      <c r="T43" s="2" t="inlineStr"/>
+      <c r="U43" s="2" t="inlineStr">
+        <is>
+          <t>10:30</t>
+        </is>
+      </c>
+      <c r="V43" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W43" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X43" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y43" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z43" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA43" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB43" s="2" t="inlineStr">
+        <is>
+          <t>135.0</t>
+        </is>
+      </c>
+      <c r="AC43" s="2" t="inlineStr">
+        <is>
+          <t>15/27</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="2" t="inlineStr"/>
+      <c r="B44" s="2" t="inlineStr">
+        <is>
+          <t>沪A65668D</t>
+        </is>
+      </c>
+      <c r="C44" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D44" s="2" t="inlineStr">
+        <is>
+          <t>10:40</t>
+        </is>
+      </c>
+      <c r="E44" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F44" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G44" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H44" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I44" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J44" s="2" t="inlineStr"/>
+      <c r="K44" s="2" t="inlineStr"/>
+      <c r="L44" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M44" s="2" t="inlineStr"/>
+      <c r="N44" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="O44" s="2" t="inlineStr">
+        <is>
+          <t>10:21</t>
+        </is>
+      </c>
+      <c r="P44" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q44" s="2" t="inlineStr"/>
+      <c r="R44" s="2" t="inlineStr"/>
+      <c r="S44" s="2" t="inlineStr"/>
+      <c r="T44" s="2" t="inlineStr"/>
+      <c r="U44" s="2" t="inlineStr">
+        <is>
+          <t>10:40</t>
+        </is>
+      </c>
+      <c r="V44" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W44" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X44" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y44" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z44" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA44" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB44" s="2" t="inlineStr"/>
+      <c r="AC44" s="2" t="inlineStr">
+        <is>
+          <t>—/27</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="2" t="inlineStr"/>
+      <c r="B45" s="2" t="inlineStr">
+        <is>
+          <t>沪A59793A</t>
+        </is>
+      </c>
+      <c r="C45" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D45" s="2" t="inlineStr">
+        <is>
+          <t>10:45</t>
+        </is>
+      </c>
+      <c r="E45" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F45" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G45" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H45" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I45" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J45" s="2" t="inlineStr"/>
+      <c r="K45" s="2" t="inlineStr"/>
+      <c r="L45" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M45" s="2" t="inlineStr"/>
+      <c r="N45" s="2" t="inlineStr">
+        <is>
+          <t>06:51</t>
+        </is>
+      </c>
+      <c r="O45" s="2" t="inlineStr">
+        <is>
+          <t>10:21</t>
+        </is>
+      </c>
+      <c r="P45" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q45" s="2" t="inlineStr"/>
+      <c r="R45" s="2" t="inlineStr"/>
+      <c r="S45" s="2" t="inlineStr"/>
+      <c r="T45" s="2" t="inlineStr"/>
+      <c r="U45" s="2" t="inlineStr">
+        <is>
+          <t>10:45</t>
+        </is>
+      </c>
+      <c r="V45" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W45" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X45" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y45" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z45" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA45" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB45" s="2" t="inlineStr">
+        <is>
+          <t>135.0</t>
+        </is>
+      </c>
+      <c r="AC45" s="2" t="inlineStr">
+        <is>
+          <t>15/27</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="2" t="inlineStr"/>
+      <c r="B46" s="2" t="inlineStr">
+        <is>
+          <t>沪A90275D</t>
+        </is>
+      </c>
+      <c r="C46" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D46" s="2" t="inlineStr">
+        <is>
+          <t>10:58</t>
+        </is>
+      </c>
+      <c r="E46" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F46" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G46" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H46" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I46" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J46" s="2" t="inlineStr"/>
+      <c r="K46" s="2" t="inlineStr"/>
+      <c r="L46" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M46" s="2" t="inlineStr"/>
+      <c r="N46" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="O46" s="2" t="inlineStr">
+        <is>
+          <t>10:21</t>
+        </is>
+      </c>
+      <c r="P46" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q46" s="2" t="inlineStr"/>
+      <c r="R46" s="2" t="inlineStr"/>
+      <c r="S46" s="2" t="inlineStr"/>
+      <c r="T46" s="2" t="inlineStr"/>
+      <c r="U46" s="2" t="inlineStr">
+        <is>
+          <t>10:58</t>
+        </is>
+      </c>
+      <c r="V46" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W46" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X46" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y46" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z46" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA46" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB46" s="2" t="inlineStr">
+        <is>
+          <t>131.0</t>
+        </is>
+      </c>
+      <c r="AC46" s="2" t="inlineStr">
+        <is>
+          <t>8/27</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="2" t="inlineStr"/>
+      <c r="B47" s="2" t="inlineStr">
+        <is>
+          <t>沪A57383A</t>
+        </is>
+      </c>
+      <c r="C47" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D47" s="2" t="inlineStr">
+        <is>
+          <t>11:05</t>
+        </is>
+      </c>
+      <c r="E47" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F47" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G47" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H47" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I47" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J47" s="2" t="inlineStr"/>
+      <c r="K47" s="2" t="inlineStr"/>
+      <c r="L47" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M47" s="2" t="inlineStr"/>
+      <c r="N47" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="O47" s="2" t="inlineStr">
+        <is>
+          <t>10:21</t>
+        </is>
+      </c>
+      <c r="P47" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q47" s="2" t="inlineStr"/>
+      <c r="R47" s="2" t="inlineStr"/>
+      <c r="S47" s="2" t="inlineStr"/>
+      <c r="T47" s="2" t="inlineStr"/>
+      <c r="U47" s="2" t="inlineStr">
+        <is>
+          <t>11:05</t>
+        </is>
+      </c>
+      <c r="V47" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W47" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X47" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y47" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z47" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA47" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB47" s="2" t="inlineStr">
+        <is>
+          <t>137.0</t>
+        </is>
+      </c>
+      <c r="AC47" s="2" t="inlineStr">
+        <is>
+          <t>18/27</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-10-31-浦东35路.xlsx
+++ b/data/export/2026-10-31-浦东35路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC47"/>
+  <dimension ref="A1:AC54"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -669,7 +669,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -708,14 +708,14 @@
       </c>
       <c r="Z2" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA2" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA2" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB2" s="2" t="inlineStr">
         <is>
           <t>128.0</t>
@@ -723,7 +723,7 @@
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>3/27</t>
+          <t>2/27</t>
         </is>
       </c>
     </row>
@@ -788,7 +788,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>10:51</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -832,17 +832,17 @@
       </c>
       <c r="AA3" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB3" s="2" t="inlineStr">
         <is>
-          <t>131.0</t>
+          <t>136.0</t>
         </is>
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>8/27</t>
+          <t>16/27</t>
         </is>
       </c>
     </row>
@@ -907,7 +907,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -951,17 +951,17 @@
       </c>
       <c r="AA4" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB4" s="2" t="inlineStr">
         <is>
-          <t>125.0</t>
+          <t>128.5</t>
         </is>
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>1/27</t>
+          <t>3/27</t>
         </is>
       </c>
     </row>
@@ -1026,7 +1026,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1065,22 +1065,22 @@
       </c>
       <c r="Z5" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA5" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA5" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB5" s="2" t="inlineStr">
         <is>
-          <t>132.0</t>
+          <t>140.0</t>
         </is>
       </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>11/27</t>
+          <t>20/27</t>
         </is>
       </c>
     </row>
@@ -1145,7 +1145,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1184,22 +1184,22 @@
       </c>
       <c r="Z6" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA6" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA6" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB6" s="2" t="inlineStr">
         <is>
-          <t>128.0</t>
+          <t>131.5</t>
         </is>
       </c>
       <c r="AC6" s="2" t="inlineStr">
         <is>
-          <t>3/27</t>
+          <t>8/27</t>
         </is>
       </c>
     </row>
@@ -1264,7 +1264,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1318,7 +1318,7 @@
       </c>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>2/27</t>
+          <t>1/27</t>
         </is>
       </c>
     </row>
@@ -1383,7 +1383,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1427,17 +1427,17 @@
       </c>
       <c r="AA8" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB8" s="2" t="inlineStr">
         <is>
-          <t>131.0</t>
+          <t>136.5</t>
         </is>
       </c>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>8/27</t>
+          <t>18/27</t>
         </is>
       </c>
     </row>
@@ -1502,7 +1502,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1556,7 +1556,7 @@
       </c>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>6/27</t>
+          <t>5/27</t>
         </is>
       </c>
     </row>
@@ -1621,7 +1621,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1675,7 +1675,7 @@
       </c>
       <c r="AC10" s="2" t="inlineStr">
         <is>
-          <t>13/27</t>
+          <t>10/27</t>
         </is>
       </c>
     </row>
@@ -1740,7 +1740,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1794,7 +1794,7 @@
       </c>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>5/27</t>
+          <t>4/27</t>
         </is>
       </c>
     </row>
@@ -1859,7 +1859,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1913,7 +1913,7 @@
       </c>
       <c r="AC12" s="2" t="inlineStr">
         <is>
-          <t>6/27</t>
+          <t>5/27</t>
         </is>
       </c>
     </row>
@@ -2105,7 +2105,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2159,7 +2159,7 @@
       </c>
       <c r="AC14" s="2" t="inlineStr">
         <is>
-          <t>14/27</t>
+          <t>11/27</t>
         </is>
       </c>
     </row>
@@ -2220,7 +2220,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2335,7 +2335,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2389,7 +2389,7 @@
       </c>
       <c r="AC16" s="2" t="inlineStr">
         <is>
-          <t>15/27</t>
+          <t>13/27</t>
         </is>
       </c>
     </row>
@@ -2454,7 +2454,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2508,7 +2508,7 @@
       </c>
       <c r="AC17" s="2" t="inlineStr">
         <is>
-          <t>15/27</t>
+          <t>13/27</t>
         </is>
       </c>
     </row>
@@ -2573,7 +2573,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2627,7 +2627,7 @@
       </c>
       <c r="AC18" s="2" t="inlineStr">
         <is>
-          <t>15/27</t>
+          <t>13/27</t>
         </is>
       </c>
     </row>
@@ -2688,7 +2688,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>10:31</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2803,7 +2803,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2857,7 +2857,7 @@
       </c>
       <c r="AC20" s="2" t="inlineStr">
         <is>
-          <t>18/27</t>
+          <t>19/27</t>
         </is>
       </c>
     </row>
@@ -2922,7 +2922,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -2976,7 +2976,7 @@
       </c>
       <c r="AC21" s="2" t="inlineStr">
         <is>
-          <t>8/27</t>
+          <t>7/27</t>
         </is>
       </c>
     </row>
@@ -3037,7 +3037,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>09:41</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -3076,7 +3076,7 @@
       </c>
       <c r="Z22" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AA22" s="2" t="inlineStr">
@@ -3236,24 +3236,24 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>10:35</t>
+          <t>10:34</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>137分钟</t>
+          <t>136分钟</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr"/>
       <c r="K24" s="2" t="inlineStr"/>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3263,7 +3263,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>10:31</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -3312,12 +3312,12 @@
       </c>
       <c r="AB24" s="2" t="inlineStr">
         <is>
-          <t>137.0</t>
+          <t>136.0</t>
         </is>
       </c>
       <c r="AC24" s="2" t="inlineStr">
         <is>
-          <t>18/27</t>
+          <t>16/27</t>
         </is>
       </c>
     </row>
@@ -3382,7 +3382,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3421,14 +3421,14 @@
       </c>
       <c r="Z25" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA25" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AA25" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB25" s="2" t="inlineStr">
         <is>
           <t>132.0</t>
@@ -3436,7 +3436,7 @@
       </c>
       <c r="AC25" s="2" t="inlineStr">
         <is>
-          <t>11/27</t>
+          <t>9/27</t>
         </is>
       </c>
     </row>
@@ -3501,7 +3501,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3540,7 +3540,7 @@
       </c>
       <c r="Z26" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AA26" s="2" t="inlineStr">
@@ -3583,32 +3583,36 @@
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>10:46</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>128分钟</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr"/>
       <c r="K27" s="2" t="inlineStr"/>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M27" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M27" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -3616,7 +3620,7 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -3640,29 +3644,29 @@
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X27" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y27" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z27" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA27" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA27" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB27" s="2" t="inlineStr">
         <is>
           <t>128.0</t>
@@ -3670,7 +3674,7 @@
       </c>
       <c r="AC27" s="2" t="inlineStr">
         <is>
-          <t>3/27</t>
+          <t>2/27</t>
         </is>
       </c>
     </row>
@@ -3698,32 +3702,36 @@
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>11:06</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>141分钟</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr"/>
       <c r="K28" s="2" t="inlineStr"/>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M28" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M28" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N28" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -3731,7 +3739,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>10:51</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -3755,17 +3763,17 @@
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X28" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y28" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z28" s="2" t="inlineStr">
@@ -3775,17 +3783,17 @@
       </c>
       <c r="AA28" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB28" s="2" t="inlineStr">
         <is>
-          <t>131.0</t>
+          <t>136.0</t>
         </is>
       </c>
       <c r="AC28" s="2" t="inlineStr">
         <is>
-          <t>8/27</t>
+          <t>16/27</t>
         </is>
       </c>
     </row>
@@ -3813,32 +3821,36 @@
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>11:02</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>134分钟</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr"/>
       <c r="K29" s="2" t="inlineStr"/>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M29" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="M29" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
           <t>07:01</t>
@@ -3846,7 +3858,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -3870,33 +3882,37 @@
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X29" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y29" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z29" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA29" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AA29" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB29" s="2" t="inlineStr"/>
+      <c r="AB29" s="2" t="inlineStr">
+        <is>
+          <t>134.0</t>
+        </is>
+      </c>
       <c r="AC29" s="2" t="inlineStr">
         <is>
-          <t>—/27</t>
+          <t>11/27</t>
         </is>
       </c>
     </row>
@@ -3924,32 +3940,36 @@
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>11:12</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>132分钟</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr"/>
       <c r="K30" s="2" t="inlineStr"/>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M30" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="M30" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -3957,7 +3977,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -3981,17 +4001,17 @@
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X30" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y30" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z30" s="2" t="inlineStr">
@@ -4001,17 +4021,17 @@
       </c>
       <c r="AA30" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB30" s="2" t="inlineStr">
         <is>
-          <t>125.0</t>
+          <t>128.5</t>
         </is>
       </c>
       <c r="AC30" s="2" t="inlineStr">
         <is>
-          <t>1/27</t>
+          <t>3/27</t>
         </is>
       </c>
     </row>
@@ -4039,32 +4059,36 @@
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>11:15</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>135分钟</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr"/>
       <c r="K31" s="2" t="inlineStr"/>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M31" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M31" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N31" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -4072,7 +4096,7 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
@@ -4096,37 +4120,37 @@
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X31" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y31" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z31" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA31" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA31" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB31" s="2" t="inlineStr">
         <is>
-          <t>128.0</t>
+          <t>131.5</t>
         </is>
       </c>
       <c r="AC31" s="2" t="inlineStr">
         <is>
-          <t>3/27</t>
+          <t>8/27</t>
         </is>
       </c>
     </row>
@@ -4154,32 +4178,36 @@
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>11:43</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>148分钟</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr"/>
       <c r="K32" s="2" t="inlineStr"/>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M32" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M32" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N32" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -4187,7 +4215,7 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
@@ -4211,37 +4239,37 @@
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X32" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y32" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z32" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA32" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA32" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB32" s="2" t="inlineStr">
         <is>
-          <t>132.0</t>
+          <t>140.0</t>
         </is>
       </c>
       <c r="AC32" s="2" t="inlineStr">
         <is>
-          <t>11/27</t>
+          <t>20/27</t>
         </is>
       </c>
     </row>
@@ -4269,32 +4297,36 @@
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>11:37</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>142分钟</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr"/>
       <c r="K33" s="2" t="inlineStr"/>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M33" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M33" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N33" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -4302,7 +4334,7 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
@@ -4326,17 +4358,17 @@
       </c>
       <c r="W33" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X33" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y33" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z33" s="2" t="inlineStr">
@@ -4346,17 +4378,17 @@
       </c>
       <c r="AA33" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB33" s="2" t="inlineStr">
         <is>
-          <t>131.0</t>
+          <t>136.5</t>
         </is>
       </c>
       <c r="AC33" s="2" t="inlineStr">
         <is>
-          <t>8/27</t>
+          <t>18/27</t>
         </is>
       </c>
     </row>
@@ -4417,7 +4449,7 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
@@ -4471,7 +4503,7 @@
       </c>
       <c r="AC34" s="2" t="inlineStr">
         <is>
-          <t>13/27</t>
+          <t>10/27</t>
         </is>
       </c>
     </row>
@@ -4532,7 +4564,7 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
@@ -4586,7 +4618,7 @@
       </c>
       <c r="AC35" s="2" t="inlineStr">
         <is>
-          <t>2/27</t>
+          <t>1/27</t>
         </is>
       </c>
     </row>
@@ -4614,12 +4646,12 @@
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>疑似区间车</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>原方向在全程33%处后消失；随后反向物理轨迹由seq37推进至seq49，推进12站，达到≥2站确认条件</t>
         </is>
       </c>
       <c r="H36" s="2" t="inlineStr">
@@ -4647,7 +4679,7 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
@@ -4655,10 +4687,26 @@
           <t>SHMAAS</t>
         </is>
       </c>
-      <c r="Q36" s="2" t="inlineStr"/>
-      <c r="R36" s="2" t="inlineStr"/>
-      <c r="S36" s="2" t="inlineStr"/>
-      <c r="T36" s="2" t="inlineStr"/>
+      <c r="Q36" s="2" t="inlineStr">
+        <is>
+          <t>物理seq22（站名待映射）</t>
+        </is>
+      </c>
+      <c r="R36" s="2" t="inlineStr">
+        <is>
+          <t>10:30</t>
+        </is>
+      </c>
+      <c r="S36" s="2" t="inlineStr">
+        <is>
+          <t>10:36</t>
+        </is>
+      </c>
+      <c r="T36" s="2" t="inlineStr">
+        <is>
+          <t>折返点按重建物理位置seq22映射；到达按末次同向ETA估算；折返发车结合首次反向物理观测取区间中点，约±5分钟；反向位置浦建路锦绣路 ETA 11分钟参与校验</t>
+        </is>
+      </c>
       <c r="U36" s="2" t="inlineStr">
         <is>
           <t>09:38</t>
@@ -4758,7 +4806,7 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
@@ -4812,7 +4860,7 @@
       </c>
       <c r="AC37" s="2" t="inlineStr">
         <is>
-          <t>6/27</t>
+          <t>5/27</t>
         </is>
       </c>
     </row>
@@ -4873,7 +4921,7 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
@@ -4927,7 +4975,7 @@
       </c>
       <c r="AC38" s="2" t="inlineStr">
         <is>
-          <t>6/27</t>
+          <t>5/27</t>
         </is>
       </c>
     </row>
@@ -4988,7 +5036,7 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
@@ -5042,7 +5090,7 @@
       </c>
       <c r="AC39" s="2" t="inlineStr">
         <is>
-          <t>14/27</t>
+          <t>11/27</t>
         </is>
       </c>
     </row>
@@ -5103,7 +5151,7 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
@@ -5157,7 +5205,7 @@
       </c>
       <c r="AC40" s="2" t="inlineStr">
         <is>
-          <t>5/27</t>
+          <t>4/27</t>
         </is>
       </c>
     </row>
@@ -5218,7 +5266,7 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
@@ -5329,7 +5377,7 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
@@ -5383,7 +5431,7 @@
       </c>
       <c r="AC42" s="2" t="inlineStr">
         <is>
-          <t>15/27</t>
+          <t>13/27</t>
         </is>
       </c>
     </row>
@@ -5444,7 +5492,7 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
@@ -5498,7 +5546,7 @@
       </c>
       <c r="AC43" s="2" t="inlineStr">
         <is>
-          <t>15/27</t>
+          <t>13/27</t>
         </is>
       </c>
     </row>
@@ -5559,7 +5607,7 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>10:31</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
@@ -5670,7 +5718,7 @@
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
@@ -5724,7 +5772,7 @@
       </c>
       <c r="AC45" s="2" t="inlineStr">
         <is>
-          <t>15/27</t>
+          <t>13/27</t>
         </is>
       </c>
     </row>
@@ -5785,7 +5833,7 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
@@ -5839,7 +5887,7 @@
       </c>
       <c r="AC46" s="2" t="inlineStr">
         <is>
-          <t>8/27</t>
+          <t>7/27</t>
         </is>
       </c>
     </row>
@@ -5900,7 +5948,7 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
@@ -5954,7 +6002,808 @@
       </c>
       <c r="AC47" s="2" t="inlineStr">
         <is>
-          <t>18/27</t>
+          <t>19/27</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="2" t="inlineStr"/>
+      <c r="B48" s="2" t="inlineStr">
+        <is>
+          <t>沪A55102D</t>
+        </is>
+      </c>
+      <c r="C48" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D48" s="2" t="inlineStr">
+        <is>
+          <t>11:16</t>
+        </is>
+      </c>
+      <c r="E48" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F48" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G48" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H48" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I48" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J48" s="2" t="inlineStr"/>
+      <c r="K48" s="2" t="inlineStr"/>
+      <c r="L48" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M48" s="2" t="inlineStr"/>
+      <c r="N48" s="2" t="inlineStr">
+        <is>
+          <t>06:51</t>
+        </is>
+      </c>
+      <c r="O48" s="2" t="inlineStr">
+        <is>
+          <t>11:21</t>
+        </is>
+      </c>
+      <c r="P48" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q48" s="2" t="inlineStr"/>
+      <c r="R48" s="2" t="inlineStr"/>
+      <c r="S48" s="2" t="inlineStr"/>
+      <c r="T48" s="2" t="inlineStr"/>
+      <c r="U48" s="2" t="inlineStr">
+        <is>
+          <t>11:16</t>
+        </is>
+      </c>
+      <c r="V48" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W48" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X48" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y48" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z48" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA48" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB48" s="2" t="inlineStr">
+        <is>
+          <t>132.0</t>
+        </is>
+      </c>
+      <c r="AC48" s="2" t="inlineStr">
+        <is>
+          <t>9/27</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="2" t="inlineStr"/>
+      <c r="B49" s="2" t="inlineStr">
+        <is>
+          <t>沪A67672D</t>
+        </is>
+      </c>
+      <c r="C49" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D49" s="2" t="inlineStr">
+        <is>
+          <t>11:30</t>
+        </is>
+      </c>
+      <c r="E49" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F49" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G49" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H49" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I49" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J49" s="2" t="inlineStr"/>
+      <c r="K49" s="2" t="inlineStr"/>
+      <c r="L49" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M49" s="2" t="inlineStr"/>
+      <c r="N49" s="2" t="inlineStr">
+        <is>
+          <t>07:41</t>
+        </is>
+      </c>
+      <c r="O49" s="2" t="inlineStr">
+        <is>
+          <t>11:21</t>
+        </is>
+      </c>
+      <c r="P49" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q49" s="2" t="inlineStr"/>
+      <c r="R49" s="2" t="inlineStr"/>
+      <c r="S49" s="2" t="inlineStr"/>
+      <c r="T49" s="2" t="inlineStr"/>
+      <c r="U49" s="2" t="inlineStr">
+        <is>
+          <t>11:30</t>
+        </is>
+      </c>
+      <c r="V49" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W49" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X49" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y49" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z49" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA49" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB49" s="2" t="inlineStr"/>
+      <c r="AC49" s="2" t="inlineStr">
+        <is>
+          <t>—/27</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="2" t="inlineStr"/>
+      <c r="B50" s="2" t="inlineStr">
+        <is>
+          <t>沪A15330A</t>
+        </is>
+      </c>
+      <c r="C50" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D50" s="2" t="inlineStr">
+        <is>
+          <t>11:34</t>
+        </is>
+      </c>
+      <c r="E50" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F50" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G50" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H50" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I50" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J50" s="2" t="inlineStr"/>
+      <c r="K50" s="2" t="inlineStr"/>
+      <c r="L50" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M50" s="2" t="inlineStr"/>
+      <c r="N50" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O50" s="2" t="inlineStr">
+        <is>
+          <t>11:21</t>
+        </is>
+      </c>
+      <c r="P50" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q50" s="2" t="inlineStr"/>
+      <c r="R50" s="2" t="inlineStr"/>
+      <c r="S50" s="2" t="inlineStr"/>
+      <c r="T50" s="2" t="inlineStr"/>
+      <c r="U50" s="2" t="inlineStr">
+        <is>
+          <t>11:34</t>
+        </is>
+      </c>
+      <c r="V50" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W50" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X50" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y50" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z50" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA50" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB50" s="2" t="inlineStr">
+        <is>
+          <t>128.0</t>
+        </is>
+      </c>
+      <c r="AC50" s="2" t="inlineStr">
+        <is>
+          <t>2/27</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="2" t="inlineStr"/>
+      <c r="B51" s="2" t="inlineStr">
+        <is>
+          <t>沪A57601A</t>
+        </is>
+      </c>
+      <c r="C51" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D51" s="2" t="inlineStr">
+        <is>
+          <t>11:50</t>
+        </is>
+      </c>
+      <c r="E51" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F51" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G51" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H51" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I51" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J51" s="2" t="inlineStr"/>
+      <c r="K51" s="2" t="inlineStr"/>
+      <c r="L51" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M51" s="2" t="inlineStr"/>
+      <c r="N51" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O51" s="2" t="inlineStr">
+        <is>
+          <t>11:21</t>
+        </is>
+      </c>
+      <c r="P51" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q51" s="2" t="inlineStr"/>
+      <c r="R51" s="2" t="inlineStr"/>
+      <c r="S51" s="2" t="inlineStr"/>
+      <c r="T51" s="2" t="inlineStr"/>
+      <c r="U51" s="2" t="inlineStr">
+        <is>
+          <t>11:50</t>
+        </is>
+      </c>
+      <c r="V51" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W51" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X51" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y51" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z51" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA51" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB51" s="2" t="inlineStr">
+        <is>
+          <t>140.0</t>
+        </is>
+      </c>
+      <c r="AC51" s="2" t="inlineStr">
+        <is>
+          <t>20/27</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="2" t="inlineStr"/>
+      <c r="B52" s="2" t="inlineStr">
+        <is>
+          <t>沪A67057D</t>
+        </is>
+      </c>
+      <c r="C52" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D52" s="2" t="inlineStr">
+        <is>
+          <t>11:50</t>
+        </is>
+      </c>
+      <c r="E52" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F52" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G52" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H52" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I52" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J52" s="2" t="inlineStr"/>
+      <c r="K52" s="2" t="inlineStr"/>
+      <c r="L52" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M52" s="2" t="inlineStr"/>
+      <c r="N52" s="2" t="inlineStr">
+        <is>
+          <t>07:01</t>
+        </is>
+      </c>
+      <c r="O52" s="2" t="inlineStr">
+        <is>
+          <t>11:21</t>
+        </is>
+      </c>
+      <c r="P52" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q52" s="2" t="inlineStr"/>
+      <c r="R52" s="2" t="inlineStr"/>
+      <c r="S52" s="2" t="inlineStr"/>
+      <c r="T52" s="2" t="inlineStr"/>
+      <c r="U52" s="2" t="inlineStr">
+        <is>
+          <t>11:50</t>
+        </is>
+      </c>
+      <c r="V52" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W52" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X52" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y52" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z52" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA52" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB52" s="2" t="inlineStr">
+        <is>
+          <t>134.0</t>
+        </is>
+      </c>
+      <c r="AC52" s="2" t="inlineStr">
+        <is>
+          <t>11/27</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="2" t="inlineStr"/>
+      <c r="B53" s="2" t="inlineStr">
+        <is>
+          <t>沪A62981D</t>
+        </is>
+      </c>
+      <c r="C53" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D53" s="2" t="inlineStr">
+        <is>
+          <t>12:05</t>
+        </is>
+      </c>
+      <c r="E53" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F53" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G53" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H53" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I53" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J53" s="2" t="inlineStr"/>
+      <c r="K53" s="2" t="inlineStr"/>
+      <c r="L53" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M53" s="2" t="inlineStr"/>
+      <c r="N53" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O53" s="2" t="inlineStr">
+        <is>
+          <t>11:21</t>
+        </is>
+      </c>
+      <c r="P53" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q53" s="2" t="inlineStr"/>
+      <c r="R53" s="2" t="inlineStr"/>
+      <c r="S53" s="2" t="inlineStr"/>
+      <c r="T53" s="2" t="inlineStr"/>
+      <c r="U53" s="2" t="inlineStr">
+        <is>
+          <t>12:05</t>
+        </is>
+      </c>
+      <c r="V53" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W53" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X53" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y53" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z53" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA53" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB53" s="2" t="inlineStr">
+        <is>
+          <t>140.0</t>
+        </is>
+      </c>
+      <c r="AC53" s="2" t="inlineStr">
+        <is>
+          <t>20/27</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="2" t="inlineStr"/>
+      <c r="B54" s="2" t="inlineStr">
+        <is>
+          <t>沪A95621D</t>
+        </is>
+      </c>
+      <c r="C54" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D54" s="2" t="inlineStr">
+        <is>
+          <t>12:15</t>
+        </is>
+      </c>
+      <c r="E54" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F54" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G54" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H54" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I54" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J54" s="2" t="inlineStr"/>
+      <c r="K54" s="2" t="inlineStr"/>
+      <c r="L54" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M54" s="2" t="inlineStr"/>
+      <c r="N54" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O54" s="2" t="inlineStr">
+        <is>
+          <t>11:21</t>
+        </is>
+      </c>
+      <c r="P54" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q54" s="2" t="inlineStr"/>
+      <c r="R54" s="2" t="inlineStr"/>
+      <c r="S54" s="2" t="inlineStr"/>
+      <c r="T54" s="2" t="inlineStr"/>
+      <c r="U54" s="2" t="inlineStr">
+        <is>
+          <t>12:15</t>
+        </is>
+      </c>
+      <c r="V54" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W54" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X54" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y54" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z54" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA54" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB54" s="2" t="inlineStr">
+        <is>
+          <t>131.5</t>
+        </is>
+      </c>
+      <c r="AC54" s="2" t="inlineStr">
+        <is>
+          <t>8/27</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-10-31-浦东35路.xlsx
+++ b/data/export/2026-10-31-浦东35路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC54"/>
+  <dimension ref="A1:AC60"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -669,7 +669,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -723,7 +723,7 @@
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>2/27</t>
+          <t>2/28</t>
         </is>
       </c>
     </row>
@@ -842,7 +842,7 @@
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>16/27</t>
+          <t>15/28</t>
         </is>
       </c>
     </row>
@@ -907,7 +907,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>11:31</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -961,7 +961,7 @@
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>3/27</t>
+          <t>3/28</t>
         </is>
       </c>
     </row>
@@ -1026,7 +1026,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1075,12 +1075,12 @@
       </c>
       <c r="AB5" s="2" t="inlineStr">
         <is>
-          <t>140.0</t>
+          <t>140.5</t>
         </is>
       </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>20/27</t>
+          <t>21/28</t>
         </is>
       </c>
     </row>
@@ -1145,7 +1145,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1199,7 +1199,7 @@
       </c>
       <c r="AC6" s="2" t="inlineStr">
         <is>
-          <t>8/27</t>
+          <t>8/28</t>
         </is>
       </c>
     </row>
@@ -1264,7 +1264,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>11:51</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1308,17 +1308,17 @@
       </c>
       <c r="AA7" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB7" s="2" t="inlineStr">
         <is>
-          <t>127.0</t>
+          <t>134.5</t>
         </is>
       </c>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>1/27</t>
+          <t>12/28</t>
         </is>
       </c>
     </row>
@@ -1383,7 +1383,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>11:31</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1437,7 +1437,7 @@
       </c>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>18/27</t>
+          <t>18/28</t>
         </is>
       </c>
     </row>
@@ -1502,7 +1502,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1541,22 +1541,22 @@
       </c>
       <c r="Z9" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA9" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA9" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB9" s="2" t="inlineStr">
         <is>
-          <t>130.0</t>
+          <t>128.5</t>
         </is>
       </c>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>5/27</t>
+          <t>3/28</t>
         </is>
       </c>
     </row>
@@ -1621,7 +1621,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>11:41</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1665,7 +1665,7 @@
       </c>
       <c r="AA10" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB10" s="2" t="inlineStr">
@@ -1675,7 +1675,7 @@
       </c>
       <c r="AC10" s="2" t="inlineStr">
         <is>
-          <t>10/27</t>
+          <t>10/28</t>
         </is>
       </c>
     </row>
@@ -1740,7 +1740,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:11</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1784,17 +1784,17 @@
       </c>
       <c r="AA11" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB11" s="2" t="inlineStr">
         <is>
-          <t>129.0</t>
+          <t>130.5</t>
         </is>
       </c>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>4/27</t>
+          <t>6/28</t>
         </is>
       </c>
     </row>
@@ -1859,7 +1859,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>11:51</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1913,7 +1913,7 @@
       </c>
       <c r="AC12" s="2" t="inlineStr">
         <is>
-          <t>5/27</t>
+          <t>5/28</t>
         </is>
       </c>
     </row>
@@ -1974,7 +1974,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -2029,7 +2029,7 @@
       </c>
       <c r="Z13" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AA13" s="2" t="inlineStr">
@@ -2040,7 +2040,7 @@
       <c r="AB13" s="2" t="inlineStr"/>
       <c r="AC13" s="2" t="inlineStr">
         <is>
-          <t>—/27</t>
+          <t>—/28</t>
         </is>
       </c>
     </row>
@@ -2105,7 +2105,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2149,17 +2149,17 @@
       </c>
       <c r="AA14" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB14" s="2" t="inlineStr">
         <is>
-          <t>134.0</t>
+          <t>141.0</t>
         </is>
       </c>
       <c r="AC14" s="2" t="inlineStr">
         <is>
-          <t>11/27</t>
+          <t>22/28</t>
         </is>
       </c>
     </row>
@@ -2220,7 +2220,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2259,18 +2259,22 @@
       </c>
       <c r="Z15" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA15" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB15" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB15" s="2" t="inlineStr">
+        <is>
+          <t>127.0</t>
+        </is>
+      </c>
       <c r="AC15" s="2" t="inlineStr">
         <is>
-          <t>—/27</t>
+          <t>1/28</t>
         </is>
       </c>
     </row>
@@ -2335,7 +2339,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2379,17 +2383,17 @@
       </c>
       <c r="AA16" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB16" s="2" t="inlineStr">
         <is>
-          <t>135.0</t>
+          <t>136.0</t>
         </is>
       </c>
       <c r="AC16" s="2" t="inlineStr">
         <is>
-          <t>13/27</t>
+          <t>15/28</t>
         </is>
       </c>
     </row>
@@ -2454,7 +2458,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2508,7 +2512,7 @@
       </c>
       <c r="AC17" s="2" t="inlineStr">
         <is>
-          <t>13/27</t>
+          <t>13/28</t>
         </is>
       </c>
     </row>
@@ -2573,7 +2577,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2612,7 +2616,7 @@
       </c>
       <c r="Z18" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA18" s="2" t="inlineStr">
@@ -2627,7 +2631,7 @@
       </c>
       <c r="AC18" s="2" t="inlineStr">
         <is>
-          <t>13/27</t>
+          <t>13/28</t>
         </is>
       </c>
     </row>
@@ -2688,7 +2692,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>10:31</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2738,7 +2742,7 @@
       <c r="AB19" s="2" t="inlineStr"/>
       <c r="AC19" s="2" t="inlineStr">
         <is>
-          <t>—/27</t>
+          <t>—/28</t>
         </is>
       </c>
     </row>
@@ -2803,7 +2807,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2857,7 +2861,7 @@
       </c>
       <c r="AC20" s="2" t="inlineStr">
         <is>
-          <t>19/27</t>
+          <t>19/28</t>
         </is>
       </c>
     </row>
@@ -2922,7 +2926,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -2976,7 +2980,7 @@
       </c>
       <c r="AC21" s="2" t="inlineStr">
         <is>
-          <t>7/27</t>
+          <t>7/28</t>
         </is>
       </c>
     </row>
@@ -3037,7 +3041,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -3087,7 +3091,7 @@
       <c r="AB22" s="2" t="inlineStr"/>
       <c r="AC22" s="2" t="inlineStr">
         <is>
-          <t>—/27</t>
+          <t>—/28</t>
         </is>
       </c>
     </row>
@@ -3198,7 +3202,7 @@
       <c r="AB23" s="2" t="inlineStr"/>
       <c r="AC23" s="2" t="inlineStr">
         <is>
-          <t>—/27</t>
+          <t>—/28</t>
         </is>
       </c>
     </row>
@@ -3317,7 +3321,7 @@
       </c>
       <c r="AC24" s="2" t="inlineStr">
         <is>
-          <t>16/27</t>
+          <t>15/28</t>
         </is>
       </c>
     </row>
@@ -3382,7 +3386,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3436,7 +3440,7 @@
       </c>
       <c r="AC25" s="2" t="inlineStr">
         <is>
-          <t>9/27</t>
+          <t>9/28</t>
         </is>
       </c>
     </row>
@@ -3501,7 +3505,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3555,7 +3559,7 @@
       </c>
       <c r="AC26" s="2" t="inlineStr">
         <is>
-          <t>20/27</t>
+          <t>20/28</t>
         </is>
       </c>
     </row>
@@ -3620,7 +3624,7 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -3674,7 +3678,7 @@
       </c>
       <c r="AC27" s="2" t="inlineStr">
         <is>
-          <t>2/27</t>
+          <t>2/28</t>
         </is>
       </c>
     </row>
@@ -3793,7 +3797,7 @@
       </c>
       <c r="AC28" s="2" t="inlineStr">
         <is>
-          <t>16/27</t>
+          <t>15/28</t>
         </is>
       </c>
     </row>
@@ -3858,7 +3862,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -3912,7 +3916,7 @@
       </c>
       <c r="AC29" s="2" t="inlineStr">
         <is>
-          <t>11/27</t>
+          <t>11/28</t>
         </is>
       </c>
     </row>
@@ -3977,7 +3981,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>11:31</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -4031,7 +4035,7 @@
       </c>
       <c r="AC30" s="2" t="inlineStr">
         <is>
-          <t>3/27</t>
+          <t>3/28</t>
         </is>
       </c>
     </row>
@@ -4096,7 +4100,7 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
@@ -4150,7 +4154,7 @@
       </c>
       <c r="AC31" s="2" t="inlineStr">
         <is>
-          <t>8/27</t>
+          <t>8/28</t>
         </is>
       </c>
     </row>
@@ -4188,24 +4192,24 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>11:43</t>
+          <t>11:44</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>148分钟</t>
+          <t>149分钟</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr"/>
       <c r="K32" s="2" t="inlineStr"/>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -4215,7 +4219,7 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
@@ -4264,12 +4268,12 @@
       </c>
       <c r="AB32" s="2" t="inlineStr">
         <is>
-          <t>140.0</t>
+          <t>140.5</t>
         </is>
       </c>
       <c r="AC32" s="2" t="inlineStr">
         <is>
-          <t>20/27</t>
+          <t>21/28</t>
         </is>
       </c>
     </row>
@@ -4334,7 +4338,7 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>11:31</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
@@ -4388,7 +4392,7 @@
       </c>
       <c r="AC33" s="2" t="inlineStr">
         <is>
-          <t>18/27</t>
+          <t>18/28</t>
         </is>
       </c>
     </row>
@@ -4416,32 +4420,36 @@
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>11:43</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>133分钟</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr"/>
       <c r="K34" s="2" t="inlineStr"/>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M34" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M34" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N34" s="2" t="inlineStr">
         <is>
           <t>06:11</t>
@@ -4449,7 +4457,7 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>11:41</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
@@ -4473,17 +4481,17 @@
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X34" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y34" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z34" s="2" t="inlineStr">
@@ -4493,7 +4501,7 @@
       </c>
       <c r="AA34" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB34" s="2" t="inlineStr">
@@ -4503,7 +4511,7 @@
       </c>
       <c r="AC34" s="2" t="inlineStr">
         <is>
-          <t>10/27</t>
+          <t>10/28</t>
         </is>
       </c>
     </row>
@@ -4531,32 +4539,36 @@
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>11:52</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>142分钟</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr"/>
       <c r="K35" s="2" t="inlineStr"/>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M35" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="M35" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="N35" s="2" t="inlineStr">
         <is>
           <t>06:11</t>
@@ -4564,7 +4576,7 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>11:51</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
@@ -4588,17 +4600,17 @@
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X35" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y35" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z35" s="2" t="inlineStr">
@@ -4608,17 +4620,17 @@
       </c>
       <c r="AA35" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB35" s="2" t="inlineStr">
         <is>
-          <t>127.0</t>
+          <t>134.5</t>
         </is>
       </c>
       <c r="AC35" s="2" t="inlineStr">
         <is>
-          <t>1/27</t>
+          <t>12/28</t>
         </is>
       </c>
     </row>
@@ -4651,7 +4663,7 @@
       </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t>原方向在全程33%处后消失；随后反向物理轨迹由seq37推进至seq49，推进12站，达到≥2站确认条件</t>
+          <t>原方向在全程33%处后消失；随后反向物理轨迹由seq37推进至seq61，推进24站，达到≥2站确认条件</t>
         </is>
       </c>
       <c r="H36" s="2" t="inlineStr">
@@ -4679,7 +4691,7 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
@@ -4734,7 +4746,7 @@
       </c>
       <c r="Z36" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AA36" s="2" t="inlineStr">
@@ -4745,7 +4757,7 @@
       <c r="AB36" s="2" t="inlineStr"/>
       <c r="AC36" s="2" t="inlineStr">
         <is>
-          <t>—/27</t>
+          <t>—/28</t>
         </is>
       </c>
     </row>
@@ -4773,32 +4785,36 @@
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>11:52</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>127分钟</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr"/>
       <c r="K37" s="2" t="inlineStr"/>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M37" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="M37" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="N37" s="2" t="inlineStr">
         <is>
           <t>06:21</t>
@@ -4806,7 +4822,7 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
@@ -4830,37 +4846,37 @@
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X37" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y37" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z37" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA37" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA37" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB37" s="2" t="inlineStr">
         <is>
-          <t>130.0</t>
+          <t>128.5</t>
         </is>
       </c>
       <c r="AC37" s="2" t="inlineStr">
         <is>
-          <t>5/27</t>
+          <t>3/28</t>
         </is>
       </c>
     </row>
@@ -4921,7 +4937,7 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>11:51</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
@@ -4975,7 +4991,7 @@
       </c>
       <c r="AC38" s="2" t="inlineStr">
         <is>
-          <t>5/27</t>
+          <t>5/28</t>
         </is>
       </c>
     </row>
@@ -5003,32 +5019,36 @@
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>12:28</t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>148分钟</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr"/>
       <c r="K39" s="2" t="inlineStr"/>
       <c r="L39" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M39" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M39" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N39" s="2" t="inlineStr">
         <is>
           <t>07:01</t>
@@ -5036,7 +5056,7 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
@@ -5060,17 +5080,17 @@
       </c>
       <c r="W39" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X39" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y39" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z39" s="2" t="inlineStr">
@@ -5080,17 +5100,17 @@
       </c>
       <c r="AA39" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB39" s="2" t="inlineStr">
         <is>
-          <t>134.0</t>
+          <t>141.0</t>
         </is>
       </c>
       <c r="AC39" s="2" t="inlineStr">
         <is>
-          <t>11/27</t>
+          <t>22/28</t>
         </is>
       </c>
     </row>
@@ -5118,32 +5138,36 @@
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>12:12</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>132分钟</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr"/>
       <c r="K40" s="2" t="inlineStr"/>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M40" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="M40" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="N40" s="2" t="inlineStr">
         <is>
           <t>06:41</t>
@@ -5151,7 +5175,7 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:11</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
@@ -5175,17 +5199,17 @@
       </c>
       <c r="W40" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X40" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y40" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z40" s="2" t="inlineStr">
@@ -5195,17 +5219,17 @@
       </c>
       <c r="AA40" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB40" s="2" t="inlineStr">
         <is>
-          <t>129.0</t>
+          <t>130.5</t>
         </is>
       </c>
       <c r="AC40" s="2" t="inlineStr">
         <is>
-          <t>4/27</t>
+          <t>6/28</t>
         </is>
       </c>
     </row>
@@ -5233,32 +5257,36 @@
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>127分钟</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr"/>
       <c r="K41" s="2" t="inlineStr"/>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M41" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="M41" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="N41" s="2" t="inlineStr">
         <is>
           <t>06:51</t>
@@ -5266,7 +5294,7 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
@@ -5290,33 +5318,37 @@
       </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X41" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y41" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z41" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA41" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB41" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB41" s="2" t="inlineStr">
+        <is>
+          <t>127.0</t>
+        </is>
+      </c>
       <c r="AC41" s="2" t="inlineStr">
         <is>
-          <t>—/27</t>
+          <t>1/28</t>
         </is>
       </c>
     </row>
@@ -5344,32 +5376,36 @@
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>12:37</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>137分钟</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr"/>
       <c r="K42" s="2" t="inlineStr"/>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M42" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M42" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N42" s="2" t="inlineStr">
         <is>
           <t>07:11</t>
@@ -5377,7 +5413,7 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
@@ -5401,17 +5437,17 @@
       </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X42" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y42" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z42" s="2" t="inlineStr">
@@ -5421,17 +5457,17 @@
       </c>
       <c r="AA42" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB42" s="2" t="inlineStr">
         <is>
-          <t>135.0</t>
+          <t>136.0</t>
         </is>
       </c>
       <c r="AC42" s="2" t="inlineStr">
         <is>
-          <t>13/27</t>
+          <t>15/28</t>
         </is>
       </c>
     </row>
@@ -5492,7 +5528,7 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
@@ -5546,7 +5582,7 @@
       </c>
       <c r="AC43" s="2" t="inlineStr">
         <is>
-          <t>13/27</t>
+          <t>13/28</t>
         </is>
       </c>
     </row>
@@ -5607,7 +5643,7 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>10:31</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
@@ -5657,7 +5693,7 @@
       <c r="AB44" s="2" t="inlineStr"/>
       <c r="AC44" s="2" t="inlineStr">
         <is>
-          <t>—/27</t>
+          <t>—/28</t>
         </is>
       </c>
     </row>
@@ -5718,7 +5754,7 @@
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
@@ -5757,7 +5793,7 @@
       </c>
       <c r="Z45" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA45" s="2" t="inlineStr">
@@ -5772,7 +5808,7 @@
       </c>
       <c r="AC45" s="2" t="inlineStr">
         <is>
-          <t>13/27</t>
+          <t>13/28</t>
         </is>
       </c>
     </row>
@@ -5833,7 +5869,7 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
@@ -5887,7 +5923,7 @@
       </c>
       <c r="AC46" s="2" t="inlineStr">
         <is>
-          <t>7/27</t>
+          <t>7/28</t>
         </is>
       </c>
     </row>
@@ -5948,7 +5984,7 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
@@ -6002,7 +6038,7 @@
       </c>
       <c r="AC47" s="2" t="inlineStr">
         <is>
-          <t>19/27</t>
+          <t>19/28</t>
         </is>
       </c>
     </row>
@@ -6063,7 +6099,7 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
@@ -6117,7 +6153,7 @@
       </c>
       <c r="AC48" s="2" t="inlineStr">
         <is>
-          <t>9/27</t>
+          <t>9/28</t>
         </is>
       </c>
     </row>
@@ -6178,7 +6214,7 @@
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
@@ -6228,7 +6264,7 @@
       <c r="AB49" s="2" t="inlineStr"/>
       <c r="AC49" s="2" t="inlineStr">
         <is>
-          <t>—/27</t>
+          <t>—/28</t>
         </is>
       </c>
     </row>
@@ -6289,7 +6325,7 @@
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
@@ -6343,7 +6379,7 @@
       </c>
       <c r="AC50" s="2" t="inlineStr">
         <is>
-          <t>2/27</t>
+          <t>2/28</t>
         </is>
       </c>
     </row>
@@ -6404,7 +6440,7 @@
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P51" s="2" t="inlineStr">
@@ -6458,7 +6494,7 @@
       </c>
       <c r="AC51" s="2" t="inlineStr">
         <is>
-          <t>20/27</t>
+          <t>20/28</t>
         </is>
       </c>
     </row>
@@ -6519,7 +6555,7 @@
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
@@ -6573,7 +6609,7 @@
       </c>
       <c r="AC52" s="2" t="inlineStr">
         <is>
-          <t>11/27</t>
+          <t>11/28</t>
         </is>
       </c>
     </row>
@@ -6634,7 +6670,7 @@
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P53" s="2" t="inlineStr">
@@ -6683,12 +6719,12 @@
       </c>
       <c r="AB53" s="2" t="inlineStr">
         <is>
-          <t>140.0</t>
+          <t>140.5</t>
         </is>
       </c>
       <c r="AC53" s="2" t="inlineStr">
         <is>
-          <t>20/27</t>
+          <t>21/28</t>
         </is>
       </c>
     </row>
@@ -6749,7 +6785,7 @@
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P54" s="2" t="inlineStr">
@@ -6803,7 +6839,685 @@
       </c>
       <c r="AC54" s="2" t="inlineStr">
         <is>
-          <t>8/27</t>
+          <t>8/28</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="2" t="inlineStr"/>
+      <c r="B55" s="2" t="inlineStr">
+        <is>
+          <t>沪A79307D</t>
+        </is>
+      </c>
+      <c r="C55" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D55" s="2" t="inlineStr">
+        <is>
+          <t>12:28</t>
+        </is>
+      </c>
+      <c r="E55" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F55" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G55" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H55" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I55" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J55" s="2" t="inlineStr"/>
+      <c r="K55" s="2" t="inlineStr"/>
+      <c r="L55" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M55" s="2" t="inlineStr"/>
+      <c r="N55" s="2" t="inlineStr">
+        <is>
+          <t>09:31</t>
+        </is>
+      </c>
+      <c r="O55" s="2" t="inlineStr">
+        <is>
+          <t>12:21</t>
+        </is>
+      </c>
+      <c r="P55" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q55" s="2" t="inlineStr"/>
+      <c r="R55" s="2" t="inlineStr"/>
+      <c r="S55" s="2" t="inlineStr"/>
+      <c r="T55" s="2" t="inlineStr"/>
+      <c r="U55" s="2" t="inlineStr">
+        <is>
+          <t>12:28</t>
+        </is>
+      </c>
+      <c r="V55" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W55" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X55" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y55" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z55" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA55" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB55" s="2" t="inlineStr"/>
+      <c r="AC55" s="2" t="inlineStr">
+        <is>
+          <t>—/28</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="2" t="inlineStr"/>
+      <c r="B56" s="2" t="inlineStr">
+        <is>
+          <t>沪A62217D</t>
+        </is>
+      </c>
+      <c r="C56" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D56" s="2" t="inlineStr">
+        <is>
+          <t>12:30</t>
+        </is>
+      </c>
+      <c r="E56" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F56" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G56" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H56" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I56" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J56" s="2" t="inlineStr"/>
+      <c r="K56" s="2" t="inlineStr"/>
+      <c r="L56" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M56" s="2" t="inlineStr"/>
+      <c r="N56" s="2" t="inlineStr">
+        <is>
+          <t>06:21</t>
+        </is>
+      </c>
+      <c r="O56" s="2" t="inlineStr">
+        <is>
+          <t>12:21</t>
+        </is>
+      </c>
+      <c r="P56" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q56" s="2" t="inlineStr"/>
+      <c r="R56" s="2" t="inlineStr"/>
+      <c r="S56" s="2" t="inlineStr"/>
+      <c r="T56" s="2" t="inlineStr"/>
+      <c r="U56" s="2" t="inlineStr">
+        <is>
+          <t>12:30</t>
+        </is>
+      </c>
+      <c r="V56" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W56" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X56" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y56" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z56" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA56" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB56" s="2" t="inlineStr">
+        <is>
+          <t>128.5</t>
+        </is>
+      </c>
+      <c r="AC56" s="2" t="inlineStr">
+        <is>
+          <t>3/28</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="2" t="inlineStr"/>
+      <c r="B57" s="2" t="inlineStr">
+        <is>
+          <t>沪A51682D</t>
+        </is>
+      </c>
+      <c r="C57" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D57" s="2" t="inlineStr">
+        <is>
+          <t>12:40</t>
+        </is>
+      </c>
+      <c r="E57" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F57" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G57" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H57" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I57" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J57" s="2" t="inlineStr"/>
+      <c r="K57" s="2" t="inlineStr"/>
+      <c r="L57" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M57" s="2" t="inlineStr"/>
+      <c r="N57" s="2" t="inlineStr">
+        <is>
+          <t>06:51</t>
+        </is>
+      </c>
+      <c r="O57" s="2" t="inlineStr">
+        <is>
+          <t>12:21</t>
+        </is>
+      </c>
+      <c r="P57" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q57" s="2" t="inlineStr"/>
+      <c r="R57" s="2" t="inlineStr"/>
+      <c r="S57" s="2" t="inlineStr"/>
+      <c r="T57" s="2" t="inlineStr"/>
+      <c r="U57" s="2" t="inlineStr">
+        <is>
+          <t>12:40</t>
+        </is>
+      </c>
+      <c r="V57" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W57" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X57" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y57" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z57" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA57" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB57" s="2" t="inlineStr"/>
+      <c r="AC57" s="2" t="inlineStr">
+        <is>
+          <t>—/28</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="2" t="inlineStr"/>
+      <c r="B58" s="2" t="inlineStr">
+        <is>
+          <t>沪A68895D</t>
+        </is>
+      </c>
+      <c r="C58" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D58" s="2" t="inlineStr">
+        <is>
+          <t>12:55</t>
+        </is>
+      </c>
+      <c r="E58" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F58" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G58" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H58" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I58" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J58" s="2" t="inlineStr"/>
+      <c r="K58" s="2" t="inlineStr"/>
+      <c r="L58" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M58" s="2" t="inlineStr"/>
+      <c r="N58" s="2" t="inlineStr">
+        <is>
+          <t>06:51</t>
+        </is>
+      </c>
+      <c r="O58" s="2" t="inlineStr">
+        <is>
+          <t>12:21</t>
+        </is>
+      </c>
+      <c r="P58" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q58" s="2" t="inlineStr"/>
+      <c r="R58" s="2" t="inlineStr"/>
+      <c r="S58" s="2" t="inlineStr"/>
+      <c r="T58" s="2" t="inlineStr"/>
+      <c r="U58" s="2" t="inlineStr">
+        <is>
+          <t>12:55</t>
+        </is>
+      </c>
+      <c r="V58" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W58" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X58" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y58" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z58" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA58" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB58" s="2" t="inlineStr">
+        <is>
+          <t>127.0</t>
+        </is>
+      </c>
+      <c r="AC58" s="2" t="inlineStr">
+        <is>
+          <t>1/28</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="2" t="inlineStr"/>
+      <c r="B59" s="2" t="inlineStr">
+        <is>
+          <t>沪A37823D</t>
+        </is>
+      </c>
+      <c r="C59" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D59" s="2" t="inlineStr">
+        <is>
+          <t>13:05</t>
+        </is>
+      </c>
+      <c r="E59" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F59" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G59" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H59" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I59" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J59" s="2" t="inlineStr"/>
+      <c r="K59" s="2" t="inlineStr"/>
+      <c r="L59" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M59" s="2" t="inlineStr"/>
+      <c r="N59" s="2" t="inlineStr">
+        <is>
+          <t>07:31</t>
+        </is>
+      </c>
+      <c r="O59" s="2" t="inlineStr">
+        <is>
+          <t>12:21</t>
+        </is>
+      </c>
+      <c r="P59" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q59" s="2" t="inlineStr"/>
+      <c r="R59" s="2" t="inlineStr"/>
+      <c r="S59" s="2" t="inlineStr"/>
+      <c r="T59" s="2" t="inlineStr"/>
+      <c r="U59" s="2" t="inlineStr">
+        <is>
+          <t>13:05</t>
+        </is>
+      </c>
+      <c r="V59" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W59" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X59" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y59" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z59" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA59" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB59" s="2" t="inlineStr"/>
+      <c r="AC59" s="2" t="inlineStr">
+        <is>
+          <t>—/28</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="2" t="inlineStr"/>
+      <c r="B60" s="2" t="inlineStr">
+        <is>
+          <t>沪A59793A</t>
+        </is>
+      </c>
+      <c r="C60" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D60" s="2" t="inlineStr">
+        <is>
+          <t>13:20</t>
+        </is>
+      </c>
+      <c r="E60" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F60" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G60" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H60" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I60" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J60" s="2" t="inlineStr"/>
+      <c r="K60" s="2" t="inlineStr"/>
+      <c r="L60" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M60" s="2" t="inlineStr"/>
+      <c r="N60" s="2" t="inlineStr">
+        <is>
+          <t>06:51</t>
+        </is>
+      </c>
+      <c r="O60" s="2" t="inlineStr">
+        <is>
+          <t>12:21</t>
+        </is>
+      </c>
+      <c r="P60" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q60" s="2" t="inlineStr"/>
+      <c r="R60" s="2" t="inlineStr"/>
+      <c r="S60" s="2" t="inlineStr"/>
+      <c r="T60" s="2" t="inlineStr"/>
+      <c r="U60" s="2" t="inlineStr">
+        <is>
+          <t>13:20</t>
+        </is>
+      </c>
+      <c r="V60" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W60" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X60" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y60" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z60" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA60" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB60" s="2" t="inlineStr">
+        <is>
+          <t>135.0</t>
+        </is>
+      </c>
+      <c r="AC60" s="2" t="inlineStr">
+        <is>
+          <t>13/28</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-10-31-浦东35路.xlsx
+++ b/data/export/2026-10-31-浦东35路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC60"/>
+  <dimension ref="A1:AC66"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -669,7 +669,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -708,14 +708,14 @@
       </c>
       <c r="Z2" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA2" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA2" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB2" s="2" t="inlineStr">
         <is>
           <t>128.0</t>
@@ -723,7 +723,7 @@
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>2/28</t>
+          <t>3/28</t>
         </is>
       </c>
     </row>
@@ -842,7 +842,7 @@
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>15/28</t>
+          <t>17/28</t>
         </is>
       </c>
     </row>
@@ -961,7 +961,7 @@
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>3/28</t>
+          <t>4/28</t>
         </is>
       </c>
     </row>
@@ -1026,7 +1026,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1080,7 +1080,7 @@
       </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>21/28</t>
+          <t>23/28</t>
         </is>
       </c>
     </row>
@@ -1145,7 +1145,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1184,7 +1184,7 @@
       </c>
       <c r="Z6" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA6" s="2" t="inlineStr">
@@ -1199,7 +1199,7 @@
       </c>
       <c r="AC6" s="2" t="inlineStr">
         <is>
-          <t>8/28</t>
+          <t>9/28</t>
         </is>
       </c>
     </row>
@@ -1318,7 +1318,7 @@
       </c>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>12/28</t>
+          <t>16/28</t>
         </is>
       </c>
     </row>
@@ -1437,7 +1437,7 @@
       </c>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>18/28</t>
+          <t>20/28</t>
         </is>
       </c>
     </row>
@@ -1502,7 +1502,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1556,7 +1556,7 @@
       </c>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>3/28</t>
+          <t>4/28</t>
         </is>
       </c>
     </row>
@@ -1675,7 +1675,7 @@
       </c>
       <c r="AC10" s="2" t="inlineStr">
         <is>
-          <t>10/28</t>
+          <t>13/28</t>
         </is>
       </c>
     </row>
@@ -1794,7 +1794,7 @@
       </c>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>6/28</t>
+          <t>7/28</t>
         </is>
       </c>
     </row>
@@ -1913,7 +1913,7 @@
       </c>
       <c r="AC12" s="2" t="inlineStr">
         <is>
-          <t>5/28</t>
+          <t>6/28</t>
         </is>
       </c>
     </row>
@@ -1974,7 +1974,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -2159,7 +2159,7 @@
       </c>
       <c r="AC14" s="2" t="inlineStr">
         <is>
-          <t>22/28</t>
+          <t>24/28</t>
         </is>
       </c>
     </row>
@@ -2220,7 +2220,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2274,7 +2274,7 @@
       </c>
       <c r="AC15" s="2" t="inlineStr">
         <is>
-          <t>1/28</t>
+          <t>2/28</t>
         </is>
       </c>
     </row>
@@ -2339,7 +2339,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2378,14 +2378,14 @@
       </c>
       <c r="Z16" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA16" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA16" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB16" s="2" t="inlineStr">
         <is>
           <t>136.0</t>
@@ -2393,7 +2393,7 @@
       </c>
       <c r="AC16" s="2" t="inlineStr">
         <is>
-          <t>15/28</t>
+          <t>17/28</t>
         </is>
       </c>
     </row>
@@ -2458,7 +2458,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>12:51</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2502,17 +2502,17 @@
       </c>
       <c r="AA17" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB17" s="2" t="inlineStr">
         <is>
-          <t>135.0</t>
+          <t>140.0</t>
         </is>
       </c>
       <c r="AC17" s="2" t="inlineStr">
         <is>
-          <t>13/28</t>
+          <t>21/28</t>
         </is>
       </c>
     </row>
@@ -2577,7 +2577,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2621,17 +2621,17 @@
       </c>
       <c r="AA18" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB18" s="2" t="inlineStr">
         <is>
-          <t>135.0</t>
+          <t>133.5</t>
         </is>
       </c>
       <c r="AC18" s="2" t="inlineStr">
         <is>
-          <t>13/28</t>
+          <t>14/28</t>
         </is>
       </c>
     </row>
@@ -2692,7 +2692,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>12:41</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2736,13 +2736,17 @@
       </c>
       <c r="AA19" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB19" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB19" s="2" t="inlineStr">
+        <is>
+          <t>123.0</t>
+        </is>
+      </c>
       <c r="AC19" s="2" t="inlineStr">
         <is>
-          <t>—/28</t>
+          <t>1/28</t>
         </is>
       </c>
     </row>
@@ -2807,7 +2811,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:11</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2851,17 +2855,17 @@
       </c>
       <c r="AA20" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB20" s="2" t="inlineStr">
         <is>
-          <t>137.0</t>
+          <t>132.0</t>
         </is>
       </c>
       <c r="AC20" s="2" t="inlineStr">
         <is>
-          <t>19/28</t>
+          <t>10/28</t>
         </is>
       </c>
     </row>
@@ -2926,7 +2930,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -2965,14 +2969,14 @@
       </c>
       <c r="Z21" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA21" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA21" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB21" s="2" t="inlineStr">
         <is>
           <t>131.0</t>
@@ -2980,7 +2984,7 @@
       </c>
       <c r="AC21" s="2" t="inlineStr">
         <is>
-          <t>7/28</t>
+          <t>8/28</t>
         </is>
       </c>
     </row>
@@ -3041,7 +3045,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -3080,18 +3084,22 @@
       </c>
       <c r="Z22" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA22" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB22" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB22" s="2" t="inlineStr">
+        <is>
+          <t>132.0</t>
+        </is>
+      </c>
       <c r="AC22" s="2" t="inlineStr">
         <is>
-          <t>—/28</t>
+          <t>10/28</t>
         </is>
       </c>
     </row>
@@ -3321,7 +3329,7 @@
       </c>
       <c r="AC24" s="2" t="inlineStr">
         <is>
-          <t>15/28</t>
+          <t>17/28</t>
         </is>
       </c>
     </row>
@@ -3386,7 +3394,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3430,7 +3438,7 @@
       </c>
       <c r="AA25" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB25" s="2" t="inlineStr">
@@ -3440,7 +3448,7 @@
       </c>
       <c r="AC25" s="2" t="inlineStr">
         <is>
-          <t>9/28</t>
+          <t>10/28</t>
         </is>
       </c>
     </row>
@@ -3505,7 +3513,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3544,7 +3552,7 @@
       </c>
       <c r="Z26" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA26" s="2" t="inlineStr">
@@ -3559,7 +3567,7 @@
       </c>
       <c r="AC26" s="2" t="inlineStr">
         <is>
-          <t>20/28</t>
+          <t>21/28</t>
         </is>
       </c>
     </row>
@@ -3624,7 +3632,7 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -3663,14 +3671,14 @@
       </c>
       <c r="Z27" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA27" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA27" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB27" s="2" t="inlineStr">
         <is>
           <t>128.0</t>
@@ -3678,7 +3686,7 @@
       </c>
       <c r="AC27" s="2" t="inlineStr">
         <is>
-          <t>2/28</t>
+          <t>3/28</t>
         </is>
       </c>
     </row>
@@ -3797,7 +3805,7 @@
       </c>
       <c r="AC28" s="2" t="inlineStr">
         <is>
-          <t>15/28</t>
+          <t>17/28</t>
         </is>
       </c>
     </row>
@@ -3862,7 +3870,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -3916,7 +3924,7 @@
       </c>
       <c r="AC29" s="2" t="inlineStr">
         <is>
-          <t>11/28</t>
+          <t>15/28</t>
         </is>
       </c>
     </row>
@@ -4035,7 +4043,7 @@
       </c>
       <c r="AC30" s="2" t="inlineStr">
         <is>
-          <t>3/28</t>
+          <t>4/28</t>
         </is>
       </c>
     </row>
@@ -4100,7 +4108,7 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
@@ -4139,7 +4147,7 @@
       </c>
       <c r="Z31" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA31" s="2" t="inlineStr">
@@ -4154,7 +4162,7 @@
       </c>
       <c r="AC31" s="2" t="inlineStr">
         <is>
-          <t>8/28</t>
+          <t>9/28</t>
         </is>
       </c>
     </row>
@@ -4219,7 +4227,7 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
@@ -4273,7 +4281,7 @@
       </c>
       <c r="AC32" s="2" t="inlineStr">
         <is>
-          <t>21/28</t>
+          <t>23/28</t>
         </is>
       </c>
     </row>
@@ -4392,7 +4400,7 @@
       </c>
       <c r="AC33" s="2" t="inlineStr">
         <is>
-          <t>18/28</t>
+          <t>20/28</t>
         </is>
       </c>
     </row>
@@ -4511,7 +4519,7 @@
       </c>
       <c r="AC34" s="2" t="inlineStr">
         <is>
-          <t>10/28</t>
+          <t>13/28</t>
         </is>
       </c>
     </row>
@@ -4630,7 +4638,7 @@
       </c>
       <c r="AC35" s="2" t="inlineStr">
         <is>
-          <t>12/28</t>
+          <t>16/28</t>
         </is>
       </c>
     </row>
@@ -4691,7 +4699,7 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
@@ -4822,7 +4830,7 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
@@ -4876,7 +4884,7 @@
       </c>
       <c r="AC37" s="2" t="inlineStr">
         <is>
-          <t>3/28</t>
+          <t>4/28</t>
         </is>
       </c>
     </row>
@@ -4991,7 +4999,7 @@
       </c>
       <c r="AC38" s="2" t="inlineStr">
         <is>
-          <t>5/28</t>
+          <t>6/28</t>
         </is>
       </c>
     </row>
@@ -5110,7 +5118,7 @@
       </c>
       <c r="AC39" s="2" t="inlineStr">
         <is>
-          <t>22/28</t>
+          <t>24/28</t>
         </is>
       </c>
     </row>
@@ -5229,7 +5237,7 @@
       </c>
       <c r="AC40" s="2" t="inlineStr">
         <is>
-          <t>6/28</t>
+          <t>7/28</t>
         </is>
       </c>
     </row>
@@ -5294,7 +5302,7 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
@@ -5348,7 +5356,7 @@
       </c>
       <c r="AC41" s="2" t="inlineStr">
         <is>
-          <t>1/28</t>
+          <t>2/28</t>
         </is>
       </c>
     </row>
@@ -5413,7 +5421,7 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
@@ -5452,14 +5460,14 @@
       </c>
       <c r="Z42" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA42" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA42" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB42" s="2" t="inlineStr">
         <is>
           <t>136.0</t>
@@ -5467,7 +5475,7 @@
       </c>
       <c r="AC42" s="2" t="inlineStr">
         <is>
-          <t>15/28</t>
+          <t>17/28</t>
         </is>
       </c>
     </row>
@@ -5495,32 +5503,36 @@
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>12:55</t>
         </is>
       </c>
       <c r="I43" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>145分钟</t>
         </is>
       </c>
       <c r="J43" s="2" t="inlineStr"/>
       <c r="K43" s="2" t="inlineStr"/>
       <c r="L43" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M43" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M43" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N43" s="2" t="inlineStr">
         <is>
           <t>07:01</t>
@@ -5528,7 +5540,7 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>12:51</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
@@ -5552,17 +5564,17 @@
       </c>
       <c r="W43" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X43" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y43" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z43" s="2" t="inlineStr">
@@ -5572,17 +5584,17 @@
       </c>
       <c r="AA43" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB43" s="2" t="inlineStr">
         <is>
-          <t>135.0</t>
+          <t>140.0</t>
         </is>
       </c>
       <c r="AC43" s="2" t="inlineStr">
         <is>
-          <t>13/28</t>
+          <t>21/28</t>
         </is>
       </c>
     </row>
@@ -5610,32 +5622,36 @@
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>12:43</t>
         </is>
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>123分钟</t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr"/>
       <c r="K44" s="2" t="inlineStr"/>
       <c r="L44" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M44" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M44" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N44" s="2" t="inlineStr">
         <is>
           <t>07:21</t>
@@ -5643,7 +5659,7 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>12:41</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
@@ -5667,17 +5683,17 @@
       </c>
       <c r="W44" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X44" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y44" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z44" s="2" t="inlineStr">
@@ -5687,13 +5703,17 @@
       </c>
       <c r="AA44" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB44" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB44" s="2" t="inlineStr">
+        <is>
+          <t>123.0</t>
+        </is>
+      </c>
       <c r="AC44" s="2" t="inlineStr">
         <is>
-          <t>—/28</t>
+          <t>1/28</t>
         </is>
       </c>
     </row>
@@ -5721,32 +5741,36 @@
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G45" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H45" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>12:57</t>
         </is>
       </c>
       <c r="I45" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>132分钟</t>
         </is>
       </c>
       <c r="J45" s="2" t="inlineStr"/>
       <c r="K45" s="2" t="inlineStr"/>
       <c r="L45" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M45" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M45" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N45" s="2" t="inlineStr">
         <is>
           <t>06:51</t>
@@ -5754,7 +5778,7 @@
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
@@ -5778,17 +5802,17 @@
       </c>
       <c r="W45" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X45" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y45" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z45" s="2" t="inlineStr">
@@ -5798,17 +5822,17 @@
       </c>
       <c r="AA45" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB45" s="2" t="inlineStr">
         <is>
-          <t>135.0</t>
+          <t>133.5</t>
         </is>
       </c>
       <c r="AC45" s="2" t="inlineStr">
         <is>
-          <t>13/28</t>
+          <t>14/28</t>
         </is>
       </c>
     </row>
@@ -5836,32 +5860,36 @@
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G46" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>13:09</t>
         </is>
       </c>
       <c r="I46" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>131分钟</t>
         </is>
       </c>
       <c r="J46" s="2" t="inlineStr"/>
       <c r="K46" s="2" t="inlineStr"/>
       <c r="L46" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M46" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M46" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N46" s="2" t="inlineStr">
         <is>
           <t>07:21</t>
@@ -5869,7 +5897,7 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
@@ -5893,29 +5921,29 @@
       </c>
       <c r="W46" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X46" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y46" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z46" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA46" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA46" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB46" s="2" t="inlineStr">
         <is>
           <t>131.0</t>
@@ -5923,7 +5951,7 @@
       </c>
       <c r="AC46" s="2" t="inlineStr">
         <is>
-          <t>7/28</t>
+          <t>8/28</t>
         </is>
       </c>
     </row>
@@ -5951,32 +5979,36 @@
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G47" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H47" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>13:12</t>
         </is>
       </c>
       <c r="I47" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>127分钟</t>
         </is>
       </c>
       <c r="J47" s="2" t="inlineStr"/>
       <c r="K47" s="2" t="inlineStr"/>
       <c r="L47" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M47" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="M47" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="N47" s="2" t="inlineStr">
         <is>
           <t>07:21</t>
@@ -5984,7 +6016,7 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:11</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
@@ -6008,17 +6040,17 @@
       </c>
       <c r="W47" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X47" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y47" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z47" s="2" t="inlineStr">
@@ -6028,17 +6060,17 @@
       </c>
       <c r="AA47" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB47" s="2" t="inlineStr">
         <is>
-          <t>137.0</t>
+          <t>132.0</t>
         </is>
       </c>
       <c r="AC47" s="2" t="inlineStr">
         <is>
-          <t>19/28</t>
+          <t>10/28</t>
         </is>
       </c>
     </row>
@@ -6066,32 +6098,36 @@
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G48" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H48" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>13:28</t>
         </is>
       </c>
       <c r="I48" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>132分钟</t>
         </is>
       </c>
       <c r="J48" s="2" t="inlineStr"/>
       <c r="K48" s="2" t="inlineStr"/>
       <c r="L48" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M48" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M48" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N48" s="2" t="inlineStr">
         <is>
           <t>06:51</t>
@@ -6099,7 +6135,7 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
@@ -6123,17 +6159,17 @@
       </c>
       <c r="W48" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X48" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y48" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z48" s="2" t="inlineStr">
@@ -6143,7 +6179,7 @@
       </c>
       <c r="AA48" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB48" s="2" t="inlineStr">
@@ -6153,7 +6189,7 @@
       </c>
       <c r="AC48" s="2" t="inlineStr">
         <is>
-          <t>9/28</t>
+          <t>10/28</t>
         </is>
       </c>
     </row>
@@ -6181,32 +6217,36 @@
       </c>
       <c r="F49" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G49" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H49" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>13:42</t>
         </is>
       </c>
       <c r="I49" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>132分钟</t>
         </is>
       </c>
       <c r="J49" s="2" t="inlineStr"/>
       <c r="K49" s="2" t="inlineStr"/>
       <c r="L49" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M49" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M49" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N49" s="2" t="inlineStr">
         <is>
           <t>07:41</t>
@@ -6214,7 +6254,7 @@
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
@@ -6238,33 +6278,37 @@
       </c>
       <c r="W49" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X49" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y49" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z49" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA49" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB49" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB49" s="2" t="inlineStr">
+        <is>
+          <t>132.0</t>
+        </is>
+      </c>
       <c r="AC49" s="2" t="inlineStr">
         <is>
-          <t>—/28</t>
+          <t>10/28</t>
         </is>
       </c>
     </row>
@@ -6292,32 +6336,36 @@
       </c>
       <c r="F50" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G50" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H50" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>13:42</t>
         </is>
       </c>
       <c r="I50" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>128分钟</t>
         </is>
       </c>
       <c r="J50" s="2" t="inlineStr"/>
       <c r="K50" s="2" t="inlineStr"/>
       <c r="L50" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M50" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M50" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N50" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -6325,7 +6373,7 @@
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
@@ -6349,29 +6397,29 @@
       </c>
       <c r="W50" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X50" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y50" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z50" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA50" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA50" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB50" s="2" t="inlineStr">
         <is>
           <t>128.0</t>
@@ -6379,7 +6427,7 @@
       </c>
       <c r="AC50" s="2" t="inlineStr">
         <is>
-          <t>2/28</t>
+          <t>3/28</t>
         </is>
       </c>
     </row>
@@ -6440,7 +6488,7 @@
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P51" s="2" t="inlineStr">
@@ -6479,7 +6527,7 @@
       </c>
       <c r="Z51" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA51" s="2" t="inlineStr">
@@ -6494,7 +6542,7 @@
       </c>
       <c r="AC51" s="2" t="inlineStr">
         <is>
-          <t>20/28</t>
+          <t>21/28</t>
         </is>
       </c>
     </row>
@@ -6555,7 +6603,7 @@
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
@@ -6609,7 +6657,7 @@
       </c>
       <c r="AC52" s="2" t="inlineStr">
         <is>
-          <t>11/28</t>
+          <t>15/28</t>
         </is>
       </c>
     </row>
@@ -6670,7 +6718,7 @@
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P53" s="2" t="inlineStr">
@@ -6724,7 +6772,7 @@
       </c>
       <c r="AC53" s="2" t="inlineStr">
         <is>
-          <t>21/28</t>
+          <t>23/28</t>
         </is>
       </c>
     </row>
@@ -6785,7 +6833,7 @@
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P54" s="2" t="inlineStr">
@@ -6824,7 +6872,7 @@
       </c>
       <c r="Z54" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA54" s="2" t="inlineStr">
@@ -6839,7 +6887,7 @@
       </c>
       <c r="AC54" s="2" t="inlineStr">
         <is>
-          <t>8/28</t>
+          <t>9/28</t>
         </is>
       </c>
     </row>
@@ -6900,7 +6948,7 @@
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P55" s="2" t="inlineStr">
@@ -7011,7 +7059,7 @@
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P56" s="2" t="inlineStr">
@@ -7065,7 +7113,7 @@
       </c>
       <c r="AC56" s="2" t="inlineStr">
         <is>
-          <t>3/28</t>
+          <t>4/28</t>
         </is>
       </c>
     </row>
@@ -7126,7 +7174,7 @@
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P57" s="2" t="inlineStr">
@@ -7237,7 +7285,7 @@
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P58" s="2" t="inlineStr">
@@ -7291,7 +7339,7 @@
       </c>
       <c r="AC58" s="2" t="inlineStr">
         <is>
-          <t>1/28</t>
+          <t>2/28</t>
         </is>
       </c>
     </row>
@@ -7352,7 +7400,7 @@
       </c>
       <c r="O59" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P59" s="2" t="inlineStr">
@@ -7463,7 +7511,7 @@
       </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P60" s="2" t="inlineStr">
@@ -7507,17 +7555,707 @@
       </c>
       <c r="AA60" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB60" s="2" t="inlineStr">
+        <is>
+          <t>133.5</t>
+        </is>
+      </c>
+      <c r="AC60" s="2" t="inlineStr">
+        <is>
+          <t>14/28</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="2" t="inlineStr"/>
+      <c r="B61" s="2" t="inlineStr">
+        <is>
+          <t>沪A02891D</t>
+        </is>
+      </c>
+      <c r="C61" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D61" s="2" t="inlineStr">
+        <is>
+          <t>13:25</t>
+        </is>
+      </c>
+      <c r="E61" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F61" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G61" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H61" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I61" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J61" s="2" t="inlineStr"/>
+      <c r="K61" s="2" t="inlineStr"/>
+      <c r="L61" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M61" s="2" t="inlineStr"/>
+      <c r="N61" s="2" t="inlineStr">
+        <is>
+          <t>07:11</t>
+        </is>
+      </c>
+      <c r="O61" s="2" t="inlineStr">
+        <is>
+          <t>13:21</t>
+        </is>
+      </c>
+      <c r="P61" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q61" s="2" t="inlineStr"/>
+      <c r="R61" s="2" t="inlineStr"/>
+      <c r="S61" s="2" t="inlineStr"/>
+      <c r="T61" s="2" t="inlineStr"/>
+      <c r="U61" s="2" t="inlineStr">
+        <is>
+          <t>13:25</t>
+        </is>
+      </c>
+      <c r="V61" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W61" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X61" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y61" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z61" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA61" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB61" s="2" t="inlineStr">
+        <is>
+          <t>136.0</t>
+        </is>
+      </c>
+      <c r="AC61" s="2" t="inlineStr">
+        <is>
+          <t>17/28</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="2" t="inlineStr"/>
+      <c r="B62" s="2" t="inlineStr">
+        <is>
+          <t>沪A67672D</t>
+        </is>
+      </c>
+      <c r="C62" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D62" s="2" t="inlineStr">
+        <is>
+          <t>13:45</t>
+        </is>
+      </c>
+      <c r="E62" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F62" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G62" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H62" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I62" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J62" s="2" t="inlineStr"/>
+      <c r="K62" s="2" t="inlineStr"/>
+      <c r="L62" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M62" s="2" t="inlineStr"/>
+      <c r="N62" s="2" t="inlineStr">
+        <is>
+          <t>07:41</t>
+        </is>
+      </c>
+      <c r="O62" s="2" t="inlineStr">
+        <is>
+          <t>13:21</t>
+        </is>
+      </c>
+      <c r="P62" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q62" s="2" t="inlineStr"/>
+      <c r="R62" s="2" t="inlineStr"/>
+      <c r="S62" s="2" t="inlineStr"/>
+      <c r="T62" s="2" t="inlineStr"/>
+      <c r="U62" s="2" t="inlineStr">
+        <is>
+          <t>13:45</t>
+        </is>
+      </c>
+      <c r="V62" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W62" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X62" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y62" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z62" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA62" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB60" s="2" t="inlineStr">
-        <is>
-          <t>135.0</t>
-        </is>
-      </c>
-      <c r="AC60" s="2" t="inlineStr">
-        <is>
-          <t>13/28</t>
+      <c r="AB62" s="2" t="inlineStr">
+        <is>
+          <t>132.0</t>
+        </is>
+      </c>
+      <c r="AC62" s="2" t="inlineStr">
+        <is>
+          <t>10/28</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="2" t="inlineStr"/>
+      <c r="B63" s="2" t="inlineStr">
+        <is>
+          <t>沪A90275D</t>
+        </is>
+      </c>
+      <c r="C63" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D63" s="2" t="inlineStr">
+        <is>
+          <t>13:45</t>
+        </is>
+      </c>
+      <c r="E63" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F63" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G63" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H63" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I63" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J63" s="2" t="inlineStr"/>
+      <c r="K63" s="2" t="inlineStr"/>
+      <c r="L63" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M63" s="2" t="inlineStr"/>
+      <c r="N63" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="O63" s="2" t="inlineStr">
+        <is>
+          <t>13:21</t>
+        </is>
+      </c>
+      <c r="P63" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q63" s="2" t="inlineStr"/>
+      <c r="R63" s="2" t="inlineStr"/>
+      <c r="S63" s="2" t="inlineStr"/>
+      <c r="T63" s="2" t="inlineStr"/>
+      <c r="U63" s="2" t="inlineStr">
+        <is>
+          <t>13:45</t>
+        </is>
+      </c>
+      <c r="V63" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W63" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X63" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y63" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z63" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA63" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB63" s="2" t="inlineStr">
+        <is>
+          <t>131.0</t>
+        </is>
+      </c>
+      <c r="AC63" s="2" t="inlineStr">
+        <is>
+          <t>8/28</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="2" t="inlineStr"/>
+      <c r="B64" s="2" t="inlineStr">
+        <is>
+          <t>沪A15330A</t>
+        </is>
+      </c>
+      <c r="C64" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D64" s="2" t="inlineStr">
+        <is>
+          <t>14:05</t>
+        </is>
+      </c>
+      <c r="E64" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F64" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G64" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H64" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I64" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J64" s="2" t="inlineStr"/>
+      <c r="K64" s="2" t="inlineStr"/>
+      <c r="L64" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M64" s="2" t="inlineStr"/>
+      <c r="N64" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O64" s="2" t="inlineStr">
+        <is>
+          <t>13:21</t>
+        </is>
+      </c>
+      <c r="P64" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q64" s="2" t="inlineStr"/>
+      <c r="R64" s="2" t="inlineStr"/>
+      <c r="S64" s="2" t="inlineStr"/>
+      <c r="T64" s="2" t="inlineStr"/>
+      <c r="U64" s="2" t="inlineStr">
+        <is>
+          <t>14:05</t>
+        </is>
+      </c>
+      <c r="V64" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W64" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X64" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y64" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z64" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA64" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB64" s="2" t="inlineStr">
+        <is>
+          <t>128.0</t>
+        </is>
+      </c>
+      <c r="AC64" s="2" t="inlineStr">
+        <is>
+          <t>3/28</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="2" t="inlineStr"/>
+      <c r="B65" s="2" t="inlineStr">
+        <is>
+          <t>沪A57601A</t>
+        </is>
+      </c>
+      <c r="C65" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D65" s="2" t="inlineStr">
+        <is>
+          <t>14:10</t>
+        </is>
+      </c>
+      <c r="E65" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F65" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G65" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H65" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I65" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J65" s="2" t="inlineStr"/>
+      <c r="K65" s="2" t="inlineStr"/>
+      <c r="L65" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M65" s="2" t="inlineStr"/>
+      <c r="N65" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O65" s="2" t="inlineStr">
+        <is>
+          <t>13:21</t>
+        </is>
+      </c>
+      <c r="P65" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q65" s="2" t="inlineStr"/>
+      <c r="R65" s="2" t="inlineStr"/>
+      <c r="S65" s="2" t="inlineStr"/>
+      <c r="T65" s="2" t="inlineStr"/>
+      <c r="U65" s="2" t="inlineStr">
+        <is>
+          <t>14:10</t>
+        </is>
+      </c>
+      <c r="V65" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W65" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X65" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y65" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z65" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA65" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB65" s="2" t="inlineStr">
+        <is>
+          <t>140.0</t>
+        </is>
+      </c>
+      <c r="AC65" s="2" t="inlineStr">
+        <is>
+          <t>21/28</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="2" t="inlineStr"/>
+      <c r="B66" s="2" t="inlineStr">
+        <is>
+          <t>沪A95621D</t>
+        </is>
+      </c>
+      <c r="C66" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D66" s="2" t="inlineStr">
+        <is>
+          <t>14:35</t>
+        </is>
+      </c>
+      <c r="E66" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F66" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G66" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H66" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I66" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J66" s="2" t="inlineStr"/>
+      <c r="K66" s="2" t="inlineStr"/>
+      <c r="L66" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M66" s="2" t="inlineStr"/>
+      <c r="N66" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O66" s="2" t="inlineStr">
+        <is>
+          <t>13:21</t>
+        </is>
+      </c>
+      <c r="P66" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q66" s="2" t="inlineStr"/>
+      <c r="R66" s="2" t="inlineStr"/>
+      <c r="S66" s="2" t="inlineStr"/>
+      <c r="T66" s="2" t="inlineStr"/>
+      <c r="U66" s="2" t="inlineStr">
+        <is>
+          <t>14:35</t>
+        </is>
+      </c>
+      <c r="V66" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W66" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X66" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y66" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z66" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA66" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB66" s="2" t="inlineStr">
+        <is>
+          <t>131.5</t>
+        </is>
+      </c>
+      <c r="AC66" s="2" t="inlineStr">
+        <is>
+          <t>9/28</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-10-31-浦东35路.xlsx
+++ b/data/export/2026-10-31-浦东35路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC66"/>
+  <dimension ref="A1:AC71"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -669,7 +669,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -718,12 +718,12 @@
       </c>
       <c r="AB2" s="2" t="inlineStr">
         <is>
-          <t>128.0</t>
+          <t>127.7</t>
         </is>
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>3/28</t>
+          <t>4/28</t>
         </is>
       </c>
     </row>
@@ -788,7 +788,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>10:51</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -827,14 +827,14 @@
       </c>
       <c r="Z3" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA3" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA3" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB3" s="2" t="inlineStr">
         <is>
           <t>136.0</t>
@@ -842,7 +842,7 @@
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>17/28</t>
+          <t>18/28</t>
         </is>
       </c>
     </row>
@@ -961,7 +961,7 @@
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>4/28</t>
+          <t>5/28</t>
         </is>
       </c>
     </row>
@@ -1026,7 +1026,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1070,17 +1070,17 @@
       </c>
       <c r="AA5" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB5" s="2" t="inlineStr">
         <is>
-          <t>140.5</t>
+          <t>139.7</t>
         </is>
       </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>23/28</t>
+          <t>22/28</t>
         </is>
       </c>
     </row>
@@ -1145,7 +1145,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1189,17 +1189,17 @@
       </c>
       <c r="AA6" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB6" s="2" t="inlineStr">
         <is>
-          <t>131.5</t>
+          <t>130.0</t>
         </is>
       </c>
       <c r="AC6" s="2" t="inlineStr">
         <is>
-          <t>9/28</t>
+          <t>7/28</t>
         </is>
       </c>
     </row>
@@ -1383,7 +1383,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>11:31</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1422,14 +1422,14 @@
       </c>
       <c r="Z8" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA8" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA8" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB8" s="2" t="inlineStr">
         <is>
           <t>136.5</t>
@@ -1437,7 +1437,7 @@
       </c>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>20/28</t>
+          <t>21/28</t>
         </is>
       </c>
     </row>
@@ -1502,7 +1502,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1546,17 +1546,17 @@
       </c>
       <c r="AA9" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB9" s="2" t="inlineStr">
         <is>
-          <t>128.5</t>
+          <t>126.7</t>
         </is>
       </c>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>4/28</t>
+          <t>2/28</t>
         </is>
       </c>
     </row>
@@ -1621,7 +1621,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>11:41</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1660,14 +1660,14 @@
       </c>
       <c r="Z10" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA10" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA10" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB10" s="2" t="inlineStr">
         <is>
           <t>133.0</t>
@@ -1675,7 +1675,7 @@
       </c>
       <c r="AC10" s="2" t="inlineStr">
         <is>
-          <t>13/28</t>
+          <t>14/28</t>
         </is>
       </c>
     </row>
@@ -1794,7 +1794,7 @@
       </c>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>7/28</t>
+          <t>9/28</t>
         </is>
       </c>
     </row>
@@ -1913,7 +1913,7 @@
       </c>
       <c r="AC12" s="2" t="inlineStr">
         <is>
-          <t>6/28</t>
+          <t>7/28</t>
         </is>
       </c>
     </row>
@@ -1974,7 +1974,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -2029,7 +2029,7 @@
       </c>
       <c r="Z13" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA13" s="2" t="inlineStr">
@@ -2220,7 +2220,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2274,7 +2274,7 @@
       </c>
       <c r="AC15" s="2" t="inlineStr">
         <is>
-          <t>2/28</t>
+          <t>3/28</t>
         </is>
       </c>
     </row>
@@ -2339,7 +2339,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2393,7 +2393,7 @@
       </c>
       <c r="AC16" s="2" t="inlineStr">
         <is>
-          <t>17/28</t>
+          <t>18/28</t>
         </is>
       </c>
     </row>
@@ -2512,7 +2512,7 @@
       </c>
       <c r="AC17" s="2" t="inlineStr">
         <is>
-          <t>21/28</t>
+          <t>23/28</t>
         </is>
       </c>
     </row>
@@ -2577,7 +2577,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2631,7 +2631,7 @@
       </c>
       <c r="AC18" s="2" t="inlineStr">
         <is>
-          <t>14/28</t>
+          <t>15/28</t>
         </is>
       </c>
     </row>
@@ -2865,7 +2865,7 @@
       </c>
       <c r="AC20" s="2" t="inlineStr">
         <is>
-          <t>10/28</t>
+          <t>11/28</t>
         </is>
       </c>
     </row>
@@ -2930,7 +2930,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -2984,7 +2984,7 @@
       </c>
       <c r="AC21" s="2" t="inlineStr">
         <is>
-          <t>8/28</t>
+          <t>10/28</t>
         </is>
       </c>
     </row>
@@ -3045,7 +3045,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -3099,7 +3099,7 @@
       </c>
       <c r="AC22" s="2" t="inlineStr">
         <is>
-          <t>10/28</t>
+          <t>11/28</t>
         </is>
       </c>
     </row>
@@ -3160,7 +3160,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>08:01</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -3199,7 +3199,7 @@
       </c>
       <c r="Z23" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AA23" s="2" t="inlineStr">
@@ -3329,7 +3329,7 @@
       </c>
       <c r="AC24" s="2" t="inlineStr">
         <is>
-          <t>17/28</t>
+          <t>18/28</t>
         </is>
       </c>
     </row>
@@ -3448,7 +3448,7 @@
       </c>
       <c r="AC25" s="2" t="inlineStr">
         <is>
-          <t>10/28</t>
+          <t>11/28</t>
         </is>
       </c>
     </row>
@@ -3513,7 +3513,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3557,17 +3557,17 @@
       </c>
       <c r="AA26" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB26" s="2" t="inlineStr">
         <is>
-          <t>140.0</t>
+          <t>135.0</t>
         </is>
       </c>
       <c r="AC26" s="2" t="inlineStr">
         <is>
-          <t>21/28</t>
+          <t>17/28</t>
         </is>
       </c>
     </row>
@@ -3632,7 +3632,7 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -3681,12 +3681,12 @@
       </c>
       <c r="AB27" s="2" t="inlineStr">
         <is>
-          <t>128.0</t>
+          <t>127.7</t>
         </is>
       </c>
       <c r="AC27" s="2" t="inlineStr">
         <is>
-          <t>3/28</t>
+          <t>4/28</t>
         </is>
       </c>
     </row>
@@ -3751,7 +3751,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>10:51</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -3790,14 +3790,14 @@
       </c>
       <c r="Z28" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA28" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA28" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB28" s="2" t="inlineStr">
         <is>
           <t>136.0</t>
@@ -3805,7 +3805,7 @@
       </c>
       <c r="AC28" s="2" t="inlineStr">
         <is>
-          <t>17/28</t>
+          <t>18/28</t>
         </is>
       </c>
     </row>
@@ -3870,7 +3870,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>13:51</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -3914,17 +3914,17 @@
       </c>
       <c r="AA29" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB29" s="2" t="inlineStr">
         <is>
-          <t>134.0</t>
+          <t>129.5</t>
         </is>
       </c>
       <c r="AC29" s="2" t="inlineStr">
         <is>
-          <t>15/28</t>
+          <t>6/28</t>
         </is>
       </c>
     </row>
@@ -4043,7 +4043,7 @@
       </c>
       <c r="AC30" s="2" t="inlineStr">
         <is>
-          <t>4/28</t>
+          <t>5/28</t>
         </is>
       </c>
     </row>
@@ -4108,7 +4108,7 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
@@ -4152,17 +4152,17 @@
       </c>
       <c r="AA31" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB31" s="2" t="inlineStr">
         <is>
-          <t>131.5</t>
+          <t>130.0</t>
         </is>
       </c>
       <c r="AC31" s="2" t="inlineStr">
         <is>
-          <t>9/28</t>
+          <t>7/28</t>
         </is>
       </c>
     </row>
@@ -4227,7 +4227,7 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
@@ -4271,17 +4271,17 @@
       </c>
       <c r="AA32" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB32" s="2" t="inlineStr">
         <is>
-          <t>140.5</t>
+          <t>139.7</t>
         </is>
       </c>
       <c r="AC32" s="2" t="inlineStr">
         <is>
-          <t>23/28</t>
+          <t>22/28</t>
         </is>
       </c>
     </row>
@@ -4346,7 +4346,7 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>11:31</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
@@ -4385,14 +4385,14 @@
       </c>
       <c r="Z33" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA33" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA33" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB33" s="2" t="inlineStr">
         <is>
           <t>136.5</t>
@@ -4400,7 +4400,7 @@
       </c>
       <c r="AC33" s="2" t="inlineStr">
         <is>
-          <t>20/28</t>
+          <t>21/28</t>
         </is>
       </c>
     </row>
@@ -4465,7 +4465,7 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>11:41</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
@@ -4504,14 +4504,14 @@
       </c>
       <c r="Z34" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA34" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA34" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB34" s="2" t="inlineStr">
         <is>
           <t>133.0</t>
@@ -4519,7 +4519,7 @@
       </c>
       <c r="AC34" s="2" t="inlineStr">
         <is>
-          <t>13/28</t>
+          <t>14/28</t>
         </is>
       </c>
     </row>
@@ -4699,7 +4699,7 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
@@ -4830,7 +4830,7 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
@@ -4874,17 +4874,17 @@
       </c>
       <c r="AA37" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB37" s="2" t="inlineStr">
         <is>
-          <t>128.5</t>
+          <t>126.7</t>
         </is>
       </c>
       <c r="AC37" s="2" t="inlineStr">
         <is>
-          <t>4/28</t>
+          <t>2/28</t>
         </is>
       </c>
     </row>
@@ -4999,7 +4999,7 @@
       </c>
       <c r="AC38" s="2" t="inlineStr">
         <is>
-          <t>6/28</t>
+          <t>7/28</t>
         </is>
       </c>
     </row>
@@ -5237,7 +5237,7 @@
       </c>
       <c r="AC40" s="2" t="inlineStr">
         <is>
-          <t>7/28</t>
+          <t>9/28</t>
         </is>
       </c>
     </row>
@@ -5302,7 +5302,7 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
@@ -5356,7 +5356,7 @@
       </c>
       <c r="AC41" s="2" t="inlineStr">
         <is>
-          <t>2/28</t>
+          <t>3/28</t>
         </is>
       </c>
     </row>
@@ -5421,7 +5421,7 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
@@ -5475,7 +5475,7 @@
       </c>
       <c r="AC42" s="2" t="inlineStr">
         <is>
-          <t>17/28</t>
+          <t>18/28</t>
         </is>
       </c>
     </row>
@@ -5594,7 +5594,7 @@
       </c>
       <c r="AC43" s="2" t="inlineStr">
         <is>
-          <t>21/28</t>
+          <t>23/28</t>
         </is>
       </c>
     </row>
@@ -5778,7 +5778,7 @@
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
@@ -5832,7 +5832,7 @@
       </c>
       <c r="AC45" s="2" t="inlineStr">
         <is>
-          <t>14/28</t>
+          <t>15/28</t>
         </is>
       </c>
     </row>
@@ -5897,7 +5897,7 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
@@ -5951,7 +5951,7 @@
       </c>
       <c r="AC46" s="2" t="inlineStr">
         <is>
-          <t>8/28</t>
+          <t>10/28</t>
         </is>
       </c>
     </row>
@@ -6070,7 +6070,7 @@
       </c>
       <c r="AC47" s="2" t="inlineStr">
         <is>
-          <t>10/28</t>
+          <t>11/28</t>
         </is>
       </c>
     </row>
@@ -6189,7 +6189,7 @@
       </c>
       <c r="AC48" s="2" t="inlineStr">
         <is>
-          <t>10/28</t>
+          <t>11/28</t>
         </is>
       </c>
     </row>
@@ -6239,12 +6239,12 @@
       <c r="K49" s="2" t="inlineStr"/>
       <c r="L49" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
         </is>
       </c>
       <c r="M49" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="N49" s="2" t="inlineStr">
@@ -6254,7 +6254,7 @@
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
@@ -6308,7 +6308,7 @@
       </c>
       <c r="AC49" s="2" t="inlineStr">
         <is>
-          <t>10/28</t>
+          <t>11/28</t>
         </is>
       </c>
     </row>
@@ -6346,12 +6346,12 @@
       </c>
       <c r="H50" s="2" t="inlineStr">
         <is>
-          <t>13:42</t>
+          <t>13:41</t>
         </is>
       </c>
       <c r="I50" s="2" t="inlineStr">
         <is>
-          <t>128分钟</t>
+          <t>127分钟</t>
         </is>
       </c>
       <c r="J50" s="2" t="inlineStr"/>
@@ -6373,7 +6373,7 @@
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
@@ -6422,12 +6422,12 @@
       </c>
       <c r="AB50" s="2" t="inlineStr">
         <is>
-          <t>128.0</t>
+          <t>127.7</t>
         </is>
       </c>
       <c r="AC50" s="2" t="inlineStr">
         <is>
-          <t>3/28</t>
+          <t>4/28</t>
         </is>
       </c>
     </row>
@@ -6455,32 +6455,36 @@
       </c>
       <c r="F51" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G51" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H51" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="I51" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>130分钟</t>
         </is>
       </c>
       <c r="J51" s="2" t="inlineStr"/>
       <c r="K51" s="2" t="inlineStr"/>
       <c r="L51" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M51" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M51" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N51" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -6488,7 +6492,7 @@
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P51" s="2" t="inlineStr">
@@ -6512,17 +6516,17 @@
       </c>
       <c r="W51" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X51" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y51" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z51" s="2" t="inlineStr">
@@ -6532,17 +6536,17 @@
       </c>
       <c r="AA51" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB51" s="2" t="inlineStr">
         <is>
-          <t>140.0</t>
+          <t>135.0</t>
         </is>
       </c>
       <c r="AC51" s="2" t="inlineStr">
         <is>
-          <t>21/28</t>
+          <t>17/28</t>
         </is>
       </c>
     </row>
@@ -6570,32 +6574,36 @@
       </c>
       <c r="F52" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G52" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H52" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>13:55</t>
         </is>
       </c>
       <c r="I52" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>125分钟</t>
         </is>
       </c>
       <c r="J52" s="2" t="inlineStr"/>
       <c r="K52" s="2" t="inlineStr"/>
       <c r="L52" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M52" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M52" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N52" s="2" t="inlineStr">
         <is>
           <t>07:01</t>
@@ -6603,7 +6611,7 @@
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>13:51</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
@@ -6627,17 +6635,17 @@
       </c>
       <c r="W52" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X52" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y52" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z52" s="2" t="inlineStr">
@@ -6647,17 +6655,17 @@
       </c>
       <c r="AA52" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB52" s="2" t="inlineStr">
         <is>
-          <t>134.0</t>
+          <t>129.5</t>
         </is>
       </c>
       <c r="AC52" s="2" t="inlineStr">
         <is>
-          <t>15/28</t>
+          <t>6/28</t>
         </is>
       </c>
     </row>
@@ -6685,32 +6693,36 @@
       </c>
       <c r="F53" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G53" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H53" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>14:23</t>
         </is>
       </c>
       <c r="I53" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>138分钟</t>
         </is>
       </c>
       <c r="J53" s="2" t="inlineStr"/>
       <c r="K53" s="2" t="inlineStr"/>
       <c r="L53" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M53" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M53" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N53" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -6718,7 +6730,7 @@
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P53" s="2" t="inlineStr">
@@ -6742,17 +6754,17 @@
       </c>
       <c r="W53" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X53" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y53" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z53" s="2" t="inlineStr">
@@ -6762,17 +6774,17 @@
       </c>
       <c r="AA53" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB53" s="2" t="inlineStr">
         <is>
-          <t>140.5</t>
+          <t>139.7</t>
         </is>
       </c>
       <c r="AC53" s="2" t="inlineStr">
         <is>
-          <t>23/28</t>
+          <t>22/28</t>
         </is>
       </c>
     </row>
@@ -6800,32 +6812,36 @@
       </c>
       <c r="F54" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G54" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H54" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="I54" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>127分钟</t>
         </is>
       </c>
       <c r="J54" s="2" t="inlineStr"/>
       <c r="K54" s="2" t="inlineStr"/>
       <c r="L54" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M54" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="M54" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="N54" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -6833,7 +6849,7 @@
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P54" s="2" t="inlineStr">
@@ -6857,17 +6873,17 @@
       </c>
       <c r="W54" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X54" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y54" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z54" s="2" t="inlineStr">
@@ -6877,17 +6893,17 @@
       </c>
       <c r="AA54" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB54" s="2" t="inlineStr">
         <is>
-          <t>131.5</t>
+          <t>130.0</t>
         </is>
       </c>
       <c r="AC54" s="2" t="inlineStr">
         <is>
-          <t>9/28</t>
+          <t>7/28</t>
         </is>
       </c>
     </row>
@@ -6915,12 +6931,12 @@
       </c>
       <c r="F55" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>疑似区间车</t>
         </is>
       </c>
       <c r="G55" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>原方向在全程34%处后消失；随后反向物理轨迹由seq38推进至seq49，推进11站，达到≥2站确认条件</t>
         </is>
       </c>
       <c r="H55" s="2" t="inlineStr">
@@ -6948,7 +6964,7 @@
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P55" s="2" t="inlineStr">
@@ -6956,10 +6972,26 @@
           <t>SHMAAS</t>
         </is>
       </c>
-      <c r="Q55" s="2" t="inlineStr"/>
-      <c r="R55" s="2" t="inlineStr"/>
-      <c r="S55" s="2" t="inlineStr"/>
-      <c r="T55" s="2" t="inlineStr"/>
+      <c r="Q55" s="2" t="inlineStr">
+        <is>
+          <t>物理seq23（站名待映射）</t>
+        </is>
+      </c>
+      <c r="R55" s="2" t="inlineStr">
+        <is>
+          <t>13:29</t>
+        </is>
+      </c>
+      <c r="S55" s="2" t="inlineStr">
+        <is>
+          <t>13:35</t>
+        </is>
+      </c>
+      <c r="T55" s="2" t="inlineStr">
+        <is>
+          <t>折返点按重建物理位置seq23映射；到达按末次同向ETA估算；折返发车结合首次反向物理观测取区间中点，约±6分钟；反向位置物理seq38（站名待映射） ETA 10分钟参与校验</t>
+        </is>
+      </c>
       <c r="U55" s="2" t="inlineStr">
         <is>
           <t>12:28</t>
@@ -7026,32 +7058,36 @@
       </c>
       <c r="F56" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G56" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H56" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>14:33</t>
         </is>
       </c>
       <c r="I56" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>123分钟</t>
         </is>
       </c>
       <c r="J56" s="2" t="inlineStr"/>
       <c r="K56" s="2" t="inlineStr"/>
       <c r="L56" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M56" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M56" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N56" s="2" t="inlineStr">
         <is>
           <t>06:21</t>
@@ -7059,7 +7095,7 @@
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P56" s="2" t="inlineStr">
@@ -7083,17 +7119,17 @@
       </c>
       <c r="W56" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X56" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y56" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z56" s="2" t="inlineStr">
@@ -7103,17 +7139,17 @@
       </c>
       <c r="AA56" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB56" s="2" t="inlineStr">
         <is>
-          <t>128.5</t>
+          <t>126.7</t>
         </is>
       </c>
       <c r="AC56" s="2" t="inlineStr">
         <is>
-          <t>4/28</t>
+          <t>2/28</t>
         </is>
       </c>
     </row>
@@ -7174,7 +7210,7 @@
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P57" s="2" t="inlineStr">
@@ -7213,7 +7249,7 @@
       </c>
       <c r="Z57" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA57" s="2" t="inlineStr">
@@ -7285,7 +7321,7 @@
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P58" s="2" t="inlineStr">
@@ -7339,7 +7375,7 @@
       </c>
       <c r="AC58" s="2" t="inlineStr">
         <is>
-          <t>2/28</t>
+          <t>3/28</t>
         </is>
       </c>
     </row>
@@ -7400,7 +7436,7 @@
       </c>
       <c r="O59" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P59" s="2" t="inlineStr">
@@ -7511,7 +7547,7 @@
       </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P60" s="2" t="inlineStr">
@@ -7565,7 +7601,7 @@
       </c>
       <c r="AC60" s="2" t="inlineStr">
         <is>
-          <t>14/28</t>
+          <t>15/28</t>
         </is>
       </c>
     </row>
@@ -7626,7 +7662,7 @@
       </c>
       <c r="O61" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P61" s="2" t="inlineStr">
@@ -7680,7 +7716,7 @@
       </c>
       <c r="AC61" s="2" t="inlineStr">
         <is>
-          <t>17/28</t>
+          <t>18/28</t>
         </is>
       </c>
     </row>
@@ -7741,7 +7777,7 @@
       </c>
       <c r="O62" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P62" s="2" t="inlineStr">
@@ -7795,7 +7831,7 @@
       </c>
       <c r="AC62" s="2" t="inlineStr">
         <is>
-          <t>10/28</t>
+          <t>11/28</t>
         </is>
       </c>
     </row>
@@ -7856,7 +7892,7 @@
       </c>
       <c r="O63" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P63" s="2" t="inlineStr">
@@ -7910,7 +7946,7 @@
       </c>
       <c r="AC63" s="2" t="inlineStr">
         <is>
-          <t>8/28</t>
+          <t>10/28</t>
         </is>
       </c>
     </row>
@@ -7971,7 +8007,7 @@
       </c>
       <c r="O64" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P64" s="2" t="inlineStr">
@@ -8020,12 +8056,12 @@
       </c>
       <c r="AB64" s="2" t="inlineStr">
         <is>
-          <t>128.0</t>
+          <t>127.7</t>
         </is>
       </c>
       <c r="AC64" s="2" t="inlineStr">
         <is>
-          <t>3/28</t>
+          <t>4/28</t>
         </is>
       </c>
     </row>
@@ -8086,7 +8122,7 @@
       </c>
       <c r="O65" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P65" s="2" t="inlineStr">
@@ -8130,17 +8166,17 @@
       </c>
       <c r="AA65" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB65" s="2" t="inlineStr">
         <is>
-          <t>140.0</t>
+          <t>135.0</t>
         </is>
       </c>
       <c r="AC65" s="2" t="inlineStr">
         <is>
-          <t>21/28</t>
+          <t>17/28</t>
         </is>
       </c>
     </row>
@@ -8148,22 +8184,22 @@
       <c r="A66" s="2" t="inlineStr"/>
       <c r="B66" s="2" t="inlineStr">
         <is>
-          <t>沪A95621D</t>
+          <t>沪A66883D</t>
         </is>
       </c>
       <c r="C66" s="2" t="inlineStr">
         <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D66" s="2" t="inlineStr">
+        <is>
+          <t>14:25</t>
+        </is>
+      </c>
+      <c r="E66" s="2" t="inlineStr">
+        <is>
           <t>东高路张杨北路</t>
-        </is>
-      </c>
-      <c r="D66" s="2" t="inlineStr">
-        <is>
-          <t>14:35</t>
-        </is>
-      </c>
-      <c r="E66" s="2" t="inlineStr">
-        <is>
-          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="F66" s="2" t="inlineStr">
@@ -8196,12 +8232,12 @@
       <c r="M66" s="2" t="inlineStr"/>
       <c r="N66" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>06:11</t>
         </is>
       </c>
       <c r="O66" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P66" s="2" t="inlineStr">
@@ -8215,47 +8251,614 @@
       <c r="T66" s="2" t="inlineStr"/>
       <c r="U66" s="2" t="inlineStr">
         <is>
+          <t>14:25</t>
+        </is>
+      </c>
+      <c r="V66" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W66" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X66" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y66" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z66" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA66" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB66" s="2" t="inlineStr">
+        <is>
+          <t>133.0</t>
+        </is>
+      </c>
+      <c r="AC66" s="2" t="inlineStr">
+        <is>
+          <t>14/28</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="2" t="inlineStr"/>
+      <c r="B67" s="2" t="inlineStr">
+        <is>
+          <t>沪A95621D</t>
+        </is>
+      </c>
+      <c r="C67" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D67" s="2" t="inlineStr">
+        <is>
           <t>14:35</t>
         </is>
       </c>
-      <c r="V66" s="2" t="inlineStr">
+      <c r="E67" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F67" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G67" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H67" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I67" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J67" s="2" t="inlineStr"/>
+      <c r="K67" s="2" t="inlineStr"/>
+      <c r="L67" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M67" s="2" t="inlineStr"/>
+      <c r="N67" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O67" s="2" t="inlineStr">
+        <is>
+          <t>14:21</t>
+        </is>
+      </c>
+      <c r="P67" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q67" s="2" t="inlineStr"/>
+      <c r="R67" s="2" t="inlineStr"/>
+      <c r="S67" s="2" t="inlineStr"/>
+      <c r="T67" s="2" t="inlineStr"/>
+      <c r="U67" s="2" t="inlineStr">
+        <is>
+          <t>14:35</t>
+        </is>
+      </c>
+      <c r="V67" s="2" t="inlineStr">
         <is>
           <t>计划发车</t>
         </is>
       </c>
-      <c r="W66" s="2" t="inlineStr">
+      <c r="W67" s="2" t="inlineStr">
         <is>
           <t>D</t>
         </is>
       </c>
-      <c r="X66" s="2" t="inlineStr">
+      <c r="X67" s="2" t="inlineStr">
         <is>
           <t>待确认</t>
         </is>
       </c>
-      <c r="Y66" s="2" t="inlineStr">
+      <c r="Y67" s="2" t="inlineStr">
         <is>
           <t>否</t>
         </is>
       </c>
-      <c r="Z66" s="2" t="inlineStr">
+      <c r="Z67" s="2" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AA66" s="2" t="inlineStr">
+      <c r="AA67" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB67" s="2" t="inlineStr">
+        <is>
+          <t>130.0</t>
+        </is>
+      </c>
+      <c r="AC67" s="2" t="inlineStr">
+        <is>
+          <t>7/28</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="2" t="inlineStr"/>
+      <c r="B68" s="2" t="inlineStr">
+        <is>
+          <t>沪A70597D</t>
+        </is>
+      </c>
+      <c r="C68" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D68" s="2" t="inlineStr">
+        <is>
+          <t>14:45</t>
+        </is>
+      </c>
+      <c r="E68" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F68" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G68" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H68" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I68" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J68" s="2" t="inlineStr"/>
+      <c r="K68" s="2" t="inlineStr"/>
+      <c r="L68" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M68" s="2" t="inlineStr"/>
+      <c r="N68" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O68" s="2" t="inlineStr">
+        <is>
+          <t>14:21</t>
+        </is>
+      </c>
+      <c r="P68" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q68" s="2" t="inlineStr"/>
+      <c r="R68" s="2" t="inlineStr"/>
+      <c r="S68" s="2" t="inlineStr"/>
+      <c r="T68" s="2" t="inlineStr"/>
+      <c r="U68" s="2" t="inlineStr">
+        <is>
+          <t>14:45</t>
+        </is>
+      </c>
+      <c r="V68" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W68" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X68" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y68" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z68" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA68" s="2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AB66" s="2" t="inlineStr">
-        <is>
-          <t>131.5</t>
-        </is>
-      </c>
-      <c r="AC66" s="2" t="inlineStr">
-        <is>
-          <t>9/28</t>
+      <c r="AB68" s="2" t="inlineStr">
+        <is>
+          <t>136.0</t>
+        </is>
+      </c>
+      <c r="AC68" s="2" t="inlineStr">
+        <is>
+          <t>18/28</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="2" t="inlineStr"/>
+      <c r="B69" s="2" t="inlineStr">
+        <is>
+          <t>沪A51682D</t>
+        </is>
+      </c>
+      <c r="C69" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D69" s="2" t="inlineStr">
+        <is>
+          <t>15:00</t>
+        </is>
+      </c>
+      <c r="E69" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F69" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G69" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H69" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I69" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J69" s="2" t="inlineStr"/>
+      <c r="K69" s="2" t="inlineStr"/>
+      <c r="L69" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M69" s="2" t="inlineStr"/>
+      <c r="N69" s="2" t="inlineStr">
+        <is>
+          <t>06:51</t>
+        </is>
+      </c>
+      <c r="O69" s="2" t="inlineStr">
+        <is>
+          <t>14:21</t>
+        </is>
+      </c>
+      <c r="P69" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q69" s="2" t="inlineStr"/>
+      <c r="R69" s="2" t="inlineStr"/>
+      <c r="S69" s="2" t="inlineStr"/>
+      <c r="T69" s="2" t="inlineStr"/>
+      <c r="U69" s="2" t="inlineStr">
+        <is>
+          <t>15:00</t>
+        </is>
+      </c>
+      <c r="V69" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W69" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X69" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y69" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z69" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA69" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB69" s="2" t="inlineStr"/>
+      <c r="AC69" s="2" t="inlineStr">
+        <is>
+          <t>—/28</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="2" t="inlineStr"/>
+      <c r="B70" s="2" t="inlineStr">
+        <is>
+          <t>沪A73927D</t>
+        </is>
+      </c>
+      <c r="C70" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D70" s="2" t="inlineStr">
+        <is>
+          <t>15:10</t>
+        </is>
+      </c>
+      <c r="E70" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F70" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G70" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H70" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I70" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J70" s="2" t="inlineStr"/>
+      <c r="K70" s="2" t="inlineStr"/>
+      <c r="L70" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M70" s="2" t="inlineStr"/>
+      <c r="N70" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O70" s="2" t="inlineStr">
+        <is>
+          <t>14:21</t>
+        </is>
+      </c>
+      <c r="P70" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q70" s="2" t="inlineStr"/>
+      <c r="R70" s="2" t="inlineStr"/>
+      <c r="S70" s="2" t="inlineStr"/>
+      <c r="T70" s="2" t="inlineStr"/>
+      <c r="U70" s="2" t="inlineStr">
+        <is>
+          <t>15:10</t>
+        </is>
+      </c>
+      <c r="V70" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W70" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X70" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y70" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z70" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA70" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB70" s="2" t="inlineStr">
+        <is>
+          <t>136.5</t>
+        </is>
+      </c>
+      <c r="AC70" s="2" t="inlineStr">
+        <is>
+          <t>21/28</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="2" t="inlineStr"/>
+      <c r="B71" s="2" t="inlineStr">
+        <is>
+          <t>沪A71572D</t>
+        </is>
+      </c>
+      <c r="C71" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D71" s="2" t="inlineStr">
+        <is>
+          <t>15:25</t>
+        </is>
+      </c>
+      <c r="E71" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F71" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G71" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H71" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I71" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J71" s="2" t="inlineStr"/>
+      <c r="K71" s="2" t="inlineStr"/>
+      <c r="L71" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M71" s="2" t="inlineStr"/>
+      <c r="N71" s="2" t="inlineStr">
+        <is>
+          <t>06:21</t>
+        </is>
+      </c>
+      <c r="O71" s="2" t="inlineStr">
+        <is>
+          <t>14:21</t>
+        </is>
+      </c>
+      <c r="P71" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q71" s="2" t="inlineStr"/>
+      <c r="R71" s="2" t="inlineStr"/>
+      <c r="S71" s="2" t="inlineStr"/>
+      <c r="T71" s="2" t="inlineStr"/>
+      <c r="U71" s="2" t="inlineStr">
+        <is>
+          <t>15:25</t>
+        </is>
+      </c>
+      <c r="V71" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W71" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X71" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y71" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z71" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA71" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB71" s="2" t="inlineStr"/>
+      <c r="AC71" s="2" t="inlineStr">
+        <is>
+          <t>—/28</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-10-31-浦东35路.xlsx
+++ b/data/export/2026-10-31-浦东35路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC71"/>
+  <dimension ref="A1:AC78"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -669,7 +669,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -723,7 +723,7 @@
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>4/28</t>
+          <t>4/29</t>
         </is>
       </c>
     </row>
@@ -788,7 +788,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -842,7 +842,7 @@
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>18/28</t>
+          <t>19/29</t>
         </is>
       </c>
     </row>
@@ -961,7 +961,7 @@
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>5/28</t>
+          <t>5/29</t>
         </is>
       </c>
     </row>
@@ -1080,7 +1080,7 @@
       </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>22/28</t>
+          <t>24/29</t>
         </is>
       </c>
     </row>
@@ -1145,7 +1145,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1199,7 +1199,7 @@
       </c>
       <c r="AC6" s="2" t="inlineStr">
         <is>
-          <t>7/28</t>
+          <t>7/29</t>
         </is>
       </c>
     </row>
@@ -1318,7 +1318,7 @@
       </c>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>16/28</t>
+          <t>16/29</t>
         </is>
       </c>
     </row>
@@ -1383,7 +1383,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1437,7 +1437,7 @@
       </c>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>21/28</t>
+          <t>22/29</t>
         </is>
       </c>
     </row>
@@ -1502,7 +1502,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1551,12 +1551,12 @@
       </c>
       <c r="AB9" s="2" t="inlineStr">
         <is>
-          <t>126.7</t>
+          <t>127.0</t>
         </is>
       </c>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>2/28</t>
+          <t>2/29</t>
         </is>
       </c>
     </row>
@@ -1621,7 +1621,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1675,7 +1675,7 @@
       </c>
       <c r="AC10" s="2" t="inlineStr">
         <is>
-          <t>14/28</t>
+          <t>13/29</t>
         </is>
       </c>
     </row>
@@ -1794,7 +1794,7 @@
       </c>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>9/28</t>
+          <t>9/29</t>
         </is>
       </c>
     </row>
@@ -1859,7 +1859,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>11:51</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1898,7 +1898,7 @@
       </c>
       <c r="Z12" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA12" s="2" t="inlineStr">
@@ -1913,7 +1913,7 @@
       </c>
       <c r="AC12" s="2" t="inlineStr">
         <is>
-          <t>7/28</t>
+          <t>7/29</t>
         </is>
       </c>
     </row>
@@ -1974,7 +1974,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -2029,18 +2029,22 @@
       </c>
       <c r="Z13" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA13" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB13" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB13" s="2" t="inlineStr">
+        <is>
+          <t>139.0</t>
+        </is>
+      </c>
       <c r="AC13" s="2" t="inlineStr">
         <is>
-          <t>—/28</t>
+          <t>23/29</t>
         </is>
       </c>
     </row>
@@ -2105,7 +2109,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2144,14 +2148,14 @@
       </c>
       <c r="Z14" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA14" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA14" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB14" s="2" t="inlineStr">
         <is>
           <t>141.0</t>
@@ -2159,7 +2163,7 @@
       </c>
       <c r="AC14" s="2" t="inlineStr">
         <is>
-          <t>24/28</t>
+          <t>26/29</t>
         </is>
       </c>
     </row>
@@ -2220,7 +2224,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:01</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2264,17 +2268,17 @@
       </c>
       <c r="AA15" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB15" s="2" t="inlineStr">
         <is>
-          <t>127.0</t>
+          <t>127.5</t>
         </is>
       </c>
       <c r="AC15" s="2" t="inlineStr">
         <is>
-          <t>3/28</t>
+          <t>3/29</t>
         </is>
       </c>
     </row>
@@ -2339,7 +2343,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2393,7 +2397,7 @@
       </c>
       <c r="AC16" s="2" t="inlineStr">
         <is>
-          <t>18/28</t>
+          <t>19/29</t>
         </is>
       </c>
     </row>
@@ -2512,7 +2516,7 @@
       </c>
       <c r="AC17" s="2" t="inlineStr">
         <is>
-          <t>23/28</t>
+          <t>25/29</t>
         </is>
       </c>
     </row>
@@ -2577,7 +2581,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2621,17 +2625,17 @@
       </c>
       <c r="AA18" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB18" s="2" t="inlineStr">
         <is>
-          <t>133.5</t>
+          <t>134.0</t>
         </is>
       </c>
       <c r="AC18" s="2" t="inlineStr">
         <is>
-          <t>15/28</t>
+          <t>15/29</t>
         </is>
       </c>
     </row>
@@ -2746,7 +2750,7 @@
       </c>
       <c r="AC19" s="2" t="inlineStr">
         <is>
-          <t>1/28</t>
+          <t>1/29</t>
         </is>
       </c>
     </row>
@@ -2865,7 +2869,7 @@
       </c>
       <c r="AC20" s="2" t="inlineStr">
         <is>
-          <t>11/28</t>
+          <t>11/29</t>
         </is>
       </c>
     </row>
@@ -2930,7 +2934,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -2984,7 +2988,7 @@
       </c>
       <c r="AC21" s="2" t="inlineStr">
         <is>
-          <t>10/28</t>
+          <t>10/29</t>
         </is>
       </c>
     </row>
@@ -3045,7 +3049,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -3089,17 +3093,17 @@
       </c>
       <c r="AA22" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB22" s="2" t="inlineStr">
         <is>
-          <t>132.0</t>
+          <t>133.5</t>
         </is>
       </c>
       <c r="AC22" s="2" t="inlineStr">
         <is>
-          <t>11/28</t>
+          <t>14/29</t>
         </is>
       </c>
     </row>
@@ -3160,7 +3164,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>14:51</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -3199,7 +3203,7 @@
       </c>
       <c r="Z23" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA23" s="2" t="inlineStr">
@@ -3210,7 +3214,7 @@
       <c r="AB23" s="2" t="inlineStr"/>
       <c r="AC23" s="2" t="inlineStr">
         <is>
-          <t>—/28</t>
+          <t>—/29</t>
         </is>
       </c>
     </row>
@@ -3329,7 +3333,7 @@
       </c>
       <c r="AC24" s="2" t="inlineStr">
         <is>
-          <t>18/28</t>
+          <t>19/29</t>
         </is>
       </c>
     </row>
@@ -3448,7 +3452,7 @@
       </c>
       <c r="AC25" s="2" t="inlineStr">
         <is>
-          <t>11/28</t>
+          <t>11/29</t>
         </is>
       </c>
     </row>
@@ -3513,7 +3517,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3567,7 +3571,7 @@
       </c>
       <c r="AC26" s="2" t="inlineStr">
         <is>
-          <t>17/28</t>
+          <t>17/29</t>
         </is>
       </c>
     </row>
@@ -3632,7 +3636,7 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -3686,7 +3690,7 @@
       </c>
       <c r="AC27" s="2" t="inlineStr">
         <is>
-          <t>4/28</t>
+          <t>4/29</t>
         </is>
       </c>
     </row>
@@ -3751,7 +3755,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -3805,7 +3809,7 @@
       </c>
       <c r="AC28" s="2" t="inlineStr">
         <is>
-          <t>18/28</t>
+          <t>19/29</t>
         </is>
       </c>
     </row>
@@ -3924,7 +3928,7 @@
       </c>
       <c r="AC29" s="2" t="inlineStr">
         <is>
-          <t>6/28</t>
+          <t>6/29</t>
         </is>
       </c>
     </row>
@@ -4043,7 +4047,7 @@
       </c>
       <c r="AC30" s="2" t="inlineStr">
         <is>
-          <t>5/28</t>
+          <t>5/29</t>
         </is>
       </c>
     </row>
@@ -4108,7 +4112,7 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
@@ -4162,7 +4166,7 @@
       </c>
       <c r="AC31" s="2" t="inlineStr">
         <is>
-          <t>7/28</t>
+          <t>7/29</t>
         </is>
       </c>
     </row>
@@ -4281,7 +4285,7 @@
       </c>
       <c r="AC32" s="2" t="inlineStr">
         <is>
-          <t>22/28</t>
+          <t>24/29</t>
         </is>
       </c>
     </row>
@@ -4346,7 +4350,7 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
@@ -4400,7 +4404,7 @@
       </c>
       <c r="AC33" s="2" t="inlineStr">
         <is>
-          <t>21/28</t>
+          <t>22/29</t>
         </is>
       </c>
     </row>
@@ -4465,7 +4469,7 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
@@ -4519,7 +4523,7 @@
       </c>
       <c r="AC34" s="2" t="inlineStr">
         <is>
-          <t>14/28</t>
+          <t>13/29</t>
         </is>
       </c>
     </row>
@@ -4638,7 +4642,7 @@
       </c>
       <c r="AC35" s="2" t="inlineStr">
         <is>
-          <t>16/28</t>
+          <t>16/29</t>
         </is>
       </c>
     </row>
@@ -4699,7 +4703,7 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:11</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
@@ -4754,7 +4758,7 @@
       </c>
       <c r="Z36" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA36" s="2" t="inlineStr">
@@ -4765,7 +4769,7 @@
       <c r="AB36" s="2" t="inlineStr"/>
       <c r="AC36" s="2" t="inlineStr">
         <is>
-          <t>—/28</t>
+          <t>—/29</t>
         </is>
       </c>
     </row>
@@ -4830,7 +4834,7 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
@@ -4879,12 +4883,12 @@
       </c>
       <c r="AB37" s="2" t="inlineStr">
         <is>
-          <t>126.7</t>
+          <t>127.0</t>
         </is>
       </c>
       <c r="AC37" s="2" t="inlineStr">
         <is>
-          <t>2/28</t>
+          <t>2/29</t>
         </is>
       </c>
     </row>
@@ -4945,7 +4949,7 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>11:51</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
@@ -4984,7 +4988,7 @@
       </c>
       <c r="Z38" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA38" s="2" t="inlineStr">
@@ -4999,7 +5003,7 @@
       </c>
       <c r="AC38" s="2" t="inlineStr">
         <is>
-          <t>7/28</t>
+          <t>7/29</t>
         </is>
       </c>
     </row>
@@ -5064,7 +5068,7 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
@@ -5103,14 +5107,14 @@
       </c>
       <c r="Z39" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA39" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA39" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB39" s="2" t="inlineStr">
         <is>
           <t>141.0</t>
@@ -5118,7 +5122,7 @@
       </c>
       <c r="AC39" s="2" t="inlineStr">
         <is>
-          <t>24/28</t>
+          <t>26/29</t>
         </is>
       </c>
     </row>
@@ -5237,7 +5241,7 @@
       </c>
       <c r="AC40" s="2" t="inlineStr">
         <is>
-          <t>9/28</t>
+          <t>9/29</t>
         </is>
       </c>
     </row>
@@ -5302,7 +5306,7 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:01</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
@@ -5346,17 +5350,17 @@
       </c>
       <c r="AA41" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB41" s="2" t="inlineStr">
         <is>
-          <t>127.0</t>
+          <t>127.5</t>
         </is>
       </c>
       <c r="AC41" s="2" t="inlineStr">
         <is>
-          <t>3/28</t>
+          <t>3/29</t>
         </is>
       </c>
     </row>
@@ -5421,7 +5425,7 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
@@ -5475,7 +5479,7 @@
       </c>
       <c r="AC42" s="2" t="inlineStr">
         <is>
-          <t>18/28</t>
+          <t>19/29</t>
         </is>
       </c>
     </row>
@@ -5594,7 +5598,7 @@
       </c>
       <c r="AC43" s="2" t="inlineStr">
         <is>
-          <t>23/28</t>
+          <t>25/29</t>
         </is>
       </c>
     </row>
@@ -5713,7 +5717,7 @@
       </c>
       <c r="AC44" s="2" t="inlineStr">
         <is>
-          <t>1/28</t>
+          <t>1/29</t>
         </is>
       </c>
     </row>
@@ -5778,7 +5782,7 @@
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
@@ -5822,17 +5826,17 @@
       </c>
       <c r="AA45" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB45" s="2" t="inlineStr">
         <is>
-          <t>133.5</t>
+          <t>134.0</t>
         </is>
       </c>
       <c r="AC45" s="2" t="inlineStr">
         <is>
-          <t>15/28</t>
+          <t>15/29</t>
         </is>
       </c>
     </row>
@@ -5897,7 +5901,7 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
@@ -5951,7 +5955,7 @@
       </c>
       <c r="AC46" s="2" t="inlineStr">
         <is>
-          <t>10/28</t>
+          <t>10/29</t>
         </is>
       </c>
     </row>
@@ -6070,7 +6074,7 @@
       </c>
       <c r="AC47" s="2" t="inlineStr">
         <is>
-          <t>11/28</t>
+          <t>11/29</t>
         </is>
       </c>
     </row>
@@ -6189,7 +6193,7 @@
       </c>
       <c r="AC48" s="2" t="inlineStr">
         <is>
-          <t>11/28</t>
+          <t>11/29</t>
         </is>
       </c>
     </row>
@@ -6254,7 +6258,7 @@
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
@@ -6298,17 +6302,17 @@
       </c>
       <c r="AA49" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB49" s="2" t="inlineStr">
         <is>
-          <t>132.0</t>
+          <t>133.5</t>
         </is>
       </c>
       <c r="AC49" s="2" t="inlineStr">
         <is>
-          <t>11/28</t>
+          <t>14/29</t>
         </is>
       </c>
     </row>
@@ -6373,7 +6377,7 @@
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
@@ -6427,7 +6431,7 @@
       </c>
       <c r="AC50" s="2" t="inlineStr">
         <is>
-          <t>4/28</t>
+          <t>4/29</t>
         </is>
       </c>
     </row>
@@ -6492,7 +6496,7 @@
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P51" s="2" t="inlineStr">
@@ -6546,7 +6550,7 @@
       </c>
       <c r="AC51" s="2" t="inlineStr">
         <is>
-          <t>17/28</t>
+          <t>17/29</t>
         </is>
       </c>
     </row>
@@ -6665,7 +6669,7 @@
       </c>
       <c r="AC52" s="2" t="inlineStr">
         <is>
-          <t>6/28</t>
+          <t>6/29</t>
         </is>
       </c>
     </row>
@@ -6784,7 +6788,7 @@
       </c>
       <c r="AC53" s="2" t="inlineStr">
         <is>
-          <t>22/28</t>
+          <t>24/29</t>
         </is>
       </c>
     </row>
@@ -6849,7 +6853,7 @@
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P54" s="2" t="inlineStr">
@@ -6903,7 +6907,7 @@
       </c>
       <c r="AC54" s="2" t="inlineStr">
         <is>
-          <t>7/28</t>
+          <t>7/29</t>
         </is>
       </c>
     </row>
@@ -6936,7 +6940,7 @@
       </c>
       <c r="G55" s="2" t="inlineStr">
         <is>
-          <t>原方向在全程34%处后消失；随后反向物理轨迹由seq38推进至seq49，推进11站，达到≥2站确认条件</t>
+          <t>原方向在全程34%处后消失；随后反向物理轨迹由seq38推进至seq57，推进19站，达到≥2站确认条件</t>
         </is>
       </c>
       <c r="H55" s="2" t="inlineStr">
@@ -6964,7 +6968,7 @@
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:11</t>
         </is>
       </c>
       <c r="P55" s="2" t="inlineStr">
@@ -7019,7 +7023,7 @@
       </c>
       <c r="Z55" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA55" s="2" t="inlineStr">
@@ -7030,7 +7034,7 @@
       <c r="AB55" s="2" t="inlineStr"/>
       <c r="AC55" s="2" t="inlineStr">
         <is>
-          <t>—/28</t>
+          <t>—/29</t>
         </is>
       </c>
     </row>
@@ -7068,24 +7072,24 @@
       </c>
       <c r="H56" s="2" t="inlineStr">
         <is>
-          <t>14:33</t>
+          <t>14:34</t>
         </is>
       </c>
       <c r="I56" s="2" t="inlineStr">
         <is>
-          <t>123分钟</t>
+          <t>124分钟</t>
         </is>
       </c>
       <c r="J56" s="2" t="inlineStr"/>
       <c r="K56" s="2" t="inlineStr"/>
       <c r="L56" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="M56" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N56" s="2" t="inlineStr">
@@ -7095,7 +7099,7 @@
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="P56" s="2" t="inlineStr">
@@ -7144,12 +7148,12 @@
       </c>
       <c r="AB56" s="2" t="inlineStr">
         <is>
-          <t>126.7</t>
+          <t>127.0</t>
         </is>
       </c>
       <c r="AC56" s="2" t="inlineStr">
         <is>
-          <t>2/28</t>
+          <t>2/29</t>
         </is>
       </c>
     </row>
@@ -7177,32 +7181,36 @@
       </c>
       <c r="F57" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G57" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H57" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>14:59</t>
         </is>
       </c>
       <c r="I57" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>139分钟</t>
         </is>
       </c>
       <c r="J57" s="2" t="inlineStr"/>
       <c r="K57" s="2" t="inlineStr"/>
       <c r="L57" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M57" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M57" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N57" s="2" t="inlineStr">
         <is>
           <t>06:51</t>
@@ -7210,7 +7218,7 @@
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P57" s="2" t="inlineStr">
@@ -7234,33 +7242,37 @@
       </c>
       <c r="W57" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X57" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y57" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z57" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA57" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB57" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB57" s="2" t="inlineStr">
+        <is>
+          <t>139.0</t>
+        </is>
+      </c>
       <c r="AC57" s="2" t="inlineStr">
         <is>
-          <t>—/28</t>
+          <t>23/29</t>
         </is>
       </c>
     </row>
@@ -7288,32 +7300,36 @@
       </c>
       <c r="F58" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G58" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H58" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>15:03</t>
         </is>
       </c>
       <c r="I58" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>128分钟</t>
         </is>
       </c>
       <c r="J58" s="2" t="inlineStr"/>
       <c r="K58" s="2" t="inlineStr"/>
       <c r="L58" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M58" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M58" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N58" s="2" t="inlineStr">
         <is>
           <t>06:51</t>
@@ -7321,7 +7337,7 @@
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:01</t>
         </is>
       </c>
       <c r="P58" s="2" t="inlineStr">
@@ -7345,17 +7361,17 @@
       </c>
       <c r="W58" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X58" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y58" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z58" s="2" t="inlineStr">
@@ -7365,17 +7381,17 @@
       </c>
       <c r="AA58" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB58" s="2" t="inlineStr">
         <is>
-          <t>127.0</t>
+          <t>127.5</t>
         </is>
       </c>
       <c r="AC58" s="2" t="inlineStr">
         <is>
-          <t>3/28</t>
+          <t>3/29</t>
         </is>
       </c>
     </row>
@@ -7403,32 +7419,36 @@
       </c>
       <c r="F59" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G59" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H59" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="I59" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>135分钟</t>
         </is>
       </c>
       <c r="J59" s="2" t="inlineStr"/>
       <c r="K59" s="2" t="inlineStr"/>
       <c r="L59" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M59" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M59" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N59" s="2" t="inlineStr">
         <is>
           <t>07:31</t>
@@ -7436,7 +7456,7 @@
       </c>
       <c r="O59" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P59" s="2" t="inlineStr">
@@ -7460,33 +7480,37 @@
       </c>
       <c r="W59" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X59" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y59" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z59" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA59" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AA59" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB59" s="2" t="inlineStr"/>
+      <c r="AB59" s="2" t="inlineStr">
+        <is>
+          <t>135.0</t>
+        </is>
+      </c>
       <c r="AC59" s="2" t="inlineStr">
         <is>
-          <t>—/28</t>
+          <t>17/29</t>
         </is>
       </c>
     </row>
@@ -7514,32 +7538,36 @@
       </c>
       <c r="F60" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G60" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H60" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>15:35</t>
         </is>
       </c>
       <c r="I60" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>135分钟</t>
         </is>
       </c>
       <c r="J60" s="2" t="inlineStr"/>
       <c r="K60" s="2" t="inlineStr"/>
       <c r="L60" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M60" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M60" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N60" s="2" t="inlineStr">
         <is>
           <t>06:51</t>
@@ -7547,7 +7575,7 @@
       </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P60" s="2" t="inlineStr">
@@ -7571,17 +7599,17 @@
       </c>
       <c r="W60" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X60" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y60" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z60" s="2" t="inlineStr">
@@ -7591,17 +7619,17 @@
       </c>
       <c r="AA60" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB60" s="2" t="inlineStr">
         <is>
-          <t>133.5</t>
+          <t>134.0</t>
         </is>
       </c>
       <c r="AC60" s="2" t="inlineStr">
         <is>
-          <t>15/28</t>
+          <t>15/29</t>
         </is>
       </c>
     </row>
@@ -7662,7 +7690,7 @@
       </c>
       <c r="O61" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P61" s="2" t="inlineStr">
@@ -7716,7 +7744,7 @@
       </c>
       <c r="AC61" s="2" t="inlineStr">
         <is>
-          <t>18/28</t>
+          <t>19/29</t>
         </is>
       </c>
     </row>
@@ -7744,32 +7772,36 @@
       </c>
       <c r="F62" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G62" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H62" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="I62" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>135分钟</t>
         </is>
       </c>
       <c r="J62" s="2" t="inlineStr"/>
       <c r="K62" s="2" t="inlineStr"/>
       <c r="L62" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M62" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M62" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N62" s="2" t="inlineStr">
         <is>
           <t>07:41</t>
@@ -7777,7 +7809,7 @@
       </c>
       <c r="O62" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P62" s="2" t="inlineStr">
@@ -7801,17 +7833,17 @@
       </c>
       <c r="W62" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X62" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y62" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z62" s="2" t="inlineStr">
@@ -7821,17 +7853,17 @@
       </c>
       <c r="AA62" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB62" s="2" t="inlineStr">
         <is>
-          <t>132.0</t>
+          <t>133.5</t>
         </is>
       </c>
       <c r="AC62" s="2" t="inlineStr">
         <is>
-          <t>11/28</t>
+          <t>14/29</t>
         </is>
       </c>
     </row>
@@ -7892,7 +7924,7 @@
       </c>
       <c r="O63" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P63" s="2" t="inlineStr">
@@ -7946,7 +7978,7 @@
       </c>
       <c r="AC63" s="2" t="inlineStr">
         <is>
-          <t>10/28</t>
+          <t>10/29</t>
         </is>
       </c>
     </row>
@@ -8007,7 +8039,7 @@
       </c>
       <c r="O64" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P64" s="2" t="inlineStr">
@@ -8061,7 +8093,7 @@
       </c>
       <c r="AC64" s="2" t="inlineStr">
         <is>
-          <t>4/28</t>
+          <t>4/29</t>
         </is>
       </c>
     </row>
@@ -8122,7 +8154,7 @@
       </c>
       <c r="O65" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P65" s="2" t="inlineStr">
@@ -8176,7 +8208,7 @@
       </c>
       <c r="AC65" s="2" t="inlineStr">
         <is>
-          <t>17/28</t>
+          <t>17/29</t>
         </is>
       </c>
     </row>
@@ -8237,7 +8269,7 @@
       </c>
       <c r="O66" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P66" s="2" t="inlineStr">
@@ -8291,7 +8323,7 @@
       </c>
       <c r="AC66" s="2" t="inlineStr">
         <is>
-          <t>14/28</t>
+          <t>13/29</t>
         </is>
       </c>
     </row>
@@ -8352,7 +8384,7 @@
       </c>
       <c r="O67" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P67" s="2" t="inlineStr">
@@ -8406,7 +8438,7 @@
       </c>
       <c r="AC67" s="2" t="inlineStr">
         <is>
-          <t>7/28</t>
+          <t>7/29</t>
         </is>
       </c>
     </row>
@@ -8467,7 +8499,7 @@
       </c>
       <c r="O68" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P68" s="2" t="inlineStr">
@@ -8521,7 +8553,7 @@
       </c>
       <c r="AC68" s="2" t="inlineStr">
         <is>
-          <t>18/28</t>
+          <t>19/29</t>
         </is>
       </c>
     </row>
@@ -8582,7 +8614,7 @@
       </c>
       <c r="O69" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P69" s="2" t="inlineStr">
@@ -8621,18 +8653,22 @@
       </c>
       <c r="Z69" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA69" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB69" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB69" s="2" t="inlineStr">
+        <is>
+          <t>139.0</t>
+        </is>
+      </c>
       <c r="AC69" s="2" t="inlineStr">
         <is>
-          <t>—/28</t>
+          <t>23/29</t>
         </is>
       </c>
     </row>
@@ -8640,22 +8676,22 @@
       <c r="A70" s="2" t="inlineStr"/>
       <c r="B70" s="2" t="inlineStr">
         <is>
-          <t>沪A73927D</t>
+          <t>沪A71572D</t>
         </is>
       </c>
       <c r="C70" s="2" t="inlineStr">
         <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D70" s="2" t="inlineStr">
+        <is>
+          <t>15:00</t>
+        </is>
+      </c>
+      <c r="E70" s="2" t="inlineStr">
+        <is>
           <t>康恩路康浦路</t>
-        </is>
-      </c>
-      <c r="D70" s="2" t="inlineStr">
-        <is>
-          <t>15:10</t>
-        </is>
-      </c>
-      <c r="E70" s="2" t="inlineStr">
-        <is>
-          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="F70" s="2" t="inlineStr">
@@ -8688,12 +8724,12 @@
       <c r="M70" s="2" t="inlineStr"/>
       <c r="N70" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>06:21</t>
         </is>
       </c>
       <c r="O70" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>14:51</t>
         </is>
       </c>
       <c r="P70" s="2" t="inlineStr">
@@ -8707,7 +8743,7 @@
       <c r="T70" s="2" t="inlineStr"/>
       <c r="U70" s="2" t="inlineStr">
         <is>
-          <t>15:10</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="V70" s="2" t="inlineStr">
@@ -8737,17 +8773,13 @@
       </c>
       <c r="AA70" s="2" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AB70" s="2" t="inlineStr">
-        <is>
-          <t>136.5</t>
-        </is>
-      </c>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB70" s="2" t="inlineStr"/>
       <c r="AC70" s="2" t="inlineStr">
         <is>
-          <t>21/28</t>
+          <t>—/29</t>
         </is>
       </c>
     </row>
@@ -8755,22 +8787,22 @@
       <c r="A71" s="2" t="inlineStr"/>
       <c r="B71" s="2" t="inlineStr">
         <is>
-          <t>沪A71572D</t>
+          <t>沪A73927D</t>
         </is>
       </c>
       <c r="C71" s="2" t="inlineStr">
         <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D71" s="2" t="inlineStr">
+        <is>
+          <t>15:10</t>
+        </is>
+      </c>
+      <c r="E71" s="2" t="inlineStr">
+        <is>
           <t>东高路张杨北路</t>
-        </is>
-      </c>
-      <c r="D71" s="2" t="inlineStr">
-        <is>
-          <t>15:25</t>
-        </is>
-      </c>
-      <c r="E71" s="2" t="inlineStr">
-        <is>
-          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="F71" s="2" t="inlineStr">
@@ -8803,12 +8835,12 @@
       <c r="M71" s="2" t="inlineStr"/>
       <c r="N71" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="O71" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P71" s="2" t="inlineStr">
@@ -8822,43 +8854,840 @@
       <c r="T71" s="2" t="inlineStr"/>
       <c r="U71" s="2" t="inlineStr">
         <is>
+          <t>15:10</t>
+        </is>
+      </c>
+      <c r="V71" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W71" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X71" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y71" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z71" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA71" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB71" s="2" t="inlineStr">
+        <is>
+          <t>136.5</t>
+        </is>
+      </c>
+      <c r="AC71" s="2" t="inlineStr">
+        <is>
+          <t>22/29</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="2" t="inlineStr"/>
+      <c r="B72" s="2" t="inlineStr">
+        <is>
+          <t>沪A79307D</t>
+        </is>
+      </c>
+      <c r="C72" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D72" s="2" t="inlineStr">
+        <is>
+          <t>15:22</t>
+        </is>
+      </c>
+      <c r="E72" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F72" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G72" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H72" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I72" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J72" s="2" t="inlineStr"/>
+      <c r="K72" s="2" t="inlineStr"/>
+      <c r="L72" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M72" s="2" t="inlineStr"/>
+      <c r="N72" s="2" t="inlineStr">
+        <is>
+          <t>09:31</t>
+        </is>
+      </c>
+      <c r="O72" s="2" t="inlineStr">
+        <is>
+          <t>15:11</t>
+        </is>
+      </c>
+      <c r="P72" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q72" s="2" t="inlineStr"/>
+      <c r="R72" s="2" t="inlineStr"/>
+      <c r="S72" s="2" t="inlineStr"/>
+      <c r="T72" s="2" t="inlineStr"/>
+      <c r="U72" s="2" t="inlineStr">
+        <is>
+          <t>15:22</t>
+        </is>
+      </c>
+      <c r="V72" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W72" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X72" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y72" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z72" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA72" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB72" s="2" t="inlineStr"/>
+      <c r="AC72" s="2" t="inlineStr">
+        <is>
+          <t>—/29</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="2" t="inlineStr"/>
+      <c r="B73" s="2" t="inlineStr">
+        <is>
+          <t>沪A51682D</t>
+        </is>
+      </c>
+      <c r="C73" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D73" s="2" t="inlineStr">
+        <is>
           <t>15:25</t>
         </is>
       </c>
-      <c r="V71" s="2" t="inlineStr">
+      <c r="E73" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F73" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G73" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H73" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I73" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J73" s="2" t="inlineStr"/>
+      <c r="K73" s="2" t="inlineStr"/>
+      <c r="L73" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M73" s="2" t="inlineStr"/>
+      <c r="N73" s="2" t="inlineStr">
+        <is>
+          <t>06:51</t>
+        </is>
+      </c>
+      <c r="O73" s="2" t="inlineStr">
+        <is>
+          <t>15:21</t>
+        </is>
+      </c>
+      <c r="P73" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q73" s="2" t="inlineStr"/>
+      <c r="R73" s="2" t="inlineStr"/>
+      <c r="S73" s="2" t="inlineStr"/>
+      <c r="T73" s="2" t="inlineStr"/>
+      <c r="U73" s="2" t="inlineStr">
+        <is>
+          <t>15:25</t>
+        </is>
+      </c>
+      <c r="V73" s="2" t="inlineStr">
         <is>
           <t>计划发车</t>
         </is>
       </c>
-      <c r="W71" s="2" t="inlineStr">
+      <c r="W73" s="2" t="inlineStr">
         <is>
           <t>D</t>
         </is>
       </c>
-      <c r="X71" s="2" t="inlineStr">
+      <c r="X73" s="2" t="inlineStr">
         <is>
           <t>待确认</t>
         </is>
       </c>
-      <c r="Y71" s="2" t="inlineStr">
+      <c r="Y73" s="2" t="inlineStr">
         <is>
           <t>否</t>
         </is>
       </c>
-      <c r="Z71" s="2" t="inlineStr">
+      <c r="Z73" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA73" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB73" s="2" t="inlineStr">
+        <is>
+          <t>139.0</t>
+        </is>
+      </c>
+      <c r="AC73" s="2" t="inlineStr">
+        <is>
+          <t>23/29</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="2" t="inlineStr"/>
+      <c r="B74" s="2" t="inlineStr">
+        <is>
+          <t>沪A71572D</t>
+        </is>
+      </c>
+      <c r="C74" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D74" s="2" t="inlineStr">
+        <is>
+          <t>15:25</t>
+        </is>
+      </c>
+      <c r="E74" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F74" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G74" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H74" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I74" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J74" s="2" t="inlineStr"/>
+      <c r="K74" s="2" t="inlineStr"/>
+      <c r="L74" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M74" s="2" t="inlineStr"/>
+      <c r="N74" s="2" t="inlineStr">
+        <is>
+          <t>06:21</t>
+        </is>
+      </c>
+      <c r="O74" s="2" t="inlineStr">
+        <is>
+          <t>14:51</t>
+        </is>
+      </c>
+      <c r="P74" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q74" s="2" t="inlineStr"/>
+      <c r="R74" s="2" t="inlineStr"/>
+      <c r="S74" s="2" t="inlineStr"/>
+      <c r="T74" s="2" t="inlineStr"/>
+      <c r="U74" s="2" t="inlineStr">
+        <is>
+          <t>15:25</t>
+        </is>
+      </c>
+      <c r="V74" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W74" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X74" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y74" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z74" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA74" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB74" s="2" t="inlineStr"/>
+      <c r="AC74" s="2" t="inlineStr">
+        <is>
+          <t>—/29</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="2" t="inlineStr"/>
+      <c r="B75" s="2" t="inlineStr">
+        <is>
+          <t>沪A72873D</t>
+        </is>
+      </c>
+      <c r="C75" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D75" s="2" t="inlineStr">
+        <is>
+          <t>15:35</t>
+        </is>
+      </c>
+      <c r="E75" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F75" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G75" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H75" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I75" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J75" s="2" t="inlineStr"/>
+      <c r="K75" s="2" t="inlineStr"/>
+      <c r="L75" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M75" s="2" t="inlineStr"/>
+      <c r="N75" s="2" t="inlineStr">
+        <is>
+          <t>06:32</t>
+        </is>
+      </c>
+      <c r="O75" s="2" t="inlineStr">
+        <is>
+          <t>15:21</t>
+        </is>
+      </c>
+      <c r="P75" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q75" s="2" t="inlineStr"/>
+      <c r="R75" s="2" t="inlineStr"/>
+      <c r="S75" s="2" t="inlineStr"/>
+      <c r="T75" s="2" t="inlineStr"/>
+      <c r="U75" s="2" t="inlineStr">
+        <is>
+          <t>15:35</t>
+        </is>
+      </c>
+      <c r="V75" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W75" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X75" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y75" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z75" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA75" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB75" s="2" t="inlineStr">
+        <is>
+          <t>130.0</t>
+        </is>
+      </c>
+      <c r="AC75" s="2" t="inlineStr">
+        <is>
+          <t>7/29</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="2" t="inlineStr"/>
+      <c r="B76" s="2" t="inlineStr">
+        <is>
+          <t>沪A15790A</t>
+        </is>
+      </c>
+      <c r="C76" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D76" s="2" t="inlineStr">
+        <is>
+          <t>15:45</t>
+        </is>
+      </c>
+      <c r="E76" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F76" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G76" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H76" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I76" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J76" s="2" t="inlineStr"/>
+      <c r="K76" s="2" t="inlineStr"/>
+      <c r="L76" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M76" s="2" t="inlineStr"/>
+      <c r="N76" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O76" s="2" t="inlineStr">
+        <is>
+          <t>15:21</t>
+        </is>
+      </c>
+      <c r="P76" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q76" s="2" t="inlineStr"/>
+      <c r="R76" s="2" t="inlineStr"/>
+      <c r="S76" s="2" t="inlineStr"/>
+      <c r="T76" s="2" t="inlineStr"/>
+      <c r="U76" s="2" t="inlineStr">
+        <is>
+          <t>15:45</t>
+        </is>
+      </c>
+      <c r="V76" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W76" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X76" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y76" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z76" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA76" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB76" s="2" t="inlineStr"/>
+      <c r="AC76" s="2" t="inlineStr">
+        <is>
+          <t>—/29</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="2" t="inlineStr"/>
+      <c r="B77" s="2" t="inlineStr">
+        <is>
+          <t>沪A62880D</t>
+        </is>
+      </c>
+      <c r="C77" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D77" s="2" t="inlineStr">
+        <is>
+          <t>16:00</t>
+        </is>
+      </c>
+      <c r="E77" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F77" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G77" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H77" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I77" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J77" s="2" t="inlineStr"/>
+      <c r="K77" s="2" t="inlineStr"/>
+      <c r="L77" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M77" s="2" t="inlineStr"/>
+      <c r="N77" s="2" t="inlineStr">
+        <is>
+          <t>07:01</t>
+        </is>
+      </c>
+      <c r="O77" s="2" t="inlineStr">
+        <is>
+          <t>15:21</t>
+        </is>
+      </c>
+      <c r="P77" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q77" s="2" t="inlineStr"/>
+      <c r="R77" s="2" t="inlineStr"/>
+      <c r="S77" s="2" t="inlineStr"/>
+      <c r="T77" s="2" t="inlineStr"/>
+      <c r="U77" s="2" t="inlineStr">
+        <is>
+          <t>16:00</t>
+        </is>
+      </c>
+      <c r="V77" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W77" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X77" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y77" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z77" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA77" s="2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA71" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB71" s="2" t="inlineStr"/>
-      <c r="AC71" s="2" t="inlineStr">
-        <is>
-          <t>—/28</t>
+      <c r="AB77" s="2" t="inlineStr">
+        <is>
+          <t>141.0</t>
+        </is>
+      </c>
+      <c r="AC77" s="2" t="inlineStr">
+        <is>
+          <t>26/29</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="2" t="inlineStr"/>
+      <c r="B78" s="2" t="inlineStr">
+        <is>
+          <t>沪A37823D</t>
+        </is>
+      </c>
+      <c r="C78" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D78" s="2" t="inlineStr">
+        <is>
+          <t>16:10</t>
+        </is>
+      </c>
+      <c r="E78" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F78" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G78" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H78" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I78" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J78" s="2" t="inlineStr"/>
+      <c r="K78" s="2" t="inlineStr"/>
+      <c r="L78" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M78" s="2" t="inlineStr"/>
+      <c r="N78" s="2" t="inlineStr">
+        <is>
+          <t>07:31</t>
+        </is>
+      </c>
+      <c r="O78" s="2" t="inlineStr">
+        <is>
+          <t>15:21</t>
+        </is>
+      </c>
+      <c r="P78" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q78" s="2" t="inlineStr"/>
+      <c r="R78" s="2" t="inlineStr"/>
+      <c r="S78" s="2" t="inlineStr"/>
+      <c r="T78" s="2" t="inlineStr"/>
+      <c r="U78" s="2" t="inlineStr">
+        <is>
+          <t>16:10</t>
+        </is>
+      </c>
+      <c r="V78" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W78" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X78" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y78" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z78" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA78" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB78" s="2" t="inlineStr">
+        <is>
+          <t>135.0</t>
+        </is>
+      </c>
+      <c r="AC78" s="2" t="inlineStr">
+        <is>
+          <t>17/29</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-10-31-浦东35路.xlsx
+++ b/data/export/2026-10-31-浦东35路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC78"/>
+  <dimension ref="A1:AC84"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -669,7 +669,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:11</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -713,17 +713,17 @@
       </c>
       <c r="AA2" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB2" s="2" t="inlineStr">
         <is>
-          <t>127.7</t>
+          <t>128.8</t>
         </is>
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>4/29</t>
+          <t>5/29</t>
         </is>
       </c>
     </row>
@@ -788,7 +788,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:11</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -842,7 +842,7 @@
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>19/29</t>
+          <t>20/29</t>
         </is>
       </c>
     </row>
@@ -907,7 +907,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>11:31</t>
+          <t>16:11</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -946,14 +946,14 @@
       </c>
       <c r="Z4" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA4" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA4" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB4" s="2" t="inlineStr">
         <is>
           <t>128.5</t>
@@ -961,7 +961,7 @@
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>5/29</t>
+          <t>4/29</t>
         </is>
       </c>
     </row>
@@ -1145,7 +1145,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:11</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>11:51</t>
+          <t>16:11</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1303,7 +1303,7 @@
       </c>
       <c r="Z7" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA7" s="2" t="inlineStr">
@@ -1383,7 +1383,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:11</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1621,7 +1621,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:11</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1665,12 +1665,12 @@
       </c>
       <c r="AA10" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB10" s="2" t="inlineStr">
         <is>
-          <t>133.0</t>
+          <t>132.7</t>
         </is>
       </c>
       <c r="AC10" s="2" t="inlineStr">
@@ -1740,7 +1740,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>12:11</t>
+          <t>16:11</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1779,7 +1779,7 @@
       </c>
       <c r="Z11" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA11" s="2" t="inlineStr">
@@ -1859,7 +1859,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:11</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1974,7 +1974,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:11</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -2109,7 +2109,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:11</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2343,7 +2343,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>15:31</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2387,17 +2387,17 @@
       </c>
       <c r="AA16" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB16" s="2" t="inlineStr">
         <is>
-          <t>136.0</t>
+          <t>135.0</t>
         </is>
       </c>
       <c r="AC16" s="2" t="inlineStr">
         <is>
-          <t>19/29</t>
+          <t>17/29</t>
         </is>
       </c>
     </row>
@@ -2581,7 +2581,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>15:31</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2696,7 +2696,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>12:41</t>
+          <t>16:11</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2735,7 +2735,7 @@
       </c>
       <c r="Z19" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA19" s="2" t="inlineStr">
@@ -2934,7 +2934,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>15:51</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -2978,12 +2978,12 @@
       </c>
       <c r="AA21" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB21" s="2" t="inlineStr">
         <is>
-          <t>131.0</t>
+          <t>130.7</t>
         </is>
       </c>
       <c r="AC21" s="2" t="inlineStr">
@@ -3049,7 +3049,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:01</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -3098,12 +3098,12 @@
       </c>
       <c r="AB22" s="2" t="inlineStr">
         <is>
-          <t>133.5</t>
+          <t>135.0</t>
         </is>
       </c>
       <c r="AC22" s="2" t="inlineStr">
         <is>
-          <t>14/29</t>
+          <t>17/29</t>
         </is>
       </c>
     </row>
@@ -3333,7 +3333,7 @@
       </c>
       <c r="AC24" s="2" t="inlineStr">
         <is>
-          <t>19/29</t>
+          <t>20/29</t>
         </is>
       </c>
     </row>
@@ -3398,7 +3398,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>16:11</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3437,7 +3437,7 @@
       </c>
       <c r="Z25" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA25" s="2" t="inlineStr">
@@ -3517,7 +3517,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:11</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3561,17 +3561,17 @@
       </c>
       <c r="AA26" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB26" s="2" t="inlineStr">
         <is>
-          <t>135.0</t>
+          <t>133.3</t>
         </is>
       </c>
       <c r="AC26" s="2" t="inlineStr">
         <is>
-          <t>17/29</t>
+          <t>14/29</t>
         </is>
       </c>
     </row>
@@ -3636,7 +3636,7 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:11</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -3680,17 +3680,17 @@
       </c>
       <c r="AA27" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB27" s="2" t="inlineStr">
         <is>
-          <t>127.7</t>
+          <t>128.8</t>
         </is>
       </c>
       <c r="AC27" s="2" t="inlineStr">
         <is>
-          <t>4/29</t>
+          <t>5/29</t>
         </is>
       </c>
     </row>
@@ -3755,7 +3755,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:11</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -3809,7 +3809,7 @@
       </c>
       <c r="AC28" s="2" t="inlineStr">
         <is>
-          <t>19/29</t>
+          <t>20/29</t>
         </is>
       </c>
     </row>
@@ -3874,7 +3874,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>13:51</t>
+          <t>16:11</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -3913,7 +3913,7 @@
       </c>
       <c r="Z29" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA29" s="2" t="inlineStr">
@@ -3993,7 +3993,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>11:31</t>
+          <t>16:11</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -4032,14 +4032,14 @@
       </c>
       <c r="Z30" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA30" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA30" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB30" s="2" t="inlineStr">
         <is>
           <t>128.5</t>
@@ -4047,7 +4047,7 @@
       </c>
       <c r="AC30" s="2" t="inlineStr">
         <is>
-          <t>5/29</t>
+          <t>4/29</t>
         </is>
       </c>
     </row>
@@ -4112,7 +4112,7 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:11</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
@@ -4350,7 +4350,7 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:11</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
@@ -4469,7 +4469,7 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:11</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
@@ -4513,12 +4513,12 @@
       </c>
       <c r="AA34" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB34" s="2" t="inlineStr">
         <is>
-          <t>133.0</t>
+          <t>132.7</t>
         </is>
       </c>
       <c r="AC34" s="2" t="inlineStr">
@@ -4588,7 +4588,7 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>11:51</t>
+          <t>16:11</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
@@ -4627,7 +4627,7 @@
       </c>
       <c r="Z35" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA35" s="2" t="inlineStr">
@@ -4703,7 +4703,7 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>15:11</t>
+          <t>16:11</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
@@ -4949,7 +4949,7 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:11</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
@@ -5068,7 +5068,7 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:11</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
@@ -5187,7 +5187,7 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>12:11</t>
+          <t>16:11</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
@@ -5226,7 +5226,7 @@
       </c>
       <c r="Z40" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA40" s="2" t="inlineStr">
@@ -5425,7 +5425,7 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>15:31</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
@@ -5469,17 +5469,17 @@
       </c>
       <c r="AA42" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB42" s="2" t="inlineStr">
         <is>
-          <t>136.0</t>
+          <t>135.0</t>
         </is>
       </c>
       <c r="AC42" s="2" t="inlineStr">
         <is>
-          <t>19/29</t>
+          <t>17/29</t>
         </is>
       </c>
     </row>
@@ -5663,7 +5663,7 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>12:41</t>
+          <t>16:11</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
@@ -5702,7 +5702,7 @@
       </c>
       <c r="Z44" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA44" s="2" t="inlineStr">
@@ -5782,7 +5782,7 @@
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>15:31</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
@@ -5901,7 +5901,7 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>15:51</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
@@ -5945,12 +5945,12 @@
       </c>
       <c r="AA46" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB46" s="2" t="inlineStr">
         <is>
-          <t>131.0</t>
+          <t>130.7</t>
         </is>
       </c>
       <c r="AC46" s="2" t="inlineStr">
@@ -6139,7 +6139,7 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>16:11</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
@@ -6178,7 +6178,7 @@
       </c>
       <c r="Z48" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA48" s="2" t="inlineStr">
@@ -6258,7 +6258,7 @@
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:01</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
@@ -6307,12 +6307,12 @@
       </c>
       <c r="AB49" s="2" t="inlineStr">
         <is>
-          <t>133.5</t>
+          <t>135.0</t>
         </is>
       </c>
       <c r="AC49" s="2" t="inlineStr">
         <is>
-          <t>14/29</t>
+          <t>17/29</t>
         </is>
       </c>
     </row>
@@ -6377,7 +6377,7 @@
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:11</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
@@ -6421,17 +6421,17 @@
       </c>
       <c r="AA50" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB50" s="2" t="inlineStr">
         <is>
-          <t>127.7</t>
+          <t>128.8</t>
         </is>
       </c>
       <c r="AC50" s="2" t="inlineStr">
         <is>
-          <t>4/29</t>
+          <t>5/29</t>
         </is>
       </c>
     </row>
@@ -6496,7 +6496,7 @@
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:11</t>
         </is>
       </c>
       <c r="P51" s="2" t="inlineStr">
@@ -6540,17 +6540,17 @@
       </c>
       <c r="AA51" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB51" s="2" t="inlineStr">
         <is>
-          <t>135.0</t>
+          <t>133.3</t>
         </is>
       </c>
       <c r="AC51" s="2" t="inlineStr">
         <is>
-          <t>17/29</t>
+          <t>14/29</t>
         </is>
       </c>
     </row>
@@ -6615,7 +6615,7 @@
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>13:51</t>
+          <t>16:11</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
@@ -6654,7 +6654,7 @@
       </c>
       <c r="Z52" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA52" s="2" t="inlineStr">
@@ -6853,7 +6853,7 @@
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:11</t>
         </is>
       </c>
       <c r="P54" s="2" t="inlineStr">
@@ -6968,7 +6968,7 @@
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>15:11</t>
+          <t>16:11</t>
         </is>
       </c>
       <c r="P55" s="2" t="inlineStr">
@@ -7218,7 +7218,7 @@
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:11</t>
         </is>
       </c>
       <c r="P57" s="2" t="inlineStr">
@@ -7456,7 +7456,7 @@
       </c>
       <c r="O59" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:11</t>
         </is>
       </c>
       <c r="P59" s="2" t="inlineStr">
@@ -7560,12 +7560,12 @@
       <c r="K60" s="2" t="inlineStr"/>
       <c r="L60" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="M60" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N60" s="2" t="inlineStr">
@@ -7575,7 +7575,7 @@
       </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>15:31</t>
         </is>
       </c>
       <c r="P60" s="2" t="inlineStr">
@@ -7657,32 +7657,36 @@
       </c>
       <c r="F61" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G61" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H61" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>15:38</t>
         </is>
       </c>
       <c r="I61" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>133分钟</t>
         </is>
       </c>
       <c r="J61" s="2" t="inlineStr"/>
       <c r="K61" s="2" t="inlineStr"/>
       <c r="L61" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M61" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M61" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N61" s="2" t="inlineStr">
         <is>
           <t>07:11</t>
@@ -7690,7 +7694,7 @@
       </c>
       <c r="O61" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>15:31</t>
         </is>
       </c>
       <c r="P61" s="2" t="inlineStr">
@@ -7714,17 +7718,17 @@
       </c>
       <c r="W61" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X61" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y61" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z61" s="2" t="inlineStr">
@@ -7734,17 +7738,17 @@
       </c>
       <c r="AA61" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB61" s="2" t="inlineStr">
         <is>
-          <t>136.0</t>
+          <t>135.0</t>
         </is>
       </c>
       <c r="AC61" s="2" t="inlineStr">
         <is>
-          <t>19/29</t>
+          <t>17/29</t>
         </is>
       </c>
     </row>
@@ -7782,24 +7786,24 @@
       </c>
       <c r="H62" s="2" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>16:03</t>
         </is>
       </c>
       <c r="I62" s="2" t="inlineStr">
         <is>
-          <t>135分钟</t>
+          <t>138分钟</t>
         </is>
       </c>
       <c r="J62" s="2" t="inlineStr"/>
       <c r="K62" s="2" t="inlineStr"/>
       <c r="L62" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="M62" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N62" s="2" t="inlineStr">
@@ -7809,7 +7813,7 @@
       </c>
       <c r="O62" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:01</t>
         </is>
       </c>
       <c r="P62" s="2" t="inlineStr">
@@ -7858,12 +7862,12 @@
       </c>
       <c r="AB62" s="2" t="inlineStr">
         <is>
-          <t>133.5</t>
+          <t>135.0</t>
         </is>
       </c>
       <c r="AC62" s="2" t="inlineStr">
         <is>
-          <t>14/29</t>
+          <t>17/29</t>
         </is>
       </c>
     </row>
@@ -7891,32 +7895,36 @@
       </c>
       <c r="F63" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G63" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H63" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>15:55</t>
         </is>
       </c>
       <c r="I63" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>130分钟</t>
         </is>
       </c>
       <c r="J63" s="2" t="inlineStr"/>
       <c r="K63" s="2" t="inlineStr"/>
       <c r="L63" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M63" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M63" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N63" s="2" t="inlineStr">
         <is>
           <t>07:21</t>
@@ -7924,7 +7932,7 @@
       </c>
       <c r="O63" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>15:51</t>
         </is>
       </c>
       <c r="P63" s="2" t="inlineStr">
@@ -7948,17 +7956,17 @@
       </c>
       <c r="W63" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X63" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y63" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z63" s="2" t="inlineStr">
@@ -7968,12 +7976,12 @@
       </c>
       <c r="AA63" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB63" s="2" t="inlineStr">
         <is>
-          <t>131.0</t>
+          <t>130.7</t>
         </is>
       </c>
       <c r="AC63" s="2" t="inlineStr">
@@ -8006,32 +8014,36 @@
       </c>
       <c r="F64" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G64" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H64" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>16:17</t>
         </is>
       </c>
       <c r="I64" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>132分钟</t>
         </is>
       </c>
       <c r="J64" s="2" t="inlineStr"/>
       <c r="K64" s="2" t="inlineStr"/>
       <c r="L64" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M64" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M64" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N64" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -8039,7 +8051,7 @@
       </c>
       <c r="O64" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:11</t>
         </is>
       </c>
       <c r="P64" s="2" t="inlineStr">
@@ -8063,17 +8075,17 @@
       </c>
       <c r="W64" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X64" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y64" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z64" s="2" t="inlineStr">
@@ -8083,17 +8095,17 @@
       </c>
       <c r="AA64" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB64" s="2" t="inlineStr">
         <is>
-          <t>127.7</t>
+          <t>128.8</t>
         </is>
       </c>
       <c r="AC64" s="2" t="inlineStr">
         <is>
-          <t>4/29</t>
+          <t>5/29</t>
         </is>
       </c>
     </row>
@@ -8121,32 +8133,36 @@
       </c>
       <c r="F65" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G65" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H65" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="I65" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>130分钟</t>
         </is>
       </c>
       <c r="J65" s="2" t="inlineStr"/>
       <c r="K65" s="2" t="inlineStr"/>
       <c r="L65" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M65" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M65" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N65" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -8154,7 +8170,7 @@
       </c>
       <c r="O65" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:11</t>
         </is>
       </c>
       <c r="P65" s="2" t="inlineStr">
@@ -8178,17 +8194,17 @@
       </c>
       <c r="W65" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X65" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y65" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z65" s="2" t="inlineStr">
@@ -8198,17 +8214,17 @@
       </c>
       <c r="AA65" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB65" s="2" t="inlineStr">
         <is>
-          <t>135.0</t>
+          <t>133.3</t>
         </is>
       </c>
       <c r="AC65" s="2" t="inlineStr">
         <is>
-          <t>17/29</t>
+          <t>14/29</t>
         </is>
       </c>
     </row>
@@ -8236,32 +8252,36 @@
       </c>
       <c r="F66" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G66" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H66" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>16:37</t>
         </is>
       </c>
       <c r="I66" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>132分钟</t>
         </is>
       </c>
       <c r="J66" s="2" t="inlineStr"/>
       <c r="K66" s="2" t="inlineStr"/>
       <c r="L66" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M66" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M66" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N66" s="2" t="inlineStr">
         <is>
           <t>06:11</t>
@@ -8269,7 +8289,7 @@
       </c>
       <c r="O66" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:11</t>
         </is>
       </c>
       <c r="P66" s="2" t="inlineStr">
@@ -8293,17 +8313,17 @@
       </c>
       <c r="W66" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X66" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y66" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z66" s="2" t="inlineStr">
@@ -8313,12 +8333,12 @@
       </c>
       <c r="AA66" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB66" s="2" t="inlineStr">
         <is>
-          <t>133.0</t>
+          <t>132.7</t>
         </is>
       </c>
       <c r="AC66" s="2" t="inlineStr">
@@ -8384,7 +8404,7 @@
       </c>
       <c r="O67" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:11</t>
         </is>
       </c>
       <c r="P67" s="2" t="inlineStr">
@@ -8499,7 +8519,7 @@
       </c>
       <c r="O68" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:11</t>
         </is>
       </c>
       <c r="P68" s="2" t="inlineStr">
@@ -8553,7 +8573,7 @@
       </c>
       <c r="AC68" s="2" t="inlineStr">
         <is>
-          <t>19/29</t>
+          <t>20/29</t>
         </is>
       </c>
     </row>
@@ -8614,7 +8634,7 @@
       </c>
       <c r="O69" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:11</t>
         </is>
       </c>
       <c r="P69" s="2" t="inlineStr">
@@ -8840,7 +8860,7 @@
       </c>
       <c r="O71" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:11</t>
         </is>
       </c>
       <c r="P71" s="2" t="inlineStr">
@@ -8955,7 +8975,7 @@
       </c>
       <c r="O72" s="2" t="inlineStr">
         <is>
-          <t>15:11</t>
+          <t>16:11</t>
         </is>
       </c>
       <c r="P72" s="2" t="inlineStr">
@@ -9066,7 +9086,7 @@
       </c>
       <c r="O73" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:11</t>
         </is>
       </c>
       <c r="P73" s="2" t="inlineStr">
@@ -9292,7 +9312,7 @@
       </c>
       <c r="O75" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:11</t>
         </is>
       </c>
       <c r="P75" s="2" t="inlineStr">
@@ -9407,7 +9427,7 @@
       </c>
       <c r="O76" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:11</t>
         </is>
       </c>
       <c r="P76" s="2" t="inlineStr">
@@ -9518,7 +9538,7 @@
       </c>
       <c r="O77" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:11</t>
         </is>
       </c>
       <c r="P77" s="2" t="inlineStr">
@@ -9633,7 +9653,7 @@
       </c>
       <c r="O78" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:11</t>
         </is>
       </c>
       <c r="P78" s="2" t="inlineStr">
@@ -9691,6 +9711,696 @@
         </is>
       </c>
     </row>
+    <row r="79">
+      <c r="A79" s="2" t="inlineStr"/>
+      <c r="B79" s="2" t="inlineStr">
+        <is>
+          <t>沪A65668D</t>
+        </is>
+      </c>
+      <c r="C79" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D79" s="2" t="inlineStr">
+        <is>
+          <t>16:15</t>
+        </is>
+      </c>
+      <c r="E79" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F79" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G79" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H79" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I79" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J79" s="2" t="inlineStr"/>
+      <c r="K79" s="2" t="inlineStr"/>
+      <c r="L79" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M79" s="2" t="inlineStr"/>
+      <c r="N79" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="O79" s="2" t="inlineStr">
+        <is>
+          <t>16:11</t>
+        </is>
+      </c>
+      <c r="P79" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q79" s="2" t="inlineStr"/>
+      <c r="R79" s="2" t="inlineStr"/>
+      <c r="S79" s="2" t="inlineStr"/>
+      <c r="T79" s="2" t="inlineStr"/>
+      <c r="U79" s="2" t="inlineStr">
+        <is>
+          <t>16:15</t>
+        </is>
+      </c>
+      <c r="V79" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W79" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X79" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y79" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z79" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA79" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB79" s="2" t="inlineStr">
+        <is>
+          <t>123.0</t>
+        </is>
+      </c>
+      <c r="AC79" s="2" t="inlineStr">
+        <is>
+          <t>1/29</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="2" t="inlineStr"/>
+      <c r="B80" s="2" t="inlineStr">
+        <is>
+          <t>沪A55102D</t>
+        </is>
+      </c>
+      <c r="C80" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D80" s="2" t="inlineStr">
+        <is>
+          <t>16:30</t>
+        </is>
+      </c>
+      <c r="E80" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F80" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G80" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H80" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I80" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J80" s="2" t="inlineStr"/>
+      <c r="K80" s="2" t="inlineStr"/>
+      <c r="L80" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M80" s="2" t="inlineStr"/>
+      <c r="N80" s="2" t="inlineStr">
+        <is>
+          <t>06:51</t>
+        </is>
+      </c>
+      <c r="O80" s="2" t="inlineStr">
+        <is>
+          <t>16:11</t>
+        </is>
+      </c>
+      <c r="P80" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q80" s="2" t="inlineStr"/>
+      <c r="R80" s="2" t="inlineStr"/>
+      <c r="S80" s="2" t="inlineStr"/>
+      <c r="T80" s="2" t="inlineStr"/>
+      <c r="U80" s="2" t="inlineStr">
+        <is>
+          <t>16:30</t>
+        </is>
+      </c>
+      <c r="V80" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W80" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X80" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y80" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z80" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA80" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB80" s="2" t="inlineStr">
+        <is>
+          <t>132.0</t>
+        </is>
+      </c>
+      <c r="AC80" s="2" t="inlineStr">
+        <is>
+          <t>11/29</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="2" t="inlineStr"/>
+      <c r="B81" s="2" t="inlineStr">
+        <is>
+          <t>沪A67712D</t>
+        </is>
+      </c>
+      <c r="C81" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D81" s="2" t="inlineStr">
+        <is>
+          <t>16:30</t>
+        </is>
+      </c>
+      <c r="E81" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F81" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G81" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H81" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I81" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J81" s="2" t="inlineStr"/>
+      <c r="K81" s="2" t="inlineStr"/>
+      <c r="L81" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M81" s="2" t="inlineStr"/>
+      <c r="N81" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O81" s="2" t="inlineStr">
+        <is>
+          <t>16:11</t>
+        </is>
+      </c>
+      <c r="P81" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q81" s="2" t="inlineStr"/>
+      <c r="R81" s="2" t="inlineStr"/>
+      <c r="S81" s="2" t="inlineStr"/>
+      <c r="T81" s="2" t="inlineStr"/>
+      <c r="U81" s="2" t="inlineStr">
+        <is>
+          <t>16:30</t>
+        </is>
+      </c>
+      <c r="V81" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W81" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X81" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y81" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z81" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA81" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB81" s="2" t="inlineStr">
+        <is>
+          <t>128.5</t>
+        </is>
+      </c>
+      <c r="AC81" s="2" t="inlineStr">
+        <is>
+          <t>4/29</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="2" t="inlineStr"/>
+      <c r="B82" s="2" t="inlineStr">
+        <is>
+          <t>沪A67057D</t>
+        </is>
+      </c>
+      <c r="C82" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D82" s="2" t="inlineStr">
+        <is>
+          <t>16:45</t>
+        </is>
+      </c>
+      <c r="E82" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F82" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G82" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H82" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I82" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J82" s="2" t="inlineStr"/>
+      <c r="K82" s="2" t="inlineStr"/>
+      <c r="L82" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M82" s="2" t="inlineStr"/>
+      <c r="N82" s="2" t="inlineStr">
+        <is>
+          <t>07:01</t>
+        </is>
+      </c>
+      <c r="O82" s="2" t="inlineStr">
+        <is>
+          <t>16:11</t>
+        </is>
+      </c>
+      <c r="P82" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q82" s="2" t="inlineStr"/>
+      <c r="R82" s="2" t="inlineStr"/>
+      <c r="S82" s="2" t="inlineStr"/>
+      <c r="T82" s="2" t="inlineStr"/>
+      <c r="U82" s="2" t="inlineStr">
+        <is>
+          <t>16:45</t>
+        </is>
+      </c>
+      <c r="V82" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W82" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X82" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y82" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z82" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA82" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB82" s="2" t="inlineStr">
+        <is>
+          <t>129.5</t>
+        </is>
+      </c>
+      <c r="AC82" s="2" t="inlineStr">
+        <is>
+          <t>6/29</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="2" t="inlineStr"/>
+      <c r="B83" s="2" t="inlineStr">
+        <is>
+          <t>沪A68375D</t>
+        </is>
+      </c>
+      <c r="C83" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D83" s="2" t="inlineStr">
+        <is>
+          <t>16:45</t>
+        </is>
+      </c>
+      <c r="E83" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F83" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G83" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H83" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I83" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J83" s="2" t="inlineStr"/>
+      <c r="K83" s="2" t="inlineStr"/>
+      <c r="L83" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M83" s="2" t="inlineStr"/>
+      <c r="N83" s="2" t="inlineStr">
+        <is>
+          <t>06:11</t>
+        </is>
+      </c>
+      <c r="O83" s="2" t="inlineStr">
+        <is>
+          <t>16:11</t>
+        </is>
+      </c>
+      <c r="P83" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q83" s="2" t="inlineStr"/>
+      <c r="R83" s="2" t="inlineStr"/>
+      <c r="S83" s="2" t="inlineStr"/>
+      <c r="T83" s="2" t="inlineStr"/>
+      <c r="U83" s="2" t="inlineStr">
+        <is>
+          <t>16:45</t>
+        </is>
+      </c>
+      <c r="V83" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W83" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X83" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y83" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z83" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA83" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB83" s="2" t="inlineStr">
+        <is>
+          <t>134.5</t>
+        </is>
+      </c>
+      <c r="AC83" s="2" t="inlineStr">
+        <is>
+          <t>16/29</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="2" t="inlineStr"/>
+      <c r="B84" s="2" t="inlineStr">
+        <is>
+          <t>沪A68261D</t>
+        </is>
+      </c>
+      <c r="C84" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D84" s="2" t="inlineStr">
+        <is>
+          <t>17:00</t>
+        </is>
+      </c>
+      <c r="E84" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F84" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G84" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H84" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I84" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J84" s="2" t="inlineStr"/>
+      <c r="K84" s="2" t="inlineStr"/>
+      <c r="L84" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M84" s="2" t="inlineStr"/>
+      <c r="N84" s="2" t="inlineStr">
+        <is>
+          <t>06:41</t>
+        </is>
+      </c>
+      <c r="O84" s="2" t="inlineStr">
+        <is>
+          <t>16:11</t>
+        </is>
+      </c>
+      <c r="P84" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q84" s="2" t="inlineStr"/>
+      <c r="R84" s="2" t="inlineStr"/>
+      <c r="S84" s="2" t="inlineStr"/>
+      <c r="T84" s="2" t="inlineStr"/>
+      <c r="U84" s="2" t="inlineStr">
+        <is>
+          <t>17:00</t>
+        </is>
+      </c>
+      <c r="V84" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W84" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X84" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y84" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z84" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA84" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB84" s="2" t="inlineStr">
+        <is>
+          <t>130.5</t>
+        </is>
+      </c>
+      <c r="AC84" s="2" t="inlineStr">
+        <is>
+          <t>9/29</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/export/2026-10-31-浦东35路.xlsx
+++ b/data/export/2026-10-31-浦东35路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC84"/>
+  <dimension ref="A1:AC85"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -788,7 +788,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>16:11</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -907,7 +907,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>16:11</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -1026,7 +1026,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1065,7 +1065,7 @@
       </c>
       <c r="Z5" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA5" s="2" t="inlineStr">
@@ -1145,7 +1145,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>16:11</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1189,17 +1189,17 @@
       </c>
       <c r="AA6" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB6" s="2" t="inlineStr">
         <is>
-          <t>130.0</t>
+          <t>130.5</t>
         </is>
       </c>
       <c r="AC6" s="2" t="inlineStr">
         <is>
-          <t>7/29</t>
+          <t>8/29</t>
         </is>
       </c>
     </row>
@@ -1264,7 +1264,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>16:11</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1383,7 +1383,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>16:11</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1621,7 +1621,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>16:11</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1670,7 +1670,7 @@
       </c>
       <c r="AB10" s="2" t="inlineStr">
         <is>
-          <t>132.7</t>
+          <t>132.3</t>
         </is>
       </c>
       <c r="AC10" s="2" t="inlineStr">
@@ -1740,7 +1740,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>16:11</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1794,7 +1794,7 @@
       </c>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>9/29</t>
+          <t>8/29</t>
         </is>
       </c>
     </row>
@@ -1859,7 +1859,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>16:11</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1974,7 +1974,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>16:11</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -2109,7 +2109,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>16:11</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2696,7 +2696,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>16:11</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -3398,7 +3398,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>16:11</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3755,7 +3755,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>16:11</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -3874,7 +3874,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>16:11</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -3993,7 +3993,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>16:11</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -4112,7 +4112,7 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>16:11</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
@@ -4156,17 +4156,17 @@
       </c>
       <c r="AA31" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB31" s="2" t="inlineStr">
         <is>
-          <t>130.0</t>
+          <t>130.5</t>
         </is>
       </c>
       <c r="AC31" s="2" t="inlineStr">
         <is>
-          <t>7/29</t>
+          <t>8/29</t>
         </is>
       </c>
     </row>
@@ -4231,7 +4231,7 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
@@ -4270,7 +4270,7 @@
       </c>
       <c r="Z32" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA32" s="2" t="inlineStr">
@@ -4350,7 +4350,7 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>16:11</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
@@ -4469,7 +4469,7 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>16:11</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
@@ -4518,7 +4518,7 @@
       </c>
       <c r="AB34" s="2" t="inlineStr">
         <is>
-          <t>132.7</t>
+          <t>132.3</t>
         </is>
       </c>
       <c r="AC34" s="2" t="inlineStr">
@@ -4588,7 +4588,7 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>16:11</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
@@ -4703,7 +4703,7 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>16:11</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
@@ -4949,7 +4949,7 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>16:11</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
@@ -5068,7 +5068,7 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>16:11</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
@@ -5187,7 +5187,7 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>16:11</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
@@ -5241,7 +5241,7 @@
       </c>
       <c r="AC40" s="2" t="inlineStr">
         <is>
-          <t>9/29</t>
+          <t>8/29</t>
         </is>
       </c>
     </row>
@@ -5663,7 +5663,7 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>16:11</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
@@ -6139,7 +6139,7 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>16:11</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
@@ -6615,7 +6615,7 @@
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>16:11</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
@@ -6734,7 +6734,7 @@
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P53" s="2" t="inlineStr">
@@ -6773,7 +6773,7 @@
       </c>
       <c r="Z53" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA53" s="2" t="inlineStr">
@@ -6853,7 +6853,7 @@
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>16:11</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P54" s="2" t="inlineStr">
@@ -6897,17 +6897,17 @@
       </c>
       <c r="AA54" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB54" s="2" t="inlineStr">
         <is>
-          <t>130.0</t>
+          <t>130.5</t>
         </is>
       </c>
       <c r="AC54" s="2" t="inlineStr">
         <is>
-          <t>7/29</t>
+          <t>8/29</t>
         </is>
       </c>
     </row>
@@ -6968,7 +6968,7 @@
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>16:11</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P55" s="2" t="inlineStr">
@@ -7218,7 +7218,7 @@
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>16:11</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P57" s="2" t="inlineStr">
@@ -7456,7 +7456,7 @@
       </c>
       <c r="O59" s="2" t="inlineStr">
         <is>
-          <t>16:11</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P59" s="2" t="inlineStr">
@@ -8262,12 +8262,12 @@
       </c>
       <c r="H66" s="2" t="inlineStr">
         <is>
-          <t>16:37</t>
+          <t>16:36</t>
         </is>
       </c>
       <c r="I66" s="2" t="inlineStr">
         <is>
-          <t>132分钟</t>
+          <t>131分钟</t>
         </is>
       </c>
       <c r="J66" s="2" t="inlineStr"/>
@@ -8289,7 +8289,7 @@
       </c>
       <c r="O66" s="2" t="inlineStr">
         <is>
-          <t>16:11</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P66" s="2" t="inlineStr">
@@ -8338,7 +8338,7 @@
       </c>
       <c r="AB66" s="2" t="inlineStr">
         <is>
-          <t>132.7</t>
+          <t>132.3</t>
         </is>
       </c>
       <c r="AC66" s="2" t="inlineStr">
@@ -8371,32 +8371,36 @@
       </c>
       <c r="F67" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G67" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H67" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>16:47</t>
         </is>
       </c>
       <c r="I67" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>132分钟</t>
         </is>
       </c>
       <c r="J67" s="2" t="inlineStr"/>
       <c r="K67" s="2" t="inlineStr"/>
       <c r="L67" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M67" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M67" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N67" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -8404,7 +8408,7 @@
       </c>
       <c r="O67" s="2" t="inlineStr">
         <is>
-          <t>16:11</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P67" s="2" t="inlineStr">
@@ -8428,17 +8432,17 @@
       </c>
       <c r="W67" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X67" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y67" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z67" s="2" t="inlineStr">
@@ -8448,17 +8452,17 @@
       </c>
       <c r="AA67" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB67" s="2" t="inlineStr">
         <is>
-          <t>130.0</t>
+          <t>130.5</t>
         </is>
       </c>
       <c r="AC67" s="2" t="inlineStr">
         <is>
-          <t>7/29</t>
+          <t>8/29</t>
         </is>
       </c>
     </row>
@@ -8519,7 +8523,7 @@
       </c>
       <c r="O68" s="2" t="inlineStr">
         <is>
-          <t>16:11</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P68" s="2" t="inlineStr">
@@ -8634,7 +8638,7 @@
       </c>
       <c r="O69" s="2" t="inlineStr">
         <is>
-          <t>16:11</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P69" s="2" t="inlineStr">
@@ -8860,7 +8864,7 @@
       </c>
       <c r="O71" s="2" t="inlineStr">
         <is>
-          <t>16:11</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P71" s="2" t="inlineStr">
@@ -8975,7 +8979,7 @@
       </c>
       <c r="O72" s="2" t="inlineStr">
         <is>
-          <t>16:11</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P72" s="2" t="inlineStr">
@@ -9086,7 +9090,7 @@
       </c>
       <c r="O73" s="2" t="inlineStr">
         <is>
-          <t>16:11</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P73" s="2" t="inlineStr">
@@ -9312,7 +9316,7 @@
       </c>
       <c r="O75" s="2" t="inlineStr">
         <is>
-          <t>16:11</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P75" s="2" t="inlineStr">
@@ -9427,7 +9431,7 @@
       </c>
       <c r="O76" s="2" t="inlineStr">
         <is>
-          <t>16:11</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P76" s="2" t="inlineStr">
@@ -9538,7 +9542,7 @@
       </c>
       <c r="O77" s="2" t="inlineStr">
         <is>
-          <t>16:11</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P77" s="2" t="inlineStr">
@@ -9653,7 +9657,7 @@
       </c>
       <c r="O78" s="2" t="inlineStr">
         <is>
-          <t>16:11</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P78" s="2" t="inlineStr">
@@ -9768,7 +9772,7 @@
       </c>
       <c r="O79" s="2" t="inlineStr">
         <is>
-          <t>16:11</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P79" s="2" t="inlineStr">
@@ -9883,7 +9887,7 @@
       </c>
       <c r="O80" s="2" t="inlineStr">
         <is>
-          <t>16:11</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P80" s="2" t="inlineStr">
@@ -9998,7 +10002,7 @@
       </c>
       <c r="O81" s="2" t="inlineStr">
         <is>
-          <t>16:11</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P81" s="2" t="inlineStr">
@@ -10113,7 +10117,7 @@
       </c>
       <c r="O82" s="2" t="inlineStr">
         <is>
-          <t>16:11</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P82" s="2" t="inlineStr">
@@ -10228,7 +10232,7 @@
       </c>
       <c r="O83" s="2" t="inlineStr">
         <is>
-          <t>16:11</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P83" s="2" t="inlineStr">
@@ -10290,22 +10294,22 @@
       <c r="A84" s="2" t="inlineStr"/>
       <c r="B84" s="2" t="inlineStr">
         <is>
-          <t>沪A68261D</t>
+          <t>沪A62981D</t>
         </is>
       </c>
       <c r="C84" s="2" t="inlineStr">
         <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D84" s="2" t="inlineStr">
+        <is>
+          <t>17:00</t>
+        </is>
+      </c>
+      <c r="E84" s="2" t="inlineStr">
+        <is>
           <t>东高路张杨北路</t>
-        </is>
-      </c>
-      <c r="D84" s="2" t="inlineStr">
-        <is>
-          <t>17:00</t>
-        </is>
-      </c>
-      <c r="E84" s="2" t="inlineStr">
-        <is>
-          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="F84" s="2" t="inlineStr">
@@ -10338,12 +10342,12 @@
       <c r="M84" s="2" t="inlineStr"/>
       <c r="N84" s="2" t="inlineStr">
         <is>
-          <t>06:41</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="O84" s="2" t="inlineStr">
         <is>
-          <t>16:11</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P84" s="2" t="inlineStr">
@@ -10382,22 +10386,137 @@
       </c>
       <c r="Z84" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA84" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB84" s="2" t="inlineStr">
+        <is>
+          <t>139.7</t>
+        </is>
+      </c>
+      <c r="AC84" s="2" t="inlineStr">
+        <is>
+          <t>24/29</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="2" t="inlineStr"/>
+      <c r="B85" s="2" t="inlineStr">
+        <is>
+          <t>沪A68261D</t>
+        </is>
+      </c>
+      <c r="C85" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D85" s="2" t="inlineStr">
+        <is>
+          <t>17:00</t>
+        </is>
+      </c>
+      <c r="E85" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F85" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G85" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H85" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I85" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J85" s="2" t="inlineStr"/>
+      <c r="K85" s="2" t="inlineStr"/>
+      <c r="L85" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M85" s="2" t="inlineStr"/>
+      <c r="N85" s="2" t="inlineStr">
+        <is>
+          <t>06:41</t>
+        </is>
+      </c>
+      <c r="O85" s="2" t="inlineStr">
+        <is>
+          <t>16:21</t>
+        </is>
+      </c>
+      <c r="P85" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q85" s="2" t="inlineStr"/>
+      <c r="R85" s="2" t="inlineStr"/>
+      <c r="S85" s="2" t="inlineStr"/>
+      <c r="T85" s="2" t="inlineStr"/>
+      <c r="U85" s="2" t="inlineStr">
+        <is>
+          <t>17:00</t>
+        </is>
+      </c>
+      <c r="V85" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W85" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X85" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y85" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z85" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA85" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AB84" s="2" t="inlineStr">
+      <c r="AB85" s="2" t="inlineStr">
         <is>
           <t>130.5</t>
         </is>
       </c>
-      <c r="AC84" s="2" t="inlineStr">
-        <is>
-          <t>9/29</t>
+      <c r="AC85" s="2" t="inlineStr">
+        <is>
+          <t>8/29</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-10-31-浦东35路.xlsx
+++ b/data/export/2026-10-31-浦东35路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC85"/>
+  <dimension ref="A1:AC92"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -788,7 +788,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -827,22 +827,22 @@
       </c>
       <c r="Z3" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA3" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA3" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB3" s="2" t="inlineStr">
         <is>
-          <t>136.0</t>
+          <t>137.7</t>
         </is>
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>20/29</t>
+          <t>22/29</t>
         </is>
       </c>
     </row>
@@ -907,7 +907,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -1026,7 +1026,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1145,7 +1145,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>16:41</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1199,7 +1199,7 @@
       </c>
       <c r="AC6" s="2" t="inlineStr">
         <is>
-          <t>8/29</t>
+          <t>7/29</t>
         </is>
       </c>
     </row>
@@ -1264,7 +1264,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1318,7 +1318,7 @@
       </c>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>16/29</t>
+          <t>15/29</t>
         </is>
       </c>
     </row>
@@ -1383,7 +1383,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1422,22 +1422,22 @@
       </c>
       <c r="Z8" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA8" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA8" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB8" s="2" t="inlineStr">
         <is>
-          <t>136.5</t>
+          <t>138.0</t>
         </is>
       </c>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>22/29</t>
+          <t>23/29</t>
         </is>
       </c>
     </row>
@@ -1502,7 +1502,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>14:31</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1541,7 +1541,7 @@
       </c>
       <c r="Z9" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA9" s="2" t="inlineStr">
@@ -1621,7 +1621,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1660,14 +1660,14 @@
       </c>
       <c r="Z10" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA10" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA10" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB10" s="2" t="inlineStr">
         <is>
           <t>132.3</t>
@@ -1675,7 +1675,7 @@
       </c>
       <c r="AC10" s="2" t="inlineStr">
         <is>
-          <t>13/29</t>
+          <t>12/29</t>
         </is>
       </c>
     </row>
@@ -1740,7 +1740,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1794,7 +1794,7 @@
       </c>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>8/29</t>
+          <t>7/29</t>
         </is>
       </c>
     </row>
@@ -1859,7 +1859,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1903,17 +1903,17 @@
       </c>
       <c r="AA12" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB12" s="2" t="inlineStr">
         <is>
-          <t>130.0</t>
+          <t>136.5</t>
         </is>
       </c>
       <c r="AC12" s="2" t="inlineStr">
         <is>
-          <t>7/29</t>
+          <t>20/29</t>
         </is>
       </c>
     </row>
@@ -1974,7 +1974,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -2029,22 +2029,22 @@
       </c>
       <c r="Z13" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA13" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB13" s="2" t="inlineStr">
         <is>
-          <t>139.0</t>
+          <t>137.5</t>
         </is>
       </c>
       <c r="AC13" s="2" t="inlineStr">
         <is>
-          <t>23/29</t>
+          <t>21/29</t>
         </is>
       </c>
     </row>
@@ -2109,7 +2109,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2224,7 +2224,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>15:01</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2263,7 +2263,7 @@
       </c>
       <c r="Z15" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA15" s="2" t="inlineStr">
@@ -2397,7 +2397,7 @@
       </c>
       <c r="AC16" s="2" t="inlineStr">
         <is>
-          <t>17/29</t>
+          <t>16/29</t>
         </is>
       </c>
     </row>
@@ -2462,7 +2462,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>12:51</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2501,7 +2501,7 @@
       </c>
       <c r="Z17" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA17" s="2" t="inlineStr">
@@ -2581,7 +2581,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>15:31</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2620,14 +2620,14 @@
       </c>
       <c r="Z18" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA18" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA18" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB18" s="2" t="inlineStr">
         <is>
           <t>134.0</t>
@@ -2635,7 +2635,7 @@
       </c>
       <c r="AC18" s="2" t="inlineStr">
         <is>
-          <t>15/29</t>
+          <t>14/29</t>
         </is>
       </c>
     </row>
@@ -2696,7 +2696,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2869,7 +2869,7 @@
       </c>
       <c r="AC20" s="2" t="inlineStr">
         <is>
-          <t>11/29</t>
+          <t>10/29</t>
         </is>
       </c>
     </row>
@@ -2988,7 +2988,7 @@
       </c>
       <c r="AC21" s="2" t="inlineStr">
         <is>
-          <t>10/29</t>
+          <t>9/29</t>
         </is>
       </c>
     </row>
@@ -3049,7 +3049,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>16:01</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -3088,7 +3088,7 @@
       </c>
       <c r="Z22" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA22" s="2" t="inlineStr">
@@ -3103,7 +3103,7 @@
       </c>
       <c r="AC22" s="2" t="inlineStr">
         <is>
-          <t>17/29</t>
+          <t>16/29</t>
         </is>
       </c>
     </row>
@@ -3333,7 +3333,7 @@
       </c>
       <c r="AC24" s="2" t="inlineStr">
         <is>
-          <t>20/29</t>
+          <t>19/29</t>
         </is>
       </c>
     </row>
@@ -3398,7 +3398,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3452,7 +3452,7 @@
       </c>
       <c r="AC25" s="2" t="inlineStr">
         <is>
-          <t>11/29</t>
+          <t>10/29</t>
         </is>
       </c>
     </row>
@@ -3571,7 +3571,7 @@
       </c>
       <c r="AC26" s="2" t="inlineStr">
         <is>
-          <t>14/29</t>
+          <t>13/29</t>
         </is>
       </c>
     </row>
@@ -3755,7 +3755,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -3794,22 +3794,22 @@
       </c>
       <c r="Z28" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA28" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA28" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB28" s="2" t="inlineStr">
         <is>
-          <t>136.0</t>
+          <t>137.7</t>
         </is>
       </c>
       <c r="AC28" s="2" t="inlineStr">
         <is>
-          <t>20/29</t>
+          <t>22/29</t>
         </is>
       </c>
     </row>
@@ -3874,7 +3874,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -3993,7 +3993,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -4112,7 +4112,7 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>16:41</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
@@ -4166,7 +4166,7 @@
       </c>
       <c r="AC31" s="2" t="inlineStr">
         <is>
-          <t>8/29</t>
+          <t>7/29</t>
         </is>
       </c>
     </row>
@@ -4231,7 +4231,7 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
@@ -4350,7 +4350,7 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
@@ -4389,22 +4389,22 @@
       </c>
       <c r="Z33" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA33" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA33" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB33" s="2" t="inlineStr">
         <is>
-          <t>136.5</t>
+          <t>138.0</t>
         </is>
       </c>
       <c r="AC33" s="2" t="inlineStr">
         <is>
-          <t>22/29</t>
+          <t>23/29</t>
         </is>
       </c>
     </row>
@@ -4469,7 +4469,7 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
@@ -4508,14 +4508,14 @@
       </c>
       <c r="Z34" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA34" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA34" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB34" s="2" t="inlineStr">
         <is>
           <t>132.3</t>
@@ -4523,7 +4523,7 @@
       </c>
       <c r="AC34" s="2" t="inlineStr">
         <is>
-          <t>13/29</t>
+          <t>12/29</t>
         </is>
       </c>
     </row>
@@ -4588,7 +4588,7 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
@@ -4642,7 +4642,7 @@
       </c>
       <c r="AC35" s="2" t="inlineStr">
         <is>
-          <t>16/29</t>
+          <t>15/29</t>
         </is>
       </c>
     </row>
@@ -4703,7 +4703,7 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
@@ -4834,7 +4834,7 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>14:31</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
@@ -4873,7 +4873,7 @@
       </c>
       <c r="Z37" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA37" s="2" t="inlineStr">
@@ -4949,7 +4949,7 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
@@ -4993,17 +4993,17 @@
       </c>
       <c r="AA38" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB38" s="2" t="inlineStr">
         <is>
-          <t>130.0</t>
+          <t>136.5</t>
         </is>
       </c>
       <c r="AC38" s="2" t="inlineStr">
         <is>
-          <t>7/29</t>
+          <t>20/29</t>
         </is>
       </c>
     </row>
@@ -5068,7 +5068,7 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
@@ -5187,7 +5187,7 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
@@ -5241,7 +5241,7 @@
       </c>
       <c r="AC40" s="2" t="inlineStr">
         <is>
-          <t>8/29</t>
+          <t>7/29</t>
         </is>
       </c>
     </row>
@@ -5306,7 +5306,7 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>15:01</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
@@ -5345,7 +5345,7 @@
       </c>
       <c r="Z41" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA41" s="2" t="inlineStr">
@@ -5479,7 +5479,7 @@
       </c>
       <c r="AC42" s="2" t="inlineStr">
         <is>
-          <t>17/29</t>
+          <t>16/29</t>
         </is>
       </c>
     </row>
@@ -5544,7 +5544,7 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>12:51</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
@@ -5583,7 +5583,7 @@
       </c>
       <c r="Z43" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA43" s="2" t="inlineStr">
@@ -5663,7 +5663,7 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
@@ -5782,7 +5782,7 @@
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>15:31</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
@@ -5821,14 +5821,14 @@
       </c>
       <c r="Z45" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA45" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA45" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB45" s="2" t="inlineStr">
         <is>
           <t>134.0</t>
@@ -5836,7 +5836,7 @@
       </c>
       <c r="AC45" s="2" t="inlineStr">
         <is>
-          <t>15/29</t>
+          <t>14/29</t>
         </is>
       </c>
     </row>
@@ -5955,7 +5955,7 @@
       </c>
       <c r="AC46" s="2" t="inlineStr">
         <is>
-          <t>10/29</t>
+          <t>9/29</t>
         </is>
       </c>
     </row>
@@ -6074,7 +6074,7 @@
       </c>
       <c r="AC47" s="2" t="inlineStr">
         <is>
-          <t>11/29</t>
+          <t>10/29</t>
         </is>
       </c>
     </row>
@@ -6139,7 +6139,7 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
@@ -6193,7 +6193,7 @@
       </c>
       <c r="AC48" s="2" t="inlineStr">
         <is>
-          <t>11/29</t>
+          <t>10/29</t>
         </is>
       </c>
     </row>
@@ -6258,7 +6258,7 @@
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>16:01</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
@@ -6297,7 +6297,7 @@
       </c>
       <c r="Z49" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA49" s="2" t="inlineStr">
@@ -6312,7 +6312,7 @@
       </c>
       <c r="AC49" s="2" t="inlineStr">
         <is>
-          <t>17/29</t>
+          <t>16/29</t>
         </is>
       </c>
     </row>
@@ -6550,7 +6550,7 @@
       </c>
       <c r="AC51" s="2" t="inlineStr">
         <is>
-          <t>14/29</t>
+          <t>13/29</t>
         </is>
       </c>
     </row>
@@ -6615,7 +6615,7 @@
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
@@ -6734,7 +6734,7 @@
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P53" s="2" t="inlineStr">
@@ -6853,7 +6853,7 @@
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>16:41</t>
         </is>
       </c>
       <c r="P54" s="2" t="inlineStr">
@@ -6907,7 +6907,7 @@
       </c>
       <c r="AC54" s="2" t="inlineStr">
         <is>
-          <t>8/29</t>
+          <t>7/29</t>
         </is>
       </c>
     </row>
@@ -6968,7 +6968,7 @@
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P55" s="2" t="inlineStr">
@@ -7099,7 +7099,7 @@
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>14:31</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P56" s="2" t="inlineStr">
@@ -7138,7 +7138,7 @@
       </c>
       <c r="Z56" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA56" s="2" t="inlineStr">
@@ -7218,7 +7218,7 @@
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P57" s="2" t="inlineStr">
@@ -7257,22 +7257,22 @@
       </c>
       <c r="Z57" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA57" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB57" s="2" t="inlineStr">
         <is>
-          <t>139.0</t>
+          <t>137.5</t>
         </is>
       </c>
       <c r="AC57" s="2" t="inlineStr">
         <is>
-          <t>23/29</t>
+          <t>21/29</t>
         </is>
       </c>
     </row>
@@ -7337,7 +7337,7 @@
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>15:01</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P58" s="2" t="inlineStr">
@@ -7376,7 +7376,7 @@
       </c>
       <c r="Z58" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA58" s="2" t="inlineStr">
@@ -7456,7 +7456,7 @@
       </c>
       <c r="O59" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P59" s="2" t="inlineStr">
@@ -7510,7 +7510,7 @@
       </c>
       <c r="AC59" s="2" t="inlineStr">
         <is>
-          <t>17/29</t>
+          <t>16/29</t>
         </is>
       </c>
     </row>
@@ -7575,7 +7575,7 @@
       </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>15:31</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P60" s="2" t="inlineStr">
@@ -7614,14 +7614,14 @@
       </c>
       <c r="Z60" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA60" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA60" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB60" s="2" t="inlineStr">
         <is>
           <t>134.0</t>
@@ -7629,7 +7629,7 @@
       </c>
       <c r="AC60" s="2" t="inlineStr">
         <is>
-          <t>15/29</t>
+          <t>14/29</t>
         </is>
       </c>
     </row>
@@ -7748,7 +7748,7 @@
       </c>
       <c r="AC61" s="2" t="inlineStr">
         <is>
-          <t>17/29</t>
+          <t>16/29</t>
         </is>
       </c>
     </row>
@@ -7813,7 +7813,7 @@
       </c>
       <c r="O62" s="2" t="inlineStr">
         <is>
-          <t>16:01</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P62" s="2" t="inlineStr">
@@ -7852,7 +7852,7 @@
       </c>
       <c r="Z62" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA62" s="2" t="inlineStr">
@@ -7867,7 +7867,7 @@
       </c>
       <c r="AC62" s="2" t="inlineStr">
         <is>
-          <t>17/29</t>
+          <t>16/29</t>
         </is>
       </c>
     </row>
@@ -7986,7 +7986,7 @@
       </c>
       <c r="AC63" s="2" t="inlineStr">
         <is>
-          <t>10/29</t>
+          <t>9/29</t>
         </is>
       </c>
     </row>
@@ -8224,7 +8224,7 @@
       </c>
       <c r="AC65" s="2" t="inlineStr">
         <is>
-          <t>14/29</t>
+          <t>13/29</t>
         </is>
       </c>
     </row>
@@ -8274,12 +8274,12 @@
       <c r="K66" s="2" t="inlineStr"/>
       <c r="L66" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="M66" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N66" s="2" t="inlineStr">
@@ -8289,7 +8289,7 @@
       </c>
       <c r="O66" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P66" s="2" t="inlineStr">
@@ -8328,14 +8328,14 @@
       </c>
       <c r="Z66" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA66" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA66" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB66" s="2" t="inlineStr">
         <is>
           <t>132.3</t>
@@ -8343,7 +8343,7 @@
       </c>
       <c r="AC66" s="2" t="inlineStr">
         <is>
-          <t>13/29</t>
+          <t>12/29</t>
         </is>
       </c>
     </row>
@@ -8408,7 +8408,7 @@
       </c>
       <c r="O67" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>16:41</t>
         </is>
       </c>
       <c r="P67" s="2" t="inlineStr">
@@ -8462,7 +8462,7 @@
       </c>
       <c r="AC67" s="2" t="inlineStr">
         <is>
-          <t>8/29</t>
+          <t>7/29</t>
         </is>
       </c>
     </row>
@@ -8490,32 +8490,36 @@
       </c>
       <c r="F68" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G68" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H68" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>17:06</t>
         </is>
       </c>
       <c r="I68" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>141分钟</t>
         </is>
       </c>
       <c r="J68" s="2" t="inlineStr"/>
       <c r="K68" s="2" t="inlineStr"/>
       <c r="L68" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M68" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±4分钟</t>
+        </is>
+      </c>
+      <c r="M68" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="N68" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -8523,7 +8527,7 @@
       </c>
       <c r="O68" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P68" s="2" t="inlineStr">
@@ -8547,37 +8551,37 @@
       </c>
       <c r="W68" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X68" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y68" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z68" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA68" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA68" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB68" s="2" t="inlineStr">
         <is>
-          <t>136.0</t>
+          <t>137.7</t>
         </is>
       </c>
       <c r="AC68" s="2" t="inlineStr">
         <is>
-          <t>20/29</t>
+          <t>22/29</t>
         </is>
       </c>
     </row>
@@ -8585,7 +8589,7 @@
       <c r="A69" s="2" t="inlineStr"/>
       <c r="B69" s="2" t="inlineStr">
         <is>
-          <t>沪A51682D</t>
+          <t>沪A71572D</t>
         </is>
       </c>
       <c r="C69" s="2" t="inlineStr">
@@ -8633,12 +8637,12 @@
       <c r="M69" s="2" t="inlineStr"/>
       <c r="N69" s="2" t="inlineStr">
         <is>
-          <t>06:51</t>
+          <t>06:21</t>
         </is>
       </c>
       <c r="O69" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>14:51</t>
         </is>
       </c>
       <c r="P69" s="2" t="inlineStr">
@@ -8677,22 +8681,18 @@
       </c>
       <c r="Z69" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA69" s="2" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AB69" s="2" t="inlineStr">
-        <is>
-          <t>139.0</t>
-        </is>
-      </c>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB69" s="2" t="inlineStr"/>
       <c r="AC69" s="2" t="inlineStr">
         <is>
-          <t>23/29</t>
+          <t>—/29</t>
         </is>
       </c>
     </row>
@@ -8700,60 +8700,64 @@
       <c r="A70" s="2" t="inlineStr"/>
       <c r="B70" s="2" t="inlineStr">
         <is>
-          <t>沪A71572D</t>
+          <t>沪A73927D</t>
         </is>
       </c>
       <c r="C70" s="2" t="inlineStr">
         <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D70" s="2" t="inlineStr">
+        <is>
+          <t>15:10</t>
+        </is>
+      </c>
+      <c r="E70" s="2" t="inlineStr">
+        <is>
           <t>东高路张杨北路</t>
         </is>
       </c>
-      <c r="D70" s="2" t="inlineStr">
-        <is>
-          <t>15:00</t>
-        </is>
-      </c>
-      <c r="E70" s="2" t="inlineStr">
-        <is>
-          <t>康恩路康浦路</t>
-        </is>
-      </c>
       <c r="F70" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G70" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H70" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>17:31</t>
         </is>
       </c>
       <c r="I70" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>141分钟</t>
         </is>
       </c>
       <c r="J70" s="2" t="inlineStr"/>
       <c r="K70" s="2" t="inlineStr"/>
       <c r="L70" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M70" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±4分钟</t>
+        </is>
+      </c>
+      <c r="M70" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="N70" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="O70" s="2" t="inlineStr">
         <is>
-          <t>14:51</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P70" s="2" t="inlineStr">
@@ -8767,7 +8771,7 @@
       <c r="T70" s="2" t="inlineStr"/>
       <c r="U70" s="2" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>15:10</t>
         </is>
       </c>
       <c r="V70" s="2" t="inlineStr">
@@ -8777,33 +8781,37 @@
       </c>
       <c r="W70" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X70" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y70" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z70" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA70" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA70" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB70" s="2" t="inlineStr"/>
+      <c r="AB70" s="2" t="inlineStr">
+        <is>
+          <t>138.0</t>
+        </is>
+      </c>
       <c r="AC70" s="2" t="inlineStr">
         <is>
-          <t>—/29</t>
+          <t>23/29</t>
         </is>
       </c>
     </row>
@@ -8811,7 +8819,7 @@
       <c r="A71" s="2" t="inlineStr"/>
       <c r="B71" s="2" t="inlineStr">
         <is>
-          <t>沪A73927D</t>
+          <t>沪A79307D</t>
         </is>
       </c>
       <c r="C71" s="2" t="inlineStr">
@@ -8821,7 +8829,7 @@
       </c>
       <c r="D71" s="2" t="inlineStr">
         <is>
-          <t>15:10</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="E71" s="2" t="inlineStr">
@@ -8831,12 +8839,12 @@
       </c>
       <c r="F71" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>疑似区间车</t>
         </is>
       </c>
       <c r="G71" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>原方向在全程36%处后消失；随后反向物理轨迹由seq38推进至seq59，推进21站，达到≥2站确认条件</t>
         </is>
       </c>
       <c r="H71" s="2" t="inlineStr">
@@ -8859,12 +8867,12 @@
       <c r="M71" s="2" t="inlineStr"/>
       <c r="N71" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>09:31</t>
         </is>
       </c>
       <c r="O71" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P71" s="2" t="inlineStr">
@@ -8872,13 +8880,29 @@
           <t>SHMAAS</t>
         </is>
       </c>
-      <c r="Q71" s="2" t="inlineStr"/>
-      <c r="R71" s="2" t="inlineStr"/>
-      <c r="S71" s="2" t="inlineStr"/>
-      <c r="T71" s="2" t="inlineStr"/>
+      <c r="Q71" s="2" t="inlineStr">
+        <is>
+          <t>物理seq24（站名待映射）</t>
+        </is>
+      </c>
+      <c r="R71" s="2" t="inlineStr">
+        <is>
+          <t>16:12</t>
+        </is>
+      </c>
+      <c r="S71" s="2" t="inlineStr">
+        <is>
+          <t>16:17</t>
+        </is>
+      </c>
+      <c r="T71" s="2" t="inlineStr">
+        <is>
+          <t>折返点按重建物理位置seq24映射；到达按末次同向ETA估算；折返发车结合首次反向物理观测取区间中点，约±4分钟；反向位置物理seq38（站名待映射） ETA 10分钟参与校验</t>
+        </is>
+      </c>
       <c r="U71" s="2" t="inlineStr">
         <is>
-          <t>15:10</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="V71" s="2" t="inlineStr">
@@ -8908,17 +8932,13 @@
       </c>
       <c r="AA71" s="2" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AB71" s="2" t="inlineStr">
-        <is>
-          <t>136.5</t>
-        </is>
-      </c>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB71" s="2" t="inlineStr"/>
       <c r="AC71" s="2" t="inlineStr">
         <is>
-          <t>22/29</t>
+          <t>—/29</t>
         </is>
       </c>
     </row>
@@ -8926,60 +8946,64 @@
       <c r="A72" s="2" t="inlineStr"/>
       <c r="B72" s="2" t="inlineStr">
         <is>
-          <t>沪A79307D</t>
+          <t>沪A51682D</t>
         </is>
       </c>
       <c r="C72" s="2" t="inlineStr">
         <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D72" s="2" t="inlineStr">
+        <is>
+          <t>15:25</t>
+        </is>
+      </c>
+      <c r="E72" s="2" t="inlineStr">
+        <is>
           <t>康恩路康浦路</t>
         </is>
       </c>
-      <c r="D72" s="2" t="inlineStr">
-        <is>
-          <t>15:22</t>
-        </is>
-      </c>
-      <c r="E72" s="2" t="inlineStr">
-        <is>
-          <t>东高路张杨北路</t>
-        </is>
-      </c>
       <c r="F72" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G72" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H72" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>17:41</t>
         </is>
       </c>
       <c r="I72" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>136分钟</t>
         </is>
       </c>
       <c r="J72" s="2" t="inlineStr"/>
       <c r="K72" s="2" t="inlineStr"/>
       <c r="L72" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M72" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M72" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N72" s="2" t="inlineStr">
         <is>
-          <t>09:31</t>
+          <t>06:51</t>
         </is>
       </c>
       <c r="O72" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P72" s="2" t="inlineStr">
@@ -8993,7 +9017,7 @@
       <c r="T72" s="2" t="inlineStr"/>
       <c r="U72" s="2" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>15:25</t>
         </is>
       </c>
       <c r="V72" s="2" t="inlineStr">
@@ -9003,17 +9027,17 @@
       </c>
       <c r="W72" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X72" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y72" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z72" s="2" t="inlineStr">
@@ -9023,13 +9047,17 @@
       </c>
       <c r="AA72" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB72" s="2" t="inlineStr"/>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB72" s="2" t="inlineStr">
+        <is>
+          <t>137.5</t>
+        </is>
+      </c>
       <c r="AC72" s="2" t="inlineStr">
         <is>
-          <t>—/29</t>
+          <t>21/29</t>
         </is>
       </c>
     </row>
@@ -9037,7 +9065,7 @@
       <c r="A73" s="2" t="inlineStr"/>
       <c r="B73" s="2" t="inlineStr">
         <is>
-          <t>沪A51682D</t>
+          <t>沪A71572D</t>
         </is>
       </c>
       <c r="C73" s="2" t="inlineStr">
@@ -9085,12 +9113,12 @@
       <c r="M73" s="2" t="inlineStr"/>
       <c r="N73" s="2" t="inlineStr">
         <is>
-          <t>06:51</t>
+          <t>06:21</t>
         </is>
       </c>
       <c r="O73" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>14:51</t>
         </is>
       </c>
       <c r="P73" s="2" t="inlineStr">
@@ -9129,22 +9157,18 @@
       </c>
       <c r="Z73" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA73" s="2" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AB73" s="2" t="inlineStr">
-        <is>
-          <t>139.0</t>
-        </is>
-      </c>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB73" s="2" t="inlineStr"/>
       <c r="AC73" s="2" t="inlineStr">
         <is>
-          <t>23/29</t>
+          <t>—/29</t>
         </is>
       </c>
     </row>
@@ -9152,60 +9176,64 @@
       <c r="A74" s="2" t="inlineStr"/>
       <c r="B74" s="2" t="inlineStr">
         <is>
-          <t>沪A71572D</t>
+          <t>沪A72873D</t>
         </is>
       </c>
       <c r="C74" s="2" t="inlineStr">
         <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D74" s="2" t="inlineStr">
+        <is>
+          <t>15:35</t>
+        </is>
+      </c>
+      <c r="E74" s="2" t="inlineStr">
+        <is>
           <t>东高路张杨北路</t>
         </is>
       </c>
-      <c r="D74" s="2" t="inlineStr">
-        <is>
-          <t>15:25</t>
-        </is>
-      </c>
-      <c r="E74" s="2" t="inlineStr">
-        <is>
-          <t>康恩路康浦路</t>
-        </is>
-      </c>
       <c r="F74" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G74" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H74" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>17:58</t>
         </is>
       </c>
       <c r="I74" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>143分钟</t>
         </is>
       </c>
       <c r="J74" s="2" t="inlineStr"/>
       <c r="K74" s="2" t="inlineStr"/>
       <c r="L74" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M74" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M74" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N74" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>06:32</t>
         </is>
       </c>
       <c r="O74" s="2" t="inlineStr">
         <is>
-          <t>14:51</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P74" s="2" t="inlineStr">
@@ -9219,7 +9247,7 @@
       <c r="T74" s="2" t="inlineStr"/>
       <c r="U74" s="2" t="inlineStr">
         <is>
-          <t>15:25</t>
+          <t>15:35</t>
         </is>
       </c>
       <c r="V74" s="2" t="inlineStr">
@@ -9229,17 +9257,17 @@
       </c>
       <c r="W74" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X74" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y74" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z74" s="2" t="inlineStr">
@@ -9249,13 +9277,17 @@
       </c>
       <c r="AA74" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB74" s="2" t="inlineStr"/>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB74" s="2" t="inlineStr">
+        <is>
+          <t>136.5</t>
+        </is>
+      </c>
       <c r="AC74" s="2" t="inlineStr">
         <is>
-          <t>—/29</t>
+          <t>20/29</t>
         </is>
       </c>
     </row>
@@ -9263,22 +9295,22 @@
       <c r="A75" s="2" t="inlineStr"/>
       <c r="B75" s="2" t="inlineStr">
         <is>
-          <t>沪A72873D</t>
+          <t>沪A15790A</t>
         </is>
       </c>
       <c r="C75" s="2" t="inlineStr">
         <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D75" s="2" t="inlineStr">
+        <is>
+          <t>15:45</t>
+        </is>
+      </c>
+      <c r="E75" s="2" t="inlineStr">
+        <is>
           <t>康恩路康浦路</t>
-        </is>
-      </c>
-      <c r="D75" s="2" t="inlineStr">
-        <is>
-          <t>15:35</t>
-        </is>
-      </c>
-      <c r="E75" s="2" t="inlineStr">
-        <is>
-          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="F75" s="2" t="inlineStr">
@@ -9311,12 +9343,12 @@
       <c r="M75" s="2" t="inlineStr"/>
       <c r="N75" s="2" t="inlineStr">
         <is>
-          <t>06:32</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="O75" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P75" s="2" t="inlineStr">
@@ -9330,7 +9362,7 @@
       <c r="T75" s="2" t="inlineStr"/>
       <c r="U75" s="2" t="inlineStr">
         <is>
-          <t>15:35</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="V75" s="2" t="inlineStr">
@@ -9355,22 +9387,18 @@
       </c>
       <c r="Z75" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AA75" s="2" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AB75" s="2" t="inlineStr">
-        <is>
-          <t>130.0</t>
-        </is>
-      </c>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB75" s="2" t="inlineStr"/>
       <c r="AC75" s="2" t="inlineStr">
         <is>
-          <t>7/29</t>
+          <t>—/29</t>
         </is>
       </c>
     </row>
@@ -9378,22 +9406,22 @@
       <c r="A76" s="2" t="inlineStr"/>
       <c r="B76" s="2" t="inlineStr">
         <is>
-          <t>沪A15790A</t>
+          <t>沪A62880D</t>
         </is>
       </c>
       <c r="C76" s="2" t="inlineStr">
         <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D76" s="2" t="inlineStr">
+        <is>
+          <t>16:00</t>
+        </is>
+      </c>
+      <c r="E76" s="2" t="inlineStr">
+        <is>
           <t>东高路张杨北路</t>
-        </is>
-      </c>
-      <c r="D76" s="2" t="inlineStr">
-        <is>
-          <t>15:45</t>
-        </is>
-      </c>
-      <c r="E76" s="2" t="inlineStr">
-        <is>
-          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="F76" s="2" t="inlineStr">
@@ -9426,12 +9454,12 @@
       <c r="M76" s="2" t="inlineStr"/>
       <c r="N76" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>07:01</t>
         </is>
       </c>
       <c r="O76" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P76" s="2" t="inlineStr">
@@ -9445,7 +9473,7 @@
       <c r="T76" s="2" t="inlineStr"/>
       <c r="U76" s="2" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="V76" s="2" t="inlineStr">
@@ -9470,18 +9498,22 @@
       </c>
       <c r="Z76" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA76" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB76" s="2" t="inlineStr"/>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB76" s="2" t="inlineStr">
+        <is>
+          <t>141.0</t>
+        </is>
+      </c>
       <c r="AC76" s="2" t="inlineStr">
         <is>
-          <t>—/29</t>
+          <t>26/29</t>
         </is>
       </c>
     </row>
@@ -9489,22 +9521,22 @@
       <c r="A77" s="2" t="inlineStr"/>
       <c r="B77" s="2" t="inlineStr">
         <is>
-          <t>沪A62880D</t>
+          <t>沪A37823D</t>
         </is>
       </c>
       <c r="C77" s="2" t="inlineStr">
         <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D77" s="2" t="inlineStr">
+        <is>
+          <t>16:10</t>
+        </is>
+      </c>
+      <c r="E77" s="2" t="inlineStr">
+        <is>
           <t>康恩路康浦路</t>
-        </is>
-      </c>
-      <c r="D77" s="2" t="inlineStr">
-        <is>
-          <t>16:00</t>
-        </is>
-      </c>
-      <c r="E77" s="2" t="inlineStr">
-        <is>
-          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="F77" s="2" t="inlineStr">
@@ -9537,12 +9569,12 @@
       <c r="M77" s="2" t="inlineStr"/>
       <c r="N77" s="2" t="inlineStr">
         <is>
-          <t>07:01</t>
+          <t>07:31</t>
         </is>
       </c>
       <c r="O77" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P77" s="2" t="inlineStr">
@@ -9556,7 +9588,7 @@
       <c r="T77" s="2" t="inlineStr"/>
       <c r="U77" s="2" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>16:10</t>
         </is>
       </c>
       <c r="V77" s="2" t="inlineStr">
@@ -9581,22 +9613,22 @@
       </c>
       <c r="Z77" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AA77" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AB77" s="2" t="inlineStr">
         <is>
-          <t>141.0</t>
+          <t>135.0</t>
         </is>
       </c>
       <c r="AC77" s="2" t="inlineStr">
         <is>
-          <t>26/29</t>
+          <t>16/29</t>
         </is>
       </c>
     </row>
@@ -9604,22 +9636,22 @@
       <c r="A78" s="2" t="inlineStr"/>
       <c r="B78" s="2" t="inlineStr">
         <is>
-          <t>沪A37823D</t>
+          <t>沪A65668D</t>
         </is>
       </c>
       <c r="C78" s="2" t="inlineStr">
         <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D78" s="2" t="inlineStr">
+        <is>
+          <t>16:15</t>
+        </is>
+      </c>
+      <c r="E78" s="2" t="inlineStr">
+        <is>
           <t>东高路张杨北路</t>
-        </is>
-      </c>
-      <c r="D78" s="2" t="inlineStr">
-        <is>
-          <t>16:10</t>
-        </is>
-      </c>
-      <c r="E78" s="2" t="inlineStr">
-        <is>
-          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="F78" s="2" t="inlineStr">
@@ -9652,12 +9684,12 @@
       <c r="M78" s="2" t="inlineStr"/>
       <c r="N78" s="2" t="inlineStr">
         <is>
-          <t>07:31</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="O78" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P78" s="2" t="inlineStr">
@@ -9671,7 +9703,7 @@
       <c r="T78" s="2" t="inlineStr"/>
       <c r="U78" s="2" t="inlineStr">
         <is>
-          <t>16:10</t>
+          <t>16:15</t>
         </is>
       </c>
       <c r="V78" s="2" t="inlineStr">
@@ -9696,7 +9728,7 @@
       </c>
       <c r="Z78" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA78" s="2" t="inlineStr">
@@ -9706,12 +9738,12 @@
       </c>
       <c r="AB78" s="2" t="inlineStr">
         <is>
-          <t>135.0</t>
+          <t>123.0</t>
         </is>
       </c>
       <c r="AC78" s="2" t="inlineStr">
         <is>
-          <t>17/29</t>
+          <t>1/29</t>
         </is>
       </c>
     </row>
@@ -9719,7 +9751,7 @@
       <c r="A79" s="2" t="inlineStr"/>
       <c r="B79" s="2" t="inlineStr">
         <is>
-          <t>沪A65668D</t>
+          <t>沪A55102D</t>
         </is>
       </c>
       <c r="C79" s="2" t="inlineStr">
@@ -9729,7 +9761,7 @@
       </c>
       <c r="D79" s="2" t="inlineStr">
         <is>
-          <t>16:15</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="E79" s="2" t="inlineStr">
@@ -9767,12 +9799,12 @@
       <c r="M79" s="2" t="inlineStr"/>
       <c r="N79" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>06:51</t>
         </is>
       </c>
       <c r="O79" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P79" s="2" t="inlineStr">
@@ -9786,7 +9818,7 @@
       <c r="T79" s="2" t="inlineStr"/>
       <c r="U79" s="2" t="inlineStr">
         <is>
-          <t>16:15</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="V79" s="2" t="inlineStr">
@@ -9816,17 +9848,17 @@
       </c>
       <c r="AA79" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB79" s="2" t="inlineStr">
         <is>
-          <t>123.0</t>
+          <t>132.0</t>
         </is>
       </c>
       <c r="AC79" s="2" t="inlineStr">
         <is>
-          <t>1/29</t>
+          <t>10/29</t>
         </is>
       </c>
     </row>
@@ -9834,22 +9866,22 @@
       <c r="A80" s="2" t="inlineStr"/>
       <c r="B80" s="2" t="inlineStr">
         <is>
-          <t>沪A55102D</t>
+          <t>沪A67712D</t>
         </is>
       </c>
       <c r="C80" s="2" t="inlineStr">
         <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D80" s="2" t="inlineStr">
+        <is>
+          <t>16:30</t>
+        </is>
+      </c>
+      <c r="E80" s="2" t="inlineStr">
+        <is>
           <t>康恩路康浦路</t>
-        </is>
-      </c>
-      <c r="D80" s="2" t="inlineStr">
-        <is>
-          <t>16:30</t>
-        </is>
-      </c>
-      <c r="E80" s="2" t="inlineStr">
-        <is>
-          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="F80" s="2" t="inlineStr">
@@ -9882,12 +9914,12 @@
       <c r="M80" s="2" t="inlineStr"/>
       <c r="N80" s="2" t="inlineStr">
         <is>
-          <t>06:51</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="O80" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P80" s="2" t="inlineStr">
@@ -9936,12 +9968,12 @@
       </c>
       <c r="AB80" s="2" t="inlineStr">
         <is>
-          <t>132.0</t>
+          <t>128.5</t>
         </is>
       </c>
       <c r="AC80" s="2" t="inlineStr">
         <is>
-          <t>11/29</t>
+          <t>4/29</t>
         </is>
       </c>
     </row>
@@ -9949,22 +9981,22 @@
       <c r="A81" s="2" t="inlineStr"/>
       <c r="B81" s="2" t="inlineStr">
         <is>
-          <t>沪A67712D</t>
+          <t>沪A67057D</t>
         </is>
       </c>
       <c r="C81" s="2" t="inlineStr">
         <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D81" s="2" t="inlineStr">
+        <is>
+          <t>16:45</t>
+        </is>
+      </c>
+      <c r="E81" s="2" t="inlineStr">
+        <is>
           <t>东高路张杨北路</t>
-        </is>
-      </c>
-      <c r="D81" s="2" t="inlineStr">
-        <is>
-          <t>16:30</t>
-        </is>
-      </c>
-      <c r="E81" s="2" t="inlineStr">
-        <is>
-          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="F81" s="2" t="inlineStr">
@@ -9997,12 +10029,12 @@
       <c r="M81" s="2" t="inlineStr"/>
       <c r="N81" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>07:01</t>
         </is>
       </c>
       <c r="O81" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P81" s="2" t="inlineStr">
@@ -10016,7 +10048,7 @@
       <c r="T81" s="2" t="inlineStr"/>
       <c r="U81" s="2" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>16:45</t>
         </is>
       </c>
       <c r="V81" s="2" t="inlineStr">
@@ -10051,12 +10083,12 @@
       </c>
       <c r="AB81" s="2" t="inlineStr">
         <is>
-          <t>128.5</t>
+          <t>129.5</t>
         </is>
       </c>
       <c r="AC81" s="2" t="inlineStr">
         <is>
-          <t>4/29</t>
+          <t>6/29</t>
         </is>
       </c>
     </row>
@@ -10064,22 +10096,22 @@
       <c r="A82" s="2" t="inlineStr"/>
       <c r="B82" s="2" t="inlineStr">
         <is>
-          <t>沪A67057D</t>
+          <t>沪A68375D</t>
         </is>
       </c>
       <c r="C82" s="2" t="inlineStr">
         <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D82" s="2" t="inlineStr">
+        <is>
+          <t>16:45</t>
+        </is>
+      </c>
+      <c r="E82" s="2" t="inlineStr">
+        <is>
           <t>康恩路康浦路</t>
-        </is>
-      </c>
-      <c r="D82" s="2" t="inlineStr">
-        <is>
-          <t>16:45</t>
-        </is>
-      </c>
-      <c r="E82" s="2" t="inlineStr">
-        <is>
-          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="F82" s="2" t="inlineStr">
@@ -10112,12 +10144,12 @@
       <c r="M82" s="2" t="inlineStr"/>
       <c r="N82" s="2" t="inlineStr">
         <is>
-          <t>07:01</t>
+          <t>06:11</t>
         </is>
       </c>
       <c r="O82" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P82" s="2" t="inlineStr">
@@ -10166,12 +10198,12 @@
       </c>
       <c r="AB82" s="2" t="inlineStr">
         <is>
-          <t>129.5</t>
+          <t>134.5</t>
         </is>
       </c>
       <c r="AC82" s="2" t="inlineStr">
         <is>
-          <t>6/29</t>
+          <t>15/29</t>
         </is>
       </c>
     </row>
@@ -10179,22 +10211,22 @@
       <c r="A83" s="2" t="inlineStr"/>
       <c r="B83" s="2" t="inlineStr">
         <is>
-          <t>沪A68375D</t>
+          <t>沪A62981D</t>
         </is>
       </c>
       <c r="C83" s="2" t="inlineStr">
         <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D83" s="2" t="inlineStr">
+        <is>
+          <t>17:00</t>
+        </is>
+      </c>
+      <c r="E83" s="2" t="inlineStr">
+        <is>
           <t>东高路张杨北路</t>
-        </is>
-      </c>
-      <c r="D83" s="2" t="inlineStr">
-        <is>
-          <t>16:45</t>
-        </is>
-      </c>
-      <c r="E83" s="2" t="inlineStr">
-        <is>
-          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="F83" s="2" t="inlineStr">
@@ -10227,12 +10259,12 @@
       <c r="M83" s="2" t="inlineStr"/>
       <c r="N83" s="2" t="inlineStr">
         <is>
-          <t>06:11</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="O83" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P83" s="2" t="inlineStr">
@@ -10246,7 +10278,7 @@
       <c r="T83" s="2" t="inlineStr"/>
       <c r="U83" s="2" t="inlineStr">
         <is>
-          <t>16:45</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="V83" s="2" t="inlineStr">
@@ -10271,22 +10303,22 @@
       </c>
       <c r="Z83" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA83" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA83" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB83" s="2" t="inlineStr">
         <is>
-          <t>134.5</t>
+          <t>139.7</t>
         </is>
       </c>
       <c r="AC83" s="2" t="inlineStr">
         <is>
-          <t>16/29</t>
+          <t>24/29</t>
         </is>
       </c>
     </row>
@@ -10294,22 +10326,22 @@
       <c r="A84" s="2" t="inlineStr"/>
       <c r="B84" s="2" t="inlineStr">
         <is>
-          <t>沪A62981D</t>
+          <t>沪A68261D</t>
         </is>
       </c>
       <c r="C84" s="2" t="inlineStr">
         <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D84" s="2" t="inlineStr">
+        <is>
+          <t>17:00</t>
+        </is>
+      </c>
+      <c r="E84" s="2" t="inlineStr">
+        <is>
           <t>康恩路康浦路</t>
-        </is>
-      </c>
-      <c r="D84" s="2" t="inlineStr">
-        <is>
-          <t>17:00</t>
-        </is>
-      </c>
-      <c r="E84" s="2" t="inlineStr">
-        <is>
-          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="F84" s="2" t="inlineStr">
@@ -10342,12 +10374,12 @@
       <c r="M84" s="2" t="inlineStr"/>
       <c r="N84" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>06:41</t>
         </is>
       </c>
       <c r="O84" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P84" s="2" t="inlineStr">
@@ -10386,22 +10418,22 @@
       </c>
       <c r="Z84" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA84" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB84" s="2" t="inlineStr">
         <is>
-          <t>139.7</t>
+          <t>130.5</t>
         </is>
       </c>
       <c r="AC84" s="2" t="inlineStr">
         <is>
-          <t>24/29</t>
+          <t>7/29</t>
         </is>
       </c>
     </row>
@@ -10409,22 +10441,22 @@
       <c r="A85" s="2" t="inlineStr"/>
       <c r="B85" s="2" t="inlineStr">
         <is>
-          <t>沪A68261D</t>
+          <t>沪A62217D</t>
         </is>
       </c>
       <c r="C85" s="2" t="inlineStr">
         <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D85" s="2" t="inlineStr">
+        <is>
+          <t>17:15</t>
+        </is>
+      </c>
+      <c r="E85" s="2" t="inlineStr">
+        <is>
           <t>东高路张杨北路</t>
-        </is>
-      </c>
-      <c r="D85" s="2" t="inlineStr">
-        <is>
-          <t>17:00</t>
-        </is>
-      </c>
-      <c r="E85" s="2" t="inlineStr">
-        <is>
-          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="F85" s="2" t="inlineStr">
@@ -10457,12 +10489,12 @@
       <c r="M85" s="2" t="inlineStr"/>
       <c r="N85" s="2" t="inlineStr">
         <is>
-          <t>06:41</t>
+          <t>06:21</t>
         </is>
       </c>
       <c r="O85" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P85" s="2" t="inlineStr">
@@ -10476,7 +10508,7 @@
       <c r="T85" s="2" t="inlineStr"/>
       <c r="U85" s="2" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>17:15</t>
         </is>
       </c>
       <c r="V85" s="2" t="inlineStr">
@@ -10501,22 +10533,827 @@
       </c>
       <c r="Z85" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA85" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA85" s="2" t="inlineStr">
+      <c r="AB85" s="2" t="inlineStr">
+        <is>
+          <t>127.0</t>
+        </is>
+      </c>
+      <c r="AC85" s="2" t="inlineStr">
+        <is>
+          <t>2/29</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="2" t="inlineStr"/>
+      <c r="B86" s="2" t="inlineStr">
+        <is>
+          <t>沪A66883D</t>
+        </is>
+      </c>
+      <c r="C86" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D86" s="2" t="inlineStr">
+        <is>
+          <t>17:15</t>
+        </is>
+      </c>
+      <c r="E86" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F86" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G86" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H86" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I86" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J86" s="2" t="inlineStr"/>
+      <c r="K86" s="2" t="inlineStr"/>
+      <c r="L86" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M86" s="2" t="inlineStr"/>
+      <c r="N86" s="2" t="inlineStr">
+        <is>
+          <t>06:11</t>
+        </is>
+      </c>
+      <c r="O86" s="2" t="inlineStr">
+        <is>
+          <t>17:21</t>
+        </is>
+      </c>
+      <c r="P86" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q86" s="2" t="inlineStr"/>
+      <c r="R86" s="2" t="inlineStr"/>
+      <c r="S86" s="2" t="inlineStr"/>
+      <c r="T86" s="2" t="inlineStr"/>
+      <c r="U86" s="2" t="inlineStr">
+        <is>
+          <t>17:15</t>
+        </is>
+      </c>
+      <c r="V86" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W86" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X86" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y86" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z86" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA86" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB86" s="2" t="inlineStr">
+        <is>
+          <t>132.3</t>
+        </is>
+      </c>
+      <c r="AC86" s="2" t="inlineStr">
+        <is>
+          <t>12/29</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="2" t="inlineStr"/>
+      <c r="B87" s="2" t="inlineStr">
+        <is>
+          <t>沪A55575A</t>
+        </is>
+      </c>
+      <c r="C87" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D87" s="2" t="inlineStr">
+        <is>
+          <t>17:30</t>
+        </is>
+      </c>
+      <c r="E87" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F87" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G87" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H87" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I87" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J87" s="2" t="inlineStr"/>
+      <c r="K87" s="2" t="inlineStr"/>
+      <c r="L87" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M87" s="2" t="inlineStr"/>
+      <c r="N87" s="2" t="inlineStr">
+        <is>
+          <t>07:01</t>
+        </is>
+      </c>
+      <c r="O87" s="2" t="inlineStr">
+        <is>
+          <t>17:21</t>
+        </is>
+      </c>
+      <c r="P87" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q87" s="2" t="inlineStr"/>
+      <c r="R87" s="2" t="inlineStr"/>
+      <c r="S87" s="2" t="inlineStr"/>
+      <c r="T87" s="2" t="inlineStr"/>
+      <c r="U87" s="2" t="inlineStr">
+        <is>
+          <t>17:30</t>
+        </is>
+      </c>
+      <c r="V87" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W87" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X87" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y87" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z87" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA87" s="2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AB85" s="2" t="inlineStr">
-        <is>
-          <t>130.5</t>
-        </is>
-      </c>
-      <c r="AC85" s="2" t="inlineStr">
-        <is>
-          <t>8/29</t>
+      <c r="AB87" s="2" t="inlineStr">
+        <is>
+          <t>140.0</t>
+        </is>
+      </c>
+      <c r="AC87" s="2" t="inlineStr">
+        <is>
+          <t>25/29</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="2" t="inlineStr"/>
+      <c r="B88" s="2" t="inlineStr">
+        <is>
+          <t>沪A68895D</t>
+        </is>
+      </c>
+      <c r="C88" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D88" s="2" t="inlineStr">
+        <is>
+          <t>17:30</t>
+        </is>
+      </c>
+      <c r="E88" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F88" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G88" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H88" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I88" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J88" s="2" t="inlineStr"/>
+      <c r="K88" s="2" t="inlineStr"/>
+      <c r="L88" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M88" s="2" t="inlineStr"/>
+      <c r="N88" s="2" t="inlineStr">
+        <is>
+          <t>06:51</t>
+        </is>
+      </c>
+      <c r="O88" s="2" t="inlineStr">
+        <is>
+          <t>17:21</t>
+        </is>
+      </c>
+      <c r="P88" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q88" s="2" t="inlineStr"/>
+      <c r="R88" s="2" t="inlineStr"/>
+      <c r="S88" s="2" t="inlineStr"/>
+      <c r="T88" s="2" t="inlineStr"/>
+      <c r="U88" s="2" t="inlineStr">
+        <is>
+          <t>17:30</t>
+        </is>
+      </c>
+      <c r="V88" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W88" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X88" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y88" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z88" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA88" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB88" s="2" t="inlineStr">
+        <is>
+          <t>127.5</t>
+        </is>
+      </c>
+      <c r="AC88" s="2" t="inlineStr">
+        <is>
+          <t>3/29</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="2" t="inlineStr"/>
+      <c r="B89" s="2" t="inlineStr">
+        <is>
+          <t>沪A59793A</t>
+        </is>
+      </c>
+      <c r="C89" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D89" s="2" t="inlineStr">
+        <is>
+          <t>17:45</t>
+        </is>
+      </c>
+      <c r="E89" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F89" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G89" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H89" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I89" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J89" s="2" t="inlineStr"/>
+      <c r="K89" s="2" t="inlineStr"/>
+      <c r="L89" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M89" s="2" t="inlineStr"/>
+      <c r="N89" s="2" t="inlineStr">
+        <is>
+          <t>06:51</t>
+        </is>
+      </c>
+      <c r="O89" s="2" t="inlineStr">
+        <is>
+          <t>17:21</t>
+        </is>
+      </c>
+      <c r="P89" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q89" s="2" t="inlineStr"/>
+      <c r="R89" s="2" t="inlineStr"/>
+      <c r="S89" s="2" t="inlineStr"/>
+      <c r="T89" s="2" t="inlineStr"/>
+      <c r="U89" s="2" t="inlineStr">
+        <is>
+          <t>17:45</t>
+        </is>
+      </c>
+      <c r="V89" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W89" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X89" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y89" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z89" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA89" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB89" s="2" t="inlineStr">
+        <is>
+          <t>134.0</t>
+        </is>
+      </c>
+      <c r="AC89" s="2" t="inlineStr">
+        <is>
+          <t>14/29</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="2" t="inlineStr"/>
+      <c r="B90" s="2" t="inlineStr">
+        <is>
+          <t>沪A70597D</t>
+        </is>
+      </c>
+      <c r="C90" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D90" s="2" t="inlineStr">
+        <is>
+          <t>17:45</t>
+        </is>
+      </c>
+      <c r="E90" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F90" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G90" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H90" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I90" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J90" s="2" t="inlineStr"/>
+      <c r="K90" s="2" t="inlineStr"/>
+      <c r="L90" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M90" s="2" t="inlineStr"/>
+      <c r="N90" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O90" s="2" t="inlineStr">
+        <is>
+          <t>17:21</t>
+        </is>
+      </c>
+      <c r="P90" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q90" s="2" t="inlineStr"/>
+      <c r="R90" s="2" t="inlineStr"/>
+      <c r="S90" s="2" t="inlineStr"/>
+      <c r="T90" s="2" t="inlineStr"/>
+      <c r="U90" s="2" t="inlineStr">
+        <is>
+          <t>17:45</t>
+        </is>
+      </c>
+      <c r="V90" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W90" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X90" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y90" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z90" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA90" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB90" s="2" t="inlineStr">
+        <is>
+          <t>137.7</t>
+        </is>
+      </c>
+      <c r="AC90" s="2" t="inlineStr">
+        <is>
+          <t>22/29</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="2" t="inlineStr"/>
+      <c r="B91" s="2" t="inlineStr">
+        <is>
+          <t>沪A67672D</t>
+        </is>
+      </c>
+      <c r="C91" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D91" s="2" t="inlineStr">
+        <is>
+          <t>18:00</t>
+        </is>
+      </c>
+      <c r="E91" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F91" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G91" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H91" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I91" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J91" s="2" t="inlineStr"/>
+      <c r="K91" s="2" t="inlineStr"/>
+      <c r="L91" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M91" s="2" t="inlineStr"/>
+      <c r="N91" s="2" t="inlineStr">
+        <is>
+          <t>07:41</t>
+        </is>
+      </c>
+      <c r="O91" s="2" t="inlineStr">
+        <is>
+          <t>17:21</t>
+        </is>
+      </c>
+      <c r="P91" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q91" s="2" t="inlineStr"/>
+      <c r="R91" s="2" t="inlineStr"/>
+      <c r="S91" s="2" t="inlineStr"/>
+      <c r="T91" s="2" t="inlineStr"/>
+      <c r="U91" s="2" t="inlineStr">
+        <is>
+          <t>18:00</t>
+        </is>
+      </c>
+      <c r="V91" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W91" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X91" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y91" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z91" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA91" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB91" s="2" t="inlineStr">
+        <is>
+          <t>135.0</t>
+        </is>
+      </c>
+      <c r="AC91" s="2" t="inlineStr">
+        <is>
+          <t>16/29</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="2" t="inlineStr"/>
+      <c r="B92" s="2" t="inlineStr">
+        <is>
+          <t>沪A73927D</t>
+        </is>
+      </c>
+      <c r="C92" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D92" s="2" t="inlineStr">
+        <is>
+          <t>18:00</t>
+        </is>
+      </c>
+      <c r="E92" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F92" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G92" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H92" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I92" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J92" s="2" t="inlineStr"/>
+      <c r="K92" s="2" t="inlineStr"/>
+      <c r="L92" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M92" s="2" t="inlineStr"/>
+      <c r="N92" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O92" s="2" t="inlineStr">
+        <is>
+          <t>17:21</t>
+        </is>
+      </c>
+      <c r="P92" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q92" s="2" t="inlineStr"/>
+      <c r="R92" s="2" t="inlineStr"/>
+      <c r="S92" s="2" t="inlineStr"/>
+      <c r="T92" s="2" t="inlineStr"/>
+      <c r="U92" s="2" t="inlineStr">
+        <is>
+          <t>18:00</t>
+        </is>
+      </c>
+      <c r="V92" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W92" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X92" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y92" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z92" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA92" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB92" s="2" t="inlineStr">
+        <is>
+          <t>138.0</t>
+        </is>
+      </c>
+      <c r="AC92" s="2" t="inlineStr">
+        <is>
+          <t>23/29</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-10-31-浦东35路.xlsx
+++ b/data/export/2026-10-31-浦东35路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC92"/>
+  <dimension ref="A1:AC101"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -723,7 +723,7 @@
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>5/29</t>
+          <t>3/29</t>
         </is>
       </c>
     </row>
@@ -788,7 +788,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -907,7 +907,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -946,22 +946,22 @@
       </c>
       <c r="Z4" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA4" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA4" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB4" s="2" t="inlineStr">
         <is>
-          <t>128.5</t>
+          <t>130.0</t>
         </is>
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>4/29</t>
+          <t>6/29</t>
         </is>
       </c>
     </row>
@@ -1026,7 +1026,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1318,7 +1318,7 @@
       </c>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>15/29</t>
+          <t>17/29</t>
         </is>
       </c>
     </row>
@@ -1383,7 +1383,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1432,7 +1432,7 @@
       </c>
       <c r="AB8" s="2" t="inlineStr">
         <is>
-          <t>138.0</t>
+          <t>138.3</t>
         </is>
       </c>
       <c r="AC8" s="2" t="inlineStr">
@@ -1502,7 +1502,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1556,7 +1556,7 @@
       </c>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>2/29</t>
+          <t>1/29</t>
         </is>
       </c>
     </row>
@@ -1621,7 +1621,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1675,7 +1675,7 @@
       </c>
       <c r="AC10" s="2" t="inlineStr">
         <is>
-          <t>12/29</t>
+          <t>13/29</t>
         </is>
       </c>
     </row>
@@ -1740,7 +1740,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1859,7 +1859,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1898,7 +1898,7 @@
       </c>
       <c r="Z12" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA12" s="2" t="inlineStr">
@@ -1908,12 +1908,12 @@
       </c>
       <c r="AB12" s="2" t="inlineStr">
         <is>
-          <t>136.5</t>
+          <t>133.5</t>
         </is>
       </c>
       <c r="AC12" s="2" t="inlineStr">
         <is>
-          <t>20/29</t>
+          <t>15/29</t>
         </is>
       </c>
     </row>
@@ -1974,7 +1974,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -2029,7 +2029,7 @@
       </c>
       <c r="Z13" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA13" s="2" t="inlineStr">
@@ -2039,12 +2039,12 @@
       </c>
       <c r="AB13" s="2" t="inlineStr">
         <is>
-          <t>137.5</t>
+          <t>140.0</t>
         </is>
       </c>
       <c r="AC13" s="2" t="inlineStr">
         <is>
-          <t>21/29</t>
+          <t>25/29</t>
         </is>
       </c>
     </row>
@@ -2109,7 +2109,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:11</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2153,17 +2153,17 @@
       </c>
       <c r="AA14" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB14" s="2" t="inlineStr">
         <is>
-          <t>141.0</t>
+          <t>141.3</t>
         </is>
       </c>
       <c r="AC14" s="2" t="inlineStr">
         <is>
-          <t>26/29</t>
+          <t>27/29</t>
         </is>
       </c>
     </row>
@@ -2224,7 +2224,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2278,7 +2278,7 @@
       </c>
       <c r="AC15" s="2" t="inlineStr">
         <is>
-          <t>3/29</t>
+          <t>2/29</t>
         </is>
       </c>
     </row>
@@ -2343,7 +2343,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>15:31</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2382,14 +2382,14 @@
       </c>
       <c r="Z16" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA16" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA16" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB16" s="2" t="inlineStr">
         <is>
           <t>135.0</t>
@@ -2397,7 +2397,7 @@
       </c>
       <c r="AC16" s="2" t="inlineStr">
         <is>
-          <t>16/29</t>
+          <t>18/29</t>
         </is>
       </c>
     </row>
@@ -2462,7 +2462,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2581,7 +2581,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2635,7 +2635,7 @@
       </c>
       <c r="AC18" s="2" t="inlineStr">
         <is>
-          <t>14/29</t>
+          <t>16/29</t>
         </is>
       </c>
     </row>
@@ -2696,7 +2696,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2740,17 +2740,17 @@
       </c>
       <c r="AA19" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB19" s="2" t="inlineStr">
         <is>
-          <t>123.0</t>
+          <t>131.5</t>
         </is>
       </c>
       <c r="AC19" s="2" t="inlineStr">
         <is>
-          <t>1/29</t>
+          <t>10/29</t>
         </is>
       </c>
     </row>
@@ -2815,7 +2815,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>13:11</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2854,14 +2854,14 @@
       </c>
       <c r="Z20" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA20" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA20" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB20" s="2" t="inlineStr">
         <is>
           <t>132.0</t>
@@ -2869,7 +2869,7 @@
       </c>
       <c r="AC20" s="2" t="inlineStr">
         <is>
-          <t>10/29</t>
+          <t>11/29</t>
         </is>
       </c>
     </row>
@@ -3049,7 +3049,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -3103,7 +3103,7 @@
       </c>
       <c r="AC22" s="2" t="inlineStr">
         <is>
-          <t>16/29</t>
+          <t>18/29</t>
         </is>
       </c>
     </row>
@@ -3164,7 +3164,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>14:51</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -3203,7 +3203,7 @@
       </c>
       <c r="Z23" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA23" s="2" t="inlineStr">
@@ -3333,7 +3333,7 @@
       </c>
       <c r="AC24" s="2" t="inlineStr">
         <is>
-          <t>19/29</t>
+          <t>21/29</t>
         </is>
       </c>
     </row>
@@ -3398,7 +3398,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3437,7 +3437,7 @@
       </c>
       <c r="Z25" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA25" s="2" t="inlineStr">
@@ -3452,7 +3452,7 @@
       </c>
       <c r="AC25" s="2" t="inlineStr">
         <is>
-          <t>10/29</t>
+          <t>11/29</t>
         </is>
       </c>
     </row>
@@ -3571,7 +3571,7 @@
       </c>
       <c r="AC26" s="2" t="inlineStr">
         <is>
-          <t>13/29</t>
+          <t>14/29</t>
         </is>
       </c>
     </row>
@@ -3690,7 +3690,7 @@
       </c>
       <c r="AC27" s="2" t="inlineStr">
         <is>
-          <t>5/29</t>
+          <t>3/29</t>
         </is>
       </c>
     </row>
@@ -3755,7 +3755,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -3874,7 +3874,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -3928,7 +3928,7 @@
       </c>
       <c r="AC29" s="2" t="inlineStr">
         <is>
-          <t>6/29</t>
+          <t>5/29</t>
         </is>
       </c>
     </row>
@@ -3993,7 +3993,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -4032,22 +4032,22 @@
       </c>
       <c r="Z30" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA30" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA30" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB30" s="2" t="inlineStr">
         <is>
-          <t>128.5</t>
+          <t>130.0</t>
         </is>
       </c>
       <c r="AC30" s="2" t="inlineStr">
         <is>
-          <t>4/29</t>
+          <t>6/29</t>
         </is>
       </c>
     </row>
@@ -4231,7 +4231,7 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
@@ -4350,7 +4350,7 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
@@ -4399,7 +4399,7 @@
       </c>
       <c r="AB33" s="2" t="inlineStr">
         <is>
-          <t>138.0</t>
+          <t>138.3</t>
         </is>
       </c>
       <c r="AC33" s="2" t="inlineStr">
@@ -4469,7 +4469,7 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
@@ -4523,7 +4523,7 @@
       </c>
       <c r="AC34" s="2" t="inlineStr">
         <is>
-          <t>12/29</t>
+          <t>13/29</t>
         </is>
       </c>
     </row>
@@ -4588,7 +4588,7 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
@@ -4642,7 +4642,7 @@
       </c>
       <c r="AC35" s="2" t="inlineStr">
         <is>
-          <t>15/29</t>
+          <t>17/29</t>
         </is>
       </c>
     </row>
@@ -4703,7 +4703,7 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
@@ -4758,7 +4758,7 @@
       </c>
       <c r="Z36" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA36" s="2" t="inlineStr">
@@ -4834,7 +4834,7 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
@@ -4888,7 +4888,7 @@
       </c>
       <c r="AC37" s="2" t="inlineStr">
         <is>
-          <t>2/29</t>
+          <t>1/29</t>
         </is>
       </c>
     </row>
@@ -4949,7 +4949,7 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
@@ -4988,7 +4988,7 @@
       </c>
       <c r="Z38" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA38" s="2" t="inlineStr">
@@ -4998,12 +4998,12 @@
       </c>
       <c r="AB38" s="2" t="inlineStr">
         <is>
-          <t>136.5</t>
+          <t>133.5</t>
         </is>
       </c>
       <c r="AC38" s="2" t="inlineStr">
         <is>
-          <t>20/29</t>
+          <t>15/29</t>
         </is>
       </c>
     </row>
@@ -5068,7 +5068,7 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:11</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
@@ -5112,17 +5112,17 @@
       </c>
       <c r="AA39" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB39" s="2" t="inlineStr">
         <is>
-          <t>141.0</t>
+          <t>141.3</t>
         </is>
       </c>
       <c r="AC39" s="2" t="inlineStr">
         <is>
-          <t>26/29</t>
+          <t>27/29</t>
         </is>
       </c>
     </row>
@@ -5187,7 +5187,7 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
@@ -5306,7 +5306,7 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
@@ -5360,7 +5360,7 @@
       </c>
       <c r="AC41" s="2" t="inlineStr">
         <is>
-          <t>3/29</t>
+          <t>2/29</t>
         </is>
       </c>
     </row>
@@ -5425,7 +5425,7 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>15:31</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
@@ -5464,14 +5464,14 @@
       </c>
       <c r="Z42" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA42" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA42" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB42" s="2" t="inlineStr">
         <is>
           <t>135.0</t>
@@ -5479,7 +5479,7 @@
       </c>
       <c r="AC42" s="2" t="inlineStr">
         <is>
-          <t>16/29</t>
+          <t>18/29</t>
         </is>
       </c>
     </row>
@@ -5544,7 +5544,7 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
@@ -5663,7 +5663,7 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
@@ -5707,17 +5707,17 @@
       </c>
       <c r="AA44" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB44" s="2" t="inlineStr">
         <is>
-          <t>123.0</t>
+          <t>131.5</t>
         </is>
       </c>
       <c r="AC44" s="2" t="inlineStr">
         <is>
-          <t>1/29</t>
+          <t>10/29</t>
         </is>
       </c>
     </row>
@@ -5782,7 +5782,7 @@
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
@@ -5836,7 +5836,7 @@
       </c>
       <c r="AC45" s="2" t="inlineStr">
         <is>
-          <t>14/29</t>
+          <t>16/29</t>
         </is>
       </c>
     </row>
@@ -6020,7 +6020,7 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>13:11</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
@@ -6059,14 +6059,14 @@
       </c>
       <c r="Z47" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA47" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA47" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB47" s="2" t="inlineStr">
         <is>
           <t>132.0</t>
@@ -6074,7 +6074,7 @@
       </c>
       <c r="AC47" s="2" t="inlineStr">
         <is>
-          <t>10/29</t>
+          <t>11/29</t>
         </is>
       </c>
     </row>
@@ -6139,7 +6139,7 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
@@ -6178,7 +6178,7 @@
       </c>
       <c r="Z48" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA48" s="2" t="inlineStr">
@@ -6193,7 +6193,7 @@
       </c>
       <c r="AC48" s="2" t="inlineStr">
         <is>
-          <t>10/29</t>
+          <t>11/29</t>
         </is>
       </c>
     </row>
@@ -6258,7 +6258,7 @@
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
@@ -6312,7 +6312,7 @@
       </c>
       <c r="AC49" s="2" t="inlineStr">
         <is>
-          <t>16/29</t>
+          <t>18/29</t>
         </is>
       </c>
     </row>
@@ -6431,7 +6431,7 @@
       </c>
       <c r="AC50" s="2" t="inlineStr">
         <is>
-          <t>5/29</t>
+          <t>3/29</t>
         </is>
       </c>
     </row>
@@ -6550,7 +6550,7 @@
       </c>
       <c r="AC51" s="2" t="inlineStr">
         <is>
-          <t>13/29</t>
+          <t>14/29</t>
         </is>
       </c>
     </row>
@@ -6615,7 +6615,7 @@
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
@@ -6669,7 +6669,7 @@
       </c>
       <c r="AC52" s="2" t="inlineStr">
         <is>
-          <t>6/29</t>
+          <t>5/29</t>
         </is>
       </c>
     </row>
@@ -6734,7 +6734,7 @@
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P53" s="2" t="inlineStr">
@@ -6968,7 +6968,7 @@
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P55" s="2" t="inlineStr">
@@ -7023,7 +7023,7 @@
       </c>
       <c r="Z55" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA55" s="2" t="inlineStr">
@@ -7099,7 +7099,7 @@
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P56" s="2" t="inlineStr">
@@ -7153,7 +7153,7 @@
       </c>
       <c r="AC56" s="2" t="inlineStr">
         <is>
-          <t>2/29</t>
+          <t>1/29</t>
         </is>
       </c>
     </row>
@@ -7218,7 +7218,7 @@
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P57" s="2" t="inlineStr">
@@ -7257,7 +7257,7 @@
       </c>
       <c r="Z57" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA57" s="2" t="inlineStr">
@@ -7267,12 +7267,12 @@
       </c>
       <c r="AB57" s="2" t="inlineStr">
         <is>
-          <t>137.5</t>
+          <t>140.0</t>
         </is>
       </c>
       <c r="AC57" s="2" t="inlineStr">
         <is>
-          <t>21/29</t>
+          <t>25/29</t>
         </is>
       </c>
     </row>
@@ -7337,7 +7337,7 @@
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P58" s="2" t="inlineStr">
@@ -7391,7 +7391,7 @@
       </c>
       <c r="AC58" s="2" t="inlineStr">
         <is>
-          <t>3/29</t>
+          <t>2/29</t>
         </is>
       </c>
     </row>
@@ -7456,7 +7456,7 @@
       </c>
       <c r="O59" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P59" s="2" t="inlineStr">
@@ -7500,7 +7500,7 @@
       </c>
       <c r="AA59" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB59" s="2" t="inlineStr">
@@ -7510,7 +7510,7 @@
       </c>
       <c r="AC59" s="2" t="inlineStr">
         <is>
-          <t>16/29</t>
+          <t>18/29</t>
         </is>
       </c>
     </row>
@@ -7575,7 +7575,7 @@
       </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P60" s="2" t="inlineStr">
@@ -7629,7 +7629,7 @@
       </c>
       <c r="AC60" s="2" t="inlineStr">
         <is>
-          <t>14/29</t>
+          <t>16/29</t>
         </is>
       </c>
     </row>
@@ -7694,7 +7694,7 @@
       </c>
       <c r="O61" s="2" t="inlineStr">
         <is>
-          <t>15:31</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P61" s="2" t="inlineStr">
@@ -7733,14 +7733,14 @@
       </c>
       <c r="Z61" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA61" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA61" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB61" s="2" t="inlineStr">
         <is>
           <t>135.0</t>
@@ -7748,7 +7748,7 @@
       </c>
       <c r="AC61" s="2" t="inlineStr">
         <is>
-          <t>16/29</t>
+          <t>18/29</t>
         </is>
       </c>
     </row>
@@ -7813,7 +7813,7 @@
       </c>
       <c r="O62" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P62" s="2" t="inlineStr">
@@ -7867,7 +7867,7 @@
       </c>
       <c r="AC62" s="2" t="inlineStr">
         <is>
-          <t>16/29</t>
+          <t>18/29</t>
         </is>
       </c>
     </row>
@@ -8105,7 +8105,7 @@
       </c>
       <c r="AC64" s="2" t="inlineStr">
         <is>
-          <t>5/29</t>
+          <t>3/29</t>
         </is>
       </c>
     </row>
@@ -8224,7 +8224,7 @@
       </c>
       <c r="AC65" s="2" t="inlineStr">
         <is>
-          <t>13/29</t>
+          <t>14/29</t>
         </is>
       </c>
     </row>
@@ -8289,7 +8289,7 @@
       </c>
       <c r="O66" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P66" s="2" t="inlineStr">
@@ -8343,7 +8343,7 @@
       </c>
       <c r="AC66" s="2" t="inlineStr">
         <is>
-          <t>12/29</t>
+          <t>13/29</t>
         </is>
       </c>
     </row>
@@ -8527,7 +8527,7 @@
       </c>
       <c r="O68" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P68" s="2" t="inlineStr">
@@ -8642,7 +8642,7 @@
       </c>
       <c r="O69" s="2" t="inlineStr">
         <is>
-          <t>14:51</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P69" s="2" t="inlineStr">
@@ -8681,7 +8681,7 @@
       </c>
       <c r="Z69" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA69" s="2" t="inlineStr">
@@ -8730,24 +8730,24 @@
       </c>
       <c r="H70" s="2" t="inlineStr">
         <is>
-          <t>17:31</t>
+          <t>17:32</t>
         </is>
       </c>
       <c r="I70" s="2" t="inlineStr">
         <is>
-          <t>141分钟</t>
+          <t>142分钟</t>
         </is>
       </c>
       <c r="J70" s="2" t="inlineStr"/>
       <c r="K70" s="2" t="inlineStr"/>
       <c r="L70" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±4分钟</t>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
         </is>
       </c>
       <c r="M70" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="N70" s="2" t="inlineStr">
@@ -8757,7 +8757,7 @@
       </c>
       <c r="O70" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P70" s="2" t="inlineStr">
@@ -8806,7 +8806,7 @@
       </c>
       <c r="AB70" s="2" t="inlineStr">
         <is>
-          <t>138.0</t>
+          <t>138.3</t>
         </is>
       </c>
       <c r="AC70" s="2" t="inlineStr">
@@ -8872,7 +8872,7 @@
       </c>
       <c r="O71" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P71" s="2" t="inlineStr">
@@ -8927,7 +8927,7 @@
       </c>
       <c r="Z71" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA71" s="2" t="inlineStr">
@@ -8976,24 +8976,24 @@
       </c>
       <c r="H72" s="2" t="inlineStr">
         <is>
-          <t>17:41</t>
+          <t>17:46</t>
         </is>
       </c>
       <c r="I72" s="2" t="inlineStr">
         <is>
-          <t>136分钟</t>
+          <t>141分钟</t>
         </is>
       </c>
       <c r="J72" s="2" t="inlineStr"/>
       <c r="K72" s="2" t="inlineStr"/>
       <c r="L72" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="M72" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N72" s="2" t="inlineStr">
@@ -9003,7 +9003,7 @@
       </c>
       <c r="O72" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P72" s="2" t="inlineStr">
@@ -9042,7 +9042,7 @@
       </c>
       <c r="Z72" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA72" s="2" t="inlineStr">
@@ -9052,12 +9052,12 @@
       </c>
       <c r="AB72" s="2" t="inlineStr">
         <is>
-          <t>137.5</t>
+          <t>140.0</t>
         </is>
       </c>
       <c r="AC72" s="2" t="inlineStr">
         <is>
-          <t>21/29</t>
+          <t>25/29</t>
         </is>
       </c>
     </row>
@@ -9118,7 +9118,7 @@
       </c>
       <c r="O73" s="2" t="inlineStr">
         <is>
-          <t>14:51</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P73" s="2" t="inlineStr">
@@ -9157,7 +9157,7 @@
       </c>
       <c r="Z73" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA73" s="2" t="inlineStr">
@@ -9206,24 +9206,24 @@
       </c>
       <c r="H74" s="2" t="inlineStr">
         <is>
-          <t>17:58</t>
+          <t>17:52</t>
         </is>
       </c>
       <c r="I74" s="2" t="inlineStr">
         <is>
-          <t>143分钟</t>
+          <t>137分钟</t>
         </is>
       </c>
       <c r="J74" s="2" t="inlineStr"/>
       <c r="K74" s="2" t="inlineStr"/>
       <c r="L74" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
         </is>
       </c>
       <c r="M74" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="N74" s="2" t="inlineStr">
@@ -9233,7 +9233,7 @@
       </c>
       <c r="O74" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P74" s="2" t="inlineStr">
@@ -9272,7 +9272,7 @@
       </c>
       <c r="Z74" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA74" s="2" t="inlineStr">
@@ -9282,12 +9282,12 @@
       </c>
       <c r="AB74" s="2" t="inlineStr">
         <is>
-          <t>136.5</t>
+          <t>133.5</t>
         </is>
       </c>
       <c r="AC74" s="2" t="inlineStr">
         <is>
-          <t>20/29</t>
+          <t>15/29</t>
         </is>
       </c>
     </row>
@@ -9315,32 +9315,36 @@
       </c>
       <c r="F75" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G75" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H75" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>17:54</t>
         </is>
       </c>
       <c r="I75" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>129分钟</t>
         </is>
       </c>
       <c r="J75" s="2" t="inlineStr"/>
       <c r="K75" s="2" t="inlineStr"/>
       <c r="L75" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M75" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M75" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N75" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -9348,7 +9352,7 @@
       </c>
       <c r="O75" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P75" s="2" t="inlineStr">
@@ -9372,33 +9376,37 @@
       </c>
       <c r="W75" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X75" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y75" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z75" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA75" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AA75" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB75" s="2" t="inlineStr"/>
+      <c r="AB75" s="2" t="inlineStr">
+        <is>
+          <t>129.0</t>
+        </is>
+      </c>
       <c r="AC75" s="2" t="inlineStr">
         <is>
-          <t>—/29</t>
+          <t>4/29</t>
         </is>
       </c>
     </row>
@@ -9426,32 +9434,36 @@
       </c>
       <c r="F76" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G76" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H76" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>18:22</t>
         </is>
       </c>
       <c r="I76" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>142分钟</t>
         </is>
       </c>
       <c r="J76" s="2" t="inlineStr"/>
       <c r="K76" s="2" t="inlineStr"/>
       <c r="L76" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M76" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±4分钟</t>
+        </is>
+      </c>
+      <c r="M76" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="N76" s="2" t="inlineStr">
         <is>
           <t>07:01</t>
@@ -9459,7 +9471,7 @@
       </c>
       <c r="O76" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:11</t>
         </is>
       </c>
       <c r="P76" s="2" t="inlineStr">
@@ -9483,17 +9495,17 @@
       </c>
       <c r="W76" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X76" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y76" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z76" s="2" t="inlineStr">
@@ -9503,17 +9515,17 @@
       </c>
       <c r="AA76" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB76" s="2" t="inlineStr">
         <is>
-          <t>141.0</t>
+          <t>141.3</t>
         </is>
       </c>
       <c r="AC76" s="2" t="inlineStr">
         <is>
-          <t>26/29</t>
+          <t>27/29</t>
         </is>
       </c>
     </row>
@@ -9541,32 +9553,36 @@
       </c>
       <c r="F77" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G77" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H77" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>18:25</t>
         </is>
       </c>
       <c r="I77" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>135分钟</t>
         </is>
       </c>
       <c r="J77" s="2" t="inlineStr"/>
       <c r="K77" s="2" t="inlineStr"/>
       <c r="L77" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M77" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M77" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N77" s="2" t="inlineStr">
         <is>
           <t>07:31</t>
@@ -9574,7 +9590,7 @@
       </c>
       <c r="O77" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P77" s="2" t="inlineStr">
@@ -9598,17 +9614,17 @@
       </c>
       <c r="W77" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X77" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y77" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z77" s="2" t="inlineStr">
@@ -9618,7 +9634,7 @@
       </c>
       <c r="AA77" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB77" s="2" t="inlineStr">
@@ -9628,7 +9644,7 @@
       </c>
       <c r="AC77" s="2" t="inlineStr">
         <is>
-          <t>16/29</t>
+          <t>18/29</t>
         </is>
       </c>
     </row>
@@ -9656,32 +9672,36 @@
       </c>
       <c r="F78" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G78" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H78" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>18:35</t>
         </is>
       </c>
       <c r="I78" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>140分钟</t>
         </is>
       </c>
       <c r="J78" s="2" t="inlineStr"/>
       <c r="K78" s="2" t="inlineStr"/>
       <c r="L78" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M78" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M78" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N78" s="2" t="inlineStr">
         <is>
           <t>07:21</t>
@@ -9689,7 +9709,7 @@
       </c>
       <c r="O78" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P78" s="2" t="inlineStr">
@@ -9713,17 +9733,17 @@
       </c>
       <c r="W78" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X78" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y78" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z78" s="2" t="inlineStr">
@@ -9733,17 +9753,17 @@
       </c>
       <c r="AA78" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB78" s="2" t="inlineStr">
         <is>
-          <t>123.0</t>
+          <t>131.5</t>
         </is>
       </c>
       <c r="AC78" s="2" t="inlineStr">
         <is>
-          <t>1/29</t>
+          <t>10/29</t>
         </is>
       </c>
     </row>
@@ -9804,7 +9824,7 @@
       </c>
       <c r="O79" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P79" s="2" t="inlineStr">
@@ -9843,7 +9863,7 @@
       </c>
       <c r="Z79" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA79" s="2" t="inlineStr">
@@ -9858,7 +9878,7 @@
       </c>
       <c r="AC79" s="2" t="inlineStr">
         <is>
-          <t>10/29</t>
+          <t>11/29</t>
         </is>
       </c>
     </row>
@@ -9886,32 +9906,36 @@
       </c>
       <c r="F80" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G80" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H80" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>18:43</t>
         </is>
       </c>
       <c r="I80" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>133分钟</t>
         </is>
       </c>
       <c r="J80" s="2" t="inlineStr"/>
       <c r="K80" s="2" t="inlineStr"/>
       <c r="L80" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M80" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M80" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N80" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -9919,7 +9943,7 @@
       </c>
       <c r="O80" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P80" s="2" t="inlineStr">
@@ -9943,37 +9967,37 @@
       </c>
       <c r="W80" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X80" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y80" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z80" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA80" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA80" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB80" s="2" t="inlineStr">
         <is>
-          <t>128.5</t>
+          <t>130.0</t>
         </is>
       </c>
       <c r="AC80" s="2" t="inlineStr">
         <is>
-          <t>4/29</t>
+          <t>6/29</t>
         </is>
       </c>
     </row>
@@ -10034,7 +10058,7 @@
       </c>
       <c r="O81" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P81" s="2" t="inlineStr">
@@ -10088,7 +10112,7 @@
       </c>
       <c r="AC81" s="2" t="inlineStr">
         <is>
-          <t>6/29</t>
+          <t>5/29</t>
         </is>
       </c>
     </row>
@@ -10149,7 +10173,7 @@
       </c>
       <c r="O82" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P82" s="2" t="inlineStr">
@@ -10203,7 +10227,7 @@
       </c>
       <c r="AC82" s="2" t="inlineStr">
         <is>
-          <t>15/29</t>
+          <t>17/29</t>
         </is>
       </c>
     </row>
@@ -10264,7 +10288,7 @@
       </c>
       <c r="O83" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P83" s="2" t="inlineStr">
@@ -10379,7 +10403,7 @@
       </c>
       <c r="O84" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P84" s="2" t="inlineStr">
@@ -10494,7 +10518,7 @@
       </c>
       <c r="O85" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P85" s="2" t="inlineStr">
@@ -10548,7 +10572,7 @@
       </c>
       <c r="AC85" s="2" t="inlineStr">
         <is>
-          <t>2/29</t>
+          <t>1/29</t>
         </is>
       </c>
     </row>
@@ -10609,7 +10633,7 @@
       </c>
       <c r="O86" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P86" s="2" t="inlineStr">
@@ -10663,7 +10687,7 @@
       </c>
       <c r="AC86" s="2" t="inlineStr">
         <is>
-          <t>12/29</t>
+          <t>13/29</t>
         </is>
       </c>
     </row>
@@ -10724,7 +10748,7 @@
       </c>
       <c r="O87" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P87" s="2" t="inlineStr">
@@ -10839,7 +10863,7 @@
       </c>
       <c r="O88" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P88" s="2" t="inlineStr">
@@ -10893,7 +10917,7 @@
       </c>
       <c r="AC88" s="2" t="inlineStr">
         <is>
-          <t>3/29</t>
+          <t>2/29</t>
         </is>
       </c>
     </row>
@@ -10954,7 +10978,7 @@
       </c>
       <c r="O89" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P89" s="2" t="inlineStr">
@@ -11008,7 +11032,7 @@
       </c>
       <c r="AC89" s="2" t="inlineStr">
         <is>
-          <t>14/29</t>
+          <t>16/29</t>
         </is>
       </c>
     </row>
@@ -11069,7 +11093,7 @@
       </c>
       <c r="O90" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P90" s="2" t="inlineStr">
@@ -11184,7 +11208,7 @@
       </c>
       <c r="O91" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P91" s="2" t="inlineStr">
@@ -11238,7 +11262,7 @@
       </c>
       <c r="AC91" s="2" t="inlineStr">
         <is>
-          <t>16/29</t>
+          <t>18/29</t>
         </is>
       </c>
     </row>
@@ -11299,7 +11323,7 @@
       </c>
       <c r="O92" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P92" s="2" t="inlineStr">
@@ -11348,12 +11372,1039 @@
       </c>
       <c r="AB92" s="2" t="inlineStr">
         <is>
-          <t>138.0</t>
+          <t>138.3</t>
         </is>
       </c>
       <c r="AC92" s="2" t="inlineStr">
         <is>
           <t>23/29</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="2" t="inlineStr"/>
+      <c r="B93" s="2" t="inlineStr">
+        <is>
+          <t>沪A51682D</t>
+        </is>
+      </c>
+      <c r="C93" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D93" s="2" t="inlineStr">
+        <is>
+          <t>18:10</t>
+        </is>
+      </c>
+      <c r="E93" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F93" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G93" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H93" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I93" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J93" s="2" t="inlineStr"/>
+      <c r="K93" s="2" t="inlineStr"/>
+      <c r="L93" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M93" s="2" t="inlineStr"/>
+      <c r="N93" s="2" t="inlineStr">
+        <is>
+          <t>06:51</t>
+        </is>
+      </c>
+      <c r="O93" s="2" t="inlineStr">
+        <is>
+          <t>18:21</t>
+        </is>
+      </c>
+      <c r="P93" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q93" s="2" t="inlineStr"/>
+      <c r="R93" s="2" t="inlineStr"/>
+      <c r="S93" s="2" t="inlineStr"/>
+      <c r="T93" s="2" t="inlineStr"/>
+      <c r="U93" s="2" t="inlineStr">
+        <is>
+          <t>18:10</t>
+        </is>
+      </c>
+      <c r="V93" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W93" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X93" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y93" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z93" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA93" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB93" s="2" t="inlineStr">
+        <is>
+          <t>140.0</t>
+        </is>
+      </c>
+      <c r="AC93" s="2" t="inlineStr">
+        <is>
+          <t>25/29</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="2" t="inlineStr"/>
+      <c r="B94" s="2" t="inlineStr">
+        <is>
+          <t>沪A79307D</t>
+        </is>
+      </c>
+      <c r="C94" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D94" s="2" t="inlineStr">
+        <is>
+          <t>18:12</t>
+        </is>
+      </c>
+      <c r="E94" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F94" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G94" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H94" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I94" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J94" s="2" t="inlineStr"/>
+      <c r="K94" s="2" t="inlineStr"/>
+      <c r="L94" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M94" s="2" t="inlineStr"/>
+      <c r="N94" s="2" t="inlineStr">
+        <is>
+          <t>09:31</t>
+        </is>
+      </c>
+      <c r="O94" s="2" t="inlineStr">
+        <is>
+          <t>18:21</t>
+        </is>
+      </c>
+      <c r="P94" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q94" s="2" t="inlineStr"/>
+      <c r="R94" s="2" t="inlineStr"/>
+      <c r="S94" s="2" t="inlineStr"/>
+      <c r="T94" s="2" t="inlineStr"/>
+      <c r="U94" s="2" t="inlineStr">
+        <is>
+          <t>18:12</t>
+        </is>
+      </c>
+      <c r="V94" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W94" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X94" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y94" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z94" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA94" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB94" s="2" t="inlineStr"/>
+      <c r="AC94" s="2" t="inlineStr">
+        <is>
+          <t>—/29</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="2" t="inlineStr"/>
+      <c r="B95" s="2" t="inlineStr">
+        <is>
+          <t>沪A57383A</t>
+        </is>
+      </c>
+      <c r="C95" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D95" s="2" t="inlineStr">
+        <is>
+          <t>18:20</t>
+        </is>
+      </c>
+      <c r="E95" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F95" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G95" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H95" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I95" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J95" s="2" t="inlineStr"/>
+      <c r="K95" s="2" t="inlineStr"/>
+      <c r="L95" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M95" s="2" t="inlineStr"/>
+      <c r="N95" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="O95" s="2" t="inlineStr">
+        <is>
+          <t>18:21</t>
+        </is>
+      </c>
+      <c r="P95" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q95" s="2" t="inlineStr"/>
+      <c r="R95" s="2" t="inlineStr"/>
+      <c r="S95" s="2" t="inlineStr"/>
+      <c r="T95" s="2" t="inlineStr"/>
+      <c r="U95" s="2" t="inlineStr">
+        <is>
+          <t>18:20</t>
+        </is>
+      </c>
+      <c r="V95" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W95" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X95" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y95" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z95" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA95" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB95" s="2" t="inlineStr">
+        <is>
+          <t>132.0</t>
+        </is>
+      </c>
+      <c r="AC95" s="2" t="inlineStr">
+        <is>
+          <t>11/29</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="2" t="inlineStr"/>
+      <c r="B96" s="2" t="inlineStr">
+        <is>
+          <t>沪A71572D</t>
+        </is>
+      </c>
+      <c r="C96" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D96" s="2" t="inlineStr">
+        <is>
+          <t>18:25</t>
+        </is>
+      </c>
+      <c r="E96" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F96" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G96" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H96" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I96" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J96" s="2" t="inlineStr"/>
+      <c r="K96" s="2" t="inlineStr"/>
+      <c r="L96" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M96" s="2" t="inlineStr"/>
+      <c r="N96" s="2" t="inlineStr">
+        <is>
+          <t>06:21</t>
+        </is>
+      </c>
+      <c r="O96" s="2" t="inlineStr">
+        <is>
+          <t>18:21</t>
+        </is>
+      </c>
+      <c r="P96" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q96" s="2" t="inlineStr"/>
+      <c r="R96" s="2" t="inlineStr"/>
+      <c r="S96" s="2" t="inlineStr"/>
+      <c r="T96" s="2" t="inlineStr"/>
+      <c r="U96" s="2" t="inlineStr">
+        <is>
+          <t>18:25</t>
+        </is>
+      </c>
+      <c r="V96" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W96" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X96" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y96" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z96" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA96" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB96" s="2" t="inlineStr"/>
+      <c r="AC96" s="2" t="inlineStr">
+        <is>
+          <t>—/29</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="2" t="inlineStr"/>
+      <c r="B97" s="2" t="inlineStr">
+        <is>
+          <t>沪A02891D</t>
+        </is>
+      </c>
+      <c r="C97" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D97" s="2" t="inlineStr">
+        <is>
+          <t>18:40</t>
+        </is>
+      </c>
+      <c r="E97" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F97" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G97" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H97" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I97" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J97" s="2" t="inlineStr"/>
+      <c r="K97" s="2" t="inlineStr"/>
+      <c r="L97" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M97" s="2" t="inlineStr"/>
+      <c r="N97" s="2" t="inlineStr">
+        <is>
+          <t>07:11</t>
+        </is>
+      </c>
+      <c r="O97" s="2" t="inlineStr">
+        <is>
+          <t>18:21</t>
+        </is>
+      </c>
+      <c r="P97" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q97" s="2" t="inlineStr"/>
+      <c r="R97" s="2" t="inlineStr"/>
+      <c r="S97" s="2" t="inlineStr"/>
+      <c r="T97" s="2" t="inlineStr"/>
+      <c r="U97" s="2" t="inlineStr">
+        <is>
+          <t>18:40</t>
+        </is>
+      </c>
+      <c r="V97" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W97" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X97" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y97" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z97" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA97" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB97" s="2" t="inlineStr">
+        <is>
+          <t>135.0</t>
+        </is>
+      </c>
+      <c r="AC97" s="2" t="inlineStr">
+        <is>
+          <t>18/29</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" s="2" t="inlineStr"/>
+      <c r="B98" s="2" t="inlineStr">
+        <is>
+          <t>沪A15790A</t>
+        </is>
+      </c>
+      <c r="C98" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D98" s="2" t="inlineStr">
+        <is>
+          <t>18:50</t>
+        </is>
+      </c>
+      <c r="E98" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F98" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G98" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H98" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I98" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J98" s="2" t="inlineStr"/>
+      <c r="K98" s="2" t="inlineStr"/>
+      <c r="L98" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M98" s="2" t="inlineStr"/>
+      <c r="N98" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O98" s="2" t="inlineStr">
+        <is>
+          <t>18:21</t>
+        </is>
+      </c>
+      <c r="P98" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q98" s="2" t="inlineStr"/>
+      <c r="R98" s="2" t="inlineStr"/>
+      <c r="S98" s="2" t="inlineStr"/>
+      <c r="T98" s="2" t="inlineStr"/>
+      <c r="U98" s="2" t="inlineStr">
+        <is>
+          <t>18:50</t>
+        </is>
+      </c>
+      <c r="V98" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W98" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X98" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y98" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z98" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA98" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB98" s="2" t="inlineStr">
+        <is>
+          <t>129.0</t>
+        </is>
+      </c>
+      <c r="AC98" s="2" t="inlineStr">
+        <is>
+          <t>4/29</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" s="2" t="inlineStr"/>
+      <c r="B99" s="2" t="inlineStr">
+        <is>
+          <t>沪A72873D</t>
+        </is>
+      </c>
+      <c r="C99" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D99" s="2" t="inlineStr">
+        <is>
+          <t>19:00</t>
+        </is>
+      </c>
+      <c r="E99" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F99" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G99" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H99" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I99" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J99" s="2" t="inlineStr"/>
+      <c r="K99" s="2" t="inlineStr"/>
+      <c r="L99" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M99" s="2" t="inlineStr"/>
+      <c r="N99" s="2" t="inlineStr">
+        <is>
+          <t>06:32</t>
+        </is>
+      </c>
+      <c r="O99" s="2" t="inlineStr">
+        <is>
+          <t>18:21</t>
+        </is>
+      </c>
+      <c r="P99" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q99" s="2" t="inlineStr"/>
+      <c r="R99" s="2" t="inlineStr"/>
+      <c r="S99" s="2" t="inlineStr"/>
+      <c r="T99" s="2" t="inlineStr"/>
+      <c r="U99" s="2" t="inlineStr">
+        <is>
+          <t>19:00</t>
+        </is>
+      </c>
+      <c r="V99" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W99" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X99" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y99" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z99" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA99" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB99" s="2" t="inlineStr">
+        <is>
+          <t>133.5</t>
+        </is>
+      </c>
+      <c r="AC99" s="2" t="inlineStr">
+        <is>
+          <t>15/29</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" s="2" t="inlineStr"/>
+      <c r="B100" s="2" t="inlineStr">
+        <is>
+          <t>沪A55102D</t>
+        </is>
+      </c>
+      <c r="C100" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D100" s="2" t="inlineStr">
+        <is>
+          <t>19:10</t>
+        </is>
+      </c>
+      <c r="E100" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F100" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G100" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H100" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I100" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J100" s="2" t="inlineStr"/>
+      <c r="K100" s="2" t="inlineStr"/>
+      <c r="L100" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M100" s="2" t="inlineStr"/>
+      <c r="N100" s="2" t="inlineStr">
+        <is>
+          <t>06:51</t>
+        </is>
+      </c>
+      <c r="O100" s="2" t="inlineStr">
+        <is>
+          <t>18:21</t>
+        </is>
+      </c>
+      <c r="P100" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q100" s="2" t="inlineStr"/>
+      <c r="R100" s="2" t="inlineStr"/>
+      <c r="S100" s="2" t="inlineStr"/>
+      <c r="T100" s="2" t="inlineStr"/>
+      <c r="U100" s="2" t="inlineStr">
+        <is>
+          <t>19:10</t>
+        </is>
+      </c>
+      <c r="V100" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W100" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X100" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y100" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z100" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA100" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB100" s="2" t="inlineStr">
+        <is>
+          <t>132.0</t>
+        </is>
+      </c>
+      <c r="AC100" s="2" t="inlineStr">
+        <is>
+          <t>11/29</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" s="2" t="inlineStr"/>
+      <c r="B101" s="2" t="inlineStr">
+        <is>
+          <t>沪A67712D</t>
+        </is>
+      </c>
+      <c r="C101" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D101" s="2" t="inlineStr">
+        <is>
+          <t>19:15</t>
+        </is>
+      </c>
+      <c r="E101" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F101" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G101" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H101" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I101" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J101" s="2" t="inlineStr"/>
+      <c r="K101" s="2" t="inlineStr"/>
+      <c r="L101" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M101" s="2" t="inlineStr"/>
+      <c r="N101" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O101" s="2" t="inlineStr">
+        <is>
+          <t>18:21</t>
+        </is>
+      </c>
+      <c r="P101" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q101" s="2" t="inlineStr"/>
+      <c r="R101" s="2" t="inlineStr"/>
+      <c r="S101" s="2" t="inlineStr"/>
+      <c r="T101" s="2" t="inlineStr"/>
+      <c r="U101" s="2" t="inlineStr">
+        <is>
+          <t>19:15</t>
+        </is>
+      </c>
+      <c r="V101" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W101" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X101" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y101" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z101" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA101" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB101" s="2" t="inlineStr">
+        <is>
+          <t>130.0</t>
+        </is>
+      </c>
+      <c r="AC101" s="2" t="inlineStr">
+        <is>
+          <t>6/29</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-10-31-浦东35路.xlsx
+++ b/data/export/2026-10-31-浦东35路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC101"/>
+  <dimension ref="A1:AC107"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -788,7 +788,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -907,7 +907,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -961,7 +961,7 @@
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>6/29</t>
+          <t>5/29</t>
         </is>
       </c>
     </row>
@@ -1026,7 +1026,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1070,17 +1070,17 @@
       </c>
       <c r="AA5" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB5" s="2" t="inlineStr">
         <is>
-          <t>139.7</t>
+          <t>140.8</t>
         </is>
       </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>24/29</t>
+          <t>26/29</t>
         </is>
       </c>
     </row>
@@ -1264,7 +1264,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1303,22 +1303,22 @@
       </c>
       <c r="Z7" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA7" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA7" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB7" s="2" t="inlineStr">
         <is>
-          <t>134.5</t>
+          <t>134.3</t>
         </is>
       </c>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>17/29</t>
+          <t>16/29</t>
         </is>
       </c>
     </row>
@@ -1383,7 +1383,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1502,7 +1502,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1546,12 +1546,12 @@
       </c>
       <c r="AA9" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB9" s="2" t="inlineStr">
         <is>
-          <t>127.0</t>
+          <t>127.5</t>
         </is>
       </c>
       <c r="AC9" s="2" t="inlineStr">
@@ -1621,7 +1621,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1665,17 +1665,17 @@
       </c>
       <c r="AA10" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB10" s="2" t="inlineStr">
         <is>
-          <t>132.3</t>
+          <t>132.2</t>
         </is>
       </c>
       <c r="AC10" s="2" t="inlineStr">
         <is>
-          <t>13/29</t>
+          <t>12/29</t>
         </is>
       </c>
     </row>
@@ -1740,7 +1740,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1779,22 +1779,22 @@
       </c>
       <c r="Z11" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA11" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA11" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB11" s="2" t="inlineStr">
         <is>
-          <t>130.5</t>
+          <t>131.7</t>
         </is>
       </c>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>7/29</t>
+          <t>10/29</t>
         </is>
       </c>
     </row>
@@ -1859,7 +1859,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1913,7 +1913,7 @@
       </c>
       <c r="AC12" s="2" t="inlineStr">
         <is>
-          <t>15/29</t>
+          <t>14/29</t>
         </is>
       </c>
     </row>
@@ -1974,7 +1974,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -2044,7 +2044,7 @@
       </c>
       <c r="AC13" s="2" t="inlineStr">
         <is>
-          <t>25/29</t>
+          <t>24/29</t>
         </is>
       </c>
     </row>
@@ -2109,7 +2109,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>18:11</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2148,7 +2148,7 @@
       </c>
       <c r="Z14" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA14" s="2" t="inlineStr">
@@ -2224,7 +2224,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2278,7 +2278,7 @@
       </c>
       <c r="AC15" s="2" t="inlineStr">
         <is>
-          <t>2/29</t>
+          <t>1/29</t>
         </is>
       </c>
     </row>
@@ -2343,7 +2343,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2397,7 +2397,7 @@
       </c>
       <c r="AC16" s="2" t="inlineStr">
         <is>
-          <t>18/29</t>
+          <t>17/29</t>
         </is>
       </c>
     </row>
@@ -2462,7 +2462,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2516,7 +2516,7 @@
       </c>
       <c r="AC17" s="2" t="inlineStr">
         <is>
-          <t>25/29</t>
+          <t>24/29</t>
         </is>
       </c>
     </row>
@@ -2581,7 +2581,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2635,7 +2635,7 @@
       </c>
       <c r="AC18" s="2" t="inlineStr">
         <is>
-          <t>16/29</t>
+          <t>15/29</t>
         </is>
       </c>
     </row>
@@ -2696,7 +2696,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2735,7 +2735,7 @@
       </c>
       <c r="Z19" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA19" s="2" t="inlineStr">
@@ -2745,12 +2745,12 @@
       </c>
       <c r="AB19" s="2" t="inlineStr">
         <is>
-          <t>131.5</t>
+          <t>130.5</t>
         </is>
       </c>
       <c r="AC19" s="2" t="inlineStr">
         <is>
-          <t>10/29</t>
+          <t>7/29</t>
         </is>
       </c>
     </row>
@@ -2815,7 +2815,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -3049,7 +3049,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -3103,7 +3103,7 @@
       </c>
       <c r="AC22" s="2" t="inlineStr">
         <is>
-          <t>18/29</t>
+          <t>17/29</t>
         </is>
       </c>
     </row>
@@ -3398,7 +3398,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3442,17 +3442,17 @@
       </c>
       <c r="AA25" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB25" s="2" t="inlineStr">
         <is>
-          <t>132.0</t>
+          <t>135.3</t>
         </is>
       </c>
       <c r="AC25" s="2" t="inlineStr">
         <is>
-          <t>11/29</t>
+          <t>20/29</t>
         </is>
       </c>
     </row>
@@ -3571,7 +3571,7 @@
       </c>
       <c r="AC26" s="2" t="inlineStr">
         <is>
-          <t>14/29</t>
+          <t>13/29</t>
         </is>
       </c>
     </row>
@@ -3755,7 +3755,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -3874,7 +3874,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -3913,17 +3913,17 @@
       </c>
       <c r="Z29" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA29" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA29" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB29" s="2" t="inlineStr">
         <is>
-          <t>129.5</t>
+          <t>130.0</t>
         </is>
       </c>
       <c r="AC29" s="2" t="inlineStr">
@@ -3993,7 +3993,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -4047,7 +4047,7 @@
       </c>
       <c r="AC30" s="2" t="inlineStr">
         <is>
-          <t>6/29</t>
+          <t>5/29</t>
         </is>
       </c>
     </row>
@@ -4231,7 +4231,7 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
@@ -4275,17 +4275,17 @@
       </c>
       <c r="AA32" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB32" s="2" t="inlineStr">
         <is>
-          <t>139.7</t>
+          <t>140.8</t>
         </is>
       </c>
       <c r="AC32" s="2" t="inlineStr">
         <is>
-          <t>24/29</t>
+          <t>26/29</t>
         </is>
       </c>
     </row>
@@ -4350,7 +4350,7 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
@@ -4469,7 +4469,7 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
@@ -4513,17 +4513,17 @@
       </c>
       <c r="AA34" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB34" s="2" t="inlineStr">
         <is>
-          <t>132.3</t>
+          <t>132.2</t>
         </is>
       </c>
       <c r="AC34" s="2" t="inlineStr">
         <is>
-          <t>13/29</t>
+          <t>12/29</t>
         </is>
       </c>
     </row>
@@ -4588,7 +4588,7 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
@@ -4627,22 +4627,22 @@
       </c>
       <c r="Z35" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA35" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA35" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB35" s="2" t="inlineStr">
         <is>
-          <t>134.5</t>
+          <t>134.3</t>
         </is>
       </c>
       <c r="AC35" s="2" t="inlineStr">
         <is>
-          <t>17/29</t>
+          <t>16/29</t>
         </is>
       </c>
     </row>
@@ -4703,7 +4703,7 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:01</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
@@ -4834,7 +4834,7 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
@@ -4878,12 +4878,12 @@
       </c>
       <c r="AA37" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB37" s="2" t="inlineStr">
         <is>
-          <t>127.0</t>
+          <t>127.5</t>
         </is>
       </c>
       <c r="AC37" s="2" t="inlineStr">
@@ -4949,7 +4949,7 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
@@ -5003,7 +5003,7 @@
       </c>
       <c r="AC38" s="2" t="inlineStr">
         <is>
-          <t>15/29</t>
+          <t>14/29</t>
         </is>
       </c>
     </row>
@@ -5068,7 +5068,7 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>18:11</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
@@ -5107,7 +5107,7 @@
       </c>
       <c r="Z39" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA39" s="2" t="inlineStr">
@@ -5187,7 +5187,7 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
@@ -5226,22 +5226,22 @@
       </c>
       <c r="Z40" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA40" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA40" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB40" s="2" t="inlineStr">
         <is>
-          <t>130.5</t>
+          <t>131.7</t>
         </is>
       </c>
       <c r="AC40" s="2" t="inlineStr">
         <is>
-          <t>7/29</t>
+          <t>10/29</t>
         </is>
       </c>
     </row>
@@ -5306,7 +5306,7 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
@@ -5360,7 +5360,7 @@
       </c>
       <c r="AC41" s="2" t="inlineStr">
         <is>
-          <t>2/29</t>
+          <t>1/29</t>
         </is>
       </c>
     </row>
@@ -5425,7 +5425,7 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
@@ -5479,7 +5479,7 @@
       </c>
       <c r="AC42" s="2" t="inlineStr">
         <is>
-          <t>18/29</t>
+          <t>17/29</t>
         </is>
       </c>
     </row>
@@ -5544,7 +5544,7 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
@@ -5598,7 +5598,7 @@
       </c>
       <c r="AC43" s="2" t="inlineStr">
         <is>
-          <t>25/29</t>
+          <t>24/29</t>
         </is>
       </c>
     </row>
@@ -5663,7 +5663,7 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
@@ -5702,7 +5702,7 @@
       </c>
       <c r="Z44" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA44" s="2" t="inlineStr">
@@ -5712,12 +5712,12 @@
       </c>
       <c r="AB44" s="2" t="inlineStr">
         <is>
-          <t>131.5</t>
+          <t>130.5</t>
         </is>
       </c>
       <c r="AC44" s="2" t="inlineStr">
         <is>
-          <t>10/29</t>
+          <t>7/29</t>
         </is>
       </c>
     </row>
@@ -5782,7 +5782,7 @@
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
@@ -5836,7 +5836,7 @@
       </c>
       <c r="AC45" s="2" t="inlineStr">
         <is>
-          <t>16/29</t>
+          <t>15/29</t>
         </is>
       </c>
     </row>
@@ -6020,7 +6020,7 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
@@ -6139,7 +6139,7 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
@@ -6183,17 +6183,17 @@
       </c>
       <c r="AA48" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB48" s="2" t="inlineStr">
         <is>
-          <t>132.0</t>
+          <t>135.3</t>
         </is>
       </c>
       <c r="AC48" s="2" t="inlineStr">
         <is>
-          <t>11/29</t>
+          <t>20/29</t>
         </is>
       </c>
     </row>
@@ -6258,7 +6258,7 @@
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
@@ -6312,7 +6312,7 @@
       </c>
       <c r="AC49" s="2" t="inlineStr">
         <is>
-          <t>18/29</t>
+          <t>17/29</t>
         </is>
       </c>
     </row>
@@ -6550,7 +6550,7 @@
       </c>
       <c r="AC51" s="2" t="inlineStr">
         <is>
-          <t>14/29</t>
+          <t>13/29</t>
         </is>
       </c>
     </row>
@@ -6615,7 +6615,7 @@
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
@@ -6654,17 +6654,17 @@
       </c>
       <c r="Z52" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA52" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA52" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB52" s="2" t="inlineStr">
         <is>
-          <t>129.5</t>
+          <t>130.0</t>
         </is>
       </c>
       <c r="AC52" s="2" t="inlineStr">
@@ -6734,7 +6734,7 @@
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P53" s="2" t="inlineStr">
@@ -6778,17 +6778,17 @@
       </c>
       <c r="AA53" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB53" s="2" t="inlineStr">
         <is>
-          <t>139.7</t>
+          <t>140.8</t>
         </is>
       </c>
       <c r="AC53" s="2" t="inlineStr">
         <is>
-          <t>24/29</t>
+          <t>26/29</t>
         </is>
       </c>
     </row>
@@ -6968,7 +6968,7 @@
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:01</t>
         </is>
       </c>
       <c r="P55" s="2" t="inlineStr">
@@ -7099,7 +7099,7 @@
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P56" s="2" t="inlineStr">
@@ -7143,12 +7143,12 @@
       </c>
       <c r="AA56" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB56" s="2" t="inlineStr">
         <is>
-          <t>127.0</t>
+          <t>127.5</t>
         </is>
       </c>
       <c r="AC56" s="2" t="inlineStr">
@@ -7218,7 +7218,7 @@
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P57" s="2" t="inlineStr">
@@ -7272,7 +7272,7 @@
       </c>
       <c r="AC57" s="2" t="inlineStr">
         <is>
-          <t>25/29</t>
+          <t>24/29</t>
         </is>
       </c>
     </row>
@@ -7337,7 +7337,7 @@
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P58" s="2" t="inlineStr">
@@ -7391,7 +7391,7 @@
       </c>
       <c r="AC58" s="2" t="inlineStr">
         <is>
-          <t>2/29</t>
+          <t>1/29</t>
         </is>
       </c>
     </row>
@@ -7456,7 +7456,7 @@
       </c>
       <c r="O59" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P59" s="2" t="inlineStr">
@@ -7495,14 +7495,14 @@
       </c>
       <c r="Z59" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA59" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA59" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB59" s="2" t="inlineStr">
         <is>
           <t>135.0</t>
@@ -7510,7 +7510,7 @@
       </c>
       <c r="AC59" s="2" t="inlineStr">
         <is>
-          <t>18/29</t>
+          <t>17/29</t>
         </is>
       </c>
     </row>
@@ -7575,7 +7575,7 @@
       </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P60" s="2" t="inlineStr">
@@ -7629,7 +7629,7 @@
       </c>
       <c r="AC60" s="2" t="inlineStr">
         <is>
-          <t>16/29</t>
+          <t>15/29</t>
         </is>
       </c>
     </row>
@@ -7694,7 +7694,7 @@
       </c>
       <c r="O61" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P61" s="2" t="inlineStr">
@@ -7748,7 +7748,7 @@
       </c>
       <c r="AC61" s="2" t="inlineStr">
         <is>
-          <t>18/29</t>
+          <t>17/29</t>
         </is>
       </c>
     </row>
@@ -7813,7 +7813,7 @@
       </c>
       <c r="O62" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P62" s="2" t="inlineStr">
@@ -7867,7 +7867,7 @@
       </c>
       <c r="AC62" s="2" t="inlineStr">
         <is>
-          <t>18/29</t>
+          <t>17/29</t>
         </is>
       </c>
     </row>
@@ -8224,7 +8224,7 @@
       </c>
       <c r="AC65" s="2" t="inlineStr">
         <is>
-          <t>14/29</t>
+          <t>13/29</t>
         </is>
       </c>
     </row>
@@ -8289,7 +8289,7 @@
       </c>
       <c r="O66" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P66" s="2" t="inlineStr">
@@ -8333,17 +8333,17 @@
       </c>
       <c r="AA66" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB66" s="2" t="inlineStr">
         <is>
-          <t>132.3</t>
+          <t>132.2</t>
         </is>
       </c>
       <c r="AC66" s="2" t="inlineStr">
         <is>
-          <t>13/29</t>
+          <t>12/29</t>
         </is>
       </c>
     </row>
@@ -8527,7 +8527,7 @@
       </c>
       <c r="O68" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P68" s="2" t="inlineStr">
@@ -8757,7 +8757,7 @@
       </c>
       <c r="O70" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P70" s="2" t="inlineStr">
@@ -8872,7 +8872,7 @@
       </c>
       <c r="O71" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:01</t>
         </is>
       </c>
       <c r="P71" s="2" t="inlineStr">
@@ -9003,7 +9003,7 @@
       </c>
       <c r="O72" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P72" s="2" t="inlineStr">
@@ -9057,7 +9057,7 @@
       </c>
       <c r="AC72" s="2" t="inlineStr">
         <is>
-          <t>25/29</t>
+          <t>24/29</t>
         </is>
       </c>
     </row>
@@ -9233,7 +9233,7 @@
       </c>
       <c r="O74" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P74" s="2" t="inlineStr">
@@ -9287,7 +9287,7 @@
       </c>
       <c r="AC74" s="2" t="inlineStr">
         <is>
-          <t>15/29</t>
+          <t>14/29</t>
         </is>
       </c>
     </row>
@@ -9352,7 +9352,7 @@
       </c>
       <c r="O75" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P75" s="2" t="inlineStr">
@@ -9471,7 +9471,7 @@
       </c>
       <c r="O76" s="2" t="inlineStr">
         <is>
-          <t>18:11</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P76" s="2" t="inlineStr">
@@ -9510,7 +9510,7 @@
       </c>
       <c r="Z76" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA76" s="2" t="inlineStr">
@@ -9590,7 +9590,7 @@
       </c>
       <c r="O77" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P77" s="2" t="inlineStr">
@@ -9629,14 +9629,14 @@
       </c>
       <c r="Z77" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA77" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA77" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB77" s="2" t="inlineStr">
         <is>
           <t>135.0</t>
@@ -9644,7 +9644,7 @@
       </c>
       <c r="AC77" s="2" t="inlineStr">
         <is>
-          <t>18/29</t>
+          <t>17/29</t>
         </is>
       </c>
     </row>
@@ -9682,24 +9682,24 @@
       </c>
       <c r="H78" s="2" t="inlineStr">
         <is>
-          <t>18:35</t>
+          <t>18:33</t>
         </is>
       </c>
       <c r="I78" s="2" t="inlineStr">
         <is>
-          <t>140分钟</t>
+          <t>138分钟</t>
         </is>
       </c>
       <c r="J78" s="2" t="inlineStr"/>
       <c r="K78" s="2" t="inlineStr"/>
       <c r="L78" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="M78" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N78" s="2" t="inlineStr">
@@ -9709,7 +9709,7 @@
       </c>
       <c r="O78" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P78" s="2" t="inlineStr">
@@ -9748,7 +9748,7 @@
       </c>
       <c r="Z78" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA78" s="2" t="inlineStr">
@@ -9758,12 +9758,12 @@
       </c>
       <c r="AB78" s="2" t="inlineStr">
         <is>
-          <t>131.5</t>
+          <t>130.5</t>
         </is>
       </c>
       <c r="AC78" s="2" t="inlineStr">
         <is>
-          <t>10/29</t>
+          <t>7/29</t>
         </is>
       </c>
     </row>
@@ -9791,32 +9791,36 @@
       </c>
       <c r="F79" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G79" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H79" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>18:52</t>
         </is>
       </c>
       <c r="I79" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>142分钟</t>
         </is>
       </c>
       <c r="J79" s="2" t="inlineStr"/>
       <c r="K79" s="2" t="inlineStr"/>
       <c r="L79" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M79" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M79" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N79" s="2" t="inlineStr">
         <is>
           <t>06:51</t>
@@ -9824,7 +9828,7 @@
       </c>
       <c r="O79" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P79" s="2" t="inlineStr">
@@ -9848,17 +9852,17 @@
       </c>
       <c r="W79" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X79" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y79" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z79" s="2" t="inlineStr">
@@ -9868,17 +9872,17 @@
       </c>
       <c r="AA79" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB79" s="2" t="inlineStr">
         <is>
-          <t>132.0</t>
+          <t>135.3</t>
         </is>
       </c>
       <c r="AC79" s="2" t="inlineStr">
         <is>
-          <t>11/29</t>
+          <t>20/29</t>
         </is>
       </c>
     </row>
@@ -9928,12 +9932,12 @@
       <c r="K80" s="2" t="inlineStr"/>
       <c r="L80" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="M80" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N80" s="2" t="inlineStr">
@@ -9943,7 +9947,7 @@
       </c>
       <c r="O80" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P80" s="2" t="inlineStr">
@@ -9997,7 +10001,7 @@
       </c>
       <c r="AC80" s="2" t="inlineStr">
         <is>
-          <t>6/29</t>
+          <t>5/29</t>
         </is>
       </c>
     </row>
@@ -10025,32 +10029,36 @@
       </c>
       <c r="F81" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G81" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H81" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>18:56</t>
         </is>
       </c>
       <c r="I81" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>131分钟</t>
         </is>
       </c>
       <c r="J81" s="2" t="inlineStr"/>
       <c r="K81" s="2" t="inlineStr"/>
       <c r="L81" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M81" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M81" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N81" s="2" t="inlineStr">
         <is>
           <t>07:01</t>
@@ -10058,7 +10066,7 @@
       </c>
       <c r="O81" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P81" s="2" t="inlineStr">
@@ -10082,32 +10090,32 @@
       </c>
       <c r="W81" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X81" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y81" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z81" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA81" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA81" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB81" s="2" t="inlineStr">
         <is>
-          <t>129.5</t>
+          <t>130.0</t>
         </is>
       </c>
       <c r="AC81" s="2" t="inlineStr">
@@ -10140,32 +10148,36 @@
       </c>
       <c r="F82" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G82" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H82" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>18:59</t>
         </is>
       </c>
       <c r="I82" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>134分钟</t>
         </is>
       </c>
       <c r="J82" s="2" t="inlineStr"/>
       <c r="K82" s="2" t="inlineStr"/>
       <c r="L82" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M82" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M82" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N82" s="2" t="inlineStr">
         <is>
           <t>06:11</t>
@@ -10173,7 +10185,7 @@
       </c>
       <c r="O82" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P82" s="2" t="inlineStr">
@@ -10197,37 +10209,37 @@
       </c>
       <c r="W82" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X82" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y82" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z82" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA82" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA82" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB82" s="2" t="inlineStr">
         <is>
-          <t>134.5</t>
+          <t>134.3</t>
         </is>
       </c>
       <c r="AC82" s="2" t="inlineStr">
         <is>
-          <t>17/29</t>
+          <t>16/29</t>
         </is>
       </c>
     </row>
@@ -10255,32 +10267,36 @@
       </c>
       <c r="F83" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G83" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H83" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>19:24</t>
         </is>
       </c>
       <c r="I83" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>144分钟</t>
         </is>
       </c>
       <c r="J83" s="2" t="inlineStr"/>
       <c r="K83" s="2" t="inlineStr"/>
       <c r="L83" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M83" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M83" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N83" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -10288,7 +10304,7 @@
       </c>
       <c r="O83" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P83" s="2" t="inlineStr">
@@ -10312,17 +10328,17 @@
       </c>
       <c r="W83" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X83" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y83" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z83" s="2" t="inlineStr">
@@ -10332,17 +10348,17 @@
       </c>
       <c r="AA83" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB83" s="2" t="inlineStr">
         <is>
-          <t>139.7</t>
+          <t>140.8</t>
         </is>
       </c>
       <c r="AC83" s="2" t="inlineStr">
         <is>
-          <t>24/29</t>
+          <t>26/29</t>
         </is>
       </c>
     </row>
@@ -10370,32 +10386,36 @@
       </c>
       <c r="F84" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G84" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H84" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>19:14</t>
         </is>
       </c>
       <c r="I84" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>134分钟</t>
         </is>
       </c>
       <c r="J84" s="2" t="inlineStr"/>
       <c r="K84" s="2" t="inlineStr"/>
       <c r="L84" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M84" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M84" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N84" s="2" t="inlineStr">
         <is>
           <t>06:41</t>
@@ -10403,7 +10423,7 @@
       </c>
       <c r="O84" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P84" s="2" t="inlineStr">
@@ -10427,37 +10447,37 @@
       </c>
       <c r="W84" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X84" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y84" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z84" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA84" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA84" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB84" s="2" t="inlineStr">
         <is>
-          <t>130.5</t>
+          <t>131.7</t>
         </is>
       </c>
       <c r="AC84" s="2" t="inlineStr">
         <is>
-          <t>7/29</t>
+          <t>10/29</t>
         </is>
       </c>
     </row>
@@ -10485,32 +10505,36 @@
       </c>
       <c r="F85" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G85" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H85" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>19:24</t>
         </is>
       </c>
       <c r="I85" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>129分钟</t>
         </is>
       </c>
       <c r="J85" s="2" t="inlineStr"/>
       <c r="K85" s="2" t="inlineStr"/>
       <c r="L85" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M85" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M85" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N85" s="2" t="inlineStr">
         <is>
           <t>06:21</t>
@@ -10518,7 +10542,7 @@
       </c>
       <c r="O85" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P85" s="2" t="inlineStr">
@@ -10542,17 +10566,17 @@
       </c>
       <c r="W85" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X85" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y85" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z85" s="2" t="inlineStr">
@@ -10562,12 +10586,12 @@
       </c>
       <c r="AA85" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB85" s="2" t="inlineStr">
         <is>
-          <t>127.0</t>
+          <t>127.5</t>
         </is>
       </c>
       <c r="AC85" s="2" t="inlineStr">
@@ -10600,32 +10624,36 @@
       </c>
       <c r="F86" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G86" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H86" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>19:27</t>
         </is>
       </c>
       <c r="I86" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>132分钟</t>
         </is>
       </c>
       <c r="J86" s="2" t="inlineStr"/>
       <c r="K86" s="2" t="inlineStr"/>
       <c r="L86" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M86" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M86" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N86" s="2" t="inlineStr">
         <is>
           <t>06:11</t>
@@ -10633,7 +10661,7 @@
       </c>
       <c r="O86" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P86" s="2" t="inlineStr">
@@ -10657,17 +10685,17 @@
       </c>
       <c r="W86" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X86" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y86" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z86" s="2" t="inlineStr">
@@ -10677,17 +10705,17 @@
       </c>
       <c r="AA86" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB86" s="2" t="inlineStr">
         <is>
-          <t>132.3</t>
+          <t>132.2</t>
         </is>
       </c>
       <c r="AC86" s="2" t="inlineStr">
         <is>
-          <t>13/29</t>
+          <t>12/29</t>
         </is>
       </c>
     </row>
@@ -10748,7 +10776,7 @@
       </c>
       <c r="O87" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P87" s="2" t="inlineStr">
@@ -10802,7 +10830,7 @@
       </c>
       <c r="AC87" s="2" t="inlineStr">
         <is>
-          <t>25/29</t>
+          <t>24/29</t>
         </is>
       </c>
     </row>
@@ -10863,7 +10891,7 @@
       </c>
       <c r="O88" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P88" s="2" t="inlineStr">
@@ -10917,7 +10945,7 @@
       </c>
       <c r="AC88" s="2" t="inlineStr">
         <is>
-          <t>2/29</t>
+          <t>1/29</t>
         </is>
       </c>
     </row>
@@ -10978,7 +11006,7 @@
       </c>
       <c r="O89" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P89" s="2" t="inlineStr">
@@ -11032,7 +11060,7 @@
       </c>
       <c r="AC89" s="2" t="inlineStr">
         <is>
-          <t>16/29</t>
+          <t>15/29</t>
         </is>
       </c>
     </row>
@@ -11093,7 +11121,7 @@
       </c>
       <c r="O90" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P90" s="2" t="inlineStr">
@@ -11208,7 +11236,7 @@
       </c>
       <c r="O91" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P91" s="2" t="inlineStr">
@@ -11262,7 +11290,7 @@
       </c>
       <c r="AC91" s="2" t="inlineStr">
         <is>
-          <t>18/29</t>
+          <t>17/29</t>
         </is>
       </c>
     </row>
@@ -11323,7 +11351,7 @@
       </c>
       <c r="O92" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P92" s="2" t="inlineStr">
@@ -11438,7 +11466,7 @@
       </c>
       <c r="O93" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P93" s="2" t="inlineStr">
@@ -11492,7 +11520,7 @@
       </c>
       <c r="AC93" s="2" t="inlineStr">
         <is>
-          <t>25/29</t>
+          <t>24/29</t>
         </is>
       </c>
     </row>
@@ -11553,7 +11581,7 @@
       </c>
       <c r="O94" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:01</t>
         </is>
       </c>
       <c r="P94" s="2" t="inlineStr">
@@ -11664,7 +11692,7 @@
       </c>
       <c r="O95" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P95" s="2" t="inlineStr">
@@ -11890,7 +11918,7 @@
       </c>
       <c r="O97" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P97" s="2" t="inlineStr">
@@ -11944,7 +11972,7 @@
       </c>
       <c r="AC97" s="2" t="inlineStr">
         <is>
-          <t>18/29</t>
+          <t>17/29</t>
         </is>
       </c>
     </row>
@@ -12005,7 +12033,7 @@
       </c>
       <c r="O98" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P98" s="2" t="inlineStr">
@@ -12120,7 +12148,7 @@
       </c>
       <c r="O99" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P99" s="2" t="inlineStr">
@@ -12174,7 +12202,7 @@
       </c>
       <c r="AC99" s="2" t="inlineStr">
         <is>
-          <t>15/29</t>
+          <t>14/29</t>
         </is>
       </c>
     </row>
@@ -12235,7 +12263,7 @@
       </c>
       <c r="O100" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P100" s="2" t="inlineStr">
@@ -12279,17 +12307,17 @@
       </c>
       <c r="AA100" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB100" s="2" t="inlineStr">
         <is>
-          <t>132.0</t>
+          <t>135.3</t>
         </is>
       </c>
       <c r="AC100" s="2" t="inlineStr">
         <is>
-          <t>11/29</t>
+          <t>20/29</t>
         </is>
       </c>
     </row>
@@ -12350,7 +12378,7 @@
       </c>
       <c r="O101" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P101" s="2" t="inlineStr">
@@ -12404,7 +12432,697 @@
       </c>
       <c r="AC101" s="2" t="inlineStr">
         <is>
-          <t>6/29</t>
+          <t>5/29</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" s="2" t="inlineStr"/>
+      <c r="B102" s="2" t="inlineStr">
+        <is>
+          <t>沪A62880D</t>
+        </is>
+      </c>
+      <c r="C102" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D102" s="2" t="inlineStr">
+        <is>
+          <t>19:20</t>
+        </is>
+      </c>
+      <c r="E102" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F102" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G102" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H102" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I102" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J102" s="2" t="inlineStr"/>
+      <c r="K102" s="2" t="inlineStr"/>
+      <c r="L102" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M102" s="2" t="inlineStr"/>
+      <c r="N102" s="2" t="inlineStr">
+        <is>
+          <t>07:01</t>
+        </is>
+      </c>
+      <c r="O102" s="2" t="inlineStr">
+        <is>
+          <t>19:21</t>
+        </is>
+      </c>
+      <c r="P102" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q102" s="2" t="inlineStr"/>
+      <c r="R102" s="2" t="inlineStr"/>
+      <c r="S102" s="2" t="inlineStr"/>
+      <c r="T102" s="2" t="inlineStr"/>
+      <c r="U102" s="2" t="inlineStr">
+        <is>
+          <t>19:20</t>
+        </is>
+      </c>
+      <c r="V102" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W102" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X102" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y102" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z102" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA102" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB102" s="2" t="inlineStr">
+        <is>
+          <t>141.3</t>
+        </is>
+      </c>
+      <c r="AC102" s="2" t="inlineStr">
+        <is>
+          <t>27/29</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" s="2" t="inlineStr"/>
+      <c r="B103" s="2" t="inlineStr">
+        <is>
+          <t>沪A37823D</t>
+        </is>
+      </c>
+      <c r="C103" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D103" s="2" t="inlineStr">
+        <is>
+          <t>19:30</t>
+        </is>
+      </c>
+      <c r="E103" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F103" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G103" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H103" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I103" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J103" s="2" t="inlineStr"/>
+      <c r="K103" s="2" t="inlineStr"/>
+      <c r="L103" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M103" s="2" t="inlineStr"/>
+      <c r="N103" s="2" t="inlineStr">
+        <is>
+          <t>07:31</t>
+        </is>
+      </c>
+      <c r="O103" s="2" t="inlineStr">
+        <is>
+          <t>19:21</t>
+        </is>
+      </c>
+      <c r="P103" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q103" s="2" t="inlineStr"/>
+      <c r="R103" s="2" t="inlineStr"/>
+      <c r="S103" s="2" t="inlineStr"/>
+      <c r="T103" s="2" t="inlineStr"/>
+      <c r="U103" s="2" t="inlineStr">
+        <is>
+          <t>19:30</t>
+        </is>
+      </c>
+      <c r="V103" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W103" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X103" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y103" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z103" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA103" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB103" s="2" t="inlineStr">
+        <is>
+          <t>135.0</t>
+        </is>
+      </c>
+      <c r="AC103" s="2" t="inlineStr">
+        <is>
+          <t>17/29</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" s="2" t="inlineStr"/>
+      <c r="B104" s="2" t="inlineStr">
+        <is>
+          <t>沪A67057D</t>
+        </is>
+      </c>
+      <c r="C104" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D104" s="2" t="inlineStr">
+        <is>
+          <t>19:30</t>
+        </is>
+      </c>
+      <c r="E104" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F104" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G104" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H104" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I104" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J104" s="2" t="inlineStr"/>
+      <c r="K104" s="2" t="inlineStr"/>
+      <c r="L104" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M104" s="2" t="inlineStr"/>
+      <c r="N104" s="2" t="inlineStr">
+        <is>
+          <t>07:01</t>
+        </is>
+      </c>
+      <c r="O104" s="2" t="inlineStr">
+        <is>
+          <t>19:21</t>
+        </is>
+      </c>
+      <c r="P104" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q104" s="2" t="inlineStr"/>
+      <c r="R104" s="2" t="inlineStr"/>
+      <c r="S104" s="2" t="inlineStr"/>
+      <c r="T104" s="2" t="inlineStr"/>
+      <c r="U104" s="2" t="inlineStr">
+        <is>
+          <t>19:30</t>
+        </is>
+      </c>
+      <c r="V104" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W104" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X104" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y104" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z104" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA104" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB104" s="2" t="inlineStr">
+        <is>
+          <t>130.0</t>
+        </is>
+      </c>
+      <c r="AC104" s="2" t="inlineStr">
+        <is>
+          <t>5/29</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" s="2" t="inlineStr"/>
+      <c r="B105" s="2" t="inlineStr">
+        <is>
+          <t>沪A65668D</t>
+        </is>
+      </c>
+      <c r="C105" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D105" s="2" t="inlineStr">
+        <is>
+          <t>19:40</t>
+        </is>
+      </c>
+      <c r="E105" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F105" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G105" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H105" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I105" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J105" s="2" t="inlineStr"/>
+      <c r="K105" s="2" t="inlineStr"/>
+      <c r="L105" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M105" s="2" t="inlineStr"/>
+      <c r="N105" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="O105" s="2" t="inlineStr">
+        <is>
+          <t>19:21</t>
+        </is>
+      </c>
+      <c r="P105" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q105" s="2" t="inlineStr"/>
+      <c r="R105" s="2" t="inlineStr"/>
+      <c r="S105" s="2" t="inlineStr"/>
+      <c r="T105" s="2" t="inlineStr"/>
+      <c r="U105" s="2" t="inlineStr">
+        <is>
+          <t>19:40</t>
+        </is>
+      </c>
+      <c r="V105" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W105" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X105" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y105" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z105" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA105" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB105" s="2" t="inlineStr">
+        <is>
+          <t>130.5</t>
+        </is>
+      </c>
+      <c r="AC105" s="2" t="inlineStr">
+        <is>
+          <t>7/29</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" s="2" t="inlineStr"/>
+      <c r="B106" s="2" t="inlineStr">
+        <is>
+          <t>沪A68375D</t>
+        </is>
+      </c>
+      <c r="C106" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D106" s="2" t="inlineStr">
+        <is>
+          <t>19:40</t>
+        </is>
+      </c>
+      <c r="E106" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F106" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G106" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H106" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I106" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J106" s="2" t="inlineStr"/>
+      <c r="K106" s="2" t="inlineStr"/>
+      <c r="L106" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M106" s="2" t="inlineStr"/>
+      <c r="N106" s="2" t="inlineStr">
+        <is>
+          <t>06:11</t>
+        </is>
+      </c>
+      <c r="O106" s="2" t="inlineStr">
+        <is>
+          <t>19:21</t>
+        </is>
+      </c>
+      <c r="P106" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q106" s="2" t="inlineStr"/>
+      <c r="R106" s="2" t="inlineStr"/>
+      <c r="S106" s="2" t="inlineStr"/>
+      <c r="T106" s="2" t="inlineStr"/>
+      <c r="U106" s="2" t="inlineStr">
+        <is>
+          <t>19:40</t>
+        </is>
+      </c>
+      <c r="V106" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W106" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X106" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y106" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z106" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA106" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB106" s="2" t="inlineStr">
+        <is>
+          <t>134.3</t>
+        </is>
+      </c>
+      <c r="AC106" s="2" t="inlineStr">
+        <is>
+          <t>16/29</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" s="2" t="inlineStr"/>
+      <c r="B107" s="2" t="inlineStr">
+        <is>
+          <t>沪A68261D</t>
+        </is>
+      </c>
+      <c r="C107" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D107" s="2" t="inlineStr">
+        <is>
+          <t>20:05</t>
+        </is>
+      </c>
+      <c r="E107" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F107" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G107" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H107" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I107" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J107" s="2" t="inlineStr"/>
+      <c r="K107" s="2" t="inlineStr"/>
+      <c r="L107" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M107" s="2" t="inlineStr"/>
+      <c r="N107" s="2" t="inlineStr">
+        <is>
+          <t>06:41</t>
+        </is>
+      </c>
+      <c r="O107" s="2" t="inlineStr">
+        <is>
+          <t>19:21</t>
+        </is>
+      </c>
+      <c r="P107" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q107" s="2" t="inlineStr"/>
+      <c r="R107" s="2" t="inlineStr"/>
+      <c r="S107" s="2" t="inlineStr"/>
+      <c r="T107" s="2" t="inlineStr"/>
+      <c r="U107" s="2" t="inlineStr">
+        <is>
+          <t>20:05</t>
+        </is>
+      </c>
+      <c r="V107" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W107" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X107" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y107" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z107" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA107" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB107" s="2" t="inlineStr">
+        <is>
+          <t>131.7</t>
+        </is>
+      </c>
+      <c r="AC107" s="2" t="inlineStr">
+        <is>
+          <t>10/29</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-10-31-浦东35路.xlsx
+++ b/data/export/2026-10-31-浦东35路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC107"/>
+  <dimension ref="A1:AC110"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -723,7 +723,7 @@
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>3/29</t>
+          <t>4/29</t>
         </is>
       </c>
     </row>
@@ -788,7 +788,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>19:51</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -832,17 +832,17 @@
       </c>
       <c r="AA3" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB3" s="2" t="inlineStr">
         <is>
-          <t>137.7</t>
+          <t>135.8</t>
         </is>
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>22/29</t>
+          <t>21/29</t>
         </is>
       </c>
     </row>
@@ -907,7 +907,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -951,7 +951,7 @@
       </c>
       <c r="AA4" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB4" s="2" t="inlineStr">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1383,7 +1383,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:11</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1427,12 +1427,12 @@
       </c>
       <c r="AA8" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB8" s="2" t="inlineStr">
         <is>
-          <t>138.3</t>
+          <t>138.0</t>
         </is>
       </c>
       <c r="AC8" s="2" t="inlineStr">
@@ -1556,7 +1556,7 @@
       </c>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>1/29</t>
+          <t>2/29</t>
         </is>
       </c>
     </row>
@@ -1740,7 +1740,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1859,7 +1859,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1913,7 +1913,7 @@
       </c>
       <c r="AC12" s="2" t="inlineStr">
         <is>
-          <t>14/29</t>
+          <t>15/29</t>
         </is>
       </c>
     </row>
@@ -2109,7 +2109,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2224,7 +2224,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>19:31</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2278,7 +2278,7 @@
       </c>
       <c r="AC15" s="2" t="inlineStr">
         <is>
-          <t>1/29</t>
+          <t>2/29</t>
         </is>
       </c>
     </row>
@@ -2343,7 +2343,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2397,7 +2397,7 @@
       </c>
       <c r="AC16" s="2" t="inlineStr">
         <is>
-          <t>17/29</t>
+          <t>18/29</t>
         </is>
       </c>
     </row>
@@ -2462,7 +2462,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2501,12 +2501,12 @@
       </c>
       <c r="Z17" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA17" s="2" t="inlineStr">
+        <is>
           <t>3</t>
-        </is>
-      </c>
-      <c r="AA17" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
         </is>
       </c>
       <c r="AB17" s="2" t="inlineStr">
@@ -2581,7 +2581,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>19:51</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2625,17 +2625,17 @@
       </c>
       <c r="AA18" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB18" s="2" t="inlineStr">
         <is>
-          <t>134.0</t>
+          <t>134.8</t>
         </is>
       </c>
       <c r="AC18" s="2" t="inlineStr">
         <is>
-          <t>15/29</t>
+          <t>17/29</t>
         </is>
       </c>
     </row>
@@ -2696,7 +2696,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2815,7 +2815,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2854,7 +2854,7 @@
       </c>
       <c r="Z20" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA20" s="2" t="inlineStr">
@@ -2934,7 +2934,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>15:51</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -2973,7 +2973,7 @@
       </c>
       <c r="Z21" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA21" s="2" t="inlineStr">
@@ -3049,7 +3049,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:01</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -3093,17 +3093,17 @@
       </c>
       <c r="AA22" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB22" s="2" t="inlineStr">
         <is>
-          <t>135.0</t>
+          <t>132.7</t>
         </is>
       </c>
       <c r="AC22" s="2" t="inlineStr">
         <is>
-          <t>17/29</t>
+          <t>13/29</t>
         </is>
       </c>
     </row>
@@ -3333,7 +3333,7 @@
       </c>
       <c r="AC24" s="2" t="inlineStr">
         <is>
-          <t>21/29</t>
+          <t>22/29</t>
         </is>
       </c>
     </row>
@@ -3398,7 +3398,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3571,7 +3571,7 @@
       </c>
       <c r="AC26" s="2" t="inlineStr">
         <is>
-          <t>13/29</t>
+          <t>14/29</t>
         </is>
       </c>
     </row>
@@ -3690,7 +3690,7 @@
       </c>
       <c r="AC27" s="2" t="inlineStr">
         <is>
-          <t>3/29</t>
+          <t>4/29</t>
         </is>
       </c>
     </row>
@@ -3755,7 +3755,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>19:51</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -3799,17 +3799,17 @@
       </c>
       <c r="AA28" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB28" s="2" t="inlineStr">
         <is>
-          <t>137.7</t>
+          <t>135.8</t>
         </is>
       </c>
       <c r="AC28" s="2" t="inlineStr">
         <is>
-          <t>22/29</t>
+          <t>21/29</t>
         </is>
       </c>
     </row>
@@ -3874,7 +3874,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -3993,7 +3993,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -4037,7 +4037,7 @@
       </c>
       <c r="AA30" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB30" s="2" t="inlineStr">
@@ -4350,7 +4350,7 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:11</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
@@ -4394,12 +4394,12 @@
       </c>
       <c r="AA33" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB33" s="2" t="inlineStr">
         <is>
-          <t>138.3</t>
+          <t>138.0</t>
         </is>
       </c>
       <c r="AC33" s="2" t="inlineStr">
@@ -4588,7 +4588,7 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
@@ -4703,7 +4703,7 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>19:01</t>
+          <t>20:11</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
@@ -4888,7 +4888,7 @@
       </c>
       <c r="AC37" s="2" t="inlineStr">
         <is>
-          <t>1/29</t>
+          <t>2/29</t>
         </is>
       </c>
     </row>
@@ -4949,7 +4949,7 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
@@ -5003,7 +5003,7 @@
       </c>
       <c r="AC38" s="2" t="inlineStr">
         <is>
-          <t>14/29</t>
+          <t>15/29</t>
         </is>
       </c>
     </row>
@@ -5068,7 +5068,7 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
@@ -5187,7 +5187,7 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
@@ -5306,7 +5306,7 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>19:31</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
@@ -5360,7 +5360,7 @@
       </c>
       <c r="AC41" s="2" t="inlineStr">
         <is>
-          <t>1/29</t>
+          <t>2/29</t>
         </is>
       </c>
     </row>
@@ -5425,7 +5425,7 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
@@ -5479,7 +5479,7 @@
       </c>
       <c r="AC42" s="2" t="inlineStr">
         <is>
-          <t>17/29</t>
+          <t>18/29</t>
         </is>
       </c>
     </row>
@@ -5544,7 +5544,7 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
@@ -5583,12 +5583,12 @@
       </c>
       <c r="Z43" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA43" s="2" t="inlineStr">
+        <is>
           <t>3</t>
-        </is>
-      </c>
-      <c r="AA43" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
         </is>
       </c>
       <c r="AB43" s="2" t="inlineStr">
@@ -5663,7 +5663,7 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
@@ -5782,7 +5782,7 @@
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>19:51</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
@@ -5826,17 +5826,17 @@
       </c>
       <c r="AA45" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB45" s="2" t="inlineStr">
         <is>
-          <t>134.0</t>
+          <t>134.8</t>
         </is>
       </c>
       <c r="AC45" s="2" t="inlineStr">
         <is>
-          <t>15/29</t>
+          <t>17/29</t>
         </is>
       </c>
     </row>
@@ -5901,7 +5901,7 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>15:51</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
@@ -5940,7 +5940,7 @@
       </c>
       <c r="Z46" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA46" s="2" t="inlineStr">
@@ -6020,7 +6020,7 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
@@ -6059,7 +6059,7 @@
       </c>
       <c r="Z47" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA47" s="2" t="inlineStr">
@@ -6139,7 +6139,7 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
@@ -6258,7 +6258,7 @@
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:01</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
@@ -6302,17 +6302,17 @@
       </c>
       <c r="AA49" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB49" s="2" t="inlineStr">
         <is>
-          <t>135.0</t>
+          <t>132.7</t>
         </is>
       </c>
       <c r="AC49" s="2" t="inlineStr">
         <is>
-          <t>17/29</t>
+          <t>13/29</t>
         </is>
       </c>
     </row>
@@ -6431,7 +6431,7 @@
       </c>
       <c r="AC50" s="2" t="inlineStr">
         <is>
-          <t>3/29</t>
+          <t>4/29</t>
         </is>
       </c>
     </row>
@@ -6550,7 +6550,7 @@
       </c>
       <c r="AC51" s="2" t="inlineStr">
         <is>
-          <t>13/29</t>
+          <t>14/29</t>
         </is>
       </c>
     </row>
@@ -6615,7 +6615,7 @@
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
@@ -6968,7 +6968,7 @@
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>19:01</t>
+          <t>20:11</t>
         </is>
       </c>
       <c r="P55" s="2" t="inlineStr">
@@ -7153,7 +7153,7 @@
       </c>
       <c r="AC56" s="2" t="inlineStr">
         <is>
-          <t>1/29</t>
+          <t>2/29</t>
         </is>
       </c>
     </row>
@@ -7337,7 +7337,7 @@
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>19:31</t>
         </is>
       </c>
       <c r="P58" s="2" t="inlineStr">
@@ -7391,7 +7391,7 @@
       </c>
       <c r="AC58" s="2" t="inlineStr">
         <is>
-          <t>1/29</t>
+          <t>2/29</t>
         </is>
       </c>
     </row>
@@ -7456,7 +7456,7 @@
       </c>
       <c r="O59" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P59" s="2" t="inlineStr">
@@ -7510,7 +7510,7 @@
       </c>
       <c r="AC59" s="2" t="inlineStr">
         <is>
-          <t>17/29</t>
+          <t>18/29</t>
         </is>
       </c>
     </row>
@@ -7575,7 +7575,7 @@
       </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>19:51</t>
         </is>
       </c>
       <c r="P60" s="2" t="inlineStr">
@@ -7619,17 +7619,17 @@
       </c>
       <c r="AA60" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB60" s="2" t="inlineStr">
         <is>
-          <t>134.0</t>
+          <t>134.8</t>
         </is>
       </c>
       <c r="AC60" s="2" t="inlineStr">
         <is>
-          <t>15/29</t>
+          <t>17/29</t>
         </is>
       </c>
     </row>
@@ -7694,7 +7694,7 @@
       </c>
       <c r="O61" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P61" s="2" t="inlineStr">
@@ -7748,7 +7748,7 @@
       </c>
       <c r="AC61" s="2" t="inlineStr">
         <is>
-          <t>17/29</t>
+          <t>18/29</t>
         </is>
       </c>
     </row>
@@ -7813,7 +7813,7 @@
       </c>
       <c r="O62" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:01</t>
         </is>
       </c>
       <c r="P62" s="2" t="inlineStr">
@@ -7857,17 +7857,17 @@
       </c>
       <c r="AA62" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB62" s="2" t="inlineStr">
         <is>
-          <t>135.0</t>
+          <t>132.7</t>
         </is>
       </c>
       <c r="AC62" s="2" t="inlineStr">
         <is>
-          <t>17/29</t>
+          <t>13/29</t>
         </is>
       </c>
     </row>
@@ -7932,7 +7932,7 @@
       </c>
       <c r="O63" s="2" t="inlineStr">
         <is>
-          <t>15:51</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P63" s="2" t="inlineStr">
@@ -7971,7 +7971,7 @@
       </c>
       <c r="Z63" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA63" s="2" t="inlineStr">
@@ -8105,7 +8105,7 @@
       </c>
       <c r="AC64" s="2" t="inlineStr">
         <is>
-          <t>3/29</t>
+          <t>4/29</t>
         </is>
       </c>
     </row>
@@ -8224,7 +8224,7 @@
       </c>
       <c r="AC65" s="2" t="inlineStr">
         <is>
-          <t>13/29</t>
+          <t>14/29</t>
         </is>
       </c>
     </row>
@@ -8527,7 +8527,7 @@
       </c>
       <c r="O68" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>19:51</t>
         </is>
       </c>
       <c r="P68" s="2" t="inlineStr">
@@ -8571,17 +8571,17 @@
       </c>
       <c r="AA68" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB68" s="2" t="inlineStr">
         <is>
-          <t>137.7</t>
+          <t>135.8</t>
         </is>
       </c>
       <c r="AC68" s="2" t="inlineStr">
         <is>
-          <t>22/29</t>
+          <t>21/29</t>
         </is>
       </c>
     </row>
@@ -8757,7 +8757,7 @@
       </c>
       <c r="O70" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:11</t>
         </is>
       </c>
       <c r="P70" s="2" t="inlineStr">
@@ -8801,12 +8801,12 @@
       </c>
       <c r="AA70" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB70" s="2" t="inlineStr">
         <is>
-          <t>138.3</t>
+          <t>138.0</t>
         </is>
       </c>
       <c r="AC70" s="2" t="inlineStr">
@@ -8872,7 +8872,7 @@
       </c>
       <c r="O71" s="2" t="inlineStr">
         <is>
-          <t>19:01</t>
+          <t>20:11</t>
         </is>
       </c>
       <c r="P71" s="2" t="inlineStr">
@@ -9233,7 +9233,7 @@
       </c>
       <c r="O74" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P74" s="2" t="inlineStr">
@@ -9287,7 +9287,7 @@
       </c>
       <c r="AC74" s="2" t="inlineStr">
         <is>
-          <t>14/29</t>
+          <t>15/29</t>
         </is>
       </c>
     </row>
@@ -9352,7 +9352,7 @@
       </c>
       <c r="O75" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P75" s="2" t="inlineStr">
@@ -9396,17 +9396,17 @@
       </c>
       <c r="AA75" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB75" s="2" t="inlineStr">
         <is>
-          <t>129.0</t>
+          <t>124.5</t>
         </is>
       </c>
       <c r="AC75" s="2" t="inlineStr">
         <is>
-          <t>4/29</t>
+          <t>1/29</t>
         </is>
       </c>
     </row>
@@ -9471,7 +9471,7 @@
       </c>
       <c r="O76" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P76" s="2" t="inlineStr">
@@ -9590,7 +9590,7 @@
       </c>
       <c r="O77" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P77" s="2" t="inlineStr">
@@ -9644,7 +9644,7 @@
       </c>
       <c r="AC77" s="2" t="inlineStr">
         <is>
-          <t>17/29</t>
+          <t>18/29</t>
         </is>
       </c>
     </row>
@@ -9709,7 +9709,7 @@
       </c>
       <c r="O78" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P78" s="2" t="inlineStr">
@@ -9828,7 +9828,7 @@
       </c>
       <c r="O79" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P79" s="2" t="inlineStr">
@@ -9947,7 +9947,7 @@
       </c>
       <c r="O80" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P80" s="2" t="inlineStr">
@@ -9991,7 +9991,7 @@
       </c>
       <c r="AA80" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB80" s="2" t="inlineStr">
@@ -10066,7 +10066,7 @@
       </c>
       <c r="O81" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P81" s="2" t="inlineStr">
@@ -10185,7 +10185,7 @@
       </c>
       <c r="O82" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P82" s="2" t="inlineStr">
@@ -10423,7 +10423,7 @@
       </c>
       <c r="O84" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P84" s="2" t="inlineStr">
@@ -10596,7 +10596,7 @@
       </c>
       <c r="AC85" s="2" t="inlineStr">
         <is>
-          <t>1/29</t>
+          <t>2/29</t>
         </is>
       </c>
     </row>
@@ -10743,32 +10743,36 @@
       </c>
       <c r="F87" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G87" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H87" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>19:50</t>
         </is>
       </c>
       <c r="I87" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>140分钟</t>
         </is>
       </c>
       <c r="J87" s="2" t="inlineStr"/>
       <c r="K87" s="2" t="inlineStr"/>
       <c r="L87" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M87" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M87" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N87" s="2" t="inlineStr">
         <is>
           <t>07:01</t>
@@ -10776,7 +10780,7 @@
       </c>
       <c r="O87" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P87" s="2" t="inlineStr">
@@ -10800,27 +10804,27 @@
       </c>
       <c r="W87" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X87" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y87" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z87" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA87" s="2" t="inlineStr">
+        <is>
           <t>3</t>
-        </is>
-      </c>
-      <c r="AA87" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
         </is>
       </c>
       <c r="AB87" s="2" t="inlineStr">
@@ -10891,7 +10895,7 @@
       </c>
       <c r="O88" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>19:31</t>
         </is>
       </c>
       <c r="P88" s="2" t="inlineStr">
@@ -10945,7 +10949,7 @@
       </c>
       <c r="AC88" s="2" t="inlineStr">
         <is>
-          <t>1/29</t>
+          <t>2/29</t>
         </is>
       </c>
     </row>
@@ -10973,32 +10977,36 @@
       </c>
       <c r="F89" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G89" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H89" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>20:02</t>
         </is>
       </c>
       <c r="I89" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>137分钟</t>
         </is>
       </c>
       <c r="J89" s="2" t="inlineStr"/>
       <c r="K89" s="2" t="inlineStr"/>
       <c r="L89" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M89" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M89" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N89" s="2" t="inlineStr">
         <is>
           <t>06:51</t>
@@ -11006,7 +11014,7 @@
       </c>
       <c r="O89" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>19:51</t>
         </is>
       </c>
       <c r="P89" s="2" t="inlineStr">
@@ -11030,17 +11038,17 @@
       </c>
       <c r="W89" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X89" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y89" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z89" s="2" t="inlineStr">
@@ -11050,17 +11058,17 @@
       </c>
       <c r="AA89" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB89" s="2" t="inlineStr">
         <is>
-          <t>134.0</t>
+          <t>134.8</t>
         </is>
       </c>
       <c r="AC89" s="2" t="inlineStr">
         <is>
-          <t>15/29</t>
+          <t>17/29</t>
         </is>
       </c>
     </row>
@@ -11088,32 +11096,36 @@
       </c>
       <c r="F90" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G90" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H90" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>19:55</t>
         </is>
       </c>
       <c r="I90" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>130分钟</t>
         </is>
       </c>
       <c r="J90" s="2" t="inlineStr"/>
       <c r="K90" s="2" t="inlineStr"/>
       <c r="L90" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M90" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M90" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N90" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -11121,7 +11133,7 @@
       </c>
       <c r="O90" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>19:51</t>
         </is>
       </c>
       <c r="P90" s="2" t="inlineStr">
@@ -11145,17 +11157,17 @@
       </c>
       <c r="W90" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X90" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y90" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z90" s="2" t="inlineStr">
@@ -11165,17 +11177,17 @@
       </c>
       <c r="AA90" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB90" s="2" t="inlineStr">
         <is>
-          <t>137.7</t>
+          <t>135.8</t>
         </is>
       </c>
       <c r="AC90" s="2" t="inlineStr">
         <is>
-          <t>22/29</t>
+          <t>21/29</t>
         </is>
       </c>
     </row>
@@ -11203,32 +11215,36 @@
       </c>
       <c r="F91" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G91" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H91" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>20:08</t>
         </is>
       </c>
       <c r="I91" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>128分钟</t>
         </is>
       </c>
       <c r="J91" s="2" t="inlineStr"/>
       <c r="K91" s="2" t="inlineStr"/>
       <c r="L91" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M91" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M91" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N91" s="2" t="inlineStr">
         <is>
           <t>07:41</t>
@@ -11236,7 +11252,7 @@
       </c>
       <c r="O91" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:01</t>
         </is>
       </c>
       <c r="P91" s="2" t="inlineStr">
@@ -11260,17 +11276,17 @@
       </c>
       <c r="W91" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X91" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y91" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z91" s="2" t="inlineStr">
@@ -11280,17 +11296,17 @@
       </c>
       <c r="AA91" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB91" s="2" t="inlineStr">
         <is>
-          <t>135.0</t>
+          <t>132.7</t>
         </is>
       </c>
       <c r="AC91" s="2" t="inlineStr">
         <is>
-          <t>17/29</t>
+          <t>13/29</t>
         </is>
       </c>
     </row>
@@ -11318,32 +11334,36 @@
       </c>
       <c r="F92" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G92" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H92" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>20:17</t>
         </is>
       </c>
       <c r="I92" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>137分钟</t>
         </is>
       </c>
       <c r="J92" s="2" t="inlineStr"/>
       <c r="K92" s="2" t="inlineStr"/>
       <c r="L92" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M92" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M92" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N92" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -11351,7 +11371,7 @@
       </c>
       <c r="O92" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:11</t>
         </is>
       </c>
       <c r="P92" s="2" t="inlineStr">
@@ -11375,17 +11395,17 @@
       </c>
       <c r="W92" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X92" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y92" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z92" s="2" t="inlineStr">
@@ -11395,12 +11415,12 @@
       </c>
       <c r="AA92" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB92" s="2" t="inlineStr">
         <is>
-          <t>138.3</t>
+          <t>138.0</t>
         </is>
       </c>
       <c r="AC92" s="2" t="inlineStr">
@@ -11548,12 +11568,12 @@
       </c>
       <c r="F94" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>疑似区间车</t>
         </is>
       </c>
       <c r="G94" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>原方向在全程34%处后消失；随后反向物理轨迹由seq41推进至seq57，推进16站，达到≥2站确认条件</t>
         </is>
       </c>
       <c r="H94" s="2" t="inlineStr">
@@ -11581,7 +11601,7 @@
       </c>
       <c r="O94" s="2" t="inlineStr">
         <is>
-          <t>19:01</t>
+          <t>20:11</t>
         </is>
       </c>
       <c r="P94" s="2" t="inlineStr">
@@ -11589,10 +11609,22 @@
           <t>SHMAAS</t>
         </is>
       </c>
-      <c r="Q94" s="2" t="inlineStr"/>
-      <c r="R94" s="2" t="inlineStr"/>
+      <c r="Q94" s="2" t="inlineStr">
+        <is>
+          <t>物理seq23（站名待映射）</t>
+        </is>
+      </c>
+      <c r="R94" s="2" t="inlineStr">
+        <is>
+          <t>19:09</t>
+        </is>
+      </c>
       <c r="S94" s="2" t="inlineStr"/>
-      <c r="T94" s="2" t="inlineStr"/>
+      <c r="T94" s="2" t="inlineStr">
+        <is>
+          <t>区间折返已由主分类器确认；折返点按重建物理位置seq23映射；现有采样不足以把折返发车时间控制在±10分钟</t>
+        </is>
+      </c>
       <c r="U94" s="2" t="inlineStr">
         <is>
           <t>18:12</t>
@@ -11692,7 +11724,7 @@
       </c>
       <c r="O95" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P95" s="2" t="inlineStr">
@@ -11731,7 +11763,7 @@
       </c>
       <c r="Z95" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA95" s="2" t="inlineStr">
@@ -11918,7 +11950,7 @@
       </c>
       <c r="O97" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P97" s="2" t="inlineStr">
@@ -11972,7 +12004,7 @@
       </c>
       <c r="AC97" s="2" t="inlineStr">
         <is>
-          <t>17/29</t>
+          <t>18/29</t>
         </is>
       </c>
     </row>
@@ -12000,32 +12032,36 @@
       </c>
       <c r="F98" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G98" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H98" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>20:50</t>
         </is>
       </c>
       <c r="I98" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>120分钟</t>
         </is>
       </c>
       <c r="J98" s="2" t="inlineStr"/>
       <c r="K98" s="2" t="inlineStr"/>
       <c r="L98" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M98" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M98" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N98" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -12033,7 +12069,7 @@
       </c>
       <c r="O98" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P98" s="2" t="inlineStr">
@@ -12057,17 +12093,17 @@
       </c>
       <c r="W98" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X98" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y98" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z98" s="2" t="inlineStr">
@@ -12077,17 +12113,17 @@
       </c>
       <c r="AA98" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB98" s="2" t="inlineStr">
         <is>
-          <t>129.0</t>
+          <t>124.5</t>
         </is>
       </c>
       <c r="AC98" s="2" t="inlineStr">
         <is>
-          <t>4/29</t>
+          <t>1/29</t>
         </is>
       </c>
     </row>
@@ -12148,7 +12184,7 @@
       </c>
       <c r="O99" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P99" s="2" t="inlineStr">
@@ -12202,7 +12238,7 @@
       </c>
       <c r="AC99" s="2" t="inlineStr">
         <is>
-          <t>14/29</t>
+          <t>15/29</t>
         </is>
       </c>
     </row>
@@ -12263,7 +12299,7 @@
       </c>
       <c r="O100" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P100" s="2" t="inlineStr">
@@ -12345,32 +12381,36 @@
       </c>
       <c r="F101" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G101" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H101" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>21:25</t>
         </is>
       </c>
       <c r="I101" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>130分钟</t>
         </is>
       </c>
       <c r="J101" s="2" t="inlineStr"/>
       <c r="K101" s="2" t="inlineStr"/>
       <c r="L101" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M101" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±4分钟</t>
+        </is>
+      </c>
+      <c r="M101" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="N101" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -12378,7 +12418,7 @@
       </c>
       <c r="O101" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P101" s="2" t="inlineStr">
@@ -12402,17 +12442,17 @@
       </c>
       <c r="W101" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X101" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y101" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z101" s="2" t="inlineStr">
@@ -12422,7 +12462,7 @@
       </c>
       <c r="AA101" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB101" s="2" t="inlineStr">
@@ -12493,7 +12533,7 @@
       </c>
       <c r="O102" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P102" s="2" t="inlineStr">
@@ -12608,7 +12648,7 @@
       </c>
       <c r="O103" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P103" s="2" t="inlineStr">
@@ -12662,7 +12702,7 @@
       </c>
       <c r="AC103" s="2" t="inlineStr">
         <is>
-          <t>17/29</t>
+          <t>18/29</t>
         </is>
       </c>
     </row>
@@ -12723,7 +12763,7 @@
       </c>
       <c r="O104" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P104" s="2" t="inlineStr">
@@ -12838,7 +12878,7 @@
       </c>
       <c r="O105" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P105" s="2" t="inlineStr">
@@ -12953,7 +12993,7 @@
       </c>
       <c r="O106" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P106" s="2" t="inlineStr">
@@ -13015,22 +13055,22 @@
       <c r="A107" s="2" t="inlineStr"/>
       <c r="B107" s="2" t="inlineStr">
         <is>
-          <t>沪A68261D</t>
+          <t>沪A90275D</t>
         </is>
       </c>
       <c r="C107" s="2" t="inlineStr">
         <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D107" s="2" t="inlineStr">
+        <is>
+          <t>20:00</t>
+        </is>
+      </c>
+      <c r="E107" s="2" t="inlineStr">
+        <is>
           <t>康恩路康浦路</t>
-        </is>
-      </c>
-      <c r="D107" s="2" t="inlineStr">
-        <is>
-          <t>20:05</t>
-        </is>
-      </c>
-      <c r="E107" s="2" t="inlineStr">
-        <is>
-          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="F107" s="2" t="inlineStr">
@@ -13063,12 +13103,12 @@
       <c r="M107" s="2" t="inlineStr"/>
       <c r="N107" s="2" t="inlineStr">
         <is>
-          <t>06:41</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="O107" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P107" s="2" t="inlineStr">
@@ -13082,47 +13122,392 @@
       <c r="T107" s="2" t="inlineStr"/>
       <c r="U107" s="2" t="inlineStr">
         <is>
+          <t>20:00</t>
+        </is>
+      </c>
+      <c r="V107" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W107" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X107" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y107" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z107" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA107" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB107" s="2" t="inlineStr">
+        <is>
+          <t>130.7</t>
+        </is>
+      </c>
+      <c r="AC107" s="2" t="inlineStr">
+        <is>
+          <t>9/29</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" s="2" t="inlineStr"/>
+      <c r="B108" s="2" t="inlineStr">
+        <is>
+          <t>沪A68261D</t>
+        </is>
+      </c>
+      <c r="C108" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D108" s="2" t="inlineStr">
+        <is>
           <t>20:05</t>
         </is>
       </c>
-      <c r="V107" s="2" t="inlineStr">
+      <c r="E108" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F108" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G108" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H108" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I108" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J108" s="2" t="inlineStr"/>
+      <c r="K108" s="2" t="inlineStr"/>
+      <c r="L108" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M108" s="2" t="inlineStr"/>
+      <c r="N108" s="2" t="inlineStr">
+        <is>
+          <t>06:41</t>
+        </is>
+      </c>
+      <c r="O108" s="2" t="inlineStr">
+        <is>
+          <t>20:21</t>
+        </is>
+      </c>
+      <c r="P108" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q108" s="2" t="inlineStr"/>
+      <c r="R108" s="2" t="inlineStr"/>
+      <c r="S108" s="2" t="inlineStr"/>
+      <c r="T108" s="2" t="inlineStr"/>
+      <c r="U108" s="2" t="inlineStr">
+        <is>
+          <t>20:05</t>
+        </is>
+      </c>
+      <c r="V108" s="2" t="inlineStr">
         <is>
           <t>计划发车</t>
         </is>
       </c>
-      <c r="W107" s="2" t="inlineStr">
+      <c r="W108" s="2" t="inlineStr">
         <is>
           <t>D</t>
         </is>
       </c>
-      <c r="X107" s="2" t="inlineStr">
+      <c r="X108" s="2" t="inlineStr">
         <is>
           <t>待确认</t>
         </is>
       </c>
-      <c r="Y107" s="2" t="inlineStr">
+      <c r="Y108" s="2" t="inlineStr">
         <is>
           <t>否</t>
         </is>
       </c>
-      <c r="Z107" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="AA107" s="2" t="inlineStr">
+      <c r="Z108" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA108" s="2" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AB107" s="2" t="inlineStr">
+      <c r="AB108" s="2" t="inlineStr">
         <is>
           <t>131.7</t>
         </is>
       </c>
-      <c r="AC107" s="2" t="inlineStr">
+      <c r="AC108" s="2" t="inlineStr">
         <is>
           <t>10/29</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" s="2" t="inlineStr"/>
+      <c r="B109" s="2" t="inlineStr">
+        <is>
+          <t>沪A55575A</t>
+        </is>
+      </c>
+      <c r="C109" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D109" s="2" t="inlineStr">
+        <is>
+          <t>20:30</t>
+        </is>
+      </c>
+      <c r="E109" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F109" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G109" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H109" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I109" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J109" s="2" t="inlineStr"/>
+      <c r="K109" s="2" t="inlineStr"/>
+      <c r="L109" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M109" s="2" t="inlineStr"/>
+      <c r="N109" s="2" t="inlineStr">
+        <is>
+          <t>07:01</t>
+        </is>
+      </c>
+      <c r="O109" s="2" t="inlineStr">
+        <is>
+          <t>20:21</t>
+        </is>
+      </c>
+      <c r="P109" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q109" s="2" t="inlineStr"/>
+      <c r="R109" s="2" t="inlineStr"/>
+      <c r="S109" s="2" t="inlineStr"/>
+      <c r="T109" s="2" t="inlineStr"/>
+      <c r="U109" s="2" t="inlineStr">
+        <is>
+          <t>20:30</t>
+        </is>
+      </c>
+      <c r="V109" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W109" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X109" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y109" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z109" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA109" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB109" s="2" t="inlineStr">
+        <is>
+          <t>140.0</t>
+        </is>
+      </c>
+      <c r="AC109" s="2" t="inlineStr">
+        <is>
+          <t>24/29</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" s="2" t="inlineStr"/>
+      <c r="B110" s="2" t="inlineStr">
+        <is>
+          <t>沪A57383A</t>
+        </is>
+      </c>
+      <c r="C110" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D110" s="2" t="inlineStr">
+        <is>
+          <t>20:55</t>
+        </is>
+      </c>
+      <c r="E110" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F110" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G110" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H110" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I110" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J110" s="2" t="inlineStr"/>
+      <c r="K110" s="2" t="inlineStr"/>
+      <c r="L110" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M110" s="2" t="inlineStr"/>
+      <c r="N110" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="O110" s="2" t="inlineStr">
+        <is>
+          <t>20:21</t>
+        </is>
+      </c>
+      <c r="P110" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q110" s="2" t="inlineStr"/>
+      <c r="R110" s="2" t="inlineStr"/>
+      <c r="S110" s="2" t="inlineStr"/>
+      <c r="T110" s="2" t="inlineStr"/>
+      <c r="U110" s="2" t="inlineStr">
+        <is>
+          <t>20:55</t>
+        </is>
+      </c>
+      <c r="V110" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W110" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X110" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y110" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z110" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA110" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB110" s="2" t="inlineStr">
+        <is>
+          <t>132.0</t>
+        </is>
+      </c>
+      <c r="AC110" s="2" t="inlineStr">
+        <is>
+          <t>11/29</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-10-31-浦东35路.xlsx
+++ b/data/export/2026-10-31-浦东35路.xlsx
@@ -723,7 +723,7 @@
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>4/29</t>
+          <t>6/29</t>
         </is>
       </c>
     </row>
@@ -907,7 +907,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:11</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -956,7 +956,7 @@
       </c>
       <c r="AB4" s="2" t="inlineStr">
         <is>
-          <t>130.0</t>
+          <t>127.8</t>
         </is>
       </c>
       <c r="AC4" s="2" t="inlineStr">
@@ -1080,7 +1080,7 @@
       </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>26/29</t>
+          <t>27/29</t>
         </is>
       </c>
     </row>
@@ -1199,7 +1199,7 @@
       </c>
       <c r="AC6" s="2" t="inlineStr">
         <is>
-          <t>7/29</t>
+          <t>8/29</t>
         </is>
       </c>
     </row>
@@ -1264,7 +1264,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1318,7 +1318,7 @@
       </c>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>16/29</t>
+          <t>17/29</t>
         </is>
       </c>
     </row>
@@ -1437,7 +1437,7 @@
       </c>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>23/29</t>
+          <t>24/29</t>
         </is>
       </c>
     </row>
@@ -1556,7 +1556,7 @@
       </c>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>2/29</t>
+          <t>3/29</t>
         </is>
       </c>
     </row>
@@ -1675,7 +1675,7 @@
       </c>
       <c r="AC10" s="2" t="inlineStr">
         <is>
-          <t>12/29</t>
+          <t>13/29</t>
         </is>
       </c>
     </row>
@@ -1740,7 +1740,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1859,7 +1859,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:01</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1903,17 +1903,17 @@
       </c>
       <c r="AA12" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB12" s="2" t="inlineStr">
         <is>
-          <t>133.5</t>
+          <t>132.0</t>
         </is>
       </c>
       <c r="AC12" s="2" t="inlineStr">
         <is>
-          <t>15/29</t>
+          <t>11/29</t>
         </is>
       </c>
     </row>
@@ -2044,7 +2044,7 @@
       </c>
       <c r="AC13" s="2" t="inlineStr">
         <is>
-          <t>24/29</t>
+          <t>25/29</t>
         </is>
       </c>
     </row>
@@ -2109,7 +2109,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2153,17 +2153,17 @@
       </c>
       <c r="AA14" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB14" s="2" t="inlineStr">
         <is>
-          <t>141.3</t>
+          <t>136.8</t>
         </is>
       </c>
       <c r="AC14" s="2" t="inlineStr">
         <is>
-          <t>27/29</t>
+          <t>23/29</t>
         </is>
       </c>
     </row>
@@ -2278,7 +2278,7 @@
       </c>
       <c r="AC15" s="2" t="inlineStr">
         <is>
-          <t>2/29</t>
+          <t>3/29</t>
         </is>
       </c>
     </row>
@@ -2343,7 +2343,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:41</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2387,17 +2387,17 @@
       </c>
       <c r="AA16" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB16" s="2" t="inlineStr">
         <is>
-          <t>135.0</t>
+          <t>133.8</t>
         </is>
       </c>
       <c r="AC16" s="2" t="inlineStr">
         <is>
-          <t>18/29</t>
+          <t>16/29</t>
         </is>
       </c>
     </row>
@@ -2462,7 +2462,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2516,7 +2516,7 @@
       </c>
       <c r="AC17" s="2" t="inlineStr">
         <is>
-          <t>24/29</t>
+          <t>25/29</t>
         </is>
       </c>
     </row>
@@ -2635,7 +2635,7 @@
       </c>
       <c r="AC18" s="2" t="inlineStr">
         <is>
-          <t>17/29</t>
+          <t>18/29</t>
         </is>
       </c>
     </row>
@@ -2696,7 +2696,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2740,17 +2740,17 @@
       </c>
       <c r="AA19" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB19" s="2" t="inlineStr">
         <is>
-          <t>130.5</t>
+          <t>126.0</t>
         </is>
       </c>
       <c r="AC19" s="2" t="inlineStr">
         <is>
-          <t>7/29</t>
+          <t>1/29</t>
         </is>
       </c>
     </row>
@@ -2815,7 +2815,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2934,7 +2934,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -3103,7 +3103,7 @@
       </c>
       <c r="AC22" s="2" t="inlineStr">
         <is>
-          <t>13/29</t>
+          <t>14/29</t>
         </is>
       </c>
     </row>
@@ -3398,7 +3398,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3571,7 +3571,7 @@
       </c>
       <c r="AC26" s="2" t="inlineStr">
         <is>
-          <t>14/29</t>
+          <t>15/29</t>
         </is>
       </c>
     </row>
@@ -3690,7 +3690,7 @@
       </c>
       <c r="AC27" s="2" t="inlineStr">
         <is>
-          <t>4/29</t>
+          <t>6/29</t>
         </is>
       </c>
     </row>
@@ -3874,7 +3874,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -3928,7 +3928,7 @@
       </c>
       <c r="AC29" s="2" t="inlineStr">
         <is>
-          <t>5/29</t>
+          <t>7/29</t>
         </is>
       </c>
     </row>
@@ -3993,7 +3993,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:11</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -4042,7 +4042,7 @@
       </c>
       <c r="AB30" s="2" t="inlineStr">
         <is>
-          <t>130.0</t>
+          <t>127.8</t>
         </is>
       </c>
       <c r="AC30" s="2" t="inlineStr">
@@ -4166,7 +4166,7 @@
       </c>
       <c r="AC31" s="2" t="inlineStr">
         <is>
-          <t>7/29</t>
+          <t>8/29</t>
         </is>
       </c>
     </row>
@@ -4285,7 +4285,7 @@
       </c>
       <c r="AC32" s="2" t="inlineStr">
         <is>
-          <t>26/29</t>
+          <t>27/29</t>
         </is>
       </c>
     </row>
@@ -4404,7 +4404,7 @@
       </c>
       <c r="AC33" s="2" t="inlineStr">
         <is>
-          <t>23/29</t>
+          <t>24/29</t>
         </is>
       </c>
     </row>
@@ -4523,7 +4523,7 @@
       </c>
       <c r="AC34" s="2" t="inlineStr">
         <is>
-          <t>12/29</t>
+          <t>13/29</t>
         </is>
       </c>
     </row>
@@ -4588,7 +4588,7 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
@@ -4642,7 +4642,7 @@
       </c>
       <c r="AC35" s="2" t="inlineStr">
         <is>
-          <t>16/29</t>
+          <t>17/29</t>
         </is>
       </c>
     </row>
@@ -4888,7 +4888,7 @@
       </c>
       <c r="AC37" s="2" t="inlineStr">
         <is>
-          <t>2/29</t>
+          <t>3/29</t>
         </is>
       </c>
     </row>
@@ -4949,7 +4949,7 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:01</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
@@ -4993,17 +4993,17 @@
       </c>
       <c r="AA38" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB38" s="2" t="inlineStr">
         <is>
-          <t>133.5</t>
+          <t>132.0</t>
         </is>
       </c>
       <c r="AC38" s="2" t="inlineStr">
         <is>
-          <t>15/29</t>
+          <t>11/29</t>
         </is>
       </c>
     </row>
@@ -5068,7 +5068,7 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
@@ -5112,17 +5112,17 @@
       </c>
       <c r="AA39" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB39" s="2" t="inlineStr">
         <is>
-          <t>141.3</t>
+          <t>136.8</t>
         </is>
       </c>
       <c r="AC39" s="2" t="inlineStr">
         <is>
-          <t>27/29</t>
+          <t>23/29</t>
         </is>
       </c>
     </row>
@@ -5187,7 +5187,7 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
@@ -5360,7 +5360,7 @@
       </c>
       <c r="AC41" s="2" t="inlineStr">
         <is>
-          <t>2/29</t>
+          <t>3/29</t>
         </is>
       </c>
     </row>
@@ -5425,7 +5425,7 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:41</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
@@ -5469,17 +5469,17 @@
       </c>
       <c r="AA42" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB42" s="2" t="inlineStr">
         <is>
-          <t>135.0</t>
+          <t>133.8</t>
         </is>
       </c>
       <c r="AC42" s="2" t="inlineStr">
         <is>
-          <t>18/29</t>
+          <t>16/29</t>
         </is>
       </c>
     </row>
@@ -5544,7 +5544,7 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
@@ -5598,7 +5598,7 @@
       </c>
       <c r="AC43" s="2" t="inlineStr">
         <is>
-          <t>24/29</t>
+          <t>25/29</t>
         </is>
       </c>
     </row>
@@ -5663,7 +5663,7 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
@@ -5707,17 +5707,17 @@
       </c>
       <c r="AA44" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB44" s="2" t="inlineStr">
         <is>
-          <t>130.5</t>
+          <t>126.0</t>
         </is>
       </c>
       <c r="AC44" s="2" t="inlineStr">
         <is>
-          <t>7/29</t>
+          <t>1/29</t>
         </is>
       </c>
     </row>
@@ -5836,7 +5836,7 @@
       </c>
       <c r="AC45" s="2" t="inlineStr">
         <is>
-          <t>17/29</t>
+          <t>18/29</t>
         </is>
       </c>
     </row>
@@ -5901,7 +5901,7 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
@@ -6020,7 +6020,7 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
@@ -6139,7 +6139,7 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
@@ -6312,7 +6312,7 @@
       </c>
       <c r="AC49" s="2" t="inlineStr">
         <is>
-          <t>13/29</t>
+          <t>14/29</t>
         </is>
       </c>
     </row>
@@ -6431,7 +6431,7 @@
       </c>
       <c r="AC50" s="2" t="inlineStr">
         <is>
-          <t>4/29</t>
+          <t>6/29</t>
         </is>
       </c>
     </row>
@@ -6550,7 +6550,7 @@
       </c>
       <c r="AC51" s="2" t="inlineStr">
         <is>
-          <t>14/29</t>
+          <t>15/29</t>
         </is>
       </c>
     </row>
@@ -6615,7 +6615,7 @@
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
@@ -6669,7 +6669,7 @@
       </c>
       <c r="AC52" s="2" t="inlineStr">
         <is>
-          <t>5/29</t>
+          <t>7/29</t>
         </is>
       </c>
     </row>
@@ -6788,7 +6788,7 @@
       </c>
       <c r="AC53" s="2" t="inlineStr">
         <is>
-          <t>26/29</t>
+          <t>27/29</t>
         </is>
       </c>
     </row>
@@ -6907,7 +6907,7 @@
       </c>
       <c r="AC54" s="2" t="inlineStr">
         <is>
-          <t>7/29</t>
+          <t>8/29</t>
         </is>
       </c>
     </row>
@@ -7153,7 +7153,7 @@
       </c>
       <c r="AC56" s="2" t="inlineStr">
         <is>
-          <t>2/29</t>
+          <t>3/29</t>
         </is>
       </c>
     </row>
@@ -7272,7 +7272,7 @@
       </c>
       <c r="AC57" s="2" t="inlineStr">
         <is>
-          <t>24/29</t>
+          <t>25/29</t>
         </is>
       </c>
     </row>
@@ -7391,7 +7391,7 @@
       </c>
       <c r="AC58" s="2" t="inlineStr">
         <is>
-          <t>2/29</t>
+          <t>3/29</t>
         </is>
       </c>
     </row>
@@ -7456,7 +7456,7 @@
       </c>
       <c r="O59" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:51</t>
         </is>
       </c>
       <c r="P59" s="2" t="inlineStr">
@@ -7510,7 +7510,7 @@
       </c>
       <c r="AC59" s="2" t="inlineStr">
         <is>
-          <t>18/29</t>
+          <t>19/29</t>
         </is>
       </c>
     </row>
@@ -7629,7 +7629,7 @@
       </c>
       <c r="AC60" s="2" t="inlineStr">
         <is>
-          <t>17/29</t>
+          <t>18/29</t>
         </is>
       </c>
     </row>
@@ -7694,7 +7694,7 @@
       </c>
       <c r="O61" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:41</t>
         </is>
       </c>
       <c r="P61" s="2" t="inlineStr">
@@ -7738,17 +7738,17 @@
       </c>
       <c r="AA61" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB61" s="2" t="inlineStr">
         <is>
-          <t>135.0</t>
+          <t>133.8</t>
         </is>
       </c>
       <c r="AC61" s="2" t="inlineStr">
         <is>
-          <t>18/29</t>
+          <t>16/29</t>
         </is>
       </c>
     </row>
@@ -7867,7 +7867,7 @@
       </c>
       <c r="AC62" s="2" t="inlineStr">
         <is>
-          <t>13/29</t>
+          <t>14/29</t>
         </is>
       </c>
     </row>
@@ -7932,7 +7932,7 @@
       </c>
       <c r="O63" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P63" s="2" t="inlineStr">
@@ -8105,7 +8105,7 @@
       </c>
       <c r="AC64" s="2" t="inlineStr">
         <is>
-          <t>4/29</t>
+          <t>6/29</t>
         </is>
       </c>
     </row>
@@ -8224,7 +8224,7 @@
       </c>
       <c r="AC65" s="2" t="inlineStr">
         <is>
-          <t>14/29</t>
+          <t>15/29</t>
         </is>
       </c>
     </row>
@@ -8343,7 +8343,7 @@
       </c>
       <c r="AC66" s="2" t="inlineStr">
         <is>
-          <t>12/29</t>
+          <t>13/29</t>
         </is>
       </c>
     </row>
@@ -8462,7 +8462,7 @@
       </c>
       <c r="AC67" s="2" t="inlineStr">
         <is>
-          <t>7/29</t>
+          <t>8/29</t>
         </is>
       </c>
     </row>
@@ -8811,7 +8811,7 @@
       </c>
       <c r="AC70" s="2" t="inlineStr">
         <is>
-          <t>23/29</t>
+          <t>24/29</t>
         </is>
       </c>
     </row>
@@ -9057,7 +9057,7 @@
       </c>
       <c r="AC72" s="2" t="inlineStr">
         <is>
-          <t>24/29</t>
+          <t>25/29</t>
         </is>
       </c>
     </row>
@@ -9233,7 +9233,7 @@
       </c>
       <c r="O74" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:01</t>
         </is>
       </c>
       <c r="P74" s="2" t="inlineStr">
@@ -9277,17 +9277,17 @@
       </c>
       <c r="AA74" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB74" s="2" t="inlineStr">
         <is>
-          <t>133.5</t>
+          <t>132.0</t>
         </is>
       </c>
       <c r="AC74" s="2" t="inlineStr">
         <is>
-          <t>15/29</t>
+          <t>11/29</t>
         </is>
       </c>
     </row>
@@ -9352,7 +9352,7 @@
       </c>
       <c r="O75" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:51</t>
         </is>
       </c>
       <c r="P75" s="2" t="inlineStr">
@@ -9401,12 +9401,12 @@
       </c>
       <c r="AB75" s="2" t="inlineStr">
         <is>
-          <t>124.5</t>
+          <t>126.5</t>
         </is>
       </c>
       <c r="AC75" s="2" t="inlineStr">
         <is>
-          <t>1/29</t>
+          <t>2/29</t>
         </is>
       </c>
     </row>
@@ -9471,7 +9471,7 @@
       </c>
       <c r="O76" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P76" s="2" t="inlineStr">
@@ -9515,17 +9515,17 @@
       </c>
       <c r="AA76" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB76" s="2" t="inlineStr">
         <is>
-          <t>141.3</t>
+          <t>136.8</t>
         </is>
       </c>
       <c r="AC76" s="2" t="inlineStr">
         <is>
-          <t>27/29</t>
+          <t>23/29</t>
         </is>
       </c>
     </row>
@@ -9590,7 +9590,7 @@
       </c>
       <c r="O77" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:51</t>
         </is>
       </c>
       <c r="P77" s="2" t="inlineStr">
@@ -9644,7 +9644,7 @@
       </c>
       <c r="AC77" s="2" t="inlineStr">
         <is>
-          <t>18/29</t>
+          <t>19/29</t>
         </is>
       </c>
     </row>
@@ -9709,7 +9709,7 @@
       </c>
       <c r="O78" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P78" s="2" t="inlineStr">
@@ -9753,17 +9753,17 @@
       </c>
       <c r="AA78" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB78" s="2" t="inlineStr">
         <is>
-          <t>130.5</t>
+          <t>126.0</t>
         </is>
       </c>
       <c r="AC78" s="2" t="inlineStr">
         <is>
-          <t>7/29</t>
+          <t>1/29</t>
         </is>
       </c>
     </row>
@@ -9828,7 +9828,7 @@
       </c>
       <c r="O79" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P79" s="2" t="inlineStr">
@@ -9947,7 +9947,7 @@
       </c>
       <c r="O80" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:11</t>
         </is>
       </c>
       <c r="P80" s="2" t="inlineStr">
@@ -9996,7 +9996,7 @@
       </c>
       <c r="AB80" s="2" t="inlineStr">
         <is>
-          <t>130.0</t>
+          <t>127.8</t>
         </is>
       </c>
       <c r="AC80" s="2" t="inlineStr">
@@ -10066,7 +10066,7 @@
       </c>
       <c r="O81" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P81" s="2" t="inlineStr">
@@ -10120,7 +10120,7 @@
       </c>
       <c r="AC81" s="2" t="inlineStr">
         <is>
-          <t>5/29</t>
+          <t>7/29</t>
         </is>
       </c>
     </row>
@@ -10185,7 +10185,7 @@
       </c>
       <c r="O82" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P82" s="2" t="inlineStr">
@@ -10239,7 +10239,7 @@
       </c>
       <c r="AC82" s="2" t="inlineStr">
         <is>
-          <t>16/29</t>
+          <t>17/29</t>
         </is>
       </c>
     </row>
@@ -10358,7 +10358,7 @@
       </c>
       <c r="AC83" s="2" t="inlineStr">
         <is>
-          <t>26/29</t>
+          <t>27/29</t>
         </is>
       </c>
     </row>
@@ -10423,7 +10423,7 @@
       </c>
       <c r="O84" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P84" s="2" t="inlineStr">
@@ -10596,7 +10596,7 @@
       </c>
       <c r="AC85" s="2" t="inlineStr">
         <is>
-          <t>2/29</t>
+          <t>3/29</t>
         </is>
       </c>
     </row>
@@ -10715,7 +10715,7 @@
       </c>
       <c r="AC86" s="2" t="inlineStr">
         <is>
-          <t>12/29</t>
+          <t>13/29</t>
         </is>
       </c>
     </row>
@@ -10780,7 +10780,7 @@
       </c>
       <c r="O87" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P87" s="2" t="inlineStr">
@@ -10834,7 +10834,7 @@
       </c>
       <c r="AC87" s="2" t="inlineStr">
         <is>
-          <t>24/29</t>
+          <t>25/29</t>
         </is>
       </c>
     </row>
@@ -10949,7 +10949,7 @@
       </c>
       <c r="AC88" s="2" t="inlineStr">
         <is>
-          <t>2/29</t>
+          <t>3/29</t>
         </is>
       </c>
     </row>
@@ -11068,7 +11068,7 @@
       </c>
       <c r="AC89" s="2" t="inlineStr">
         <is>
-          <t>17/29</t>
+          <t>18/29</t>
         </is>
       </c>
     </row>
@@ -11306,7 +11306,7 @@
       </c>
       <c r="AC91" s="2" t="inlineStr">
         <is>
-          <t>13/29</t>
+          <t>14/29</t>
         </is>
       </c>
     </row>
@@ -11425,7 +11425,7 @@
       </c>
       <c r="AC92" s="2" t="inlineStr">
         <is>
-          <t>23/29</t>
+          <t>24/29</t>
         </is>
       </c>
     </row>
@@ -11540,7 +11540,7 @@
       </c>
       <c r="AC93" s="2" t="inlineStr">
         <is>
-          <t>24/29</t>
+          <t>25/29</t>
         </is>
       </c>
     </row>
@@ -11724,7 +11724,7 @@
       </c>
       <c r="O95" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P95" s="2" t="inlineStr">
@@ -11917,32 +11917,36 @@
       </c>
       <c r="F97" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G97" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H97" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>20:50</t>
         </is>
       </c>
       <c r="I97" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>130分钟</t>
         </is>
       </c>
       <c r="J97" s="2" t="inlineStr"/>
       <c r="K97" s="2" t="inlineStr"/>
       <c r="L97" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M97" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M97" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N97" s="2" t="inlineStr">
         <is>
           <t>07:11</t>
@@ -11950,7 +11954,7 @@
       </c>
       <c r="O97" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:41</t>
         </is>
       </c>
       <c r="P97" s="2" t="inlineStr">
@@ -11974,17 +11978,17 @@
       </c>
       <c r="W97" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X97" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y97" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z97" s="2" t="inlineStr">
@@ -11994,17 +11998,17 @@
       </c>
       <c r="AA97" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB97" s="2" t="inlineStr">
         <is>
-          <t>135.0</t>
+          <t>133.8</t>
         </is>
       </c>
       <c r="AC97" s="2" t="inlineStr">
         <is>
-          <t>18/29</t>
+          <t>16/29</t>
         </is>
       </c>
     </row>
@@ -12042,24 +12046,24 @@
       </c>
       <c r="H98" s="2" t="inlineStr">
         <is>
-          <t>20:50</t>
+          <t>20:54</t>
         </is>
       </c>
       <c r="I98" s="2" t="inlineStr">
         <is>
-          <t>120分钟</t>
+          <t>124分钟</t>
         </is>
       </c>
       <c r="J98" s="2" t="inlineStr"/>
       <c r="K98" s="2" t="inlineStr"/>
       <c r="L98" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="M98" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N98" s="2" t="inlineStr">
@@ -12069,7 +12073,7 @@
       </c>
       <c r="O98" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:51</t>
         </is>
       </c>
       <c r="P98" s="2" t="inlineStr">
@@ -12118,12 +12122,12 @@
       </c>
       <c r="AB98" s="2" t="inlineStr">
         <is>
-          <t>124.5</t>
+          <t>126.5</t>
         </is>
       </c>
       <c r="AC98" s="2" t="inlineStr">
         <is>
-          <t>1/29</t>
+          <t>2/29</t>
         </is>
       </c>
     </row>
@@ -12151,32 +12155,36 @@
       </c>
       <c r="F99" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G99" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H99" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>21:09</t>
         </is>
       </c>
       <c r="I99" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>129分钟</t>
         </is>
       </c>
       <c r="J99" s="2" t="inlineStr"/>
       <c r="K99" s="2" t="inlineStr"/>
       <c r="L99" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M99" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M99" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N99" s="2" t="inlineStr">
         <is>
           <t>06:32</t>
@@ -12184,7 +12192,7 @@
       </c>
       <c r="O99" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:01</t>
         </is>
       </c>
       <c r="P99" s="2" t="inlineStr">
@@ -12208,17 +12216,17 @@
       </c>
       <c r="W99" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X99" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y99" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z99" s="2" t="inlineStr">
@@ -12228,17 +12236,17 @@
       </c>
       <c r="AA99" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB99" s="2" t="inlineStr">
         <is>
-          <t>133.5</t>
+          <t>132.0</t>
         </is>
       </c>
       <c r="AC99" s="2" t="inlineStr">
         <is>
-          <t>15/29</t>
+          <t>11/29</t>
         </is>
       </c>
     </row>
@@ -12266,12 +12274,12 @@
       </c>
       <c r="F100" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>疑似区间车</t>
         </is>
       </c>
       <c r="G100" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>原方向在全程49%处后消失；随后反向物理轨迹由seq29推进至seq62，推进33站，达到≥2站确认条件</t>
         </is>
       </c>
       <c r="H100" s="2" t="inlineStr">
@@ -12299,7 +12307,7 @@
       </c>
       <c r="O100" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P100" s="2" t="inlineStr">
@@ -12307,10 +12315,26 @@
           <t>SHMAAS</t>
         </is>
       </c>
-      <c r="Q100" s="2" t="inlineStr"/>
-      <c r="R100" s="2" t="inlineStr"/>
-      <c r="S100" s="2" t="inlineStr"/>
-      <c r="T100" s="2" t="inlineStr"/>
+      <c r="Q100" s="2" t="inlineStr">
+        <is>
+          <t>物理seq32（站名待映射）</t>
+        </is>
+      </c>
+      <c r="R100" s="2" t="inlineStr">
+        <is>
+          <t>20:02</t>
+        </is>
+      </c>
+      <c r="S100" s="2" t="inlineStr">
+        <is>
+          <t>20:12</t>
+        </is>
+      </c>
+      <c r="T100" s="2" t="inlineStr">
+        <is>
+          <t>折返点按重建物理位置seq32映射；到达按末次同向ETA估算；折返发车结合首次反向物理观测取区间中点，约±9分钟；反向位置锦绣路花木路 ETA 0分钟参与校验</t>
+        </is>
+      </c>
       <c r="U100" s="2" t="inlineStr">
         <is>
           <t>19:10</t>
@@ -12391,24 +12415,24 @@
       </c>
       <c r="H101" s="2" t="inlineStr">
         <is>
-          <t>21:25</t>
+          <t>21:16</t>
         </is>
       </c>
       <c r="I101" s="2" t="inlineStr">
         <is>
-          <t>130分钟</t>
+          <t>121分钟</t>
         </is>
       </c>
       <c r="J101" s="2" t="inlineStr"/>
       <c r="K101" s="2" t="inlineStr"/>
       <c r="L101" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±4分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="M101" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N101" s="2" t="inlineStr">
@@ -12418,7 +12442,7 @@
       </c>
       <c r="O101" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:11</t>
         </is>
       </c>
       <c r="P101" s="2" t="inlineStr">
@@ -12467,7 +12491,7 @@
       </c>
       <c r="AB101" s="2" t="inlineStr">
         <is>
-          <t>130.0</t>
+          <t>127.8</t>
         </is>
       </c>
       <c r="AC101" s="2" t="inlineStr">
@@ -12500,32 +12524,36 @@
       </c>
       <c r="F102" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G102" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H102" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>21:23</t>
         </is>
       </c>
       <c r="I102" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>123分钟</t>
         </is>
       </c>
       <c r="J102" s="2" t="inlineStr"/>
       <c r="K102" s="2" t="inlineStr"/>
       <c r="L102" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M102" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M102" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N102" s="2" t="inlineStr">
         <is>
           <t>07:01</t>
@@ -12533,7 +12561,7 @@
       </c>
       <c r="O102" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P102" s="2" t="inlineStr">
@@ -12557,17 +12585,17 @@
       </c>
       <c r="W102" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X102" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y102" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z102" s="2" t="inlineStr">
@@ -12577,17 +12605,17 @@
       </c>
       <c r="AA102" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB102" s="2" t="inlineStr">
         <is>
-          <t>141.3</t>
+          <t>136.8</t>
         </is>
       </c>
       <c r="AC102" s="2" t="inlineStr">
         <is>
-          <t>27/29</t>
+          <t>23/29</t>
         </is>
       </c>
     </row>
@@ -12648,7 +12676,7 @@
       </c>
       <c r="O103" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:51</t>
         </is>
       </c>
       <c r="P103" s="2" t="inlineStr">
@@ -12702,7 +12730,7 @@
       </c>
       <c r="AC103" s="2" t="inlineStr">
         <is>
-          <t>18/29</t>
+          <t>19/29</t>
         </is>
       </c>
     </row>
@@ -12730,12 +12758,12 @@
       </c>
       <c r="F104" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>疑似区间车</t>
         </is>
       </c>
       <c r="G104" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>原方向在全程49%处后消失；随后反向物理轨迹由seq28推进至seq54，推进26站，达到≥2站确认条件</t>
         </is>
       </c>
       <c r="H104" s="2" t="inlineStr">
@@ -12763,7 +12791,7 @@
       </c>
       <c r="O104" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P104" s="2" t="inlineStr">
@@ -12771,10 +12799,26 @@
           <t>SHMAAS</t>
         </is>
       </c>
-      <c r="Q104" s="2" t="inlineStr"/>
-      <c r="R104" s="2" t="inlineStr"/>
-      <c r="S104" s="2" t="inlineStr"/>
-      <c r="T104" s="2" t="inlineStr"/>
+      <c r="Q104" s="2" t="inlineStr">
+        <is>
+          <t>物理seq32（站名待映射）</t>
+        </is>
+      </c>
+      <c r="R104" s="2" t="inlineStr">
+        <is>
+          <t>20:22</t>
+        </is>
+      </c>
+      <c r="S104" s="2" t="inlineStr">
+        <is>
+          <t>20:27</t>
+        </is>
+      </c>
+      <c r="T104" s="2" t="inlineStr">
+        <is>
+          <t>折返点按重建物理位置seq32映射；到达按末次同向ETA估算；折返发车结合首次反向物理观测取区间中点，约±5分钟；反向位置物理seq28（站名待映射） ETA 0分钟参与校验</t>
+        </is>
+      </c>
       <c r="U104" s="2" t="inlineStr">
         <is>
           <t>19:30</t>
@@ -12817,7 +12861,7 @@
       </c>
       <c r="AC104" s="2" t="inlineStr">
         <is>
-          <t>5/29</t>
+          <t>7/29</t>
         </is>
       </c>
     </row>
@@ -12845,32 +12889,36 @@
       </c>
       <c r="F105" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G105" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H105" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>21:37</t>
         </is>
       </c>
       <c r="I105" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>117分钟</t>
         </is>
       </c>
       <c r="J105" s="2" t="inlineStr"/>
       <c r="K105" s="2" t="inlineStr"/>
       <c r="L105" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M105" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M105" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N105" s="2" t="inlineStr">
         <is>
           <t>07:21</t>
@@ -12878,7 +12926,7 @@
       </c>
       <c r="O105" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P105" s="2" t="inlineStr">
@@ -12902,17 +12950,17 @@
       </c>
       <c r="W105" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X105" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y105" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z105" s="2" t="inlineStr">
@@ -12922,17 +12970,17 @@
       </c>
       <c r="AA105" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB105" s="2" t="inlineStr">
         <is>
-          <t>130.5</t>
+          <t>126.0</t>
         </is>
       </c>
       <c r="AC105" s="2" t="inlineStr">
         <is>
-          <t>7/29</t>
+          <t>1/29</t>
         </is>
       </c>
     </row>
@@ -12993,7 +13041,7 @@
       </c>
       <c r="O106" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P106" s="2" t="inlineStr">
@@ -13047,7 +13095,7 @@
       </c>
       <c r="AC106" s="2" t="inlineStr">
         <is>
-          <t>16/29</t>
+          <t>17/29</t>
         </is>
       </c>
     </row>
@@ -13108,7 +13156,7 @@
       </c>
       <c r="O107" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P107" s="2" t="inlineStr">
@@ -13223,7 +13271,7 @@
       </c>
       <c r="O108" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P108" s="2" t="inlineStr">
@@ -13338,7 +13386,7 @@
       </c>
       <c r="O109" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P109" s="2" t="inlineStr">
@@ -13392,7 +13440,7 @@
       </c>
       <c r="AC109" s="2" t="inlineStr">
         <is>
-          <t>24/29</t>
+          <t>25/29</t>
         </is>
       </c>
     </row>
@@ -13453,7 +13501,7 @@
       </c>
       <c r="O110" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P110" s="2" t="inlineStr">

--- a/data/export/2026-10-31-浦东35路.xlsx
+++ b/data/export/2026-10-31-浦东35路.xlsx
@@ -723,7 +723,7 @@
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>6/29</t>
+          <t>7/29</t>
         </is>
       </c>
     </row>
@@ -1199,7 +1199,7 @@
       </c>
       <c r="AC6" s="2" t="inlineStr">
         <is>
-          <t>8/29</t>
+          <t>9/29</t>
         </is>
       </c>
     </row>
@@ -1264,7 +1264,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:51</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1308,12 +1308,12 @@
       </c>
       <c r="AA7" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB7" s="2" t="inlineStr">
         <is>
-          <t>134.3</t>
+          <t>134.8</t>
         </is>
       </c>
       <c r="AC7" s="2" t="inlineStr">
@@ -1556,7 +1556,7 @@
       </c>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>3/29</t>
+          <t>2/29</t>
         </is>
       </c>
     </row>
@@ -1740,7 +1740,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:51</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -2278,7 +2278,7 @@
       </c>
       <c r="AC15" s="2" t="inlineStr">
         <is>
-          <t>3/29</t>
+          <t>2/29</t>
         </is>
       </c>
     </row>
@@ -2462,7 +2462,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:51</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2635,7 +2635,7 @@
       </c>
       <c r="AC18" s="2" t="inlineStr">
         <is>
-          <t>18/29</t>
+          <t>17/29</t>
         </is>
       </c>
     </row>
@@ -2696,7 +2696,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:41</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2745,12 +2745,12 @@
       </c>
       <c r="AB19" s="2" t="inlineStr">
         <is>
-          <t>126.0</t>
+          <t>127.7</t>
         </is>
       </c>
       <c r="AC19" s="2" t="inlineStr">
         <is>
-          <t>1/29</t>
+          <t>4/29</t>
         </is>
       </c>
     </row>
@@ -2815,7 +2815,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:51</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2934,7 +2934,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:51</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -2978,17 +2978,17 @@
       </c>
       <c r="AA21" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB21" s="2" t="inlineStr">
         <is>
-          <t>130.7</t>
+          <t>128.0</t>
         </is>
       </c>
       <c r="AC21" s="2" t="inlineStr">
         <is>
-          <t>9/29</t>
+          <t>6/29</t>
         </is>
       </c>
     </row>
@@ -3690,7 +3690,7 @@
       </c>
       <c r="AC27" s="2" t="inlineStr">
         <is>
-          <t>6/29</t>
+          <t>7/29</t>
         </is>
       </c>
     </row>
@@ -3874,7 +3874,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:41</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -3928,7 +3928,7 @@
       </c>
       <c r="AC29" s="2" t="inlineStr">
         <is>
-          <t>7/29</t>
+          <t>8/29</t>
         </is>
       </c>
     </row>
@@ -4166,7 +4166,7 @@
       </c>
       <c r="AC31" s="2" t="inlineStr">
         <is>
-          <t>8/29</t>
+          <t>9/29</t>
         </is>
       </c>
     </row>
@@ -4588,7 +4588,7 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:51</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
@@ -4632,12 +4632,12 @@
       </c>
       <c r="AA35" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB35" s="2" t="inlineStr">
         <is>
-          <t>134.3</t>
+          <t>134.8</t>
         </is>
       </c>
       <c r="AC35" s="2" t="inlineStr">
@@ -4888,7 +4888,7 @@
       </c>
       <c r="AC37" s="2" t="inlineStr">
         <is>
-          <t>3/29</t>
+          <t>2/29</t>
         </is>
       </c>
     </row>
@@ -5187,7 +5187,7 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:51</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
@@ -5360,7 +5360,7 @@
       </c>
       <c r="AC41" s="2" t="inlineStr">
         <is>
-          <t>3/29</t>
+          <t>2/29</t>
         </is>
       </c>
     </row>
@@ -5544,7 +5544,7 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:51</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
@@ -5663,7 +5663,7 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:41</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
@@ -5712,12 +5712,12 @@
       </c>
       <c r="AB44" s="2" t="inlineStr">
         <is>
-          <t>126.0</t>
+          <t>127.7</t>
         </is>
       </c>
       <c r="AC44" s="2" t="inlineStr">
         <is>
-          <t>1/29</t>
+          <t>4/29</t>
         </is>
       </c>
     </row>
@@ -5836,7 +5836,7 @@
       </c>
       <c r="AC45" s="2" t="inlineStr">
         <is>
-          <t>18/29</t>
+          <t>17/29</t>
         </is>
       </c>
     </row>
@@ -5901,7 +5901,7 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:51</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
@@ -5945,17 +5945,17 @@
       </c>
       <c r="AA46" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB46" s="2" t="inlineStr">
         <is>
-          <t>130.7</t>
+          <t>128.0</t>
         </is>
       </c>
       <c r="AC46" s="2" t="inlineStr">
         <is>
-          <t>9/29</t>
+          <t>6/29</t>
         </is>
       </c>
     </row>
@@ -6020,7 +6020,7 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:51</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
@@ -6431,7 +6431,7 @@
       </c>
       <c r="AC50" s="2" t="inlineStr">
         <is>
-          <t>6/29</t>
+          <t>7/29</t>
         </is>
       </c>
     </row>
@@ -6615,7 +6615,7 @@
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:41</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
@@ -6669,7 +6669,7 @@
       </c>
       <c r="AC52" s="2" t="inlineStr">
         <is>
-          <t>7/29</t>
+          <t>8/29</t>
         </is>
       </c>
     </row>
@@ -6907,7 +6907,7 @@
       </c>
       <c r="AC54" s="2" t="inlineStr">
         <is>
-          <t>8/29</t>
+          <t>9/29</t>
         </is>
       </c>
     </row>
@@ -7153,7 +7153,7 @@
       </c>
       <c r="AC56" s="2" t="inlineStr">
         <is>
-          <t>3/29</t>
+          <t>2/29</t>
         </is>
       </c>
     </row>
@@ -7391,7 +7391,7 @@
       </c>
       <c r="AC58" s="2" t="inlineStr">
         <is>
-          <t>3/29</t>
+          <t>2/29</t>
         </is>
       </c>
     </row>
@@ -7629,7 +7629,7 @@
       </c>
       <c r="AC60" s="2" t="inlineStr">
         <is>
-          <t>18/29</t>
+          <t>17/29</t>
         </is>
       </c>
     </row>
@@ -7932,7 +7932,7 @@
       </c>
       <c r="O63" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:51</t>
         </is>
       </c>
       <c r="P63" s="2" t="inlineStr">
@@ -7976,17 +7976,17 @@
       </c>
       <c r="AA63" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB63" s="2" t="inlineStr">
         <is>
-          <t>130.7</t>
+          <t>128.0</t>
         </is>
       </c>
       <c r="AC63" s="2" t="inlineStr">
         <is>
-          <t>9/29</t>
+          <t>6/29</t>
         </is>
       </c>
     </row>
@@ -8105,7 +8105,7 @@
       </c>
       <c r="AC64" s="2" t="inlineStr">
         <is>
-          <t>6/29</t>
+          <t>7/29</t>
         </is>
       </c>
     </row>
@@ -8462,7 +8462,7 @@
       </c>
       <c r="AC67" s="2" t="inlineStr">
         <is>
-          <t>8/29</t>
+          <t>9/29</t>
         </is>
       </c>
     </row>
@@ -9406,7 +9406,7 @@
       </c>
       <c r="AC75" s="2" t="inlineStr">
         <is>
-          <t>2/29</t>
+          <t>1/29</t>
         </is>
       </c>
     </row>
@@ -9709,7 +9709,7 @@
       </c>
       <c r="O78" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:41</t>
         </is>
       </c>
       <c r="P78" s="2" t="inlineStr">
@@ -9758,12 +9758,12 @@
       </c>
       <c r="AB78" s="2" t="inlineStr">
         <is>
-          <t>126.0</t>
+          <t>127.7</t>
         </is>
       </c>
       <c r="AC78" s="2" t="inlineStr">
         <is>
-          <t>1/29</t>
+          <t>4/29</t>
         </is>
       </c>
     </row>
@@ -10066,7 +10066,7 @@
       </c>
       <c r="O81" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:41</t>
         </is>
       </c>
       <c r="P81" s="2" t="inlineStr">
@@ -10120,7 +10120,7 @@
       </c>
       <c r="AC81" s="2" t="inlineStr">
         <is>
-          <t>7/29</t>
+          <t>8/29</t>
         </is>
       </c>
     </row>
@@ -10185,7 +10185,7 @@
       </c>
       <c r="O82" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:51</t>
         </is>
       </c>
       <c r="P82" s="2" t="inlineStr">
@@ -10229,12 +10229,12 @@
       </c>
       <c r="AA82" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB82" s="2" t="inlineStr">
         <is>
-          <t>134.3</t>
+          <t>134.8</t>
         </is>
       </c>
       <c r="AC82" s="2" t="inlineStr">
@@ -10423,7 +10423,7 @@
       </c>
       <c r="O84" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:51</t>
         </is>
       </c>
       <c r="P84" s="2" t="inlineStr">
@@ -10596,7 +10596,7 @@
       </c>
       <c r="AC85" s="2" t="inlineStr">
         <is>
-          <t>3/29</t>
+          <t>2/29</t>
         </is>
       </c>
     </row>
@@ -10780,7 +10780,7 @@
       </c>
       <c r="O87" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:51</t>
         </is>
       </c>
       <c r="P87" s="2" t="inlineStr">
@@ -10949,7 +10949,7 @@
       </c>
       <c r="AC88" s="2" t="inlineStr">
         <is>
-          <t>3/29</t>
+          <t>2/29</t>
         </is>
       </c>
     </row>
@@ -11068,7 +11068,7 @@
       </c>
       <c r="AC89" s="2" t="inlineStr">
         <is>
-          <t>18/29</t>
+          <t>17/29</t>
         </is>
       </c>
     </row>
@@ -11724,7 +11724,7 @@
       </c>
       <c r="O95" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:51</t>
         </is>
       </c>
       <c r="P95" s="2" t="inlineStr">
@@ -12127,7 +12127,7 @@
       </c>
       <c r="AC98" s="2" t="inlineStr">
         <is>
-          <t>2/29</t>
+          <t>1/29</t>
         </is>
       </c>
     </row>
@@ -12763,7 +12763,7 @@
       </c>
       <c r="G104" s="2" t="inlineStr">
         <is>
-          <t>原方向在全程49%处后消失；随后反向物理轨迹由seq28推进至seq54，推进26站，达到≥2站确认条件</t>
+          <t>原方向在全程49%处后消失；随后反向物理轨迹由seq28推进至seq64，推进36站，达到≥2站确认条件</t>
         </is>
       </c>
       <c r="H104" s="2" t="inlineStr">
@@ -12791,7 +12791,7 @@
       </c>
       <c r="O104" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:41</t>
         </is>
       </c>
       <c r="P104" s="2" t="inlineStr">
@@ -12861,7 +12861,7 @@
       </c>
       <c r="AC104" s="2" t="inlineStr">
         <is>
-          <t>7/29</t>
+          <t>8/29</t>
         </is>
       </c>
     </row>
@@ -12899,24 +12899,24 @@
       </c>
       <c r="H105" s="2" t="inlineStr">
         <is>
-          <t>21:37</t>
+          <t>21:42</t>
         </is>
       </c>
       <c r="I105" s="2" t="inlineStr">
         <is>
-          <t>117分钟</t>
+          <t>122分钟</t>
         </is>
       </c>
       <c r="J105" s="2" t="inlineStr"/>
       <c r="K105" s="2" t="inlineStr"/>
       <c r="L105" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
         </is>
       </c>
       <c r="M105" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="N105" s="2" t="inlineStr">
@@ -12926,7 +12926,7 @@
       </c>
       <c r="O105" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:41</t>
         </is>
       </c>
       <c r="P105" s="2" t="inlineStr">
@@ -12975,12 +12975,12 @@
       </c>
       <c r="AB105" s="2" t="inlineStr">
         <is>
-          <t>126.0</t>
+          <t>127.7</t>
         </is>
       </c>
       <c r="AC105" s="2" t="inlineStr">
         <is>
-          <t>1/29</t>
+          <t>4/29</t>
         </is>
       </c>
     </row>
@@ -13008,32 +13008,36 @@
       </c>
       <c r="F106" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G106" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H106" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>21:56</t>
         </is>
       </c>
       <c r="I106" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>136分钟</t>
         </is>
       </c>
       <c r="J106" s="2" t="inlineStr"/>
       <c r="K106" s="2" t="inlineStr"/>
       <c r="L106" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M106" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M106" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N106" s="2" t="inlineStr">
         <is>
           <t>06:11</t>
@@ -13041,7 +13045,7 @@
       </c>
       <c r="O106" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:51</t>
         </is>
       </c>
       <c r="P106" s="2" t="inlineStr">
@@ -13065,17 +13069,17 @@
       </c>
       <c r="W106" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X106" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y106" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z106" s="2" t="inlineStr">
@@ -13085,12 +13089,12 @@
       </c>
       <c r="AA106" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB106" s="2" t="inlineStr">
         <is>
-          <t>134.3</t>
+          <t>134.8</t>
         </is>
       </c>
       <c r="AC106" s="2" t="inlineStr">
@@ -13123,32 +13127,36 @@
       </c>
       <c r="F107" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G107" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H107" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>22:00</t>
         </is>
       </c>
       <c r="I107" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>120分钟</t>
         </is>
       </c>
       <c r="J107" s="2" t="inlineStr"/>
       <c r="K107" s="2" t="inlineStr"/>
       <c r="L107" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M107" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M107" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N107" s="2" t="inlineStr">
         <is>
           <t>07:21</t>
@@ -13156,7 +13164,7 @@
       </c>
       <c r="O107" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:51</t>
         </is>
       </c>
       <c r="P107" s="2" t="inlineStr">
@@ -13180,17 +13188,17 @@
       </c>
       <c r="W107" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X107" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y107" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z107" s="2" t="inlineStr">
@@ -13200,17 +13208,17 @@
       </c>
       <c r="AA107" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB107" s="2" t="inlineStr">
         <is>
-          <t>130.7</t>
+          <t>128.0</t>
         </is>
       </c>
       <c r="AC107" s="2" t="inlineStr">
         <is>
-          <t>9/29</t>
+          <t>6/29</t>
         </is>
       </c>
     </row>
@@ -13271,7 +13279,7 @@
       </c>
       <c r="O108" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:51</t>
         </is>
       </c>
       <c r="P108" s="2" t="inlineStr">
@@ -13386,7 +13394,7 @@
       </c>
       <c r="O109" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:51</t>
         </is>
       </c>
       <c r="P109" s="2" t="inlineStr">
@@ -13501,7 +13509,7 @@
       </c>
       <c r="O110" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:51</t>
         </is>
       </c>
       <c r="P110" s="2" t="inlineStr">
